--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="193">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,345 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
+    <t>Turkish Super League</t>
+  </si>
+  <si>
+    <t>English Sky Bet Championship</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Portuguese Primeira Liga</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>02:30:00</t>
+  </si>
+  <si>
+    <t>03:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:45:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
+    <t>Aucas</t>
+  </si>
+  <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
+    <t>Santos Laguna</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Tijuana</t>
+  </si>
+  <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Zalaegerszeg</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>FC Dziugas</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Trinec</t>
+  </si>
+  <si>
+    <t>Hacken</t>
+  </si>
+  <si>
+    <t>Sporting Gijon</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
+    <t>Brondby</t>
+  </si>
+  <si>
+    <t>Estudiantes Rio Cuarto</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>Jong FC Utrecht</t>
+  </si>
+  <si>
+    <t>Jong Ajax Amsterdam</t>
+  </si>
+  <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>FK Novi Pazar</t>
+  </si>
+  <si>
+    <t>Arda</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
+    <t>Deportivo</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>LDU</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Guadalajara</t>
+  </si>
+  <si>
+    <t>Alianza FC Valledupar</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Ilves</t>
+  </si>
+  <si>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
+    <t>FK Suduva</t>
+  </si>
+  <si>
+    <t>Septemvri</t>
+  </si>
+  <si>
+    <t>Usti nad Labem</t>
+  </si>
+  <si>
+    <t>Halmstads</t>
+  </si>
+  <si>
+    <t>Sabadell</t>
+  </si>
+  <si>
+    <t>Puszcza Niepolomice</t>
+  </si>
+  <si>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
+    <t>Atl Tucuman</t>
+  </si>
+  <si>
+    <t>Jong AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>KA Akureyri</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia</t>
+  </si>
+  <si>
+    <t>Botosani</t>
+  </si>
+  <si>
+    <t>Goztepe</t>
+  </si>
+  <si>
+    <t>Wrexham</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Eldense</t>
+  </si>
+  <si>
+    <t>CA Independiente</t>
+  </si>
+  <si>
+    <t>2026-08-15 00:48:44</t>
   </si>
 </sst>
 </file>
@@ -585,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1167,8234 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2">
+        <v>2.48</v>
+      </c>
+      <c r="G2">
+        <v>3.05</v>
+      </c>
+      <c r="H2">
+        <v>2.48</v>
+      </c>
+      <c r="I2">
+        <v>3.1</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>5.2</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.97</v>
+      </c>
+      <c r="O2">
+        <v>1.27</v>
+      </c>
+      <c r="P2">
+        <v>1.97</v>
+      </c>
+      <c r="Q2">
+        <v>1.8</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>1.81</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.47</v>
+      </c>
+      <c r="W2">
+        <v>1.49</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3">
+        <v>2.3</v>
+      </c>
+      <c r="G3">
+        <v>2.62</v>
+      </c>
+      <c r="H3">
+        <v>3.15</v>
+      </c>
+      <c r="I3">
+        <v>3.8</v>
+      </c>
+      <c r="J3">
+        <v>3.2</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.74</v>
+      </c>
+      <c r="O3">
+        <v>1.02</v>
+      </c>
+      <c r="P3">
+        <v>1.66</v>
+      </c>
+      <c r="Q3">
+        <v>2.14</v>
+      </c>
+      <c r="R3">
+        <v>1.23</v>
+      </c>
+      <c r="S3">
+        <v>2.48</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.36</v>
+      </c>
+      <c r="W3">
+        <v>1.61</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>1.01</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>1.01</v>
+      </c>
+      <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3">
+        <v>1.01</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.01</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>3.75</v>
+      </c>
+      <c r="BI3">
+        <v>2.48</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3.2</v>
+      </c>
+      <c r="H4">
+        <v>2.34</v>
+      </c>
+      <c r="I4">
+        <v>2.44</v>
+      </c>
+      <c r="J4">
+        <v>3.7</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1.32</v>
+      </c>
+      <c r="M4">
+        <v>1.05</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>1.23</v>
+      </c>
+      <c r="P4">
+        <v>2.36</v>
+      </c>
+      <c r="Q4">
+        <v>1.69</v>
+      </c>
+      <c r="R4">
+        <v>1.53</v>
+      </c>
+      <c r="S4">
+        <v>2.74</v>
+      </c>
+      <c r="T4">
+        <v>1.59</v>
+      </c>
+      <c r="U4">
+        <v>2.52</v>
+      </c>
+      <c r="V4">
+        <v>1.69</v>
+      </c>
+      <c r="W4">
+        <v>1.46</v>
+      </c>
+      <c r="X4">
+        <v>30</v>
+      </c>
+      <c r="Y4">
+        <v>15.5</v>
+      </c>
+      <c r="Z4">
+        <v>21</v>
+      </c>
+      <c r="AA4">
+        <v>60</v>
+      </c>
+      <c r="AB4">
+        <v>19.5</v>
+      </c>
+      <c r="AC4">
+        <v>9.6</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>30</v>
+      </c>
+      <c r="AF4">
+        <v>32</v>
+      </c>
+      <c r="AG4">
+        <v>16</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>320</v>
+      </c>
+      <c r="AK4">
+        <v>50</v>
+      </c>
+      <c r="AL4">
+        <v>80</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>34</v>
+      </c>
+      <c r="AO4">
+        <v>17.5</v>
+      </c>
+      <c r="AP4">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>13</v>
+      </c>
+      <c r="AS4">
+        <v>25</v>
+      </c>
+      <c r="AT4">
+        <v>12.5</v>
+      </c>
+      <c r="AU4">
+        <v>7.4</v>
+      </c>
+      <c r="AV4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>15.5</v>
+      </c>
+      <c r="AX4">
+        <v>17</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>12</v>
+      </c>
+      <c r="BA4">
+        <v>25</v>
+      </c>
+      <c r="BB4">
+        <v>32</v>
+      </c>
+      <c r="BC4">
+        <v>19.5</v>
+      </c>
+      <c r="BD4">
+        <v>26</v>
+      </c>
+      <c r="BE4">
+        <v>42</v>
+      </c>
+      <c r="BF4">
+        <v>16.5</v>
+      </c>
+      <c r="BG4">
+        <v>11.5</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5">
+        <v>4.9</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>1.46</v>
+      </c>
+      <c r="I5">
+        <v>1.64</v>
+      </c>
+      <c r="J5">
+        <v>4.4</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>4.7</v>
+      </c>
+      <c r="O5">
+        <v>1.16</v>
+      </c>
+      <c r="P5">
+        <v>2.2</v>
+      </c>
+      <c r="Q5">
+        <v>1.5</v>
+      </c>
+      <c r="R5">
+        <v>1.48</v>
+      </c>
+      <c r="S5">
+        <v>2.22</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>2.56</v>
+      </c>
+      <c r="W5">
+        <v>1.14</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>15.5</v>
+      </c>
+      <c r="Z5">
+        <v>15.5</v>
+      </c>
+      <c r="AA5">
+        <v>21</v>
+      </c>
+      <c r="AB5">
+        <v>38</v>
+      </c>
+      <c r="AC5">
+        <v>15.5</v>
+      </c>
+      <c r="AD5">
+        <v>14.5</v>
+      </c>
+      <c r="AE5">
+        <v>21</v>
+      </c>
+      <c r="AF5">
+        <v>75</v>
+      </c>
+      <c r="AG5">
+        <v>34</v>
+      </c>
+      <c r="AH5">
+        <v>28</v>
+      </c>
+      <c r="AI5">
+        <v>40</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>100</v>
+      </c>
+      <c r="AL5">
+        <v>90</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>95</v>
+      </c>
+      <c r="AO5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP5">
+        <v>2.72</v>
+      </c>
+      <c r="AQ5">
+        <v>2.3</v>
+      </c>
+      <c r="AR5">
+        <v>2.3</v>
+      </c>
+      <c r="AS5">
+        <v>2.4</v>
+      </c>
+      <c r="AT5">
+        <v>2.54</v>
+      </c>
+      <c r="AU5">
+        <v>2.3</v>
+      </c>
+      <c r="AV5">
+        <v>2.28</v>
+      </c>
+      <c r="AW5">
+        <v>11</v>
+      </c>
+      <c r="AX5">
+        <v>2.62</v>
+      </c>
+      <c r="AY5">
+        <v>17</v>
+      </c>
+      <c r="AZ5">
+        <v>2.48</v>
+      </c>
+      <c r="BA5">
+        <v>2.54</v>
+      </c>
+      <c r="BB5">
+        <v>2.72</v>
+      </c>
+      <c r="BC5">
+        <v>2.64</v>
+      </c>
+      <c r="BD5">
+        <v>2.64</v>
+      </c>
+      <c r="BE5">
+        <v>2.72</v>
+      </c>
+      <c r="BF5">
+        <v>2.64</v>
+      </c>
+      <c r="BG5">
+        <v>4.3</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6">
+        <v>1.04</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.03</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.01</v>
+      </c>
+      <c r="O6">
+        <v>1.01</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>1.01</v>
+      </c>
+      <c r="S6">
+        <v>1.01</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4.4</v>
+      </c>
+      <c r="H7">
+        <v>1.85</v>
+      </c>
+      <c r="I7">
+        <v>1.92</v>
+      </c>
+      <c r="J7">
+        <v>4.1</v>
+      </c>
+      <c r="K7">
+        <v>4.4</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.02</v>
+      </c>
+      <c r="N7">
+        <v>5.2</v>
+      </c>
+      <c r="O7">
+        <v>1.21</v>
+      </c>
+      <c r="P7">
+        <v>2.42</v>
+      </c>
+      <c r="Q7">
+        <v>1.63</v>
+      </c>
+      <c r="R7">
+        <v>1.56</v>
+      </c>
+      <c r="S7">
+        <v>2.52</v>
+      </c>
+      <c r="T7">
+        <v>1.62</v>
+      </c>
+      <c r="U7">
+        <v>2.42</v>
+      </c>
+      <c r="V7">
+        <v>2.08</v>
+      </c>
+      <c r="W7">
+        <v>1.29</v>
+      </c>
+      <c r="X7">
+        <v>23</v>
+      </c>
+      <c r="Y7">
+        <v>12.5</v>
+      </c>
+      <c r="Z7">
+        <v>14</v>
+      </c>
+      <c r="AA7">
+        <v>22</v>
+      </c>
+      <c r="AB7">
+        <v>21</v>
+      </c>
+      <c r="AC7">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>11.5</v>
+      </c>
+      <c r="AE7">
+        <v>18</v>
+      </c>
+      <c r="AF7">
+        <v>36</v>
+      </c>
+      <c r="AG7">
+        <v>17.5</v>
+      </c>
+      <c r="AH7">
+        <v>17</v>
+      </c>
+      <c r="AI7">
+        <v>34</v>
+      </c>
+      <c r="AJ7">
+        <v>110</v>
+      </c>
+      <c r="AK7">
+        <v>46</v>
+      </c>
+      <c r="AL7">
+        <v>55</v>
+      </c>
+      <c r="AM7">
+        <v>80</v>
+      </c>
+      <c r="AN7">
+        <v>36</v>
+      </c>
+      <c r="AO7">
+        <v>9</v>
+      </c>
+      <c r="AP7">
+        <v>20</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>12</v>
+      </c>
+      <c r="AS7">
+        <v>19</v>
+      </c>
+      <c r="AT7">
+        <v>18.5</v>
+      </c>
+      <c r="AU7">
+        <v>9</v>
+      </c>
+      <c r="AV7">
+        <v>9.4</v>
+      </c>
+      <c r="AW7">
+        <v>15.5</v>
+      </c>
+      <c r="AX7">
+        <v>30</v>
+      </c>
+      <c r="AY7">
+        <v>15.5</v>
+      </c>
+      <c r="AZ7">
+        <v>14.5</v>
+      </c>
+      <c r="BA7">
+        <v>24</v>
+      </c>
+      <c r="BB7">
+        <v>34</v>
+      </c>
+      <c r="BC7">
+        <v>38</v>
+      </c>
+      <c r="BD7">
+        <v>34</v>
+      </c>
+      <c r="BE7">
+        <v>55</v>
+      </c>
+      <c r="BF7">
+        <v>23</v>
+      </c>
+      <c r="BG7">
+        <v>8</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8">
+        <v>3.35</v>
+      </c>
+      <c r="G8">
+        <v>3.7</v>
+      </c>
+      <c r="H8">
+        <v>2.18</v>
+      </c>
+      <c r="I8">
+        <v>2.34</v>
+      </c>
+      <c r="J8">
+        <v>3.55</v>
+      </c>
+      <c r="K8">
+        <v>3.85</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8">
+        <v>1.27</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>1.84</v>
+      </c>
+      <c r="R8">
+        <v>1.18</v>
+      </c>
+      <c r="S8">
+        <v>1.84</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.74</v>
+      </c>
+      <c r="W8">
+        <v>1.37</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>12.5</v>
+      </c>
+      <c r="AQ8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR8">
+        <v>10.5</v>
+      </c>
+      <c r="AS8">
+        <v>21</v>
+      </c>
+      <c r="AT8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW8">
+        <v>17.5</v>
+      </c>
+      <c r="AX8">
+        <v>18</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>12.5</v>
+      </c>
+      <c r="BA8">
+        <v>26</v>
+      </c>
+      <c r="BB8">
+        <v>40</v>
+      </c>
+      <c r="BC8">
+        <v>26</v>
+      </c>
+      <c r="BD8">
+        <v>29</v>
+      </c>
+      <c r="BE8">
+        <v>40</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9">
+        <v>1.16</v>
+      </c>
+      <c r="G9">
+        <v>10.5</v>
+      </c>
+      <c r="H9">
+        <v>1.11</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>320</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.03</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10">
+        <v>2.46</v>
+      </c>
+      <c r="G10">
+        <v>3.6</v>
+      </c>
+      <c r="H10">
+        <v>2.16</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>3.15</v>
+      </c>
+      <c r="K10">
+        <v>7.8</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.06</v>
+      </c>
+      <c r="Q10">
+        <v>1.54</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11">
+        <v>2.44</v>
+      </c>
+      <c r="G11">
+        <v>3.05</v>
+      </c>
+      <c r="H11">
+        <v>2.72</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>4.2</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.14</v>
+      </c>
+      <c r="Q11">
+        <v>1.51</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12">
+        <v>6.2</v>
+      </c>
+      <c r="G12">
+        <v>48</v>
+      </c>
+      <c r="H12">
+        <v>1.46</v>
+      </c>
+      <c r="I12">
+        <v>1.8</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>6.6</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.08</v>
+      </c>
+      <c r="Q12">
+        <v>1.51</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13">
+        <v>1.85</v>
+      </c>
+      <c r="G13">
+        <v>2.16</v>
+      </c>
+      <c r="H13">
+        <v>3.4</v>
+      </c>
+      <c r="I13">
+        <v>5.3</v>
+      </c>
+      <c r="J13">
+        <v>3.3</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.5</v>
+      </c>
+      <c r="O13">
+        <v>1.34</v>
+      </c>
+      <c r="P13">
+        <v>1.72</v>
+      </c>
+      <c r="Q13">
+        <v>1.84</v>
+      </c>
+      <c r="R13">
+        <v>1.26</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.23</v>
+      </c>
+      <c r="W13">
+        <v>1.86</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14">
+        <v>2.98</v>
+      </c>
+      <c r="G14">
+        <v>4.6</v>
+      </c>
+      <c r="H14">
+        <v>1.99</v>
+      </c>
+      <c r="I14">
+        <v>2.64</v>
+      </c>
+      <c r="J14">
+        <v>2.94</v>
+      </c>
+      <c r="K14">
+        <v>3.55</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.53</v>
+      </c>
+      <c r="Q14">
+        <v>2.06</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15">
+        <v>1.84</v>
+      </c>
+      <c r="G15">
+        <v>2.32</v>
+      </c>
+      <c r="H15">
+        <v>3.85</v>
+      </c>
+      <c r="I15">
+        <v>5.8</v>
+      </c>
+      <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
+        <v>5.1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.58</v>
+      </c>
+      <c r="Q15">
+        <v>1.98</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16">
+        <v>3.1</v>
+      </c>
+      <c r="G16">
+        <v>4.6</v>
+      </c>
+      <c r="H16">
+        <v>1.93</v>
+      </c>
+      <c r="I16">
+        <v>2.2</v>
+      </c>
+      <c r="J16">
+        <v>3.85</v>
+      </c>
+      <c r="K16">
+        <v>6.4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.12</v>
+      </c>
+      <c r="Q16">
+        <v>1.66</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17">
+        <v>1.33</v>
+      </c>
+      <c r="G17">
+        <v>1.4</v>
+      </c>
+      <c r="H17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="J17">
+        <v>5.8</v>
+      </c>
+      <c r="K17">
+        <v>6.8</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.88</v>
+      </c>
+      <c r="Q17">
+        <v>1.39</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18">
+        <v>1.87</v>
+      </c>
+      <c r="G18">
+        <v>1.99</v>
+      </c>
+      <c r="H18">
+        <v>4.6</v>
+      </c>
+      <c r="I18">
+        <v>5.9</v>
+      </c>
+      <c r="J18">
+        <v>3.4</v>
+      </c>
+      <c r="K18">
+        <v>3.75</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.25</v>
+      </c>
+      <c r="Q18">
+        <v>2.22</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19">
+        <v>1.68</v>
+      </c>
+      <c r="G19">
+        <v>1.9</v>
+      </c>
+      <c r="H19">
+        <v>2.1</v>
+      </c>
+      <c r="I19">
+        <v>7.2</v>
+      </c>
+      <c r="J19">
+        <v>3.8</v>
+      </c>
+      <c r="K19">
+        <v>1000</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19">
+        <v>1.75</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20">
+        <v>1.47</v>
+      </c>
+      <c r="G20">
+        <v>1.52</v>
+      </c>
+      <c r="H20">
+        <v>7.2</v>
+      </c>
+      <c r="I20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J20">
+        <v>4.7</v>
+      </c>
+      <c r="K20">
+        <v>5.2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2.3</v>
+      </c>
+      <c r="Q20">
+        <v>1.63</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21">
+        <v>2.48</v>
+      </c>
+      <c r="G21">
+        <v>3.8</v>
+      </c>
+      <c r="H21">
+        <v>2.5</v>
+      </c>
+      <c r="I21">
+        <v>3.6</v>
+      </c>
+      <c r="J21">
+        <v>2.52</v>
+      </c>
+      <c r="K21">
+        <v>3.4</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.25</v>
+      </c>
+      <c r="Q21">
+        <v>2.92</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22">
+        <v>1.67</v>
+      </c>
+      <c r="G22">
+        <v>2.12</v>
+      </c>
+      <c r="H22">
+        <v>3.1</v>
+      </c>
+      <c r="I22">
+        <v>6.2</v>
+      </c>
+      <c r="J22">
+        <v>4.2</v>
+      </c>
+      <c r="K22">
+        <v>13</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
+        <v>1.26</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23">
+        <v>3.25</v>
+      </c>
+      <c r="G23">
+        <v>4.8</v>
+      </c>
+      <c r="H23">
+        <v>1.86</v>
+      </c>
+      <c r="I23">
+        <v>2.42</v>
+      </c>
+      <c r="J23">
+        <v>3.4</v>
+      </c>
+      <c r="K23">
+        <v>6.8</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.18</v>
+      </c>
+      <c r="Q23">
+        <v>1.46</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24">
+        <v>2.68</v>
+      </c>
+      <c r="G24">
+        <v>3.4</v>
+      </c>
+      <c r="H24">
+        <v>2.24</v>
+      </c>
+      <c r="I24">
+        <v>2.6</v>
+      </c>
+      <c r="J24">
+        <v>3.75</v>
+      </c>
+      <c r="K24">
+        <v>5.6</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.58</v>
+      </c>
+      <c r="Q24">
+        <v>1.45</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.24</v>
+      </c>
+      <c r="Q25">
+        <v>1.01</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>7.4</v>
+      </c>
+      <c r="H26">
+        <v>1.78</v>
+      </c>
+      <c r="I26">
+        <v>2.4</v>
+      </c>
+      <c r="J26">
+        <v>3.3</v>
+      </c>
+      <c r="K26">
+        <v>9.6</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.87</v>
+      </c>
+      <c r="Q26">
+        <v>1.6</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27">
+        <v>1.71</v>
+      </c>
+      <c r="G27">
+        <v>2.02</v>
+      </c>
+      <c r="H27">
+        <v>4.2</v>
+      </c>
+      <c r="I27">
+        <v>6.6</v>
+      </c>
+      <c r="J27">
+        <v>3.3</v>
+      </c>
+      <c r="K27">
+        <v>5.7</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.68</v>
+      </c>
+      <c r="Q27">
+        <v>1.86</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28">
+        <v>1.52</v>
+      </c>
+      <c r="G28">
+        <v>1.68</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J28">
+        <v>4.2</v>
+      </c>
+      <c r="K28">
+        <v>6.8</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>4.3</v>
+      </c>
+      <c r="O28">
+        <v>1.2</v>
+      </c>
+      <c r="P28">
+        <v>2.16</v>
+      </c>
+      <c r="Q28">
+        <v>1.66</v>
+      </c>
+      <c r="R28">
+        <v>1.46</v>
+      </c>
+      <c r="S28">
+        <v>2.56</v>
+      </c>
+      <c r="T28">
+        <v>1.01</v>
+      </c>
+      <c r="U28">
+        <v>1.01</v>
+      </c>
+      <c r="V28">
+        <v>1.13</v>
+      </c>
+      <c r="W28">
+        <v>2.48</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28">
+        <v>1.01</v>
+      </c>
+      <c r="AR28">
+        <v>1.01</v>
+      </c>
+      <c r="AS28">
+        <v>1.01</v>
+      </c>
+      <c r="AT28">
+        <v>1.01</v>
+      </c>
+      <c r="AU28">
+        <v>1.01</v>
+      </c>
+      <c r="AV28">
+        <v>1.01</v>
+      </c>
+      <c r="AW28">
+        <v>1.01</v>
+      </c>
+      <c r="AX28">
+        <v>1.01</v>
+      </c>
+      <c r="AY28">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28">
+        <v>1.01</v>
+      </c>
+      <c r="BA28">
+        <v>1.01</v>
+      </c>
+      <c r="BB28">
+        <v>1.01</v>
+      </c>
+      <c r="BC28">
+        <v>1.01</v>
+      </c>
+      <c r="BD28">
+        <v>1.01</v>
+      </c>
+      <c r="BE28">
+        <v>1.01</v>
+      </c>
+      <c r="BF28">
+        <v>1.01</v>
+      </c>
+      <c r="BG28">
+        <v>1.01</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.01</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.01</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.01</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.01</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29">
+        <v>2.12</v>
+      </c>
+      <c r="G29">
+        <v>2.72</v>
+      </c>
+      <c r="H29">
+        <v>2.84</v>
+      </c>
+      <c r="I29">
+        <v>4.4</v>
+      </c>
+      <c r="J29">
+        <v>2.9</v>
+      </c>
+      <c r="K29">
+        <v>3.55</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1.76</v>
+      </c>
+      <c r="Q29">
+        <v>1.01</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30">
+        <v>2.56</v>
+      </c>
+      <c r="G30">
+        <v>2.6</v>
+      </c>
+      <c r="H30">
+        <v>2.94</v>
+      </c>
+      <c r="I30">
+        <v>2.96</v>
+      </c>
+      <c r="J30">
+        <v>3.65</v>
+      </c>
+      <c r="K30">
+        <v>3.7</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1.05</v>
+      </c>
+      <c r="N30">
+        <v>4.4</v>
+      </c>
+      <c r="O30">
+        <v>1.25</v>
+      </c>
+      <c r="P30">
+        <v>2.16</v>
+      </c>
+      <c r="Q30">
+        <v>1.77</v>
+      </c>
+      <c r="R30">
+        <v>1.46</v>
+      </c>
+      <c r="S30">
+        <v>2.92</v>
+      </c>
+      <c r="T30">
+        <v>1.64</v>
+      </c>
+      <c r="U30">
+        <v>2.4</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>18.5</v>
+      </c>
+      <c r="Y30">
+        <v>15.5</v>
+      </c>
+      <c r="Z30">
+        <v>26</v>
+      </c>
+      <c r="AA30">
+        <v>55</v>
+      </c>
+      <c r="AB30">
+        <v>13</v>
+      </c>
+      <c r="AC30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD30">
+        <v>14</v>
+      </c>
+      <c r="AE30">
+        <v>34</v>
+      </c>
+      <c r="AF30">
+        <v>19</v>
+      </c>
+      <c r="AG30">
+        <v>12.5</v>
+      </c>
+      <c r="AH30">
+        <v>16.5</v>
+      </c>
+      <c r="AI30">
+        <v>44</v>
+      </c>
+      <c r="AJ30">
+        <v>80</v>
+      </c>
+      <c r="AK30">
+        <v>30</v>
+      </c>
+      <c r="AL30">
+        <v>40</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>18.5</v>
+      </c>
+      <c r="AO30">
+        <v>24</v>
+      </c>
+      <c r="AP30">
+        <v>16</v>
+      </c>
+      <c r="AQ30">
+        <v>12.5</v>
+      </c>
+      <c r="AR30">
+        <v>17</v>
+      </c>
+      <c r="AS30">
+        <v>25</v>
+      </c>
+      <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>7.4</v>
+      </c>
+      <c r="AV30">
+        <v>12</v>
+      </c>
+      <c r="AW30">
+        <v>19</v>
+      </c>
+      <c r="AX30">
+        <v>15.5</v>
+      </c>
+      <c r="AY30">
+        <v>9.6</v>
+      </c>
+      <c r="AZ30">
+        <v>13.5</v>
+      </c>
+      <c r="BA30">
+        <v>23</v>
+      </c>
+      <c r="BB30">
+        <v>23</v>
+      </c>
+      <c r="BC30">
+        <v>21</v>
+      </c>
+      <c r="BD30">
+        <v>22</v>
+      </c>
+      <c r="BE30">
+        <v>32</v>
+      </c>
+      <c r="BF30">
+        <v>15.5</v>
+      </c>
+      <c r="BG30">
+        <v>19.5</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.01</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.01</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.01</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.01</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.01</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31">
+        <v>2.4</v>
+      </c>
+      <c r="G31">
+        <v>2.44</v>
+      </c>
+      <c r="H31">
+        <v>3.65</v>
+      </c>
+      <c r="I31">
+        <v>3.75</v>
+      </c>
+      <c r="J31">
+        <v>3.15</v>
+      </c>
+      <c r="K31">
+        <v>3.2</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.11</v>
+      </c>
+      <c r="N31">
+        <v>2.98</v>
+      </c>
+      <c r="O31">
+        <v>1.48</v>
+      </c>
+      <c r="P31">
+        <v>1.65</v>
+      </c>
+      <c r="Q31">
+        <v>2.44</v>
+      </c>
+      <c r="R31">
+        <v>1.24</v>
+      </c>
+      <c r="S31">
+        <v>4.8</v>
+      </c>
+      <c r="T31">
+        <v>2.02</v>
+      </c>
+      <c r="U31">
+        <v>1.92</v>
+      </c>
+      <c r="V31">
+        <v>1.36</v>
+      </c>
+      <c r="W31">
+        <v>1.69</v>
+      </c>
+      <c r="X31">
+        <v>9.6</v>
+      </c>
+      <c r="Y31">
+        <v>11</v>
+      </c>
+      <c r="Z31">
+        <v>24</v>
+      </c>
+      <c r="AA31">
+        <v>85</v>
+      </c>
+      <c r="AB31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC31">
+        <v>6.8</v>
+      </c>
+      <c r="AD31">
+        <v>15.5</v>
+      </c>
+      <c r="AE31">
+        <v>55</v>
+      </c>
+      <c r="AF31">
+        <v>14</v>
+      </c>
+      <c r="AG31">
+        <v>12</v>
+      </c>
+      <c r="AH31">
+        <v>20</v>
+      </c>
+      <c r="AI31">
+        <v>80</v>
+      </c>
+      <c r="AJ31">
+        <v>36</v>
+      </c>
+      <c r="AK31">
+        <v>32</v>
+      </c>
+      <c r="AL31">
+        <v>55</v>
+      </c>
+      <c r="AM31">
+        <v>160</v>
+      </c>
+      <c r="AN31">
+        <v>29</v>
+      </c>
+      <c r="AO31">
+        <v>65</v>
+      </c>
+      <c r="AP31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ31">
+        <v>10</v>
+      </c>
+      <c r="AR31">
+        <v>20</v>
+      </c>
+      <c r="AS31">
+        <v>32</v>
+      </c>
+      <c r="AT31">
+        <v>7.6</v>
+      </c>
+      <c r="AU31">
+        <v>6.4</v>
+      </c>
+      <c r="AV31">
+        <v>14</v>
+      </c>
+      <c r="AW31">
+        <v>27</v>
+      </c>
+      <c r="AX31">
+        <v>12.5</v>
+      </c>
+      <c r="AY31">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31">
+        <v>18</v>
+      </c>
+      <c r="BA31">
+        <v>34</v>
+      </c>
+      <c r="BB31">
+        <v>21</v>
+      </c>
+      <c r="BC31">
+        <v>20</v>
+      </c>
+      <c r="BD31">
+        <v>30</v>
+      </c>
+      <c r="BE31">
+        <v>44</v>
+      </c>
+      <c r="BF31">
+        <v>19</v>
+      </c>
+      <c r="BG31">
+        <v>32</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.01</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.01</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.01</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.01</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.01</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.01</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>1.24</v>
+      </c>
+      <c r="Q32">
+        <v>1.01</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33">
+        <v>13.5</v>
+      </c>
+      <c r="G33">
+        <v>19.5</v>
+      </c>
+      <c r="H33">
+        <v>1.23</v>
+      </c>
+      <c r="I33">
+        <v>1.27</v>
+      </c>
+      <c r="J33">
+        <v>6.8</v>
+      </c>
+      <c r="K33">
+        <v>7.4</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>2.12</v>
+      </c>
+      <c r="Q33">
+        <v>1.53</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33">
+        <v>0</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>0</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+      <c r="BQ33">
+        <v>0</v>
+      </c>
+      <c r="BR33">
+        <v>0</v>
+      </c>
+      <c r="BS33">
+        <v>0</v>
+      </c>
+      <c r="BT33">
+        <v>0</v>
+      </c>
+      <c r="BU33">
+        <v>0</v>
+      </c>
+      <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
+        <v>0</v>
+      </c>
+      <c r="BX33">
+        <v>0</v>
+      </c>
+      <c r="BY33">
+        <v>0</v>
+      </c>
+      <c r="BZ33">
+        <v>0</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34">
+        <v>1.37</v>
+      </c>
+      <c r="G34">
+        <v>1.38</v>
+      </c>
+      <c r="H34">
+        <v>10.5</v>
+      </c>
+      <c r="I34">
+        <v>12.5</v>
+      </c>
+      <c r="J34">
+        <v>5.2</v>
+      </c>
+      <c r="K34">
+        <v>5.8</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1.05</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>2.26</v>
+      </c>
+      <c r="Q34">
+        <v>1.66</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35">
+        <v>2.34</v>
+      </c>
+      <c r="G35">
+        <v>2.56</v>
+      </c>
+      <c r="H35">
+        <v>3.6</v>
+      </c>
+      <c r="I35">
+        <v>4.2</v>
+      </c>
+      <c r="J35">
+        <v>2.86</v>
+      </c>
+      <c r="K35">
+        <v>3.15</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1.25</v>
+      </c>
+      <c r="Q35">
+        <v>1.01</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
+        <v>0</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>0</v>
+      </c>
+      <c r="BY35">
+        <v>0</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -592,7 +592,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 00:48:44</t>
+    <t>2026-08-15 03:14:44</t>
   </si>
 </sst>
 </file>
@@ -1186,13 +1186,13 @@
         <v>158</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I2">
         <v>3.1</v>
@@ -1201,7 +1201,7 @@
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1210,13 +1210,13 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
         <v>1.27</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
         <v>1.8</v>
@@ -1237,7 +1237,7 @@
         <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1431,13 +1431,13 @@
         <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
         <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
         <v>3.2</v>
@@ -1446,13 +1446,13 @@
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
         <v>1.02</v>
@@ -1461,13 +1461,13 @@
         <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1479,7 +1479,7 @@
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1590,10 +1590,10 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1673,7 +1673,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
         <v>2.34</v>
@@ -1682,13 +1682,13 @@
         <v>2.44</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1703,16 +1703,16 @@
         <v>2.36</v>
       </c>
       <c r="Q4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
         <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
         <v>2.52</v>
@@ -1724,100 +1724,100 @@
         <v>1.46</v>
       </c>
       <c r="X4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AB4">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AF4">
+        <v>24</v>
+      </c>
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>16</v>
+      </c>
+      <c r="AI4">
+        <v>34</v>
+      </c>
+      <c r="AJ4">
+        <v>300</v>
+      </c>
+      <c r="AK4">
         <v>32</v>
       </c>
-      <c r="AG4">
-        <v>16</v>
-      </c>
-      <c r="AH4">
-        <v>19</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
-      <c r="AJ4">
-        <v>320</v>
-      </c>
-      <c r="AK4">
-        <v>50</v>
-      </c>
       <c r="AL4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AO4">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AP4">
         <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
         <v>25</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX4">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>25</v>
       </c>
       <c r="BB4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD4">
         <v>26</v>
@@ -1826,70 +1826,70 @@
         <v>42</v>
       </c>
       <c r="BF4">
+        <v>20</v>
+      </c>
+      <c r="BG4">
+        <v>12</v>
+      </c>
+      <c r="BH4">
+        <v>4.5</v>
+      </c>
+      <c r="BI4">
+        <v>3.25</v>
+      </c>
+      <c r="BJ4">
+        <v>10</v>
+      </c>
+      <c r="BK4">
+        <v>6.8</v>
+      </c>
+      <c r="BL4">
+        <v>100</v>
+      </c>
+      <c r="BM4">
+        <v>60</v>
+      </c>
+      <c r="BN4">
+        <v>7.4</v>
+      </c>
+      <c r="BO4">
+        <v>5.1</v>
+      </c>
+      <c r="BP4">
+        <v>25</v>
+      </c>
+      <c r="BQ4">
         <v>16.5</v>
       </c>
-      <c r="BG4">
-        <v>11.5</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.01</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.01</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
         <v>192</v>
@@ -1918,7 +1918,7 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I5">
         <v>1.64</v>
@@ -1945,10 +1945,10 @@
         <v>2.2</v>
       </c>
       <c r="Q5">
+        <v>1.52</v>
+      </c>
+      <c r="R5">
         <v>1.5</v>
-      </c>
-      <c r="R5">
-        <v>1.48</v>
       </c>
       <c r="S5">
         <v>2.22</v>
@@ -2017,34 +2017,34 @@
         <v>95</v>
       </c>
       <c r="AO5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AQ5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AR5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AS5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AT5">
         <v>2.54</v>
       </c>
       <c r="AU5">
+        <v>2.32</v>
+      </c>
+      <c r="AV5">
         <v>2.3</v>
-      </c>
-      <c r="AV5">
-        <v>2.28</v>
       </c>
       <c r="AW5">
         <v>11</v>
       </c>
       <c r="AX5">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AY5">
         <v>17</v>
@@ -2053,22 +2053,22 @@
         <v>2.48</v>
       </c>
       <c r="BA5">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BC5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BD5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BE5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BF5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BG5">
         <v>4.3</v>
@@ -2396,46 +2396,46 @@
         <v>163</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G7">
         <v>4.4</v>
       </c>
       <c r="H7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
         <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R7">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S7">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T7">
         <v>1.62</v>
@@ -2444,7 +2444,7 @@
         <v>2.42</v>
       </c>
       <c r="V7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W7">
         <v>1.29</v>
@@ -2459,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="AA7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB7">
         <v>21</v>
@@ -2471,7 +2471,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF7">
         <v>36</v>
@@ -2483,16 +2483,16 @@
         <v>17</v>
       </c>
       <c r="AI7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK7">
         <v>46</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>80</v>
@@ -2501,7 +2501,7 @@
         <v>36</v>
       </c>
       <c r="AO7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AP7">
         <v>20</v>
@@ -2519,7 +2519,7 @@
         <v>18.5</v>
       </c>
       <c r="AU7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7">
         <v>9.4</v>
@@ -2534,7 +2534,7 @@
         <v>15.5</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA7">
         <v>24</v>
@@ -2546,16 +2546,16 @@
         <v>38</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BE7">
         <v>55</v>
       </c>
       <c r="BF7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2644,7 +2644,7 @@
         <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I8">
         <v>2.34</v>
@@ -2662,28 +2662,28 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O8">
         <v>1.27</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S8">
-        <v>1.84</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
         <v>1.01</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.74</v>
@@ -2880,7 +2880,7 @@
         <v>165</v>
       </c>
       <c r="F9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G9">
         <v>10.5</v>
@@ -3122,7 +3122,7 @@
         <v>166</v>
       </c>
       <c r="F10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
         <v>3.6</v>
@@ -3134,10 +3134,10 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3152,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>3.05</v>
       </c>
       <c r="H11">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I11">
         <v>3</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q11">
         <v>1.51</v>
@@ -3606,22 +3606,22 @@
         <v>168</v>
       </c>
       <c r="F12">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="G12">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H12">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="I12">
         <v>1.8</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>1.51</v>
@@ -3848,22 +3848,22 @@
         <v>169</v>
       </c>
       <c r="F13">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
         <v>5.3</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3878,16 +3878,16 @@
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3899,7 +3899,7 @@
         <v>1.23</v>
       </c>
       <c r="W13">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4090,22 +4090,22 @@
         <v>170</v>
       </c>
       <c r="F14">
-        <v>2.98</v>
+        <v>1.08</v>
       </c>
       <c r="G14">
         <v>4.6</v>
       </c>
       <c r="H14">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="I14">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q14">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4332,22 +4332,22 @@
         <v>171</v>
       </c>
       <c r="F15">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G15">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="H15">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
         <v>3.25</v>
       </c>
       <c r="K15">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q15">
         <v>1.98</v>
@@ -4577,19 +4577,19 @@
         <v>3.1</v>
       </c>
       <c r="G16">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>1.93</v>
+        <v>1.06</v>
       </c>
       <c r="I16">
         <v>2.2</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>1.83</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>410</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4604,10 +4604,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4816,22 +4816,22 @@
         <v>173</v>
       </c>
       <c r="F17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H17">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="J17">
         <v>5.8</v>
       </c>
       <c r="K17">
-        <v>6.8</v>
+        <v>70</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4846,10 +4846,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>1.87</v>
       </c>
       <c r="G18">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H18">
         <v>4.6</v>
@@ -5070,7 +5070,7 @@
         <v>5.9</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K18">
         <v>3.75</v>
@@ -5091,7 +5091,7 @@
         <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5300,16 +5300,16 @@
         <v>175</v>
       </c>
       <c r="F19">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G19">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I19">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J19">
         <v>3.8</v>
@@ -5333,7 +5333,7 @@
         <v>2</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5542,10 +5542,10 @@
         <v>176</v>
       </c>
       <c r="F20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G20">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H20">
         <v>7.2</v>
@@ -5554,7 +5554,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K20">
         <v>5.2</v>
@@ -5572,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q20">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5784,22 +5784,22 @@
         <v>177</v>
       </c>
       <c r="F21">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="G21">
         <v>3.8</v>
       </c>
       <c r="H21">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="I21">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6026,22 +6026,22 @@
         <v>178</v>
       </c>
       <c r="F22">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H22">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K22">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6056,10 +6056,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q22">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6268,22 +6268,22 @@
         <v>179</v>
       </c>
       <c r="F23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G23">
         <v>4.8</v>
       </c>
       <c r="H23">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="I23">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K23">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6298,10 +6298,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6510,22 +6510,22 @@
         <v>180</v>
       </c>
       <c r="F24">
-        <v>2.68</v>
+        <v>1.63</v>
       </c>
       <c r="G24">
         <v>3.4</v>
       </c>
       <c r="H24">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="I24">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J24">
         <v>3.75</v>
       </c>
       <c r="K24">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6994,22 +6994,22 @@
         <v>182</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G26">
         <v>7.4</v>
       </c>
       <c r="H26">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I26">
         <v>2.4</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
         <v>1.6</v>
@@ -7242,16 +7242,16 @@
         <v>2.02</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="I27">
         <v>6.6</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         <v>1.52</v>
       </c>
       <c r="G28">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -7502,22 +7502,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="O28">
         <v>1.2</v>
       </c>
       <c r="P28">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R28">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7529,7 +7529,7 @@
         <v>1.13</v>
       </c>
       <c r="W28">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7720,7 +7720,7 @@
         <v>185</v>
       </c>
       <c r="F29">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G29">
         <v>2.72</v>
@@ -7729,10 +7729,10 @@
         <v>2.84</v>
       </c>
       <c r="I29">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J29">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K29">
         <v>3.55</v>
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q29">
         <v>1.01</v>
@@ -7971,7 +7971,7 @@
         <v>2.94</v>
       </c>
       <c r="I30">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J30">
         <v>3.65</v>
@@ -8019,7 +8019,7 @@
         <v>18.5</v>
       </c>
       <c r="Y30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z30">
         <v>26</v>
@@ -8049,13 +8049,13 @@
         <v>16.5</v>
       </c>
       <c r="AI30">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
         <v>80</v>
       </c>
       <c r="AK30">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL30">
         <v>40</v>
@@ -8079,7 +8079,7 @@
         <v>17</v>
       </c>
       <c r="AS30">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
@@ -8097,13 +8097,13 @@
         <v>15.5</v>
       </c>
       <c r="AY30">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30">
         <v>13.5</v>
       </c>
       <c r="BA30">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB30">
         <v>23</v>
@@ -8240,7 +8240,7 @@
         <v>2.44</v>
       </c>
       <c r="R31">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S31">
         <v>4.8</v>
@@ -8264,7 +8264,7 @@
         <v>11</v>
       </c>
       <c r="Z31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA31">
         <v>85</v>
@@ -8294,7 +8294,7 @@
         <v>80</v>
       </c>
       <c r="AJ31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK31">
         <v>32</v>
@@ -8688,10 +8688,10 @@
         <v>189</v>
       </c>
       <c r="F33">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="G33">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="H33">
         <v>1.23</v>
@@ -8718,10 +8718,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q33">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8930,22 +8930,22 @@
         <v>190</v>
       </c>
       <c r="F34">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="G34">
         <v>1.38</v>
       </c>
       <c r="H34">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="I34">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="J34">
         <v>5.2</v>
       </c>
       <c r="K34">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9172,22 +9172,22 @@
         <v>191</v>
       </c>
       <c r="F35">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="G35">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H35">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I35">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="J35">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="K35">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="L35">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="189">
   <si>
     <t>League</t>
   </si>
@@ -268,18 +268,15 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
   </si>
   <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Lithuanian A Lyga</t>
-  </si>
-  <si>
-    <t>Finnish Veikkausliiga</t>
-  </si>
-  <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
@@ -298,12 +295,12 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
     <t>Polish I Liga</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>01:10:00</t>
   </si>
   <si>
-    <t>01:15:00</t>
-  </si>
-  <si>
     <t>02:30:00</t>
   </si>
   <si>
@@ -400,24 +394,21 @@
     <t>Santos Laguna</t>
   </si>
   <si>
-    <t>Once Caldas</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
     <t>Tijuana</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
-    <t>Fk Siauliai</t>
-  </si>
-  <si>
-    <t>Gnistan</t>
-  </si>
-  <si>
     <t>Zalaegerszeg</t>
   </si>
   <si>
@@ -439,12 +430,12 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
+    <t>Brondby</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Brondby</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
@@ -502,24 +493,21 @@
     <t>Guadalajara</t>
   </si>
   <si>
-    <t>Alianza FC Valledupar</t>
-  </si>
-  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>Cruz Azul</t>
   </si>
   <si>
+    <t>Ilves</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
     <t>Zorya</t>
   </si>
   <si>
-    <t>Panevezys</t>
-  </si>
-  <si>
-    <t>Ilves</t>
-  </si>
-  <si>
     <t>Ferencvaros</t>
   </si>
   <si>
@@ -541,12 +529,12 @@
     <t>Sabadell</t>
   </si>
   <si>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
     <t>Puszcza Niepolomice</t>
   </si>
   <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -592,7 +580,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 03:14:44</t>
+    <t>2026-08-15 05:40:33</t>
   </si>
 </sst>
 </file>
@@ -924,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1174,16 +1162,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
         <v>104</v>
       </c>
-      <c r="C2" t="s">
-        <v>105</v>
-      </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2">
         <v>2.5</v>
@@ -1408,7 +1396,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1416,16 +1404,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" t="s">
-        <v>105</v>
-      </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F3">
         <v>2.3</v>
@@ -1650,7 +1638,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1658,16 +1646,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1682,13 +1670,13 @@
         <v>2.44</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1697,10 +1685,10 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
         <v>1.7</v>
@@ -1715,7 +1703,7 @@
         <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
         <v>1.69</v>
@@ -1730,7 +1718,7 @@
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA4">
         <v>34</v>
@@ -1763,7 +1751,7 @@
         <v>300</v>
       </c>
       <c r="AK4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1781,19 +1769,19 @@
         <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>10</v>
@@ -1805,13 +1793,13 @@
         <v>19.5</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BB4">
         <v>28</v>
@@ -1820,16 +1808,16 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BE4">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH4">
         <v>4.5</v>
@@ -1892,7 +1880,7 @@
         <v>14</v>
       </c>
       <c r="CB4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1900,16 +1888,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F5">
         <v>4.9</v>
@@ -2134,186 +2122,186 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F6">
+        <v>4.1</v>
+      </c>
+      <c r="G6">
+        <v>4.4</v>
+      </c>
+      <c r="H6">
+        <v>1.86</v>
+      </c>
+      <c r="I6">
+        <v>1.91</v>
+      </c>
+      <c r="J6">
+        <v>4.2</v>
+      </c>
+      <c r="K6">
+        <v>4.4</v>
+      </c>
+      <c r="L6">
+        <v>1.3</v>
+      </c>
+      <c r="M6">
         <v>1.04</v>
       </c>
-      <c r="G6">
-        <v>1000</v>
-      </c>
-      <c r="H6">
-        <v>1.04</v>
-      </c>
-      <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6">
-        <v>1.03</v>
-      </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2376,186 +2364,186 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="G7">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="H7">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="I7">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="T7">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="W7">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
         <v>12.5</v>
       </c>
-      <c r="Z7">
-        <v>14</v>
-      </c>
-      <c r="AA7">
+      <c r="AQ7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7">
+        <v>10.5</v>
+      </c>
+      <c r="AS7">
         <v>21</v>
       </c>
-      <c r="AB7">
-        <v>21</v>
-      </c>
-      <c r="AC7">
+      <c r="AT7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU7">
+        <v>6.6</v>
+      </c>
+      <c r="AV7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW7">
+        <v>17.5</v>
+      </c>
+      <c r="AX7">
+        <v>18</v>
+      </c>
+      <c r="AY7">
         <v>10</v>
       </c>
-      <c r="AD7">
-        <v>11.5</v>
-      </c>
-      <c r="AE7">
-        <v>17.5</v>
-      </c>
-      <c r="AF7">
-        <v>36</v>
-      </c>
-      <c r="AG7">
-        <v>17.5</v>
-      </c>
-      <c r="AH7">
-        <v>17</v>
-      </c>
-      <c r="AI7">
-        <v>32</v>
-      </c>
-      <c r="AJ7">
-        <v>100</v>
-      </c>
-      <c r="AK7">
-        <v>46</v>
-      </c>
-      <c r="AL7">
-        <v>46</v>
-      </c>
-      <c r="AM7">
-        <v>80</v>
-      </c>
-      <c r="AN7">
-        <v>36</v>
-      </c>
-      <c r="AO7">
-        <v>9.4</v>
-      </c>
-      <c r="AP7">
-        <v>20</v>
-      </c>
-      <c r="AQ7">
-        <v>11</v>
-      </c>
-      <c r="AR7">
-        <v>12</v>
-      </c>
-      <c r="AS7">
-        <v>19</v>
-      </c>
-      <c r="AT7">
-        <v>18.5</v>
-      </c>
-      <c r="AU7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV7">
-        <v>9.4</v>
-      </c>
-      <c r="AW7">
-        <v>15.5</v>
-      </c>
-      <c r="AX7">
-        <v>30</v>
-      </c>
-      <c r="AY7">
-        <v>15.5</v>
-      </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB7">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BC7">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE7">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BF7">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2618,249 +2606,249 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="I8">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2868,34 +2856,34 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F9">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>320</v>
+        <v>7.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2910,10 +2898,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3102,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3110,34 +3098,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="H10">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>7.4</v>
+        <v>320</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3152,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.08</v>
+        <v>1.03</v>
       </c>
       <c r="Q10">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3344,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3352,34 +3340,34 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F11">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="G11">
-        <v>3.05</v>
+        <v>26</v>
       </c>
       <c r="H11">
-        <v>2.66</v>
+        <v>1.48</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3394,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q11">
         <v>1.51</v>
@@ -3586,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3594,518 +3582,518 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F12">
-        <v>5.7</v>
+        <v>1.87</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>2.18</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="I12">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F13">
-        <v>1.87</v>
+        <v>3.4</v>
       </c>
       <c r="G13">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="H13">
-        <v>3.55</v>
+        <v>1.94</v>
       </c>
       <c r="I13">
+        <v>2.6</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
         <v>5.3</v>
       </c>
-      <c r="J13">
-        <v>3.4</v>
-      </c>
-      <c r="K13">
-        <v>3.85</v>
-      </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F14">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="H14">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="I14">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4120,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4312,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4320,34 +4308,34 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F15">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="G15">
-        <v>2.12</v>
+        <v>4.6</v>
       </c>
       <c r="H15">
-        <v>4.2</v>
+        <v>1.93</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4362,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4554,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4562,34 +4550,34 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F16">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="H16">
-        <v>1.06</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>2.2</v>
+        <v>19.5</v>
       </c>
       <c r="J16">
-        <v>1.83</v>
+        <v>5.8</v>
       </c>
       <c r="K16">
-        <v>410</v>
+        <v>70</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4604,10 +4592,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4796,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4804,40 +4792,40 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F17">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="G17">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="I17">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="J17">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="K17">
-        <v>70</v>
+        <v>3.7</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4846,10 +4834,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5038,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5046,40 +5034,40 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F18">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="G18">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="H18">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="I18">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J18">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="K18">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5088,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>2.24</v>
+        <v>1.6</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5280,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5288,16 +5276,16 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F19">
         <v>1.7</v>
@@ -5306,7 +5294,7 @@
         <v>1.89</v>
       </c>
       <c r="H19">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I19">
         <v>6.8</v>
@@ -5315,7 +5303,7 @@
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5522,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5530,34 +5518,34 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F20">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="G20">
-        <v>1.49</v>
+        <v>3.8</v>
       </c>
       <c r="H20">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="I20">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="J20">
-        <v>4.9</v>
+        <v>2.58</v>
       </c>
       <c r="K20">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5572,10 +5560,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.6</v>
+        <v>2.96</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5764,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5772,34 +5760,34 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F21">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="G21">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>1.76</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="J21">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="K21">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5814,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q21">
-        <v>2.96</v>
+        <v>1.28</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6006,42 +5994,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F22">
-        <v>1.69</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="H22">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="I22">
-        <v>5.4</v>
+        <v>2.36</v>
       </c>
       <c r="J22">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K22">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6056,10 +6044,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6248,42 +6236,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F23">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="H23">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="I23">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K23">
-        <v>6.6</v>
+        <v>440</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6298,10 +6286,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q23">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6490,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6498,34 +6486,34 @@
         <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F24">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6540,10 +6528,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6732,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6740,34 +6728,34 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6782,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6974,42 +6962,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F26">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="G26">
-        <v>7.4</v>
+        <v>2.02</v>
       </c>
       <c r="H26">
-        <v>1.77</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
         <v>3.4</v>
       </c>
       <c r="K26">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7024,10 +7012,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q26">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7216,491 +7204,491 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F27">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="G27">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="H27">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="Q27">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F28">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="G28">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="I28">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="J28">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="K28">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R28">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7708,64 +7696,64 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F29">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="G29">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H29">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="I29">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="J29">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="K29">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P29">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7774,175 +7762,175 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7950,179 +7938,179 @@
         <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F30">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G30">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="H30">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="I30">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="K30">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N30">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O30">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="P30">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="Q30">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="R30">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="S30">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="T30">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X30">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y30">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA30">
+        <v>75</v>
+      </c>
+      <c r="AB30">
+        <v>8.6</v>
+      </c>
+      <c r="AC30">
+        <v>6.8</v>
+      </c>
+      <c r="AD30">
+        <v>15.5</v>
+      </c>
+      <c r="AE30">
         <v>55</v>
       </c>
-      <c r="AB30">
-        <v>13</v>
-      </c>
-      <c r="AC30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD30">
+      <c r="AF30">
         <v>14</v>
       </c>
-      <c r="AE30">
+      <c r="AG30">
+        <v>12</v>
+      </c>
+      <c r="AH30">
+        <v>19.5</v>
+      </c>
+      <c r="AI30">
+        <v>70</v>
+      </c>
+      <c r="AJ30">
         <v>34</v>
       </c>
-      <c r="AF30">
-        <v>19</v>
-      </c>
-      <c r="AG30">
+      <c r="AK30">
+        <v>30</v>
+      </c>
+      <c r="AL30">
+        <v>50</v>
+      </c>
+      <c r="AM30">
+        <v>140</v>
+      </c>
+      <c r="AN30">
+        <v>29</v>
+      </c>
+      <c r="AO30">
+        <v>60</v>
+      </c>
+      <c r="AP30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ30">
+        <v>10</v>
+      </c>
+      <c r="AR30">
+        <v>20</v>
+      </c>
+      <c r="AS30">
+        <v>32</v>
+      </c>
+      <c r="AT30">
+        <v>7.8</v>
+      </c>
+      <c r="AU30">
+        <v>6.4</v>
+      </c>
+      <c r="AV30">
+        <v>14</v>
+      </c>
+      <c r="AW30">
+        <v>27</v>
+      </c>
+      <c r="AX30">
         <v>12.5</v>
-      </c>
-      <c r="AH30">
-        <v>16.5</v>
-      </c>
-      <c r="AI30">
-        <v>90</v>
-      </c>
-      <c r="AJ30">
-        <v>80</v>
-      </c>
-      <c r="AK30">
-        <v>27</v>
-      </c>
-      <c r="AL30">
-        <v>40</v>
-      </c>
-      <c r="AM30">
-        <v>1000</v>
-      </c>
-      <c r="AN30">
-        <v>18.5</v>
-      </c>
-      <c r="AO30">
-        <v>24</v>
-      </c>
-      <c r="AP30">
-        <v>16</v>
-      </c>
-      <c r="AQ30">
-        <v>12.5</v>
-      </c>
-      <c r="AR30">
-        <v>17</v>
-      </c>
-      <c r="AS30">
-        <v>36</v>
-      </c>
-      <c r="AT30">
-        <v>11.5</v>
-      </c>
-      <c r="AU30">
-        <v>7.4</v>
-      </c>
-      <c r="AV30">
-        <v>12</v>
-      </c>
-      <c r="AW30">
-        <v>19</v>
-      </c>
-      <c r="AX30">
-        <v>15.5</v>
       </c>
       <c r="AY30">
         <v>10.5</v>
       </c>
       <c r="AZ30">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
+        <v>32</v>
+      </c>
+      <c r="BB30">
+        <v>21</v>
+      </c>
+      <c r="BC30">
+        <v>25</v>
+      </c>
+      <c r="BD30">
+        <v>42</v>
+      </c>
+      <c r="BE30">
+        <v>42</v>
+      </c>
+      <c r="BF30">
+        <v>24</v>
+      </c>
+      <c r="BG30">
         <v>30</v>
       </c>
-      <c r="BB30">
-        <v>23</v>
-      </c>
-      <c r="BC30">
-        <v>21</v>
-      </c>
-      <c r="BD30">
-        <v>22</v>
-      </c>
-      <c r="BE30">
-        <v>32</v>
-      </c>
-      <c r="BF30">
-        <v>15.5</v>
-      </c>
-      <c r="BG30">
-        <v>19.5</v>
-      </c>
       <c r="BH30">
         <v>1000</v>
       </c>
@@ -8184,532 +8172,532 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F31">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q31">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="R31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BG31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32">
+        <v>12.5</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+      <c r="H32">
+        <v>1.23</v>
+      </c>
+      <c r="I32">
+        <v>1.27</v>
+      </c>
+      <c r="J32">
+        <v>6.8</v>
+      </c>
+      <c r="K32">
+        <v>7.4</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>1.25</v>
+      </c>
+      <c r="Q32">
+        <v>1.01</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>0</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
         <v>188</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.24</v>
-      </c>
-      <c r="Q32">
-        <v>1.01</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
-      <c r="BV32">
-        <v>0</v>
-      </c>
-      <c r="BW32">
-        <v>0</v>
-      </c>
-      <c r="BX32">
-        <v>0</v>
-      </c>
-      <c r="BY32">
-        <v>0</v>
-      </c>
-      <c r="BZ32">
-        <v>0</v>
-      </c>
-      <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
         <v>103</v>
       </c>
-      <c r="B33" t="s">
-        <v>104</v>
-      </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F33">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>1.43</v>
       </c>
       <c r="H33">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="I33">
-        <v>1.27</v>
+        <v>38</v>
       </c>
       <c r="J33">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="K33">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -8718,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q33">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8910,48 +8898,48 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F34">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="G34">
-        <v>1.38</v>
+        <v>2.58</v>
       </c>
       <c r="H34">
+        <v>3.55</v>
+      </c>
+      <c r="I34">
         <v>9.4</v>
       </c>
-      <c r="I34">
-        <v>38</v>
-      </c>
       <c r="J34">
-        <v>5.2</v>
+        <v>2.82</v>
       </c>
       <c r="K34">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -8960,10 +8948,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9152,249 +9140,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="35" spans="1:80">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" t="s">
-        <v>191</v>
-      </c>
-      <c r="F35">
-        <v>1.75</v>
-      </c>
-      <c r="G35">
-        <v>2.58</v>
-      </c>
-      <c r="H35">
-        <v>3.55</v>
-      </c>
-      <c r="I35">
-        <v>10.5</v>
-      </c>
-      <c r="J35">
-        <v>2.82</v>
-      </c>
-      <c r="K35">
-        <v>6.8</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>1.25</v>
-      </c>
-      <c r="Q35">
-        <v>1.01</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <v>0</v>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
-        <v>0</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>0</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>0</v>
-      </c>
-      <c r="BC35">
-        <v>0</v>
-      </c>
-      <c r="BD35">
-        <v>0</v>
-      </c>
-      <c r="BE35">
-        <v>0</v>
-      </c>
-      <c r="BF35">
-        <v>0</v>
-      </c>
-      <c r="BG35">
-        <v>0</v>
-      </c>
-      <c r="BH35">
-        <v>0</v>
-      </c>
-      <c r="BI35">
-        <v>0</v>
-      </c>
-      <c r="BJ35">
-        <v>0</v>
-      </c>
-      <c r="BK35">
-        <v>0</v>
-      </c>
-      <c r="BL35">
-        <v>0</v>
-      </c>
-      <c r="BM35">
-        <v>0</v>
-      </c>
-      <c r="BN35">
-        <v>0</v>
-      </c>
-      <c r="BO35">
-        <v>0</v>
-      </c>
-      <c r="BP35">
-        <v>0</v>
-      </c>
-      <c r="BQ35">
-        <v>0</v>
-      </c>
-      <c r="BR35">
-        <v>0</v>
-      </c>
-      <c r="BS35">
-        <v>0</v>
-      </c>
-      <c r="BT35">
-        <v>0</v>
-      </c>
-      <c r="BU35">
-        <v>0</v>
-      </c>
-      <c r="BV35">
-        <v>0</v>
-      </c>
-      <c r="BW35">
-        <v>0</v>
-      </c>
-      <c r="BX35">
-        <v>0</v>
-      </c>
-      <c r="BY35">
-        <v>0</v>
-      </c>
-      <c r="BZ35">
-        <v>0</v>
-      </c>
-      <c r="CA35">
-        <v>0</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -580,7 +580,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 05:40:33</t>
+    <t>2026-08-15 08:05:28</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1452,7 @@
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>3.75</v>
@@ -1703,7 +1703,7 @@
         <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V4">
         <v>1.69</v>
@@ -1760,7 +1760,7 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO4">
         <v>15</v>
@@ -1820,64 +1820,64 @@
         <v>12.5</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>188</v>
@@ -1903,7 +1903,7 @@
         <v>4.9</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5">
         <v>1.47</v>
@@ -1915,7 +1915,7 @@
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2384,22 +2384,22 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H7">
         <v>2.22</v>
       </c>
       <c r="I7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J7">
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2408,13 +2408,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O7">
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2432,10 +2432,10 @@
         <v>2.16</v>
       </c>
       <c r="V7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2629,7 +2629,7 @@
         <v>2.44</v>
       </c>
       <c r="G8">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H8">
         <v>2.66</v>
@@ -2638,7 +2638,7 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
         <v>4.2</v>
@@ -3594,7 +3594,7 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G12">
         <v>2.18</v>
@@ -3618,7 +3618,7 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O12">
         <v>1.34</v>
@@ -4078,22 +4078,22 @@
         <v>167</v>
       </c>
       <c r="F14">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G14">
         <v>2.12</v>
       </c>
       <c r="H14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I14">
         <v>5.1</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>169</v>
       </c>
       <c r="F16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G16">
         <v>1.41</v>
@@ -4571,13 +4571,13 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="J16">
         <v>5.8</v>
       </c>
       <c r="K16">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4804,19 +4804,19 @@
         <v>170</v>
       </c>
       <c r="F17">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
         <v>4.6</v>
       </c>
       <c r="I17">
-        <v>60</v>
+        <v>5.8</v>
       </c>
       <c r="J17">
-        <v>3.3</v>
+        <v>1.21</v>
       </c>
       <c r="K17">
         <v>3.7</v>
@@ -5049,7 +5049,7 @@
         <v>1.46</v>
       </c>
       <c r="G18">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="H18">
         <v>6.2</v>
@@ -5545,7 +5545,7 @@
         <v>2.58</v>
       </c>
       <c r="K20">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5775,19 +5775,19 @@
         <v>1.69</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I21">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J21">
         <v>4.4</v>
       </c>
       <c r="K21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>3.5</v>
       </c>
       <c r="K22">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6262,7 +6262,7 @@
         <v>3.4</v>
       </c>
       <c r="H23">
-        <v>1.44</v>
+        <v>2.24</v>
       </c>
       <c r="I23">
         <v>2.58</v>
@@ -7744,7 +7744,7 @@
         <v>1.77</v>
       </c>
       <c r="R29">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S29">
         <v>2.92</v>
@@ -7813,7 +7813,7 @@
         <v>18.5</v>
       </c>
       <c r="AO29">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AP29">
         <v>16</v>
@@ -7950,7 +7950,7 @@
         <v>183</v>
       </c>
       <c r="F30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G30">
         <v>2.44</v>
@@ -7986,7 +7986,7 @@
         <v>2.36</v>
       </c>
       <c r="R30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
         <v>4.6</v>
@@ -8434,10 +8434,10 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G32">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H32">
         <v>1.23</v>
@@ -8467,7 +8467,7 @@
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8676,19 +8676,19 @@
         <v>186</v>
       </c>
       <c r="F33">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="G33">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H33">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="I33">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="J33">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K33">
         <v>5.9</v>
@@ -8709,7 +8709,7 @@
         <v>2.26</v>
       </c>
       <c r="Q33">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R33">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -580,7 +580,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 08:05:28</t>
+    <t>2026-08-15 10:28:51</t>
   </si>
 </sst>
 </file>
@@ -1416,22 +1416,22 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
         <v>2.6</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1440,10 +1440,10 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
         <v>1.66</v>
@@ -1664,7 +1664,7 @@
         <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
         <v>2.44</v>
@@ -1697,7 +1697,7 @@
         <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T4">
         <v>1.6</v>
@@ -1736,7 +1736,7 @@
         <v>24</v>
       </c>
       <c r="AF4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG4">
         <v>14</v>
@@ -1751,7 +1751,7 @@
         <v>300</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1811,7 +1811,7 @@
         <v>22</v>
       </c>
       <c r="BE4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1900,58 +1900,58 @@
         <v>158</v>
       </c>
       <c r="F5">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="G5">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="H5">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="I5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.86</v>
       </c>
       <c r="I6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J6">
         <v>4.2</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
         <v>1.3</v>
@@ -2175,7 +2175,7 @@
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -2868,7 +2868,7 @@
         <v>162</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="G9">
         <v>3.6</v>
@@ -2883,7 +2883,7 @@
         <v>3.25</v>
       </c>
       <c r="K9">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>163</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G10">
         <v>10.5</v>
@@ -3352,7 +3352,7 @@
         <v>164</v>
       </c>
       <c r="F11">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G11">
         <v>26</v>
@@ -3367,7 +3367,7 @@
         <v>3.5</v>
       </c>
       <c r="K11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3594,13 +3594,13 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="G12">
         <v>2.18</v>
       </c>
       <c r="H12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
         <v>5.3</v>
@@ -3615,10 +3615,10 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
         <v>1.34</v>
@@ -3627,7 +3627,7 @@
         <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
         <v>1.28</v>
@@ -3836,7 +3836,7 @@
         <v>166</v>
       </c>
       <c r="F13">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>4.6</v>
@@ -3851,7 +3851,7 @@
         <v>3</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>169</v>
       </c>
       <c r="F16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G16">
         <v>1.41</v>
@@ -4577,7 +4577,7 @@
         <v>5.8</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>2.1</v>
       </c>
       <c r="H17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I17">
         <v>5.8</v>
@@ -5049,16 +5049,16 @@
         <v>1.46</v>
       </c>
       <c r="G18">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H18">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I18">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K18">
         <v>5.2</v>
@@ -5076,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5536,7 +5536,7 @@
         <v>3.8</v>
       </c>
       <c r="H20">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="I20">
         <v>3.65</v>
@@ -5775,19 +5775,19 @@
         <v>1.69</v>
       </c>
       <c r="G21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J21">
         <v>4.4</v>
       </c>
       <c r="K21">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>3.5</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>3.4</v>
       </c>
       <c r="H23">
-        <v>2.24</v>
+        <v>1.43</v>
       </c>
       <c r="I23">
         <v>2.58</v>
       </c>
       <c r="J23">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="K23">
         <v>440</v>
@@ -7227,7 +7227,7 @@
         <v>1.52</v>
       </c>
       <c r="G27">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -7466,10 +7466,10 @@
         <v>181</v>
       </c>
       <c r="F28">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G28">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H28">
         <v>3.6</v>
@@ -7478,7 +7478,7 @@
         <v>4.6</v>
       </c>
       <c r="J28">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K28">
         <v>3.55</v>
@@ -7708,16 +7708,16 @@
         <v>182</v>
       </c>
       <c r="F29">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G29">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H29">
+        <v>2.92</v>
+      </c>
+      <c r="I29">
         <v>2.96</v>
-      </c>
-      <c r="I29">
-        <v>2.98</v>
       </c>
       <c r="J29">
         <v>3.65</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="AL29">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AM29">
         <v>1000</v>
@@ -7995,7 +7995,7 @@
         <v>1.98</v>
       </c>
       <c r="U30">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V30">
         <v>1.37</v>
@@ -8052,7 +8052,7 @@
         <v>140</v>
       </c>
       <c r="AN30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO30">
         <v>60</v>
@@ -8437,10 +8437,10 @@
         <v>13</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I32">
         <v>1.27</v>
@@ -8918,7 +8918,7 @@
         <v>187</v>
       </c>
       <c r="F34">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="G34">
         <v>2.58</v>
@@ -8927,13 +8927,13 @@
         <v>3.55</v>
       </c>
       <c r="I34">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="J34">
         <v>2.82</v>
       </c>
       <c r="K34">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="L34">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="192">
   <si>
     <t>League</t>
   </si>
@@ -268,15 +268,18 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
-    <t>Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
@@ -295,12 +298,12 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -400,15 +403,18 @@
     <t>Tijuana</t>
   </si>
   <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava II</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
     <t>Fk Siauliai</t>
   </si>
   <si>
-    <t>Polissya Zhytomyr</t>
-  </si>
-  <si>
     <t>Zalaegerszeg</t>
   </si>
   <si>
@@ -430,12 +436,12 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
     <t>Brondby</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
@@ -499,15 +505,18 @@
     <t>Cruz Azul</t>
   </si>
   <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>FK Humenne</t>
+  </si>
+  <si>
     <t>Ilves</t>
   </si>
   <si>
     <t>Panevezys</t>
   </si>
   <si>
-    <t>Zorya</t>
-  </si>
-  <si>
     <t>Ferencvaros</t>
   </si>
   <si>
@@ -529,12 +538,12 @@
     <t>Sabadell</t>
   </si>
   <si>
+    <t>Puszcza Niepolomice</t>
+  </si>
+  <si>
     <t>SonderjyskE</t>
   </si>
   <si>
-    <t>Puszcza Niepolomice</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -580,7 +589,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 10:28:51</t>
+    <t>2026-08-15 12:51:40</t>
   </si>
 </sst>
 </file>
@@ -912,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1162,16 +1171,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F2">
         <v>2.5</v>
@@ -1396,7 +1405,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1404,34 +1413,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F3">
         <v>2.36</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1464,7 +1473,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
         <v>1.62</v>
@@ -1578,67 +1587,67 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="CB3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1646,16 +1655,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1691,7 +1700,7 @@
         <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
         <v>1.53</v>
@@ -1700,10 +1709,10 @@
         <v>2.78</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U4">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V4">
         <v>1.69</v>
@@ -1718,13 +1727,13 @@
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA4">
         <v>34</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
@@ -1748,10 +1757,10 @@
         <v>34</v>
       </c>
       <c r="AJ4">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AK4">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1811,7 +1820,7 @@
         <v>22</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1880,7 +1889,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1888,34 +1897,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H5">
         <v>1.56</v>
       </c>
       <c r="I5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1936,10 +1945,10 @@
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
         <v>1.67</v>
@@ -1948,7 +1957,7 @@
         <v>2.24</v>
       </c>
       <c r="V5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="W5">
         <v>1.17</v>
@@ -2122,7 +2131,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2130,16 +2139,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F6">
         <v>4.1</v>
@@ -2169,13 +2178,13 @@
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -2187,7 +2196,7 @@
         <v>1.62</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
         <v>2.1</v>
@@ -2202,7 +2211,7 @@
         <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>21</v>
@@ -2214,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
         <v>17.5</v>
@@ -2232,7 +2241,7 @@
         <v>32</v>
       </c>
       <c r="AJ6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
         <v>46</v>
@@ -2286,13 +2295,13 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BC6">
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2364,7 +2373,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2372,179 +2381,179 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F7">
         <v>3.3</v>
       </c>
       <c r="G7">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
         <v>2.36</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>1.98</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S7">
         <v>2.96</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V7">
         <v>1.73</v>
       </c>
       <c r="W7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
+        <v>9.6</v>
+      </c>
+      <c r="AR7">
+        <v>11.5</v>
+      </c>
+      <c r="AS7">
+        <v>19</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>9.6</v>
+      </c>
+      <c r="AW7">
+        <v>16</v>
+      </c>
+      <c r="AX7">
+        <v>16.5</v>
+      </c>
+      <c r="AY7">
+        <v>11</v>
+      </c>
+      <c r="AZ7">
+        <v>13</v>
+      </c>
+      <c r="BA7">
+        <v>23</v>
+      </c>
+      <c r="BB7">
+        <v>42</v>
+      </c>
+      <c r="BC7">
+        <v>22</v>
+      </c>
+      <c r="BD7">
+        <v>26</v>
+      </c>
+      <c r="BE7">
+        <v>42</v>
+      </c>
+      <c r="BF7">
+        <v>21</v>
+      </c>
+      <c r="BG7">
         <v>12.5</v>
       </c>
-      <c r="AQ7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR7">
-        <v>10.5</v>
-      </c>
-      <c r="AS7">
-        <v>21</v>
-      </c>
-      <c r="AT7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU7">
-        <v>6.6</v>
-      </c>
-      <c r="AV7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW7">
-        <v>17.5</v>
-      </c>
-      <c r="AX7">
-        <v>18</v>
-      </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>12.5</v>
-      </c>
-      <c r="BA7">
-        <v>26</v>
-      </c>
-      <c r="BB7">
-        <v>40</v>
-      </c>
-      <c r="BC7">
-        <v>26</v>
-      </c>
-      <c r="BD7">
-        <v>29</v>
-      </c>
-      <c r="BE7">
-        <v>40</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
-      </c>
       <c r="BH7">
         <v>1000</v>
       </c>
@@ -2606,7 +2615,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2614,241 +2623,241 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F8">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="G8">
-        <v>2.96</v>
+        <v>10.5</v>
       </c>
       <c r="H8">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>320</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="Q8">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2856,241 +2865,241 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F9">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="G9">
+        <v>2.14</v>
+      </c>
+      <c r="H9">
         <v>3.6</v>
       </c>
-      <c r="H9">
-        <v>2.16</v>
-      </c>
       <c r="I9">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3098,232 +3107,232 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F10">
-        <v>1.22</v>
+        <v>2.48</v>
       </c>
       <c r="G10">
-        <v>10.5</v>
+        <v>2.72</v>
       </c>
       <c r="H10">
-        <v>1.11</v>
+        <v>2.66</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K10">
-        <v>320</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3332,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3340,34 +3349,34 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
         <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F11">
-        <v>5.9</v>
+        <v>2.66</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="I11">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3382,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3574,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3582,34 +3591,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F12">
-        <v>1.89</v>
+        <v>5.9</v>
       </c>
       <c r="G12">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="H12">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3618,22 +3627,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3642,10 +3651,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="W12">
-        <v>1.84</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3810,290 +3819,290 @@
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
-        <v>1.94</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
         <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F14">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>2.12</v>
+        <v>4.6</v>
       </c>
       <c r="H14">
-        <v>4.3</v>
+        <v>1.94</v>
       </c>
       <c r="I14">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4108,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4300,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4308,34 +4317,34 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F15">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="G15">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="H15">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="I15">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4350,10 +4359,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q15">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4542,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4550,34 +4559,34 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
         <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F16">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="G16">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>1.93</v>
       </c>
       <c r="I16">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="J16">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4592,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4784,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4792,40 +4801,40 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F17">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="G17">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H17">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I17">
+        <v>13</v>
+      </c>
+      <c r="J17">
         <v>5.8</v>
       </c>
-      <c r="J17">
-        <v>1.21</v>
-      </c>
       <c r="K17">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4834,10 +4843,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q17">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5026,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5034,40 +5043,40 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F18">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="G18">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H18">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="I18">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="J18">
-        <v>4.9</v>
+        <v>1.21</v>
       </c>
       <c r="K18">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5076,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5268,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5276,34 +5285,34 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F19">
         <v>1.7</v>
       </c>
       <c r="G19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H19">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="I19">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>330</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5321,7 +5330,7 @@
         <v>2</v>
       </c>
       <c r="Q19">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5510,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5518,34 +5527,34 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
         <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F20">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="G20">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="H20">
-        <v>2.82</v>
+        <v>6.6</v>
       </c>
       <c r="I20">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>2.58</v>
+        <v>4.7</v>
       </c>
       <c r="K20">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5560,10 +5569,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q20">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5572,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5752,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5760,34 +5769,34 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F21">
-        <v>1.69</v>
+        <v>2.9</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="H21">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="I21">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
-        <v>4.4</v>
+        <v>2.58</v>
       </c>
       <c r="K21">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5802,10 +5811,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>1.28</v>
+        <v>2.96</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5994,42 +6003,42 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="I22">
-        <v>2.36</v>
+        <v>5.2</v>
       </c>
       <c r="J22">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K22">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6044,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q22">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6236,42 +6245,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F23">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="G23">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="H23">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="I23">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="J23">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="K23">
-        <v>440</v>
+        <v>6.2</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6286,10 +6295,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6478,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6486,34 +6495,34 @@
         <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6528,10 +6537,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6720,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6728,34 +6737,34 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6770,10 +6779,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6962,42 +6971,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F26">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="G26">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>1.77</v>
       </c>
       <c r="I26">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K26">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7012,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7204,491 +7213,491 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
         <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F27">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="G27">
+        <v>2.02</v>
+      </c>
+      <c r="H27">
+        <v>3.85</v>
+      </c>
+      <c r="I27">
+        <v>6.6</v>
+      </c>
+      <c r="J27">
+        <v>3.4</v>
+      </c>
+      <c r="K27">
+        <v>6.6</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>1.68</v>
       </c>
-      <c r="H27">
-        <v>5</v>
-      </c>
-      <c r="I27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J27">
-        <v>4.2</v>
-      </c>
-      <c r="K27">
-        <v>6.8</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.01</v>
-      </c>
-      <c r="N27">
-        <v>4.3</v>
-      </c>
-      <c r="O27">
-        <v>1.2</v>
-      </c>
-      <c r="P27">
-        <v>2.16</v>
-      </c>
       <c r="Q27">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="R27">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F28">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="G28">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="H28">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="K28">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P28">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7696,64 +7705,64 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
         <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F29">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="G29">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="H29">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="I29">
-        <v>2.96</v>
+        <v>3.95</v>
       </c>
       <c r="J29">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K29">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>1.25</v>
       </c>
-      <c r="P29">
-        <v>2.16</v>
-      </c>
       <c r="Q29">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R29">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7762,175 +7771,175 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BG29">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7938,178 +7947,178 @@
         <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F30">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="G30">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H30">
+        <v>2.92</v>
+      </c>
+      <c r="I30">
+        <v>2.96</v>
+      </c>
+      <c r="J30">
+        <v>3.6</v>
+      </c>
+      <c r="K30">
         <v>3.65</v>
       </c>
-      <c r="I30">
-        <v>3.7</v>
-      </c>
-      <c r="J30">
-        <v>3.15</v>
-      </c>
-      <c r="K30">
-        <v>3.2</v>
-      </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
+        <v>1.25</v>
+      </c>
+      <c r="P30">
+        <v>2.16</v>
+      </c>
+      <c r="Q30">
+        <v>1.76</v>
+      </c>
+      <c r="R30">
         <v>1.45</v>
       </c>
-      <c r="P30">
-        <v>1.69</v>
-      </c>
-      <c r="Q30">
-        <v>2.36</v>
-      </c>
-      <c r="R30">
-        <v>1.25</v>
-      </c>
       <c r="S30">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="T30">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="U30">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Y30">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Z30">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA30">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB30">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AC30">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE30">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF30">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AG30">
         <v>12</v>
       </c>
       <c r="AH30">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI30">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ30">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK30">
         <v>30</v>
       </c>
       <c r="AL30">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM30">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AO30">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AP30">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AQ30">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR30">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS30">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AT30">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU30">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW30">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AX30">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY30">
         <v>10.5</v>
       </c>
       <c r="AZ30">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA30">
+        <v>23</v>
+      </c>
+      <c r="BB30">
+        <v>22</v>
+      </c>
+      <c r="BC30">
+        <v>21</v>
+      </c>
+      <c r="BD30">
+        <v>21</v>
+      </c>
+      <c r="BE30">
         <v>32</v>
       </c>
-      <c r="BB30">
-        <v>21</v>
-      </c>
-      <c r="BC30">
-        <v>25</v>
-      </c>
-      <c r="BD30">
-        <v>42</v>
-      </c>
-      <c r="BE30">
-        <v>42</v>
-      </c>
       <c r="BF30">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="BG30">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8172,302 +8181,302 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
         <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P31">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>1.24</v>
       </c>
-      <c r="I32">
-        <v>1.27</v>
-      </c>
-      <c r="J32">
-        <v>6.8</v>
-      </c>
-      <c r="K32">
-        <v>7.4</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.25</v>
-      </c>
       <c r="Q32">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8656,48 +8665,48 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
         <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F33">
-        <v>1.35</v>
+        <v>14.5</v>
       </c>
       <c r="G33">
-        <v>1.38</v>
+        <v>17.5</v>
       </c>
       <c r="H33">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>1.27</v>
       </c>
       <c r="J33">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="K33">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -8706,10 +8715,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q33">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8898,249 +8907,491 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
         <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F34">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="G34">
-        <v>2.58</v>
+        <v>1.38</v>
       </c>
       <c r="H34">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="I34">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="J34">
-        <v>2.82</v>
+        <v>5.2</v>
       </c>
       <c r="K34">
+        <v>5.9</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1.05</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>2.26</v>
+      </c>
+      <c r="Q34">
+        <v>1.68</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34">
+        <v>0</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BI34">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>0</v>
+      </c>
+      <c r="BN34">
+        <v>0</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>0</v>
+      </c>
+      <c r="BQ34">
+        <v>0</v>
+      </c>
+      <c r="BR34">
+        <v>0</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+      <c r="BT34">
+        <v>0</v>
+      </c>
+      <c r="BU34">
+        <v>0</v>
+      </c>
+      <c r="BV34">
+        <v>0</v>
+      </c>
+      <c r="BW34">
+        <v>0</v>
+      </c>
+      <c r="BX34">
+        <v>0</v>
+      </c>
+      <c r="BY34">
+        <v>0</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35">
+        <v>2.36</v>
+      </c>
+      <c r="G35">
+        <v>2.56</v>
+      </c>
+      <c r="H35">
         <v>3.6</v>
       </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>1.25</v>
-      </c>
-      <c r="Q34">
-        <v>1.01</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>0</v>
-      </c>
-      <c r="BC34">
-        <v>0</v>
-      </c>
-      <c r="BD34">
-        <v>0</v>
-      </c>
-      <c r="BE34">
-        <v>0</v>
-      </c>
-      <c r="BF34">
-        <v>0</v>
-      </c>
-      <c r="BG34">
-        <v>0</v>
-      </c>
-      <c r="BH34">
-        <v>0</v>
-      </c>
-      <c r="BI34">
-        <v>0</v>
-      </c>
-      <c r="BJ34">
-        <v>0</v>
-      </c>
-      <c r="BK34">
-        <v>0</v>
-      </c>
-      <c r="BL34">
-        <v>0</v>
-      </c>
-      <c r="BM34">
-        <v>0</v>
-      </c>
-      <c r="BN34">
-        <v>0</v>
-      </c>
-      <c r="BO34">
-        <v>0</v>
-      </c>
-      <c r="BP34">
-        <v>0</v>
-      </c>
-      <c r="BQ34">
-        <v>0</v>
-      </c>
-      <c r="BR34">
-        <v>0</v>
-      </c>
-      <c r="BS34">
-        <v>0</v>
-      </c>
-      <c r="BT34">
-        <v>0</v>
-      </c>
-      <c r="BU34">
-        <v>0</v>
-      </c>
-      <c r="BV34">
-        <v>0</v>
-      </c>
-      <c r="BW34">
-        <v>0</v>
-      </c>
-      <c r="BX34">
-        <v>0</v>
-      </c>
-      <c r="BY34">
-        <v>0</v>
-      </c>
-      <c r="BZ34">
-        <v>0</v>
-      </c>
-      <c r="CA34">
-        <v>0</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>188</v>
+      <c r="I35">
+        <v>4.1</v>
+      </c>
+      <c r="J35">
+        <v>2.86</v>
+      </c>
+      <c r="K35">
+        <v>3.2</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1.43</v>
+      </c>
+      <c r="Q35">
+        <v>2.56</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>0</v>
+      </c>
+      <c r="BT35">
+        <v>0</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>0</v>
+      </c>
+      <c r="BY35">
+        <v>0</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="185">
   <si>
     <t>League</t>
   </si>
@@ -298,18 +298,15 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
     <t>Polish I Liga</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
-    <t>Dutch Eerste Divisie</t>
-  </si>
-  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
@@ -436,24 +433,15 @@
     <t>Sporting Gijon</t>
   </si>
   <si>
+    <t>Brondby</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Brondby</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
-    <t>De Graafschap</t>
-  </si>
-  <si>
-    <t>Jong FC Utrecht</t>
-  </si>
-  <si>
-    <t>Jong Ajax Amsterdam</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -538,24 +526,15 @@
     <t>Sabadell</t>
   </si>
   <si>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
     <t>Puszcza Niepolomice</t>
   </si>
   <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
-    <t>Jong AZ Alkmaar</t>
-  </si>
-  <si>
-    <t>Vitesse Arnhem</t>
-  </si>
-  <si>
-    <t>Emmen</t>
-  </si>
-  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
@@ -589,7 +568,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 12:51:40</t>
+    <t>2026-08-15 15:11:18</t>
   </si>
 </sst>
 </file>
@@ -921,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1171,178 +1150,178 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
         <v>104</v>
       </c>
-      <c r="C2" t="s">
-        <v>105</v>
-      </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G2">
+        <v>2.94</v>
+      </c>
+      <c r="H2">
+        <v>2.58</v>
+      </c>
+      <c r="I2">
+        <v>2.98</v>
+      </c>
+      <c r="J2">
+        <v>3.35</v>
+      </c>
+      <c r="K2">
+        <v>3.95</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.95</v>
+      </c>
+      <c r="O2">
+        <v>1.23</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>1.83</v>
+      </c>
+      <c r="R2">
+        <v>1.38</v>
+      </c>
+      <c r="S2">
         <v>3.1</v>
       </c>
-      <c r="H2">
-        <v>2.52</v>
-      </c>
-      <c r="I2">
-        <v>3.1</v>
-      </c>
-      <c r="J2">
-        <v>3.25</v>
-      </c>
-      <c r="K2">
-        <v>4.8</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>1.96</v>
-      </c>
-      <c r="O2">
-        <v>1.27</v>
-      </c>
-      <c r="P2">
-        <v>1.96</v>
-      </c>
-      <c r="Q2">
-        <v>1.8</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
-        <v>1.81</v>
-      </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1405,7 +1384,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1413,16 +1392,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" t="s">
-        <v>105</v>
-      </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F3">
         <v>2.36</v>
@@ -1443,7 +1422,7 @@
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
         <v>1.01</v>
@@ -1647,7 +1626,7 @@
         <v>25</v>
       </c>
       <c r="CB3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1655,16 +1634,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1727,7 +1706,7 @@
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA4">
         <v>34</v>
@@ -1787,7 +1766,7 @@
         <v>21</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU4">
         <v>8</v>
@@ -1799,7 +1778,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AY4">
         <v>12</v>
@@ -1820,13 +1799,13 @@
         <v>22</v>
       </c>
       <c r="BE4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1889,7 +1868,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1897,16 +1876,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1915,91 +1894,91 @@
         <v>6.6</v>
       </c>
       <c r="H5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J5">
         <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
         <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
         <v>2.24</v>
       </c>
       <c r="V5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB5">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AC5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AF5">
         <v>75</v>
       </c>
       <c r="AG5">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK5">
         <v>100</v>
@@ -2008,67 +1987,67 @@
         <v>90</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN5">
         <v>95</v>
       </c>
       <c r="AO5">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AP5">
-        <v>2.74</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>2.32</v>
+        <v>9.4</v>
       </c>
       <c r="AS5">
-        <v>2.42</v>
+        <v>13</v>
       </c>
       <c r="AT5">
-        <v>2.54</v>
+        <v>6.8</v>
       </c>
       <c r="AU5">
-        <v>2.32</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX5">
-        <v>2.64</v>
+        <v>7.6</v>
       </c>
       <c r="AY5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ5">
-        <v>2.48</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>2.56</v>
+        <v>20</v>
       </c>
       <c r="BB5">
-        <v>2.74</v>
+        <v>8.4</v>
       </c>
       <c r="BC5">
-        <v>2.66</v>
+        <v>8</v>
       </c>
       <c r="BD5">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>2.74</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2131,7 +2110,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2139,31 +2118,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F6">
+        <v>4.2</v>
+      </c>
+      <c r="G6">
+        <v>4.5</v>
+      </c>
+      <c r="H6">
+        <v>1.88</v>
+      </c>
+      <c r="I6">
+        <v>1.89</v>
+      </c>
+      <c r="J6">
         <v>4.1</v>
-      </c>
-      <c r="G6">
-        <v>4.4</v>
-      </c>
-      <c r="H6">
-        <v>1.86</v>
-      </c>
-      <c r="I6">
-        <v>1.9</v>
-      </c>
-      <c r="J6">
-        <v>4.2</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2175,31 +2154,31 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
         <v>1.62</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W6">
         <v>1.29</v>
@@ -2235,7 +2214,7 @@
         <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
         <v>32</v>
@@ -2295,13 +2274,13 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BC6">
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2310,70 +2289,70 @@
         <v>30</v>
       </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2381,34 +2360,34 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H7">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I7">
         <v>2.36</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2417,7 +2396,7 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O7">
         <v>1.27</v>
@@ -2429,13 +2408,13 @@
         <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S7">
         <v>2.96</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U7">
         <v>2.22</v>
@@ -2501,7 +2480,7 @@
         <v>20</v>
       </c>
       <c r="AP7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
         <v>9.6</v>
@@ -2531,19 +2510,19 @@
         <v>11</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB7">
         <v>42</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE7">
         <v>42</v>
@@ -2615,7 +2594,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2623,31 +2602,31 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>1.24</v>
       </c>
       <c r="G8">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>320</v>
@@ -2674,7 +2653,7 @@
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2686,7 +2665,7 @@
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2857,7 +2836,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2865,25 +2844,25 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G9">
         <v>2.14</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -2892,7 +2871,7 @@
         <v>3.45</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3099,7 +3078,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3107,16 +3086,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F10">
         <v>2.48</v>
@@ -3128,10 +3107,10 @@
         <v>2.66</v>
       </c>
       <c r="I10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K10">
         <v>4.6</v>
@@ -3167,7 +3146,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
         <v>1.58</v>
@@ -3341,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3349,16 +3328,16 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F11">
         <v>2.66</v>
@@ -3370,7 +3349,7 @@
         <v>2.16</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -3379,202 +3358,202 @@
         <v>6.4</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
         <v>1.53</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3583,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3591,34 +3570,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F12">
         <v>5.9</v>
       </c>
       <c r="G12">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="I12">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3642,7 +3621,7 @@
         <v>1.46</v>
       </c>
       <c r="S12">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3651,10 +3630,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3825,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3833,16 +3812,16 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -3851,223 +3830,223 @@
         <v>2.18</v>
       </c>
       <c r="H13">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
         <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="Q13">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
         <v>1.84</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB13" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4075,16 +4054,16 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -4093,7 +4072,7 @@
         <v>4.6</v>
       </c>
       <c r="H14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I14">
         <v>2.6</v>
@@ -4102,19 +4081,19 @@
         <v>3</v>
       </c>
       <c r="K14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P14">
         <v>1.59</v>
@@ -4123,184 +4102,184 @@
         <v>1.96</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4309,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4317,16 +4296,16 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F15">
         <v>1.91</v>
@@ -4341,22 +4320,22 @@
         <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>3.7</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P15">
         <v>1.6</v>
@@ -4365,193 +4344,193 @@
         <v>2.12</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4559,22 +4538,22 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F16">
         <v>3.1</v>
       </c>
       <c r="G16">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H16">
         <v>1.93</v>
@@ -4589,16 +4568,16 @@
         <v>6.4</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
         <v>2.1</v>
@@ -4607,184 +4586,184 @@
         <v>1.67</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4793,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4801,241 +4780,241 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G17">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H17">
         <v>8.800000000000001</v>
       </c>
       <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>5.9</v>
+      </c>
+      <c r="K17">
+        <v>6.6</v>
+      </c>
+      <c r="L17">
+        <v>1.19</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>6.6</v>
+      </c>
+      <c r="O17">
+        <v>1.16</v>
+      </c>
+      <c r="P17">
+        <v>2.92</v>
+      </c>
+      <c r="Q17">
+        <v>1.46</v>
+      </c>
+      <c r="R17">
+        <v>1.76</v>
+      </c>
+      <c r="S17">
+        <v>2.16</v>
+      </c>
+      <c r="T17">
+        <v>1.78</v>
+      </c>
+      <c r="U17">
+        <v>2.12</v>
+      </c>
+      <c r="V17">
+        <v>1.11</v>
+      </c>
+      <c r="W17">
+        <v>3.55</v>
+      </c>
+      <c r="X17">
+        <v>40</v>
+      </c>
+      <c r="Y17">
+        <v>46</v>
+      </c>
+      <c r="Z17">
+        <v>100</v>
+      </c>
+      <c r="AA17">
+        <v>310</v>
+      </c>
+      <c r="AB17">
         <v>13</v>
       </c>
-      <c r="J17">
-        <v>5.8</v>
-      </c>
-      <c r="K17">
-        <v>8.4</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>2.88</v>
-      </c>
-      <c r="Q17">
-        <v>1.4</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB17" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5043,22 +5022,22 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F18">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G18">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="H18">
         <v>4.9</v>
@@ -5067,217 +5046,217 @@
         <v>5.8</v>
       </c>
       <c r="J18">
-        <v>1.21</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
         <v>3.7</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5285,241 +5264,241 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F19">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="H19">
+        <v>7.2</v>
+      </c>
+      <c r="I19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J19">
+        <v>4.9</v>
+      </c>
+      <c r="K19">
+        <v>5.1</v>
+      </c>
+      <c r="L19">
+        <v>1.27</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>4.5</v>
+      </c>
+      <c r="O19">
+        <v>1.2</v>
+      </c>
+      <c r="P19">
+        <v>2.32</v>
+      </c>
+      <c r="Q19">
+        <v>1.62</v>
+      </c>
+      <c r="R19">
+        <v>1.5</v>
+      </c>
+      <c r="S19">
+        <v>2.56</v>
+      </c>
+      <c r="T19">
+        <v>1.73</v>
+      </c>
+      <c r="U19">
+        <v>1.99</v>
+      </c>
+      <c r="V19">
+        <v>1.14</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>26</v>
+      </c>
+      <c r="Y19">
+        <v>38</v>
+      </c>
+      <c r="Z19">
+        <v>80</v>
+      </c>
+      <c r="AA19">
+        <v>280</v>
+      </c>
+      <c r="AB19">
+        <v>13</v>
+      </c>
+      <c r="AC19">
+        <v>13</v>
+      </c>
+      <c r="AD19">
+        <v>32</v>
+      </c>
+      <c r="AE19">
+        <v>120</v>
+      </c>
+      <c r="AF19">
+        <v>10.5</v>
+      </c>
+      <c r="AG19">
+        <v>11.5</v>
+      </c>
+      <c r="AH19">
+        <v>27</v>
+      </c>
+      <c r="AI19">
+        <v>110</v>
+      </c>
+      <c r="AJ19">
+        <v>15.5</v>
+      </c>
+      <c r="AK19">
+        <v>17</v>
+      </c>
+      <c r="AL19">
+        <v>36</v>
+      </c>
+      <c r="AM19">
+        <v>130</v>
+      </c>
+      <c r="AN19">
+        <v>8</v>
+      </c>
+      <c r="AO19">
+        <v>120</v>
+      </c>
+      <c r="AP19">
+        <v>4.1</v>
+      </c>
+      <c r="AQ19">
+        <v>23</v>
+      </c>
+      <c r="AR19">
+        <v>55</v>
+      </c>
+      <c r="AS19">
         <v>4.7</v>
       </c>
-      <c r="I19">
-        <v>6.4</v>
-      </c>
-      <c r="J19">
-        <v>3.8</v>
-      </c>
-      <c r="K19">
-        <v>5</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>2</v>
-      </c>
-      <c r="Q19">
-        <v>1.78</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
       <c r="AT19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5527,232 +5506,232 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F20">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="G20">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="H20">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
+        <v>5.9</v>
+      </c>
+      <c r="J20">
+        <v>3.8</v>
+      </c>
+      <c r="K20">
+        <v>4.7</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>3.6</v>
+      </c>
+      <c r="O20">
+        <v>1.27</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <v>1.78</v>
+      </c>
+      <c r="R20">
+        <v>1.36</v>
+      </c>
+      <c r="S20">
+        <v>2.96</v>
+      </c>
+      <c r="T20">
+        <v>1.01</v>
+      </c>
+      <c r="U20">
+        <v>1.85</v>
+      </c>
+      <c r="V20">
+        <v>1.2</v>
+      </c>
+      <c r="W20">
+        <v>2.12</v>
+      </c>
+      <c r="X20">
+        <v>22</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>85</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>85</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
         <v>8</v>
       </c>
-      <c r="J20">
-        <v>4.7</v>
-      </c>
-      <c r="K20">
-        <v>5.2</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>2.32</v>
-      </c>
-      <c r="Q20">
-        <v>1.62</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>1.01</v>
-      </c>
-      <c r="U20">
-        <v>1.93</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
       <c r="AY20">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5761,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5769,16 +5748,16 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F21">
         <v>2.9</v>
@@ -5787,223 +5766,223 @@
         <v>3.8</v>
       </c>
       <c r="H21">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I21">
         <v>3.65</v>
       </c>
       <c r="J21">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q21">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6011,34 +5990,34 @@
         <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F22">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6053,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6245,42 +6224,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F23">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="H23">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="I23">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J23">
         <v>3.5</v>
       </c>
       <c r="K23">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6295,10 +6274,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q23">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6487,42 +6466,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
         <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F24">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G24">
+        <v>2.02</v>
+      </c>
+      <c r="H24">
+        <v>3.85</v>
+      </c>
+      <c r="I24">
+        <v>6.6</v>
+      </c>
+      <c r="J24">
         <v>3.4</v>
       </c>
-      <c r="H24">
-        <v>1.43</v>
-      </c>
-      <c r="I24">
-        <v>2.58</v>
-      </c>
-      <c r="J24">
-        <v>1.08</v>
-      </c>
       <c r="K24">
-        <v>440</v>
+        <v>6.6</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6537,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q24">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6729,249 +6708,249 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6979,34 +6958,34 @@
         <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F26">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>2.42</v>
       </c>
       <c r="H26">
-        <v>1.77</v>
+        <v>3.6</v>
       </c>
       <c r="I26">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="J26">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K26">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7021,10 +7000,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="Q26">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7213,72 +7192,72 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F27">
-        <v>1.71</v>
+        <v>2.56</v>
       </c>
       <c r="G27">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="H27">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>2.96</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K27">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P27">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="Q27">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7287,354 +7266,354 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
         <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F28">
-        <v>1.52</v>
+        <v>2.38</v>
       </c>
       <c r="G28">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="I28">
-        <v>8.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="J28">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="K28">
+        <v>3.2</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.11</v>
+      </c>
+      <c r="N28">
+        <v>3.1</v>
+      </c>
+      <c r="O28">
+        <v>1.45</v>
+      </c>
+      <c r="P28">
+        <v>1.69</v>
+      </c>
+      <c r="Q28">
+        <v>2.36</v>
+      </c>
+      <c r="R28">
+        <v>1.25</v>
+      </c>
+      <c r="S28">
+        <v>4.6</v>
+      </c>
+      <c r="T28">
+        <v>1.98</v>
+      </c>
+      <c r="U28">
+        <v>1.98</v>
+      </c>
+      <c r="V28">
+        <v>1.36</v>
+      </c>
+      <c r="W28">
+        <v>1.7</v>
+      </c>
+      <c r="X28">
+        <v>10.5</v>
+      </c>
+      <c r="Y28">
+        <v>11.5</v>
+      </c>
+      <c r="Z28">
+        <v>24</v>
+      </c>
+      <c r="AA28">
+        <v>75</v>
+      </c>
+      <c r="AB28">
+        <v>8.6</v>
+      </c>
+      <c r="AC28">
         <v>6.8</v>
       </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.01</v>
-      </c>
-      <c r="N28">
-        <v>4.3</v>
-      </c>
-      <c r="O28">
-        <v>1.2</v>
-      </c>
-      <c r="P28">
-        <v>2.08</v>
-      </c>
-      <c r="Q28">
-        <v>1.66</v>
-      </c>
-      <c r="R28">
-        <v>1.44</v>
-      </c>
-      <c r="S28">
-        <v>2.58</v>
-      </c>
-      <c r="T28">
-        <v>1.01</v>
-      </c>
-      <c r="U28">
-        <v>1.01</v>
-      </c>
-      <c r="V28">
-        <v>1.13</v>
-      </c>
-      <c r="W28">
-        <v>2.48</v>
-      </c>
-      <c r="X28">
-        <v>1000</v>
-      </c>
-      <c r="Y28">
-        <v>1000</v>
-      </c>
-      <c r="Z28">
-        <v>1000</v>
-      </c>
-      <c r="AA28">
-        <v>1000</v>
-      </c>
-      <c r="AB28">
-        <v>1000</v>
-      </c>
-      <c r="AC28">
-        <v>1000</v>
-      </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7697,314 +7676,314 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1.24</v>
+      </c>
+      <c r="Q29">
+        <v>1.01</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
         <v>184</v>
-      </c>
-      <c r="F29">
-        <v>2.24</v>
-      </c>
-      <c r="G29">
-        <v>2.42</v>
-      </c>
-      <c r="H29">
-        <v>3.6</v>
-      </c>
-      <c r="I29">
-        <v>3.95</v>
-      </c>
-      <c r="J29">
-        <v>3.2</v>
-      </c>
-      <c r="K29">
-        <v>3.55</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>1.25</v>
-      </c>
-      <c r="Q29">
-        <v>1.01</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>0</v>
-      </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
-      <c r="AP29">
-        <v>0</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29">
-        <v>0</v>
-      </c>
-      <c r="AV29">
-        <v>0</v>
-      </c>
-      <c r="AW29">
-        <v>0</v>
-      </c>
-      <c r="AX29">
-        <v>0</v>
-      </c>
-      <c r="AY29">
-        <v>0</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>0</v>
-      </c>
-      <c r="BC29">
-        <v>0</v>
-      </c>
-      <c r="BD29">
-        <v>0</v>
-      </c>
-      <c r="BE29">
-        <v>0</v>
-      </c>
-      <c r="BF29">
-        <v>0</v>
-      </c>
-      <c r="BG29">
-        <v>0</v>
-      </c>
-      <c r="BH29">
-        <v>0</v>
-      </c>
-      <c r="BI29">
-        <v>0</v>
-      </c>
-      <c r="BJ29">
-        <v>0</v>
-      </c>
-      <c r="BK29">
-        <v>0</v>
-      </c>
-      <c r="BL29">
-        <v>0</v>
-      </c>
-      <c r="BM29">
-        <v>0</v>
-      </c>
-      <c r="BN29">
-        <v>0</v>
-      </c>
-      <c r="BO29">
-        <v>0</v>
-      </c>
-      <c r="BP29">
-        <v>0</v>
-      </c>
-      <c r="BQ29">
-        <v>0</v>
-      </c>
-      <c r="BR29">
-        <v>0</v>
-      </c>
-      <c r="BS29">
-        <v>0</v>
-      </c>
-      <c r="BT29">
-        <v>0</v>
-      </c>
-      <c r="BU29">
-        <v>0</v>
-      </c>
-      <c r="BV29">
-        <v>0</v>
-      </c>
-      <c r="BW29">
-        <v>0</v>
-      </c>
-      <c r="BX29">
-        <v>0</v>
-      </c>
-      <c r="BY29">
-        <v>0</v>
-      </c>
-      <c r="BZ29">
-        <v>0</v>
-      </c>
-      <c r="CA29">
-        <v>0</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
         <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F30">
-        <v>2.56</v>
+        <v>15</v>
       </c>
       <c r="G30">
-        <v>2.6</v>
+        <v>17.5</v>
       </c>
       <c r="H30">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="I30">
-        <v>2.96</v>
+        <v>1.27</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q30">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="R30">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -8013,452 +7992,452 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB30">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF30">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG30">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F31">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="G31">
-        <v>2.46</v>
+        <v>1.38</v>
       </c>
       <c r="H31">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="K31">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P31">
+        <v>2.26</v>
+      </c>
+      <c r="Q31">
         <v>1.69</v>
       </c>
-      <c r="Q31">
-        <v>2.36</v>
-      </c>
       <c r="R31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG31">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8473,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8665,733 +8644,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:80">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" t="s">
-        <v>188</v>
-      </c>
-      <c r="F33">
-        <v>14.5</v>
-      </c>
-      <c r="G33">
-        <v>17.5</v>
-      </c>
-      <c r="H33">
-        <v>1.24</v>
-      </c>
-      <c r="I33">
-        <v>1.27</v>
-      </c>
-      <c r="J33">
-        <v>6.8</v>
-      </c>
-      <c r="K33">
-        <v>7.4</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>2.18</v>
-      </c>
-      <c r="Q33">
-        <v>1.5</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AI33">
-        <v>0</v>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>0</v>
-      </c>
-      <c r="AN33">
-        <v>0</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>0</v>
-      </c>
-      <c r="AQ33">
-        <v>0</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33">
-        <v>0</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33">
-        <v>0</v>
-      </c>
-      <c r="AV33">
-        <v>0</v>
-      </c>
-      <c r="AW33">
-        <v>0</v>
-      </c>
-      <c r="AX33">
-        <v>0</v>
-      </c>
-      <c r="AY33">
-        <v>0</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>0</v>
-      </c>
-      <c r="BC33">
-        <v>0</v>
-      </c>
-      <c r="BD33">
-        <v>0</v>
-      </c>
-      <c r="BE33">
-        <v>0</v>
-      </c>
-      <c r="BF33">
-        <v>0</v>
-      </c>
-      <c r="BG33">
-        <v>0</v>
-      </c>
-      <c r="BH33">
-        <v>0</v>
-      </c>
-      <c r="BI33">
-        <v>0</v>
-      </c>
-      <c r="BJ33">
-        <v>0</v>
-      </c>
-      <c r="BK33">
-        <v>0</v>
-      </c>
-      <c r="BL33">
-        <v>0</v>
-      </c>
-      <c r="BM33">
-        <v>0</v>
-      </c>
-      <c r="BN33">
-        <v>0</v>
-      </c>
-      <c r="BO33">
-        <v>0</v>
-      </c>
-      <c r="BP33">
-        <v>0</v>
-      </c>
-      <c r="BQ33">
-        <v>0</v>
-      </c>
-      <c r="BR33">
-        <v>0</v>
-      </c>
-      <c r="BS33">
-        <v>0</v>
-      </c>
-      <c r="BT33">
-        <v>0</v>
-      </c>
-      <c r="BU33">
-        <v>0</v>
-      </c>
-      <c r="BV33">
-        <v>0</v>
-      </c>
-      <c r="BW33">
-        <v>0</v>
-      </c>
-      <c r="BX33">
-        <v>0</v>
-      </c>
-      <c r="BY33">
-        <v>0</v>
-      </c>
-      <c r="BZ33">
-        <v>0</v>
-      </c>
-      <c r="CA33">
-        <v>0</v>
-      </c>
-      <c r="CB33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" spans="1:80">
-      <c r="A34" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34">
-        <v>1.35</v>
-      </c>
-      <c r="G34">
-        <v>1.38</v>
-      </c>
-      <c r="H34">
-        <v>9.6</v>
-      </c>
-      <c r="I34">
-        <v>12.5</v>
-      </c>
-      <c r="J34">
-        <v>5.2</v>
-      </c>
-      <c r="K34">
-        <v>5.9</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>1.05</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>2.26</v>
-      </c>
-      <c r="Q34">
-        <v>1.68</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>0</v>
-      </c>
-      <c r="BC34">
-        <v>0</v>
-      </c>
-      <c r="BD34">
-        <v>0</v>
-      </c>
-      <c r="BE34">
-        <v>0</v>
-      </c>
-      <c r="BF34">
-        <v>0</v>
-      </c>
-      <c r="BG34">
-        <v>0</v>
-      </c>
-      <c r="BH34">
-        <v>0</v>
-      </c>
-      <c r="BI34">
-        <v>0</v>
-      </c>
-      <c r="BJ34">
-        <v>0</v>
-      </c>
-      <c r="BK34">
-        <v>0</v>
-      </c>
-      <c r="BL34">
-        <v>0</v>
-      </c>
-      <c r="BM34">
-        <v>0</v>
-      </c>
-      <c r="BN34">
-        <v>0</v>
-      </c>
-      <c r="BO34">
-        <v>0</v>
-      </c>
-      <c r="BP34">
-        <v>0</v>
-      </c>
-      <c r="BQ34">
-        <v>0</v>
-      </c>
-      <c r="BR34">
-        <v>0</v>
-      </c>
-      <c r="BS34">
-        <v>0</v>
-      </c>
-      <c r="BT34">
-        <v>0</v>
-      </c>
-      <c r="BU34">
-        <v>0</v>
-      </c>
-      <c r="BV34">
-        <v>0</v>
-      </c>
-      <c r="BW34">
-        <v>0</v>
-      </c>
-      <c r="BX34">
-        <v>0</v>
-      </c>
-      <c r="BY34">
-        <v>0</v>
-      </c>
-      <c r="BZ34">
-        <v>0</v>
-      </c>
-      <c r="CA34">
-        <v>0</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="35" spans="1:80">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" t="s">
-        <v>190</v>
-      </c>
-      <c r="F35">
-        <v>2.36</v>
-      </c>
-      <c r="G35">
-        <v>2.56</v>
-      </c>
-      <c r="H35">
-        <v>3.6</v>
-      </c>
-      <c r="I35">
-        <v>4.1</v>
-      </c>
-      <c r="J35">
-        <v>2.86</v>
-      </c>
-      <c r="K35">
-        <v>3.2</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>1.43</v>
-      </c>
-      <c r="Q35">
-        <v>2.56</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <v>0</v>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
-        <v>0</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>0</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>0</v>
-      </c>
-      <c r="BC35">
-        <v>0</v>
-      </c>
-      <c r="BD35">
-        <v>0</v>
-      </c>
-      <c r="BE35">
-        <v>0</v>
-      </c>
-      <c r="BF35">
-        <v>0</v>
-      </c>
-      <c r="BG35">
-        <v>0</v>
-      </c>
-      <c r="BH35">
-        <v>0</v>
-      </c>
-      <c r="BI35">
-        <v>0</v>
-      </c>
-      <c r="BJ35">
-        <v>0</v>
-      </c>
-      <c r="BK35">
-        <v>0</v>
-      </c>
-      <c r="BL35">
-        <v>0</v>
-      </c>
-      <c r="BM35">
-        <v>0</v>
-      </c>
-      <c r="BN35">
-        <v>0</v>
-      </c>
-      <c r="BO35">
-        <v>0</v>
-      </c>
-      <c r="BP35">
-        <v>0</v>
-      </c>
-      <c r="BQ35">
-        <v>0</v>
-      </c>
-      <c r="BR35">
-        <v>0</v>
-      </c>
-      <c r="BS35">
-        <v>0</v>
-      </c>
-      <c r="BT35">
-        <v>0</v>
-      </c>
-      <c r="BU35">
-        <v>0</v>
-      </c>
-      <c r="BV35">
-        <v>0</v>
-      </c>
-      <c r="BW35">
-        <v>0</v>
-      </c>
-      <c r="BX35">
-        <v>0</v>
-      </c>
-      <c r="BY35">
-        <v>0</v>
-      </c>
-      <c r="BZ35">
-        <v>0</v>
-      </c>
-      <c r="CA35">
-        <v>0</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="205">
   <si>
     <t>League</t>
   </si>
@@ -268,12 +268,12 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Slovakian 2 Liga</t>
-  </si>
-  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -292,21 +292,27 @@
     <t>Czech 2 Liga</t>
   </si>
   <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
     <t>Swedish Allsvenskan</t>
   </si>
   <si>
-    <t>Spanish Segunda Division</t>
-  </si>
-  <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
@@ -400,12 +406,12 @@
     <t>Tijuana</t>
   </si>
   <si>
+    <t>Slovan Bratislava II</t>
+  </si>
+  <si>
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
-    <t>Slovan Bratislava II</t>
-  </si>
-  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -427,21 +433,42 @@
     <t>Trinec</t>
   </si>
   <si>
+    <t>Sporting Gijon</t>
+  </si>
+  <si>
+    <t>Brondby</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
     <t>Hacken</t>
   </si>
   <si>
-    <t>Sporting Gijon</t>
-  </si>
-  <si>
-    <t>Brondby</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>Jong FC Utrecht</t>
+  </si>
+  <si>
+    <t>Jong Ajax Amsterdam</t>
+  </si>
+  <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
+    <t>Volsungur</t>
+  </si>
+  <si>
+    <t>IR Reykjavik</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -463,6 +490,12 @@
     <t>Deportivo</t>
   </si>
   <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>Throttur</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
@@ -493,12 +526,12 @@
     <t>Cruz Azul</t>
   </si>
   <si>
+    <t>FK Humenne</t>
+  </si>
+  <si>
     <t>Zorya</t>
   </si>
   <si>
-    <t>FK Humenne</t>
-  </si>
-  <si>
     <t>Ilves</t>
   </si>
   <si>
@@ -520,21 +553,42 @@
     <t>Usti nad Labem</t>
   </si>
   <si>
+    <t>Sabadell</t>
+  </si>
+  <si>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
+    <t>Puszcza Niepolomice</t>
+  </si>
+  <si>
     <t>Halmstads</t>
   </si>
   <si>
-    <t>Sabadell</t>
-  </si>
-  <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
-    <t>Puszcza Niepolomice</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
+    <t>Jong AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Grotta</t>
+  </si>
+  <si>
+    <t>Aegir</t>
+  </si>
+  <si>
+    <t>IF Vestri</t>
+  </si>
+  <si>
+    <t>Njardvik</t>
+  </si>
+  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
@@ -556,6 +610,12 @@
     <t>Elche</t>
   </si>
   <si>
+    <t>HK Kopavogur</t>
+  </si>
+  <si>
+    <t>Fylkir</t>
+  </si>
+  <si>
     <t>Stjarnan</t>
   </si>
   <si>
@@ -568,7 +628,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 15:11:18</t>
+    <t>2026-08-15 17:30:10</t>
   </si>
 </sst>
 </file>
@@ -900,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1150,16 +1210,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F2">
         <v>2.56</v>
@@ -1177,10 +1237,10 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1189,7 +1249,7 @@
         <v>3.95</v>
       </c>
       <c r="O2">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
         <v>2</v>
@@ -1207,7 +1267,7 @@
         <v>1.56</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
         <v>1.5</v>
@@ -1384,7 +1444,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1392,19 +1452,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
         <v>2.62</v>
@@ -1413,157 +1473,157 @@
         <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.46</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.62</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH3">
         <v>3.15</v>
@@ -1626,7 +1686,7 @@
         <v>25</v>
       </c>
       <c r="CB3" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1634,16 +1694,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1706,7 +1766,7 @@
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA4">
         <v>34</v>
@@ -1724,7 +1784,7 @@
         <v>24</v>
       </c>
       <c r="AF4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AG4">
         <v>14</v>
@@ -1739,7 +1799,7 @@
         <v>290</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1754,7 +1814,7 @@
         <v>15</v>
       </c>
       <c r="AP4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
@@ -1868,7 +1928,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1876,16 +1936,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1927,13 +1987,13 @@
         <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T5">
         <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
         <v>2.66</v>
@@ -2110,7 +2170,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2118,22 +2178,22 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F6">
         <v>4.2</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H6">
         <v>1.88</v>
@@ -2172,7 +2232,7 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U6">
         <v>2.5</v>
@@ -2190,7 +2250,7 @@
         <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA6">
         <v>21</v>
@@ -2199,7 +2259,7 @@
         <v>21</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
@@ -2280,7 +2340,7 @@
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2352,7 +2412,7 @@
         <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2360,31 +2420,31 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F7">
         <v>3.35</v>
       </c>
       <c r="G7">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
         <v>2.36</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>3.75</v>
@@ -2393,7 +2453,7 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>3.95</v>
@@ -2402,28 +2462,28 @@
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q7">
         <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S7">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V7">
         <v>1.73</v>
       </c>
       <c r="W7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
         <v>20</v>
@@ -2525,7 +2585,7 @@
         <v>30</v>
       </c>
       <c r="BE7">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF7">
         <v>21</v>
@@ -2594,7 +2654,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2602,184 +2662,184 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="F8">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
+        <v>2.14</v>
+      </c>
+      <c r="H8">
+        <v>3.85</v>
+      </c>
+      <c r="I8">
+        <v>4.9</v>
+      </c>
+      <c r="J8">
+        <v>3.55</v>
+      </c>
+      <c r="K8">
+        <v>4.1</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>3.6</v>
+      </c>
+      <c r="O8">
+        <v>1.28</v>
+      </c>
+      <c r="P8">
+        <v>1.94</v>
+      </c>
+      <c r="Q8">
+        <v>1.84</v>
+      </c>
+      <c r="R8">
+        <v>1.34</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>1.63</v>
+      </c>
+      <c r="U8">
+        <v>1.93</v>
+      </c>
+      <c r="V8">
+        <v>1.27</v>
+      </c>
+      <c r="W8">
+        <v>1.87</v>
+      </c>
+      <c r="X8">
+        <v>19</v>
+      </c>
+      <c r="Y8">
+        <v>19</v>
+      </c>
+      <c r="Z8">
+        <v>38</v>
+      </c>
+      <c r="AA8">
         <v>110</v>
       </c>
-      <c r="H8">
-        <v>1.12</v>
-      </c>
-      <c r="I8">
-        <v>1000</v>
-      </c>
-      <c r="J8">
-        <v>1.12</v>
-      </c>
-      <c r="K8">
-        <v>320</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.18</v>
-      </c>
-      <c r="O8">
-        <v>1.01</v>
-      </c>
-      <c r="P8">
-        <v>1.18</v>
-      </c>
-      <c r="Q8">
-        <v>1.01</v>
-      </c>
-      <c r="R8">
-        <v>1.18</v>
-      </c>
-      <c r="S8">
-        <v>1.34</v>
-      </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2836,7 +2896,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2844,34 +2904,34 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F9">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="G9">
-        <v>2.14</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>1.14</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>320</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2880,22 +2940,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.45</v>
+        <v>1.18</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.93</v>
+        <v>1.18</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>2.82</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2904,10 +2964,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.87</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3018,10 +3078,10 @@
         <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3078,7 +3138,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3086,34 +3146,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F10">
         <v>2.48</v>
       </c>
       <c r="G10">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H10">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3134,22 +3194,22 @@
         <v>1.51</v>
       </c>
       <c r="R10">
+        <v>1.54</v>
+      </c>
+      <c r="S10">
+        <v>2.5</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
         <v>1.48</v>
       </c>
-      <c r="S10">
-        <v>2.22</v>
-      </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.46</v>
-      </c>
       <c r="W10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3320,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3328,16 +3388,16 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F11">
         <v>2.66</v>
@@ -3562,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3570,16 +3630,16 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F12">
         <v>5.9</v>
@@ -3804,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3812,16 +3872,16 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -3842,7 +3902,7 @@
         <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -3995,13 +4055,13 @@
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
         <v>4.9</v>
@@ -4013,13 +4073,13 @@
         <v>16</v>
       </c>
       <c r="BQ13">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BT13">
         <v>7.6</v>
@@ -4031,22 +4091,22 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4054,16 +4114,16 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -4288,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4296,31 +4356,31 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F15">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="G15">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H15">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K15">
         <v>3.7</v>
@@ -4356,10 +4416,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W15">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4530,7 +4590,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4538,16 +4598,16 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F16">
         <v>3.1</v>
@@ -4772,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4780,241 +4840,241 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F17">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="G17">
-        <v>1.39</v>
+        <v>1.93</v>
       </c>
       <c r="H17">
+        <v>5.1</v>
+      </c>
+      <c r="I17">
+        <v>5.9</v>
+      </c>
+      <c r="J17">
+        <v>3.35</v>
+      </c>
+      <c r="K17">
+        <v>3.75</v>
+      </c>
+      <c r="L17">
+        <v>1.38</v>
+      </c>
+      <c r="M17">
+        <v>1.1</v>
+      </c>
+      <c r="N17">
+        <v>2.92</v>
+      </c>
+      <c r="O17">
+        <v>1.44</v>
+      </c>
+      <c r="P17">
+        <v>1.63</v>
+      </c>
+      <c r="Q17">
+        <v>2.28</v>
+      </c>
+      <c r="R17">
+        <v>1.24</v>
+      </c>
+      <c r="S17">
+        <v>4.3</v>
+      </c>
+      <c r="T17">
+        <v>2.06</v>
+      </c>
+      <c r="U17">
+        <v>1.78</v>
+      </c>
+      <c r="V17">
+        <v>1.2</v>
+      </c>
+      <c r="W17">
+        <v>2.06</v>
+      </c>
+      <c r="X17">
+        <v>12.5</v>
+      </c>
+      <c r="Y17">
+        <v>17</v>
+      </c>
+      <c r="Z17">
+        <v>48</v>
+      </c>
+      <c r="AA17">
+        <v>180</v>
+      </c>
+      <c r="AB17">
+        <v>7.2</v>
+      </c>
+      <c r="AC17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17">
+        <v>25</v>
+      </c>
+      <c r="AE17">
+        <v>110</v>
+      </c>
+      <c r="AF17">
+        <v>12</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>27</v>
+      </c>
+      <c r="AI17">
+        <v>120</v>
+      </c>
+      <c r="AJ17">
+        <v>25</v>
+      </c>
+      <c r="AK17">
+        <v>27</v>
+      </c>
+      <c r="AL17">
+        <v>60</v>
+      </c>
+      <c r="AM17">
+        <v>200</v>
+      </c>
+      <c r="AN17">
+        <v>21</v>
+      </c>
+      <c r="AO17">
+        <v>160</v>
+      </c>
+      <c r="AP17">
+        <v>9.4</v>
+      </c>
+      <c r="AQ17">
+        <v>12.5</v>
+      </c>
+      <c r="AR17">
+        <v>29</v>
+      </c>
+      <c r="AS17">
+        <v>5.5</v>
+      </c>
+      <c r="AT17">
+        <v>6</v>
+      </c>
+      <c r="AU17">
+        <v>6.8</v>
+      </c>
+      <c r="AV17">
+        <v>18</v>
+      </c>
+      <c r="AW17">
+        <v>5.4</v>
+      </c>
+      <c r="AX17">
         <v>8.800000000000001</v>
       </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <v>5.9</v>
-      </c>
-      <c r="K17">
-        <v>6.6</v>
-      </c>
-      <c r="L17">
-        <v>1.19</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>6.6</v>
-      </c>
-      <c r="O17">
-        <v>1.16</v>
-      </c>
-      <c r="P17">
-        <v>2.92</v>
-      </c>
-      <c r="Q17">
-        <v>1.46</v>
-      </c>
-      <c r="R17">
-        <v>1.76</v>
-      </c>
-      <c r="S17">
-        <v>2.16</v>
-      </c>
-      <c r="T17">
-        <v>1.78</v>
-      </c>
-      <c r="U17">
-        <v>2.12</v>
-      </c>
-      <c r="V17">
-        <v>1.11</v>
-      </c>
-      <c r="W17">
-        <v>3.55</v>
-      </c>
-      <c r="X17">
-        <v>40</v>
-      </c>
-      <c r="Y17">
-        <v>46</v>
-      </c>
-      <c r="Z17">
-        <v>100</v>
-      </c>
-      <c r="AA17">
-        <v>310</v>
-      </c>
-      <c r="AB17">
-        <v>13</v>
-      </c>
-      <c r="AC17">
-        <v>17</v>
-      </c>
-      <c r="AD17">
-        <v>40</v>
-      </c>
-      <c r="AE17">
-        <v>130</v>
-      </c>
-      <c r="AF17">
-        <v>12.5</v>
-      </c>
-      <c r="AG17">
-        <v>11</v>
-      </c>
-      <c r="AH17">
-        <v>28</v>
-      </c>
-      <c r="AI17">
-        <v>100</v>
-      </c>
-      <c r="AJ17">
-        <v>14</v>
-      </c>
-      <c r="AK17">
-        <v>16</v>
-      </c>
-      <c r="AL17">
-        <v>34</v>
-      </c>
-      <c r="AM17">
-        <v>120</v>
-      </c>
-      <c r="AN17">
-        <v>4.9</v>
-      </c>
-      <c r="AO17">
-        <v>130</v>
-      </c>
-      <c r="AP17">
-        <v>5</v>
-      </c>
-      <c r="AQ17">
-        <v>5.1</v>
-      </c>
-      <c r="AR17">
-        <v>5.5</v>
-      </c>
-      <c r="AS17">
-        <v>5.7</v>
-      </c>
-      <c r="AT17">
-        <v>11</v>
-      </c>
-      <c r="AU17">
-        <v>13</v>
-      </c>
-      <c r="AV17">
-        <v>5</v>
-      </c>
-      <c r="AW17">
-        <v>5.5</v>
-      </c>
-      <c r="AX17">
+      <c r="AY17">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY17">
-        <v>9.6</v>
-      </c>
       <c r="AZ17">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA17">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB17">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BC17">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BD17">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="BE17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF17">
-        <v>3.85</v>
+        <v>13.5</v>
       </c>
       <c r="BG17">
         <v>5.5</v>
       </c>
       <c r="BH17">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5022,178 +5082,178 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F18">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="G18">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="H18">
+        <v>7.2</v>
+      </c>
+      <c r="I18">
+        <v>8.4</v>
+      </c>
+      <c r="J18">
         <v>4.9</v>
       </c>
-      <c r="I18">
-        <v>5.8</v>
-      </c>
-      <c r="J18">
-        <v>3.35</v>
-      </c>
       <c r="K18">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P18">
+        <v>2.32</v>
+      </c>
+      <c r="Q18">
         <v>1.66</v>
       </c>
-      <c r="Q18">
-        <v>2.28</v>
-      </c>
       <c r="R18">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="T18">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="U18">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W18">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="X18">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Z18">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AA18">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE18">
         <v>110</v>
       </c>
       <c r="AF18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG18">
+        <v>11.5</v>
+      </c>
+      <c r="AH18">
+        <v>23</v>
+      </c>
+      <c r="AI18">
+        <v>95</v>
+      </c>
+      <c r="AJ18">
+        <v>14</v>
+      </c>
+      <c r="AK18">
+        <v>15.5</v>
+      </c>
+      <c r="AL18">
+        <v>32</v>
+      </c>
+      <c r="AM18">
+        <v>120</v>
+      </c>
+      <c r="AN18">
+        <v>6.6</v>
+      </c>
+      <c r="AO18">
+        <v>120</v>
+      </c>
+      <c r="AP18">
+        <v>19</v>
+      </c>
+      <c r="AQ18">
+        <v>25</v>
+      </c>
+      <c r="AR18">
+        <v>55</v>
+      </c>
+      <c r="AS18">
+        <v>10</v>
+      </c>
+      <c r="AT18">
+        <v>8.4</v>
+      </c>
+      <c r="AU18">
+        <v>10</v>
+      </c>
+      <c r="AV18">
+        <v>25</v>
+      </c>
+      <c r="AW18">
+        <v>9.6</v>
+      </c>
+      <c r="AX18">
+        <v>8.6</v>
+      </c>
+      <c r="AY18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
+        <v>11.5</v>
+      </c>
+      <c r="BB18">
         <v>12</v>
       </c>
-      <c r="AG18">
-        <v>12</v>
-      </c>
-      <c r="AH18">
-        <v>27</v>
-      </c>
-      <c r="AI18">
-        <v>120</v>
-      </c>
-      <c r="AJ18">
-        <v>25</v>
-      </c>
-      <c r="AK18">
-        <v>27</v>
-      </c>
-      <c r="AL18">
-        <v>60</v>
-      </c>
-      <c r="AM18">
-        <v>200</v>
-      </c>
-      <c r="AN18">
-        <v>21</v>
-      </c>
-      <c r="AO18">
-        <v>160</v>
-      </c>
-      <c r="AP18">
-        <v>9.4</v>
-      </c>
-      <c r="AQ18">
-        <v>12.5</v>
-      </c>
-      <c r="AR18">
-        <v>29</v>
-      </c>
-      <c r="AS18">
-        <v>5.5</v>
-      </c>
-      <c r="AT18">
-        <v>6</v>
-      </c>
-      <c r="AU18">
-        <v>6.8</v>
-      </c>
-      <c r="AV18">
-        <v>18</v>
-      </c>
-      <c r="AW18">
-        <v>5.4</v>
-      </c>
-      <c r="AX18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18">
-        <v>19.5</v>
-      </c>
-      <c r="BA18">
-        <v>5.4</v>
-      </c>
-      <c r="BB18">
-        <v>18</v>
-      </c>
       <c r="BC18">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BD18">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="BE18">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF18">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG18">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5256,7 +5316,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5264,241 +5324,241 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F19">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="G19">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="H19">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
+        <v>1.35</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>3.95</v>
+      </c>
+      <c r="O19">
         <v>1.27</v>
       </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>4.5</v>
-      </c>
-      <c r="O19">
-        <v>1.2</v>
-      </c>
       <c r="P19">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q19">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="S19">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="T19">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W19">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="X19">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Z19">
+        <v>50</v>
+      </c>
+      <c r="AA19">
+        <v>150</v>
+      </c>
+      <c r="AB19">
+        <v>11.5</v>
+      </c>
+      <c r="AC19">
+        <v>11</v>
+      </c>
+      <c r="AD19">
+        <v>24</v>
+      </c>
+      <c r="AE19">
         <v>80</v>
       </c>
-      <c r="AA19">
-        <v>280</v>
-      </c>
-      <c r="AB19">
-        <v>13</v>
-      </c>
-      <c r="AC19">
-        <v>13</v>
-      </c>
-      <c r="AD19">
-        <v>32</v>
-      </c>
-      <c r="AE19">
-        <v>120</v>
-      </c>
       <c r="AF19">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI19">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ19">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AK19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AL19">
         <v>36</v>
       </c>
       <c r="AM19">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN19">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AO19">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AP19">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AQ19">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AR19">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AS19">
-        <v>4.7</v>
+        <v>80</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>4.6</v>
+        <v>46</v>
       </c>
       <c r="AX19">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ19">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>4.6</v>
+        <v>46</v>
       </c>
       <c r="BB19">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD19">
         <v>24</v>
       </c>
       <c r="BE19">
-        <v>4.6</v>
+        <v>70</v>
       </c>
       <c r="BF19">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG19">
-        <v>4.6</v>
+        <v>48</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5506,241 +5566,241 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="G20">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="H20">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
         <v>5.9</v>
       </c>
-      <c r="J20">
-        <v>3.8</v>
-      </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="Q20">
+        <v>1.46</v>
+      </c>
+      <c r="R20">
         <v>1.78</v>
       </c>
-      <c r="R20">
-        <v>1.36</v>
-      </c>
       <c r="S20">
-        <v>2.96</v>
+        <v>2.16</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="X20">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE20">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI20">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX20">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH20">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BI20">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK20">
-        <v>6.2</v>
+        <v>2.72</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="BN20">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO20">
         <v>3</v>
       </c>
       <c r="BP20">
+        <v>10.5</v>
+      </c>
+      <c r="BQ20">
+        <v>5.1</v>
+      </c>
+      <c r="BR20">
+        <v>26</v>
+      </c>
+      <c r="BS20">
+        <v>2.94</v>
+      </c>
+      <c r="BT20">
         <v>17.5</v>
       </c>
-      <c r="BQ20">
-        <v>7.2</v>
-      </c>
-      <c r="BR20">
-        <v>38</v>
-      </c>
-      <c r="BS20">
-        <v>15</v>
-      </c>
-      <c r="BT20">
-        <v>12.5</v>
-      </c>
       <c r="BU20">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>21</v>
+        <v>3.15</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="CB20" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5748,178 +5808,178 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F21">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G21">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H21">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="I21">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J21">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="K21">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L21">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N21">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y21">
+        <v>9.4</v>
+      </c>
+      <c r="Z21">
+        <v>22</v>
+      </c>
+      <c r="AA21">
+        <v>70</v>
+      </c>
+      <c r="AB21">
+        <v>9.6</v>
+      </c>
+      <c r="AC21">
+        <v>8.4</v>
+      </c>
+      <c r="AD21">
+        <v>18</v>
+      </c>
+      <c r="AE21">
+        <v>65</v>
+      </c>
+      <c r="AF21">
+        <v>23</v>
+      </c>
+      <c r="AG21">
+        <v>18.5</v>
+      </c>
+      <c r="AH21">
+        <v>32</v>
+      </c>
+      <c r="AI21">
+        <v>110</v>
+      </c>
+      <c r="AJ21">
+        <v>75</v>
+      </c>
+      <c r="AK21">
+        <v>70</v>
+      </c>
+      <c r="AL21">
+        <v>110</v>
+      </c>
+      <c r="AM21">
+        <v>300</v>
+      </c>
+      <c r="AN21">
+        <v>95</v>
+      </c>
+      <c r="AO21">
+        <v>90</v>
+      </c>
+      <c r="AP21">
+        <v>6.2</v>
+      </c>
+      <c r="AQ21">
+        <v>5.9</v>
+      </c>
+      <c r="AR21">
+        <v>13</v>
+      </c>
+      <c r="AS21">
+        <v>4.1</v>
+      </c>
+      <c r="AT21">
+        <v>6</v>
+      </c>
+      <c r="AU21">
+        <v>6</v>
+      </c>
+      <c r="AV21">
+        <v>12.5</v>
+      </c>
+      <c r="AW21">
+        <v>4.1</v>
+      </c>
+      <c r="AX21">
+        <v>13.5</v>
+      </c>
+      <c r="AY21">
         <v>11</v>
       </c>
-      <c r="Z21">
-        <v>26</v>
-      </c>
-      <c r="AA21">
-        <v>85</v>
-      </c>
-      <c r="AB21">
-        <v>11.5</v>
-      </c>
-      <c r="AC21">
-        <v>10</v>
-      </c>
-      <c r="AD21">
-        <v>21</v>
-      </c>
-      <c r="AE21">
-        <v>75</v>
-      </c>
-      <c r="AF21">
-        <v>28</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>38</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>90</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>100</v>
-      </c>
-      <c r="AO21">
-        <v>100</v>
-      </c>
-      <c r="AP21">
-        <v>1.93</v>
-      </c>
-      <c r="AQ21">
-        <v>1.64</v>
-      </c>
-      <c r="AR21">
-        <v>1.79</v>
-      </c>
-      <c r="AS21">
-        <v>1.88</v>
-      </c>
-      <c r="AT21">
-        <v>1.65</v>
-      </c>
-      <c r="AU21">
-        <v>1.61</v>
-      </c>
-      <c r="AV21">
-        <v>1.76</v>
-      </c>
-      <c r="AW21">
-        <v>1.88</v>
-      </c>
-      <c r="AX21">
-        <v>1.8</v>
-      </c>
-      <c r="AY21">
-        <v>1.93</v>
-      </c>
       <c r="AZ21">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="BA21">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="BB21">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BC21">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="BD21">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="BE21">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="BF21">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BG21">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5982,7 +6042,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5990,760 +6050,760 @@
         <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F23">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="H23">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="I23">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>5.3</v>
+      </c>
+      <c r="O23">
+        <v>1.17</v>
+      </c>
+      <c r="P23">
+        <v>2.48</v>
+      </c>
+      <c r="Q23">
+        <v>1.53</v>
+      </c>
+      <c r="R23">
+        <v>1.57</v>
+      </c>
+      <c r="S23">
+        <v>2.34</v>
+      </c>
+      <c r="T23">
+        <v>1.53</v>
+      </c>
+      <c r="U23">
+        <v>2.5</v>
+      </c>
+      <c r="V23">
+        <v>1.83</v>
+      </c>
+      <c r="W23">
+        <v>1.35</v>
+      </c>
+      <c r="X23">
+        <v>30</v>
+      </c>
+      <c r="Y23">
+        <v>15</v>
+      </c>
+      <c r="Z23">
+        <v>17</v>
+      </c>
+      <c r="AA23">
+        <v>26</v>
+      </c>
+      <c r="AB23">
+        <v>21</v>
+      </c>
+      <c r="AC23">
+        <v>11</v>
+      </c>
+      <c r="AD23">
+        <v>12</v>
+      </c>
+      <c r="AE23">
+        <v>20</v>
+      </c>
+      <c r="AF23">
+        <v>32</v>
+      </c>
+      <c r="AG23">
+        <v>16</v>
+      </c>
+      <c r="AH23">
+        <v>16</v>
+      </c>
+      <c r="AI23">
+        <v>28</v>
+      </c>
+      <c r="AJ23">
+        <v>70</v>
+      </c>
+      <c r="AK23">
+        <v>36</v>
+      </c>
+      <c r="AL23">
+        <v>38</v>
+      </c>
+      <c r="AM23">
+        <v>70</v>
+      </c>
+      <c r="AN23">
+        <v>25</v>
+      </c>
+      <c r="AO23">
+        <v>10.5</v>
+      </c>
+      <c r="AP23">
+        <v>19.5</v>
+      </c>
+      <c r="AQ23">
+        <v>12</v>
+      </c>
+      <c r="AR23">
+        <v>13.5</v>
+      </c>
+      <c r="AS23">
+        <v>21</v>
+      </c>
+      <c r="AT23">
+        <v>16.5</v>
+      </c>
+      <c r="AU23">
         <v>8.800000000000001</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>1.89</v>
-      </c>
-      <c r="Q23">
-        <v>1.6</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>0</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
       <c r="AV23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F24">
-        <v>1.71</v>
+        <v>2.68</v>
       </c>
       <c r="G24">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="H24">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="I24">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J24">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K24">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P24">
-        <v>1.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q24">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
         <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F25">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="G25">
-        <v>1.67</v>
+        <v>110</v>
       </c>
       <c r="H25">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="I25">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>4.2</v>
+        <v>1.14</v>
       </c>
       <c r="K25">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6752,22 +6812,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="R25">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S25">
-        <v>2.58</v>
+        <v>1.07</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6776,10 +6836,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="W25">
-        <v>2.48</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6836,10 +6896,10 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
         <v>1.01</v>
@@ -6848,22 +6908,22 @@
         <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
         <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
         <v>1.01</v>
@@ -6872,19 +6932,19 @@
         <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
         <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
@@ -6950,428 +7010,428 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
         <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G26">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H26">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I26">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J26">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K26">
-        <v>3.55</v>
+        <v>330</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P26">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q26">
-        <v>1.9</v>
+        <v>1.09</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F27">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="G27">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H27">
-        <v>2.94</v>
+        <v>1.1</v>
       </c>
       <c r="I27">
-        <v>2.96</v>
+        <v>110</v>
       </c>
       <c r="J27">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="O27">
+        <v>1.1</v>
+      </c>
+      <c r="P27">
         <v>1.25</v>
       </c>
-      <c r="P27">
-        <v>2.16</v>
-      </c>
       <c r="Q27">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="R27">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="S27">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="T27">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7434,186 +7494,186 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F28">
-        <v>2.38</v>
+        <v>1.1</v>
       </c>
       <c r="G28">
-        <v>2.42</v>
+        <v>110</v>
       </c>
       <c r="H28">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="I28">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="J28">
-        <v>3.15</v>
+        <v>1.14</v>
       </c>
       <c r="K28">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="O28">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="P28">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S28">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="T28">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="W28">
-        <v>1.7</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7676,24 +7736,24 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -7714,937 +7774,3115 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P29">
+        <v>1.25</v>
+      </c>
+      <c r="Q29">
+        <v>1.08</v>
+      </c>
+      <c r="R29">
         <v>1.24</v>
       </c>
-      <c r="Q29">
-        <v>1.01</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F30">
+        <v>3.25</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>1.91</v>
+      </c>
+      <c r="I30">
+        <v>2.22</v>
+      </c>
+      <c r="J30">
+        <v>1.02</v>
+      </c>
+      <c r="K30">
+        <v>4.2</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>3.95</v>
+      </c>
+      <c r="O30">
+        <v>1.24</v>
+      </c>
+      <c r="P30">
+        <v>1.89</v>
+      </c>
+      <c r="Q30">
+        <v>1.6</v>
+      </c>
+      <c r="R30">
+        <v>1.33</v>
+      </c>
+      <c r="S30">
+        <v>2.72</v>
+      </c>
+      <c r="T30">
+        <v>1.47</v>
+      </c>
+      <c r="U30">
+        <v>1.83</v>
+      </c>
+      <c r="V30">
+        <v>1.81</v>
+      </c>
+      <c r="W30">
+        <v>1.29</v>
+      </c>
+      <c r="X30">
+        <v>22</v>
+      </c>
+      <c r="Y30">
+        <v>12</v>
+      </c>
+      <c r="Z30">
+        <v>15.5</v>
+      </c>
+      <c r="AA30">
+        <v>27</v>
+      </c>
+      <c r="AB30">
+        <v>18</v>
+      </c>
+      <c r="AC30">
+        <v>9.6</v>
+      </c>
+      <c r="AD30">
+        <v>12</v>
+      </c>
+      <c r="AE30">
+        <v>25</v>
+      </c>
+      <c r="AF30">
+        <v>32</v>
+      </c>
+      <c r="AG30">
+        <v>17.5</v>
+      </c>
+      <c r="AH30">
+        <v>18.5</v>
+      </c>
+      <c r="AI30">
+        <v>40</v>
+      </c>
+      <c r="AJ30">
+        <v>90</v>
+      </c>
+      <c r="AK30">
+        <v>55</v>
+      </c>
+      <c r="AL30">
+        <v>60</v>
+      </c>
+      <c r="AM30">
+        <v>100</v>
+      </c>
+      <c r="AN30">
+        <v>44</v>
+      </c>
+      <c r="AO30">
+        <v>14</v>
+      </c>
+      <c r="AP30">
+        <v>12.5</v>
+      </c>
+      <c r="AQ30">
+        <v>8</v>
+      </c>
+      <c r="AR30">
+        <v>10</v>
+      </c>
+      <c r="AS30">
+        <v>18</v>
+      </c>
+      <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>6.6</v>
+      </c>
+      <c r="AV30">
+        <v>8</v>
+      </c>
+      <c r="AW30">
         <v>15</v>
       </c>
-      <c r="G30">
-        <v>17.5</v>
-      </c>
-      <c r="H30">
-        <v>1.24</v>
-      </c>
-      <c r="I30">
-        <v>1.27</v>
-      </c>
-      <c r="J30">
-        <v>6.8</v>
-      </c>
-      <c r="K30">
-        <v>7.4</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>2.34</v>
-      </c>
-      <c r="Q30">
-        <v>1.5</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>0</v>
-      </c>
-      <c r="AO30">
-        <v>0</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
       <c r="AX30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F31">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="G31">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="J31">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="K31">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P31">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="Q31">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32">
+        <v>1.55</v>
+      </c>
+      <c r="G32">
+        <v>1.67</v>
+      </c>
+      <c r="H32">
+        <v>5.4</v>
+      </c>
+      <c r="I32">
+        <v>7.6</v>
+      </c>
+      <c r="J32">
+        <v>4.2</v>
+      </c>
+      <c r="K32">
+        <v>6.4</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>2.7</v>
+      </c>
+      <c r="O32">
+        <v>1.2</v>
+      </c>
+      <c r="P32">
+        <v>2.08</v>
+      </c>
+      <c r="Q32">
+        <v>1.66</v>
+      </c>
+      <c r="R32">
+        <v>1.44</v>
+      </c>
+      <c r="S32">
+        <v>2.58</v>
+      </c>
+      <c r="T32">
+        <v>1.01</v>
+      </c>
+      <c r="U32">
+        <v>1.01</v>
+      </c>
+      <c r="V32">
+        <v>1.15</v>
+      </c>
+      <c r="W32">
+        <v>2.48</v>
+      </c>
+      <c r="X32">
+        <v>24</v>
+      </c>
+      <c r="Y32">
+        <v>28</v>
+      </c>
+      <c r="Z32">
+        <v>60</v>
+      </c>
+      <c r="AA32">
+        <v>180</v>
+      </c>
+      <c r="AB32">
+        <v>12</v>
+      </c>
+      <c r="AC32">
+        <v>12</v>
+      </c>
+      <c r="AD32">
+        <v>27</v>
+      </c>
+      <c r="AE32">
+        <v>90</v>
+      </c>
+      <c r="AF32">
+        <v>12.5</v>
+      </c>
+      <c r="AG32">
+        <v>12</v>
+      </c>
+      <c r="AH32">
+        <v>23</v>
+      </c>
+      <c r="AI32">
+        <v>85</v>
+      </c>
+      <c r="AJ32">
+        <v>18</v>
+      </c>
+      <c r="AK32">
+        <v>18.5</v>
+      </c>
+      <c r="AL32">
+        <v>36</v>
+      </c>
+      <c r="AM32">
+        <v>110</v>
+      </c>
+      <c r="AN32">
+        <v>8.6</v>
+      </c>
+      <c r="AO32">
+        <v>95</v>
+      </c>
+      <c r="AP32">
+        <v>16</v>
+      </c>
+      <c r="AQ32">
+        <v>18</v>
+      </c>
+      <c r="AR32">
+        <v>4.7</v>
+      </c>
+      <c r="AS32">
+        <v>5</v>
+      </c>
+      <c r="AT32">
+        <v>7.8</v>
+      </c>
+      <c r="AU32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>17.5</v>
+      </c>
+      <c r="AW32">
+        <v>4.8</v>
+      </c>
+      <c r="AX32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY32">
+        <v>7.8</v>
+      </c>
+      <c r="AZ32">
+        <v>4.2</v>
+      </c>
+      <c r="BA32">
+        <v>4.8</v>
+      </c>
+      <c r="BB32">
+        <v>12</v>
+      </c>
+      <c r="BC32">
+        <v>12</v>
+      </c>
+      <c r="BD32">
+        <v>4.5</v>
+      </c>
+      <c r="BE32">
+        <v>4.9</v>
+      </c>
+      <c r="BF32">
+        <v>5.9</v>
+      </c>
+      <c r="BG32">
+        <v>4.8</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.01</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.01</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.01</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.01</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33">
+        <v>2.24</v>
+      </c>
+      <c r="G33">
+        <v>2.4</v>
+      </c>
+      <c r="H33">
+        <v>3.6</v>
+      </c>
+      <c r="I33">
+        <v>3.85</v>
+      </c>
+      <c r="J33">
+        <v>3.25</v>
+      </c>
+      <c r="K33">
+        <v>3.5</v>
+      </c>
+      <c r="L33">
+        <v>1.34</v>
+      </c>
+      <c r="M33">
+        <v>1.08</v>
+      </c>
+      <c r="N33">
+        <v>3.3</v>
+      </c>
+      <c r="O33">
+        <v>1.37</v>
+      </c>
+      <c r="P33">
+        <v>1.78</v>
+      </c>
+      <c r="Q33">
+        <v>2.08</v>
+      </c>
+      <c r="R33">
+        <v>1.3</v>
+      </c>
+      <c r="S33">
+        <v>3.85</v>
+      </c>
+      <c r="T33">
+        <v>1.83</v>
+      </c>
+      <c r="U33">
+        <v>2.04</v>
+      </c>
+      <c r="V33">
+        <v>1.35</v>
+      </c>
+      <c r="W33">
+        <v>1.71</v>
+      </c>
+      <c r="X33">
+        <v>12.5</v>
+      </c>
+      <c r="Y33">
+        <v>13</v>
+      </c>
+      <c r="Z33">
+        <v>38</v>
+      </c>
+      <c r="AA33">
+        <v>100</v>
+      </c>
+      <c r="AB33">
+        <v>9.4</v>
+      </c>
+      <c r="AC33">
+        <v>7.6</v>
+      </c>
+      <c r="AD33">
+        <v>15.5</v>
+      </c>
+      <c r="AE33">
+        <v>60</v>
+      </c>
+      <c r="AF33">
+        <v>14.5</v>
+      </c>
+      <c r="AG33">
+        <v>11.5</v>
+      </c>
+      <c r="AH33">
+        <v>26</v>
+      </c>
+      <c r="AI33">
+        <v>85</v>
+      </c>
+      <c r="AJ33">
+        <v>46</v>
+      </c>
+      <c r="AK33">
+        <v>27</v>
+      </c>
+      <c r="AL33">
+        <v>55</v>
+      </c>
+      <c r="AM33">
+        <v>130</v>
+      </c>
+      <c r="AN33">
+        <v>22</v>
+      </c>
+      <c r="AO33">
+        <v>65</v>
+      </c>
+      <c r="AP33">
+        <v>9</v>
+      </c>
+      <c r="AQ33">
+        <v>11</v>
+      </c>
+      <c r="AR33">
+        <v>15</v>
+      </c>
+      <c r="AS33">
+        <v>9.4</v>
+      </c>
+      <c r="AT33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU33">
+        <v>6.6</v>
+      </c>
+      <c r="AV33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW33">
+        <v>27</v>
+      </c>
+      <c r="AX33">
+        <v>12.5</v>
+      </c>
+      <c r="AY33">
+        <v>10</v>
+      </c>
+      <c r="AZ33">
+        <v>6.6</v>
+      </c>
+      <c r="BA33">
+        <v>9</v>
+      </c>
+      <c r="BB33">
+        <v>7.8</v>
+      </c>
+      <c r="BC33">
+        <v>20</v>
+      </c>
+      <c r="BD33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE33">
+        <v>9.6</v>
+      </c>
+      <c r="BF33">
+        <v>13.5</v>
+      </c>
+      <c r="BG33">
+        <v>30</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34">
+        <v>2.56</v>
+      </c>
+      <c r="G34">
+        <v>2.6</v>
+      </c>
+      <c r="H34">
+        <v>2.94</v>
+      </c>
+      <c r="I34">
+        <v>2.98</v>
+      </c>
+      <c r="J34">
+        <v>3.6</v>
+      </c>
+      <c r="K34">
+        <v>3.65</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.05</v>
+      </c>
+      <c r="N34">
+        <v>4.4</v>
+      </c>
+      <c r="O34">
+        <v>1.25</v>
+      </c>
+      <c r="P34">
+        <v>2.16</v>
+      </c>
+      <c r="Q34">
+        <v>1.76</v>
+      </c>
+      <c r="R34">
+        <v>1.45</v>
+      </c>
+      <c r="S34">
+        <v>2.92</v>
+      </c>
+      <c r="T34">
+        <v>1.64</v>
+      </c>
+      <c r="U34">
+        <v>2.38</v>
+      </c>
+      <c r="V34">
+        <v>1.5</v>
+      </c>
+      <c r="W34">
+        <v>1.62</v>
+      </c>
+      <c r="X34">
+        <v>18.5</v>
+      </c>
+      <c r="Y34">
+        <v>15</v>
+      </c>
+      <c r="Z34">
+        <v>21</v>
+      </c>
+      <c r="AA34">
+        <v>50</v>
+      </c>
+      <c r="AB34">
+        <v>13</v>
+      </c>
+      <c r="AC34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD34">
+        <v>13.5</v>
+      </c>
+      <c r="AE34">
+        <v>34</v>
+      </c>
+      <c r="AF34">
+        <v>18.5</v>
+      </c>
+      <c r="AG34">
+        <v>12</v>
+      </c>
+      <c r="AH34">
+        <v>16.5</v>
+      </c>
+      <c r="AI34">
+        <v>40</v>
+      </c>
+      <c r="AJ34">
+        <v>80</v>
+      </c>
+      <c r="AK34">
+        <v>27</v>
+      </c>
+      <c r="AL34">
+        <v>36</v>
+      </c>
+      <c r="AM34">
+        <v>75</v>
+      </c>
+      <c r="AN34">
+        <v>21</v>
+      </c>
+      <c r="AO34">
+        <v>23</v>
+      </c>
+      <c r="AP34">
+        <v>16</v>
+      </c>
+      <c r="AQ34">
+        <v>12.5</v>
+      </c>
+      <c r="AR34">
+        <v>17.5</v>
+      </c>
+      <c r="AS34">
+        <v>38</v>
+      </c>
+      <c r="AT34">
+        <v>11.5</v>
+      </c>
+      <c r="AU34">
+        <v>7.6</v>
+      </c>
+      <c r="AV34">
+        <v>12</v>
+      </c>
+      <c r="AW34">
+        <v>26</v>
+      </c>
+      <c r="AX34">
+        <v>16</v>
+      </c>
+      <c r="AY34">
+        <v>10.5</v>
+      </c>
+      <c r="AZ34">
+        <v>14</v>
+      </c>
+      <c r="BA34">
+        <v>32</v>
+      </c>
+      <c r="BB34">
+        <v>32</v>
+      </c>
+      <c r="BC34">
+        <v>22</v>
+      </c>
+      <c r="BD34">
+        <v>30</v>
+      </c>
+      <c r="BE34">
+        <v>32</v>
+      </c>
+      <c r="BF34">
+        <v>15.5</v>
+      </c>
+      <c r="BG34">
+        <v>20</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.01</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35">
+        <v>2.38</v>
+      </c>
+      <c r="G35">
+        <v>2.42</v>
+      </c>
+      <c r="H35">
+        <v>3.65</v>
+      </c>
+      <c r="I35">
+        <v>3.75</v>
+      </c>
+      <c r="J35">
+        <v>3.15</v>
+      </c>
+      <c r="K35">
+        <v>3.2</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.11</v>
+      </c>
+      <c r="N35">
+        <v>3.1</v>
+      </c>
+      <c r="O35">
+        <v>1.45</v>
+      </c>
+      <c r="P35">
+        <v>1.69</v>
+      </c>
+      <c r="Q35">
+        <v>2.36</v>
+      </c>
+      <c r="R35">
+        <v>1.25</v>
+      </c>
+      <c r="S35">
+        <v>4.6</v>
+      </c>
+      <c r="T35">
+        <v>1.98</v>
+      </c>
+      <c r="U35">
+        <v>1.96</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.7</v>
+      </c>
+      <c r="X35">
+        <v>10</v>
+      </c>
+      <c r="Y35">
+        <v>11.5</v>
+      </c>
+      <c r="Z35">
+        <v>24</v>
+      </c>
+      <c r="AA35">
+        <v>75</v>
+      </c>
+      <c r="AB35">
+        <v>8.6</v>
+      </c>
+      <c r="AC35">
+        <v>6.8</v>
+      </c>
+      <c r="AD35">
+        <v>15.5</v>
+      </c>
+      <c r="AE35">
+        <v>55</v>
+      </c>
+      <c r="AF35">
+        <v>14</v>
+      </c>
+      <c r="AG35">
+        <v>12</v>
+      </c>
+      <c r="AH35">
+        <v>19.5</v>
+      </c>
+      <c r="AI35">
+        <v>70</v>
+      </c>
+      <c r="AJ35">
+        <v>34</v>
+      </c>
+      <c r="AK35">
+        <v>30</v>
+      </c>
+      <c r="AL35">
+        <v>50</v>
+      </c>
+      <c r="AM35">
+        <v>140</v>
+      </c>
+      <c r="AN35">
+        <v>28</v>
+      </c>
+      <c r="AO35">
+        <v>60</v>
+      </c>
+      <c r="AP35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ35">
+        <v>10.5</v>
+      </c>
+      <c r="AR35">
+        <v>21</v>
+      </c>
+      <c r="AS35">
+        <v>60</v>
+      </c>
+      <c r="AT35">
+        <v>7.8</v>
+      </c>
+      <c r="AU35">
+        <v>6.6</v>
+      </c>
+      <c r="AV35">
+        <v>14</v>
+      </c>
+      <c r="AW35">
+        <v>44</v>
+      </c>
+      <c r="AX35">
+        <v>12.5</v>
+      </c>
+      <c r="AY35">
+        <v>10.5</v>
+      </c>
+      <c r="AZ35">
+        <v>19</v>
+      </c>
+      <c r="BA35">
+        <v>60</v>
+      </c>
+      <c r="BB35">
+        <v>29</v>
+      </c>
+      <c r="BC35">
+        <v>26</v>
+      </c>
+      <c r="BD35">
+        <v>46</v>
+      </c>
+      <c r="BE35">
+        <v>42</v>
+      </c>
+      <c r="BF35">
+        <v>24</v>
+      </c>
+      <c r="BG35">
+        <v>50</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36">
+        <v>1.1</v>
+      </c>
+      <c r="G36">
+        <v>110</v>
+      </c>
+      <c r="H36">
+        <v>1.1</v>
+      </c>
+      <c r="I36">
+        <v>1000</v>
+      </c>
+      <c r="J36">
+        <v>1.1</v>
+      </c>
+      <c r="K36">
+        <v>1000</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>1.25</v>
+      </c>
+      <c r="O36">
+        <v>1.06</v>
+      </c>
+      <c r="P36">
+        <v>1.25</v>
+      </c>
+      <c r="Q36">
+        <v>1.06</v>
+      </c>
+      <c r="R36">
+        <v>1.24</v>
+      </c>
+      <c r="S36">
+        <v>1.06</v>
+      </c>
+      <c r="T36">
+        <v>1.01</v>
+      </c>
+      <c r="U36">
+        <v>1.01</v>
+      </c>
+      <c r="V36">
+        <v>1.01</v>
+      </c>
+      <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36">
+        <v>1.01</v>
+      </c>
+      <c r="AR36">
+        <v>1.01</v>
+      </c>
+      <c r="AS36">
+        <v>1.01</v>
+      </c>
+      <c r="AT36">
+        <v>1.01</v>
+      </c>
+      <c r="AU36">
+        <v>1.01</v>
+      </c>
+      <c r="AV36">
+        <v>1.01</v>
+      </c>
+      <c r="AW36">
+        <v>1.01</v>
+      </c>
+      <c r="AX36">
+        <v>1.01</v>
+      </c>
+      <c r="AY36">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36">
+        <v>1.01</v>
+      </c>
+      <c r="BA36">
+        <v>1.01</v>
+      </c>
+      <c r="BB36">
+        <v>1.01</v>
+      </c>
+      <c r="BC36">
+        <v>1.01</v>
+      </c>
+      <c r="BD36">
+        <v>1.01</v>
+      </c>
+      <c r="BE36">
+        <v>1.01</v>
+      </c>
+      <c r="BF36">
+        <v>1.01</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>1000</v>
+      </c>
+      <c r="BO36">
+        <v>1.01</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.01</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" t="s">
+        <v>199</v>
+      </c>
+      <c r="F37">
+        <v>1.22</v>
+      </c>
+      <c r="G37">
+        <v>110</v>
+      </c>
+      <c r="H37">
+        <v>1.22</v>
+      </c>
+      <c r="I37">
+        <v>110</v>
+      </c>
+      <c r="J37">
+        <v>1.13</v>
+      </c>
+      <c r="K37">
+        <v>520</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.01</v>
+      </c>
+      <c r="N37">
+        <v>1.25</v>
+      </c>
+      <c r="O37">
+        <v>1.15</v>
+      </c>
+      <c r="P37">
+        <v>1.25</v>
+      </c>
+      <c r="Q37">
+        <v>1.15</v>
+      </c>
+      <c r="R37">
+        <v>1.24</v>
+      </c>
+      <c r="S37">
+        <v>1.15</v>
+      </c>
+      <c r="T37">
+        <v>1.01</v>
+      </c>
+      <c r="U37">
+        <v>1.01</v>
+      </c>
+      <c r="V37">
+        <v>1.05</v>
+      </c>
+      <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1000</v>
+      </c>
+      <c r="Y37">
+        <v>1000</v>
+      </c>
+      <c r="Z37">
+        <v>1000</v>
+      </c>
+      <c r="AA37">
+        <v>1000</v>
+      </c>
+      <c r="AB37">
+        <v>1000</v>
+      </c>
+      <c r="AC37">
+        <v>1000</v>
+      </c>
+      <c r="AD37">
+        <v>1000</v>
+      </c>
+      <c r="AE37">
+        <v>1000</v>
+      </c>
+      <c r="AF37">
+        <v>1000</v>
+      </c>
+      <c r="AG37">
+        <v>1000</v>
+      </c>
+      <c r="AH37">
+        <v>1000</v>
+      </c>
+      <c r="AI37">
+        <v>1000</v>
+      </c>
+      <c r="AJ37">
+        <v>1000</v>
+      </c>
+      <c r="AK37">
+        <v>1000</v>
+      </c>
+      <c r="AL37">
+        <v>1000</v>
+      </c>
+      <c r="AM37">
+        <v>1000</v>
+      </c>
+      <c r="AN37">
+        <v>1000</v>
+      </c>
+      <c r="AO37">
+        <v>1000</v>
+      </c>
+      <c r="AP37">
+        <v>1.01</v>
+      </c>
+      <c r="AQ37">
+        <v>1.01</v>
+      </c>
+      <c r="AR37">
+        <v>1.01</v>
+      </c>
+      <c r="AS37">
+        <v>1.01</v>
+      </c>
+      <c r="AT37">
+        <v>1.01</v>
+      </c>
+      <c r="AU37">
+        <v>1.01</v>
+      </c>
+      <c r="AV37">
+        <v>1.01</v>
+      </c>
+      <c r="AW37">
+        <v>1.01</v>
+      </c>
+      <c r="AX37">
+        <v>1.01</v>
+      </c>
+      <c r="AY37">
+        <v>1.01</v>
+      </c>
+      <c r="AZ37">
+        <v>1.01</v>
+      </c>
+      <c r="BA37">
+        <v>1.01</v>
+      </c>
+      <c r="BB37">
+        <v>1.01</v>
+      </c>
+      <c r="BC37">
+        <v>1.01</v>
+      </c>
+      <c r="BD37">
+        <v>1.01</v>
+      </c>
+      <c r="BE37">
+        <v>1.01</v>
+      </c>
+      <c r="BF37">
+        <v>1.01</v>
+      </c>
+      <c r="BG37">
+        <v>1.01</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>1.01</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>1.01</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>1.01</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>1.01</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>1.01</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>1.25</v>
+      </c>
+      <c r="O38">
+        <v>1.05</v>
+      </c>
+      <c r="P38">
+        <v>1.25</v>
+      </c>
+      <c r="Q38">
+        <v>1.05</v>
+      </c>
+      <c r="R38">
+        <v>1.24</v>
+      </c>
+      <c r="S38">
+        <v>1.05</v>
+      </c>
+      <c r="T38">
+        <v>1.01</v>
+      </c>
+      <c r="U38">
+        <v>1.01</v>
+      </c>
+      <c r="V38">
+        <v>1.01</v>
+      </c>
+      <c r="W38">
+        <v>1.01</v>
+      </c>
+      <c r="X38">
+        <v>1000</v>
+      </c>
+      <c r="Y38">
+        <v>1000</v>
+      </c>
+      <c r="Z38">
+        <v>1000</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>1000</v>
+      </c>
+      <c r="AC38">
+        <v>1000</v>
+      </c>
+      <c r="AD38">
+        <v>1000</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>1000</v>
+      </c>
+      <c r="AG38">
+        <v>1000</v>
+      </c>
+      <c r="AH38">
+        <v>1000</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>1000</v>
+      </c>
+      <c r="AK38">
+        <v>1000</v>
+      </c>
+      <c r="AL38">
+        <v>1000</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>1000</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38">
+        <v>1.01</v>
+      </c>
+      <c r="AR38">
+        <v>1.01</v>
+      </c>
+      <c r="AS38">
+        <v>1.01</v>
+      </c>
+      <c r="AT38">
+        <v>1.01</v>
+      </c>
+      <c r="AU38">
+        <v>1.01</v>
+      </c>
+      <c r="AV38">
+        <v>1.01</v>
+      </c>
+      <c r="AW38">
+        <v>1.01</v>
+      </c>
+      <c r="AX38">
+        <v>1.01</v>
+      </c>
+      <c r="AY38">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38">
+        <v>1.01</v>
+      </c>
+      <c r="BA38">
+        <v>1.01</v>
+      </c>
+      <c r="BB38">
+        <v>1.01</v>
+      </c>
+      <c r="BC38">
+        <v>1.01</v>
+      </c>
+      <c r="BD38">
+        <v>1.01</v>
+      </c>
+      <c r="BE38">
+        <v>1.01</v>
+      </c>
+      <c r="BF38">
+        <v>1.01</v>
+      </c>
+      <c r="BG38">
+        <v>1.01</v>
+      </c>
+      <c r="BH38">
+        <v>1000</v>
+      </c>
+      <c r="BI38">
+        <v>1.01</v>
+      </c>
+      <c r="BJ38">
+        <v>1000</v>
+      </c>
+      <c r="BK38">
+        <v>1.01</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>1.01</v>
+      </c>
+      <c r="BN38">
+        <v>1000</v>
+      </c>
+      <c r="BO38">
+        <v>1.01</v>
+      </c>
+      <c r="BP38">
+        <v>1000</v>
+      </c>
+      <c r="BQ38">
+        <v>1.01</v>
+      </c>
+      <c r="BR38">
+        <v>1000</v>
+      </c>
+      <c r="BS38">
+        <v>1.01</v>
+      </c>
+      <c r="BT38">
+        <v>1000</v>
+      </c>
+      <c r="BU38">
+        <v>1.01</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>1.01</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>1.01</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
+        <v>1.01</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>18</v>
+      </c>
+      <c r="H39">
+        <v>1.24</v>
+      </c>
+      <c r="I39">
+        <v>1.25</v>
+      </c>
+      <c r="J39">
+        <v>6.8</v>
+      </c>
+      <c r="K39">
+        <v>7.4</v>
+      </c>
+      <c r="L39">
+        <v>1.01</v>
+      </c>
+      <c r="M39">
+        <v>1.03</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39">
+        <v>1.2</v>
+      </c>
+      <c r="P39">
+        <v>2.4</v>
+      </c>
+      <c r="Q39">
+        <v>1.61</v>
+      </c>
+      <c r="R39">
+        <v>1.56</v>
+      </c>
+      <c r="S39">
+        <v>2.5</v>
+      </c>
+      <c r="T39">
+        <v>2.26</v>
+      </c>
+      <c r="U39">
+        <v>1.65</v>
+      </c>
+      <c r="V39">
+        <v>5</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>26</v>
+      </c>
+      <c r="Y39">
+        <v>9.4</v>
+      </c>
+      <c r="Z39">
+        <v>8</v>
+      </c>
+      <c r="AA39">
+        <v>9.6</v>
+      </c>
+      <c r="AB39">
+        <v>55</v>
+      </c>
+      <c r="AC39">
+        <v>16.5</v>
+      </c>
+      <c r="AD39">
+        <v>12.5</v>
+      </c>
+      <c r="AE39">
+        <v>15.5</v>
+      </c>
+      <c r="AF39">
+        <v>200</v>
+      </c>
+      <c r="AG39">
+        <v>70</v>
+      </c>
+      <c r="AH39">
+        <v>50</v>
+      </c>
+      <c r="AI39">
+        <v>60</v>
+      </c>
+      <c r="AJ39">
+        <v>1000</v>
+      </c>
+      <c r="AK39">
+        <v>370</v>
+      </c>
+      <c r="AL39">
+        <v>260</v>
+      </c>
+      <c r="AM39">
+        <v>290</v>
+      </c>
+      <c r="AN39">
+        <v>580</v>
+      </c>
+      <c r="AO39">
+        <v>4.6</v>
+      </c>
+      <c r="AP39">
+        <v>20</v>
+      </c>
+      <c r="AQ39">
+        <v>7.6</v>
+      </c>
+      <c r="AR39">
+        <v>6.6</v>
+      </c>
+      <c r="AS39">
+        <v>7.8</v>
+      </c>
+      <c r="AT39">
+        <v>32</v>
+      </c>
+      <c r="AU39">
+        <v>13</v>
+      </c>
+      <c r="AV39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW39">
+        <v>12.5</v>
+      </c>
+      <c r="AX39">
+        <v>8.6</v>
+      </c>
+      <c r="AY39">
+        <v>7.8</v>
+      </c>
+      <c r="AZ39">
+        <v>30</v>
+      </c>
+      <c r="BA39">
+        <v>34</v>
+      </c>
+      <c r="BB39">
+        <v>9</v>
+      </c>
+      <c r="BC39">
+        <v>8.6</v>
+      </c>
+      <c r="BD39">
+        <v>8.6</v>
+      </c>
+      <c r="BE39">
+        <v>8.6</v>
+      </c>
+      <c r="BF39">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG39">
+        <v>3.9</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>1.01</v>
+      </c>
+      <c r="BJ39">
+        <v>20</v>
+      </c>
+      <c r="BK39">
+        <v>8.4</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>21</v>
+      </c>
+      <c r="BN39">
+        <v>25</v>
+      </c>
+      <c r="BO39">
+        <v>10.5</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>21</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>21</v>
+      </c>
+      <c r="BT39">
+        <v>4.9</v>
+      </c>
+      <c r="BU39">
+        <v>2.54</v>
+      </c>
+      <c r="BV39">
+        <v>9.6</v>
+      </c>
+      <c r="BW39">
+        <v>4.4</v>
+      </c>
+      <c r="BX39">
+        <v>36</v>
+      </c>
+      <c r="BY39">
+        <v>14.5</v>
+      </c>
+      <c r="BZ39">
+        <v>15</v>
+      </c>
+      <c r="CA39">
+        <v>6.4</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:80">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40">
+        <v>1.36</v>
+      </c>
+      <c r="G40">
+        <v>1.38</v>
+      </c>
+      <c r="H40">
+        <v>10</v>
+      </c>
+      <c r="I40">
+        <v>12.5</v>
+      </c>
+      <c r="J40">
+        <v>5.3</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40">
+        <v>1.31</v>
+      </c>
+      <c r="M40">
+        <v>1.05</v>
+      </c>
+      <c r="N40">
+        <v>4.5</v>
+      </c>
+      <c r="O40">
+        <v>1.22</v>
+      </c>
+      <c r="P40">
+        <v>2.26</v>
+      </c>
+      <c r="Q40">
+        <v>1.69</v>
+      </c>
+      <c r="R40">
+        <v>1.46</v>
+      </c>
+      <c r="S40">
+        <v>2.74</v>
+      </c>
+      <c r="T40">
+        <v>2.08</v>
+      </c>
+      <c r="U40">
+        <v>1.64</v>
+      </c>
+      <c r="V40">
+        <v>1.1</v>
+      </c>
+      <c r="W40">
+        <v>3.6</v>
+      </c>
+      <c r="X40">
+        <v>25</v>
+      </c>
+      <c r="Y40">
+        <v>40</v>
+      </c>
+      <c r="Z40">
+        <v>130</v>
+      </c>
+      <c r="AA40">
+        <v>540</v>
+      </c>
+      <c r="AB40">
+        <v>10.5</v>
+      </c>
+      <c r="AC40">
+        <v>15.5</v>
+      </c>
+      <c r="AD40">
+        <v>48</v>
+      </c>
+      <c r="AE40">
+        <v>230</v>
+      </c>
+      <c r="AF40">
+        <v>8.4</v>
+      </c>
+      <c r="AG40">
+        <v>13</v>
+      </c>
+      <c r="AH40">
+        <v>38</v>
+      </c>
+      <c r="AI40">
+        <v>180</v>
+      </c>
+      <c r="AJ40">
+        <v>13</v>
+      </c>
+      <c r="AK40">
+        <v>18.5</v>
+      </c>
+      <c r="AL40">
+        <v>50</v>
+      </c>
+      <c r="AM40">
+        <v>220</v>
+      </c>
+      <c r="AN40">
+        <v>5.9</v>
+      </c>
+      <c r="AO40">
+        <v>330</v>
+      </c>
+      <c r="AP40">
+        <v>15</v>
+      </c>
+      <c r="AQ40">
+        <v>4.7</v>
+      </c>
+      <c r="AR40">
+        <v>5.1</v>
+      </c>
+      <c r="AS40">
+        <v>5.3</v>
+      </c>
+      <c r="AT40">
+        <v>6.4</v>
+      </c>
+      <c r="AU40">
+        <v>10.5</v>
+      </c>
+      <c r="AV40">
+        <v>4.8</v>
+      </c>
+      <c r="AW40">
+        <v>5.2</v>
+      </c>
+      <c r="AX40">
+        <v>6</v>
+      </c>
+      <c r="AY40">
+        <v>8</v>
+      </c>
+      <c r="AZ40">
+        <v>4.7</v>
+      </c>
+      <c r="BA40">
+        <v>5.2</v>
+      </c>
+      <c r="BB40">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC40">
+        <v>11</v>
+      </c>
+      <c r="BD40">
+        <v>4.8</v>
+      </c>
+      <c r="BE40">
+        <v>5.2</v>
+      </c>
+      <c r="BF40">
+        <v>4.3</v>
+      </c>
+      <c r="BG40">
+        <v>5.3</v>
+      </c>
+      <c r="BH40">
+        <v>1000</v>
+      </c>
+      <c r="BI40">
+        <v>1.01</v>
+      </c>
+      <c r="BJ40">
+        <v>18</v>
+      </c>
+      <c r="BK40">
+        <v>7.6</v>
+      </c>
+      <c r="BL40">
+        <v>1000</v>
+      </c>
+      <c r="BM40">
+        <v>21</v>
+      </c>
+      <c r="BN40">
+        <v>5.1</v>
+      </c>
+      <c r="BO40">
+        <v>2.6</v>
+      </c>
+      <c r="BP40">
+        <v>11</v>
+      </c>
+      <c r="BQ40">
+        <v>4.9</v>
+      </c>
+      <c r="BR40">
+        <v>36</v>
+      </c>
+      <c r="BS40">
+        <v>14.5</v>
+      </c>
+      <c r="BT40">
+        <v>20</v>
+      </c>
+      <c r="BU40">
+        <v>8.4</v>
+      </c>
+      <c r="BV40">
+        <v>1000</v>
+      </c>
+      <c r="BW40">
+        <v>21</v>
+      </c>
+      <c r="BX40">
+        <v>1000</v>
+      </c>
+      <c r="BY40">
+        <v>21</v>
+      </c>
+      <c r="BZ40">
+        <v>18.5</v>
+      </c>
+      <c r="CA40">
+        <v>8</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:80">
+      <c r="A41" t="s">
         <v>96</v>
       </c>
-      <c r="B32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32">
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41">
         <v>2.36</v>
       </c>
-      <c r="G32">
+      <c r="G41">
         <v>2.56</v>
       </c>
-      <c r="H32">
+      <c r="H41">
         <v>3.65</v>
       </c>
-      <c r="I32">
+      <c r="I41">
         <v>4.1</v>
       </c>
-      <c r="J32">
+      <c r="J41">
         <v>2.86</v>
       </c>
-      <c r="K32">
+      <c r="K41">
         <v>3.1</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
+      <c r="L41">
+        <v>1.63</v>
+      </c>
+      <c r="M41">
+        <v>1.01</v>
+      </c>
+      <c r="N41">
         <v>1.45</v>
       </c>
-      <c r="Q32">
-        <v>2.84</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
-      <c r="BV32">
-        <v>0</v>
-      </c>
-      <c r="BW32">
-        <v>0</v>
-      </c>
-      <c r="BX32">
-        <v>0</v>
-      </c>
-      <c r="BY32">
-        <v>0</v>
-      </c>
-      <c r="BZ32">
-        <v>0</v>
-      </c>
-      <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>184</v>
+      <c r="O41">
+        <v>1.59</v>
+      </c>
+      <c r="P41">
+        <v>1.45</v>
+      </c>
+      <c r="Q41">
+        <v>2.8</v>
+      </c>
+      <c r="R41">
+        <v>1.12</v>
+      </c>
+      <c r="S41">
+        <v>2.8</v>
+      </c>
+      <c r="T41">
+        <v>1.01</v>
+      </c>
+      <c r="U41">
+        <v>1.65</v>
+      </c>
+      <c r="V41">
+        <v>1.32</v>
+      </c>
+      <c r="W41">
+        <v>1.64</v>
+      </c>
+      <c r="X41">
+        <v>1000</v>
+      </c>
+      <c r="Y41">
+        <v>1000</v>
+      </c>
+      <c r="Z41">
+        <v>1000</v>
+      </c>
+      <c r="AA41">
+        <v>1000</v>
+      </c>
+      <c r="AB41">
+        <v>1000</v>
+      </c>
+      <c r="AC41">
+        <v>1000</v>
+      </c>
+      <c r="AD41">
+        <v>1000</v>
+      </c>
+      <c r="AE41">
+        <v>1000</v>
+      </c>
+      <c r="AF41">
+        <v>1000</v>
+      </c>
+      <c r="AG41">
+        <v>1000</v>
+      </c>
+      <c r="AH41">
+        <v>1000</v>
+      </c>
+      <c r="AI41">
+        <v>1000</v>
+      </c>
+      <c r="AJ41">
+        <v>1000</v>
+      </c>
+      <c r="AK41">
+        <v>1000</v>
+      </c>
+      <c r="AL41">
+        <v>1000</v>
+      </c>
+      <c r="AM41">
+        <v>1000</v>
+      </c>
+      <c r="AN41">
+        <v>1000</v>
+      </c>
+      <c r="AO41">
+        <v>1000</v>
+      </c>
+      <c r="AP41">
+        <v>6.4</v>
+      </c>
+      <c r="AQ41">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR41">
+        <v>17.5</v>
+      </c>
+      <c r="AS41">
+        <v>48</v>
+      </c>
+      <c r="AT41">
+        <v>5.7</v>
+      </c>
+      <c r="AU41">
+        <v>6</v>
+      </c>
+      <c r="AV41">
+        <v>13.5</v>
+      </c>
+      <c r="AW41">
+        <v>42</v>
+      </c>
+      <c r="AX41">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY41">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ41">
+        <v>20</v>
+      </c>
+      <c r="BA41">
+        <v>85</v>
+      </c>
+      <c r="BB41">
+        <v>27</v>
+      </c>
+      <c r="BC41">
+        <v>27</v>
+      </c>
+      <c r="BD41">
+        <v>46</v>
+      </c>
+      <c r="BE41">
+        <v>100</v>
+      </c>
+      <c r="BF41">
+        <v>1.01</v>
+      </c>
+      <c r="BG41">
+        <v>1.01</v>
+      </c>
+      <c r="BH41">
+        <v>1000</v>
+      </c>
+      <c r="BI41">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41">
+        <v>1000</v>
+      </c>
+      <c r="BK41">
+        <v>1.01</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>1.01</v>
+      </c>
+      <c r="BN41">
+        <v>1000</v>
+      </c>
+      <c r="BO41">
+        <v>1.01</v>
+      </c>
+      <c r="BP41">
+        <v>1000</v>
+      </c>
+      <c r="BQ41">
+        <v>1.01</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
+        <v>1.01</v>
+      </c>
+      <c r="BT41">
+        <v>1000</v>
+      </c>
+      <c r="BU41">
+        <v>1.01</v>
+      </c>
+      <c r="BV41">
+        <v>1000</v>
+      </c>
+      <c r="BW41">
+        <v>1.01</v>
+      </c>
+      <c r="BX41">
+        <v>1000</v>
+      </c>
+      <c r="BY41">
+        <v>1.01</v>
+      </c>
+      <c r="BZ41">
+        <v>1000</v>
+      </c>
+      <c r="CA41">
+        <v>1.01</v>
+      </c>
+      <c r="CB41" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="208">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,9 @@
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
+    <t>Azerbaijan Premier League</t>
+  </si>
+  <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
@@ -418,6 +421,9 @@
     <t>Fk Siauliai</t>
   </si>
   <si>
+    <t>Qarabag FK</t>
+  </si>
+  <si>
     <t>Zalaegerszeg</t>
   </si>
   <si>
@@ -538,6 +544,9 @@
     <t>Panevezys</t>
   </si>
   <si>
+    <t>Shamakhi FK</t>
+  </si>
+  <si>
     <t>Ferencvaros</t>
   </si>
   <si>
@@ -628,7 +637,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 17:30:10</t>
+    <t>2026-08-15 19:47:42</t>
   </si>
 </sst>
 </file>
@@ -960,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB41"/>
+  <dimension ref="A1:CB42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1210,16 +1219,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F2">
         <v>2.56</v>
@@ -1237,7 +1246,7 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.29</v>
@@ -1255,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R2">
         <v>1.38</v>
@@ -1444,7 +1453,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1452,16 +1461,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>2.38</v>
@@ -1494,7 +1503,7 @@
         <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
@@ -1686,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="CB3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1694,16 +1703,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1724,7 +1733,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1814,7 +1823,7 @@
         <v>15</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
@@ -1838,7 +1847,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AY4">
         <v>12</v>
@@ -1868,67 +1877,67 @@
         <v>13</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1936,19 +1945,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G5">
         <v>6.6</v>
@@ -2047,7 +2056,7 @@
         <v>90</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5">
         <v>95</v>
@@ -2062,16 +2071,16 @@
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5">
         <v>13</v>
       </c>
       <c r="AT5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV5">
         <v>9.199999999999999</v>
@@ -2080,13 +2089,13 @@
         <v>13</v>
       </c>
       <c r="AX5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY5">
         <v>20</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA5">
         <v>20</v>
@@ -2104,7 +2113,7 @@
         <v>8</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
         <v>5.8</v>
@@ -2170,7 +2179,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2178,16 +2187,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>4.2</v>
@@ -2196,7 +2205,7 @@
         <v>4.4</v>
       </c>
       <c r="H6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I6">
         <v>1.89</v>
@@ -2223,7 +2232,7 @@
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.58</v>
@@ -2232,7 +2241,7 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
         <v>2.5</v>
@@ -2259,7 +2268,7 @@
         <v>21</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
@@ -2274,7 +2283,7 @@
         <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI6">
         <v>32</v>
@@ -2340,7 +2349,7 @@
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2412,7 +2421,7 @@
         <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2420,28 +2429,28 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F7">
         <v>3.35</v>
       </c>
       <c r="G7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J7">
         <v>3.5</v>
@@ -2456,28 +2465,28 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P7">
         <v>2.04</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S7">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T7">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V7">
         <v>1.73</v>
@@ -2486,46 +2495,46 @@
         <v>1.4</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA7">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AB7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AF7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AG7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
         <v>690</v>
       </c>
       <c r="AK7">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AL7">
         <v>140</v>
@@ -2534,55 +2543,55 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP7">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR7">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7">
         <v>19</v>
       </c>
       <c r="AT7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AX7">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB7">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BC7">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BD7">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BE7">
         <v>34</v>
@@ -2591,7 +2600,7 @@
         <v>21</v>
       </c>
       <c r="BG7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2654,7 +2663,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2662,16 +2671,16 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F8">
         <v>1.9</v>
@@ -2698,10 +2707,10 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
         <v>1.94</v>
@@ -2716,10 +2725,10 @@
         <v>3</v>
       </c>
       <c r="T8">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
         <v>1.27</v>
@@ -2896,7 +2905,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2904,16 +2913,16 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F9">
         <v>1.26</v>
@@ -2922,13 +2931,13 @@
         <v>110</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="K9">
         <v>320</v>
@@ -2940,22 +2949,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2967,7 +2976,7 @@
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3138,7 +3147,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3146,16 +3155,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F10">
         <v>2.48</v>
@@ -3167,10 +3176,10 @@
         <v>2.7</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
         <v>4.4</v>
@@ -3206,10 +3215,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3380,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3388,16 +3397,16 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F11">
         <v>2.66</v>
@@ -3424,13 +3433,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="O11">
         <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q11">
         <v>1.53</v>
@@ -3622,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3630,34 +3639,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F12">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3666,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3690,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3864,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3872,542 +3881,542 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="G13">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="H13">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="I13">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="T13">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>2.48</v>
       </c>
       <c r="W13">
-        <v>1.84</v>
+        <v>1.16</v>
       </c>
       <c r="X13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
         <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="H14">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="I14">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="Q14">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BI14">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
         <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F15">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="H15">
-        <v>3.85</v>
+        <v>1.96</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J15">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O15">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q15">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4416,61 +4425,61 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.79</v>
+        <v>1.27</v>
       </c>
       <c r="X15">
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4479,61 +4488,61 @@
         <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI15">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
@@ -4584,13 +4593,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4598,58 +4607,58 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F16">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="G16">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="H16">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="I16">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S16">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4658,61 +4667,61 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="X16">
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4721,61 +4730,61 @@
         <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
@@ -4826,13 +4835,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4840,178 +4849,178 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F17">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="G17">
+        <v>4.1</v>
+      </c>
+      <c r="H17">
         <v>1.93</v>
       </c>
-      <c r="H17">
-        <v>5.1</v>
-      </c>
       <c r="I17">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="L17">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="S17">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="T17">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="W17">
-        <v>2.06</v>
+        <v>1.32</v>
       </c>
       <c r="X17">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5068,13 +5077,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5082,178 +5091,178 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18">
+        <v>1.82</v>
+      </c>
+      <c r="G18">
+        <v>1.93</v>
+      </c>
+      <c r="H18">
+        <v>5.1</v>
+      </c>
+      <c r="I18">
+        <v>5.9</v>
+      </c>
+      <c r="J18">
+        <v>3.4</v>
+      </c>
+      <c r="K18">
+        <v>3.75</v>
+      </c>
+      <c r="L18">
+        <v>1.38</v>
+      </c>
+      <c r="M18">
+        <v>1.1</v>
+      </c>
+      <c r="N18">
+        <v>2.92</v>
+      </c>
+      <c r="O18">
+        <v>1.44</v>
+      </c>
+      <c r="P18">
+        <v>1.63</v>
+      </c>
+      <c r="Q18">
+        <v>2.28</v>
+      </c>
+      <c r="R18">
+        <v>1.24</v>
+      </c>
+      <c r="S18">
+        <v>4.3</v>
+      </c>
+      <c r="T18">
+        <v>2.06</v>
+      </c>
+      <c r="U18">
+        <v>1.78</v>
+      </c>
+      <c r="V18">
+        <v>1.2</v>
+      </c>
+      <c r="W18">
+        <v>2.06</v>
+      </c>
+      <c r="X18">
+        <v>12.5</v>
+      </c>
+      <c r="Y18">
+        <v>17</v>
+      </c>
+      <c r="Z18">
+        <v>48</v>
+      </c>
+      <c r="AA18">
         <v>180</v>
       </c>
-      <c r="F18">
-        <v>1.47</v>
-      </c>
-      <c r="G18">
-        <v>1.49</v>
-      </c>
-      <c r="H18">
+      <c r="AB18">
         <v>7.2</v>
       </c>
-      <c r="I18">
-        <v>8.4</v>
-      </c>
-      <c r="J18">
-        <v>4.9</v>
-      </c>
-      <c r="K18">
-        <v>5.1</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>4.8</v>
-      </c>
-      <c r="O18">
-        <v>1.22</v>
-      </c>
-      <c r="P18">
-        <v>2.32</v>
-      </c>
-      <c r="Q18">
-        <v>1.66</v>
-      </c>
-      <c r="R18">
-        <v>1.5</v>
-      </c>
-      <c r="S18">
-        <v>2.6</v>
-      </c>
-      <c r="T18">
-        <v>1.82</v>
-      </c>
-      <c r="U18">
-        <v>2.02</v>
-      </c>
-      <c r="V18">
-        <v>1.14</v>
-      </c>
-      <c r="W18">
-        <v>3</v>
-      </c>
-      <c r="X18">
-        <v>22</v>
-      </c>
-      <c r="Y18">
-        <v>32</v>
-      </c>
-      <c r="Z18">
-        <v>70</v>
-      </c>
-      <c r="AA18">
-        <v>270</v>
-      </c>
-      <c r="AB18">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AC18">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE18">
         <v>110</v>
       </c>
       <c r="AF18">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI18">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ18">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AK18">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AL18">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AO18">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AP18">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AQ18">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AR18">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AS18">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AT18">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AU18">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV18">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AW18">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB18">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BC18">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BD18">
-        <v>26</v>
+        <v>5.2</v>
       </c>
       <c r="BE18">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF18">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG18">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5316,7 +5325,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5324,241 +5333,241 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F19">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="H19">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L19">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R19">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="S19">
+        <v>2.68</v>
+      </c>
+      <c r="T19">
+        <v>1.82</v>
+      </c>
+      <c r="U19">
+        <v>2.02</v>
+      </c>
+      <c r="V19">
+        <v>1.14</v>
+      </c>
+      <c r="W19">
         <v>3</v>
       </c>
-      <c r="T19">
-        <v>1.76</v>
-      </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-      <c r="V19">
-        <v>1.19</v>
-      </c>
-      <c r="W19">
-        <v>2.12</v>
-      </c>
       <c r="X19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Z19">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AA19">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="AB19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC19">
         <v>11.5</v>
       </c>
-      <c r="AC19">
-        <v>11</v>
-      </c>
       <c r="AD19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE19">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AF19">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>23</v>
       </c>
       <c r="AI19">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AK19">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AL19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM19">
         <v>120</v>
       </c>
       <c r="AN19">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="AO19">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AP19">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AQ19">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AR19">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AS19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="AT19">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AV19">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AW19">
-        <v>46</v>
+        <v>9.6</v>
       </c>
       <c r="AX19">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY19">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA19">
-        <v>46</v>
+        <v>11.5</v>
       </c>
       <c r="BB19">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BC19">
         <v>13</v>
       </c>
       <c r="BD19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE19">
-        <v>70</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG19">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="BH19">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5566,241 +5575,241 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F20">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="G20">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="H20">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="J20">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="O20">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="R20">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="S20">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V20">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="X20">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Y20">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AA20">
-        <v>310</v>
+        <v>150</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AE20">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AF20">
+        <v>14</v>
+      </c>
+      <c r="AG20">
         <v>12.5</v>
       </c>
-      <c r="AG20">
-        <v>11</v>
-      </c>
       <c r="AH20">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ20">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AK20">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AL20">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM20">
         <v>120</v>
       </c>
       <c r="AN20">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AP20">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="AS20">
-        <v>5.7</v>
+        <v>80</v>
       </c>
       <c r="AT20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>14.5</v>
+      </c>
+      <c r="AW20">
+        <v>46</v>
+      </c>
+      <c r="AX20">
+        <v>8.4</v>
+      </c>
+      <c r="AY20">
+        <v>7.6</v>
+      </c>
+      <c r="AZ20">
+        <v>14</v>
+      </c>
+      <c r="BA20">
+        <v>46</v>
+      </c>
+      <c r="BB20">
+        <v>13.5</v>
+      </c>
+      <c r="BC20">
         <v>13</v>
       </c>
-      <c r="AV20">
-        <v>5</v>
-      </c>
-      <c r="AW20">
-        <v>5.5</v>
-      </c>
-      <c r="AX20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20">
+      <c r="BD20">
+        <v>24</v>
+      </c>
+      <c r="BE20">
+        <v>70</v>
+      </c>
+      <c r="BF20">
+        <v>7.8</v>
+      </c>
+      <c r="BG20">
+        <v>48</v>
+      </c>
+      <c r="BH20">
+        <v>4.3</v>
+      </c>
+      <c r="BI20">
+        <v>2.92</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>7.2</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
         <v>21</v>
       </c>
-      <c r="BA20">
-        <v>5.5</v>
-      </c>
-      <c r="BB20">
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>3.45</v>
+      </c>
+      <c r="BP20">
+        <v>14.5</v>
+      </c>
+      <c r="BQ20">
+        <v>8.6</v>
+      </c>
+      <c r="BR20">
+        <v>32</v>
+      </c>
+      <c r="BS20">
+        <v>18</v>
+      </c>
+      <c r="BT20">
         <v>10.5</v>
       </c>
-      <c r="BC20">
-        <v>12</v>
-      </c>
-      <c r="BD20">
-        <v>21</v>
-      </c>
-      <c r="BE20">
-        <v>5.5</v>
-      </c>
-      <c r="BF20">
-        <v>3.85</v>
-      </c>
-      <c r="BG20">
-        <v>5.5</v>
-      </c>
-      <c r="BH20">
+      <c r="BU20">
         <v>6.2</v>
       </c>
-      <c r="BI20">
-        <v>3.5</v>
-      </c>
-      <c r="BJ20">
-        <v>15</v>
-      </c>
-      <c r="BK20">
-        <v>2.72</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>3.3</v>
-      </c>
-      <c r="BN20">
-        <v>5.6</v>
-      </c>
-      <c r="BO20">
-        <v>3</v>
-      </c>
-      <c r="BP20">
-        <v>10.5</v>
-      </c>
-      <c r="BQ20">
-        <v>5.1</v>
-      </c>
-      <c r="BR20">
-        <v>26</v>
-      </c>
-      <c r="BS20">
-        <v>2.94</v>
-      </c>
-      <c r="BT20">
-        <v>17.5</v>
-      </c>
-      <c r="BU20">
-        <v>2.78</v>
-      </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW20">
-        <v>3.2</v>
+        <v>29</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY20">
-        <v>3.15</v>
+        <v>32</v>
       </c>
       <c r="BZ20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA20">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5808,241 +5817,241 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
         <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F21">
+        <v>1.36</v>
+      </c>
+      <c r="G21">
+        <v>1.39</v>
+      </c>
+      <c r="H21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>5.9</v>
+      </c>
+      <c r="K21">
+        <v>6.6</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.02</v>
+      </c>
+      <c r="N21">
+        <v>6.6</v>
+      </c>
+      <c r="O21">
+        <v>1.16</v>
+      </c>
+      <c r="P21">
+        <v>2.92</v>
+      </c>
+      <c r="Q21">
+        <v>1.46</v>
+      </c>
+      <c r="R21">
+        <v>1.77</v>
+      </c>
+      <c r="S21">
+        <v>2.16</v>
+      </c>
+      <c r="T21">
+        <v>1.79</v>
+      </c>
+      <c r="U21">
+        <v>2.12</v>
+      </c>
+      <c r="V21">
+        <v>1.11</v>
+      </c>
+      <c r="W21">
+        <v>3.55</v>
+      </c>
+      <c r="X21">
+        <v>40</v>
+      </c>
+      <c r="Y21">
+        <v>46</v>
+      </c>
+      <c r="Z21">
+        <v>100</v>
+      </c>
+      <c r="AA21">
+        <v>310</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>17</v>
+      </c>
+      <c r="AD21">
+        <v>40</v>
+      </c>
+      <c r="AE21">
+        <v>130</v>
+      </c>
+      <c r="AF21">
+        <v>12.5</v>
+      </c>
+      <c r="AG21">
+        <v>11</v>
+      </c>
+      <c r="AH21">
+        <v>28</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
+      </c>
+      <c r="AJ21">
+        <v>14</v>
+      </c>
+      <c r="AK21">
+        <v>16</v>
+      </c>
+      <c r="AL21">
+        <v>34</v>
+      </c>
+      <c r="AM21">
+        <v>120</v>
+      </c>
+      <c r="AN21">
+        <v>4.9</v>
+      </c>
+      <c r="AO21">
+        <v>130</v>
+      </c>
+      <c r="AP21">
+        <v>5</v>
+      </c>
+      <c r="AQ21">
+        <v>5.1</v>
+      </c>
+      <c r="AR21">
+        <v>5.5</v>
+      </c>
+      <c r="AS21">
+        <v>5.7</v>
+      </c>
+      <c r="AT21">
+        <v>11</v>
+      </c>
+      <c r="AU21">
+        <v>13</v>
+      </c>
+      <c r="AV21">
+        <v>5</v>
+      </c>
+      <c r="AW21">
+        <v>5.5</v>
+      </c>
+      <c r="AX21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21">
+        <v>21</v>
+      </c>
+      <c r="BA21">
+        <v>5.5</v>
+      </c>
+      <c r="BB21">
+        <v>10.5</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>21</v>
+      </c>
+      <c r="BE21">
+        <v>5.5</v>
+      </c>
+      <c r="BF21">
+        <v>3.85</v>
+      </c>
+      <c r="BG21">
+        <v>5.5</v>
+      </c>
+      <c r="BH21">
+        <v>6.2</v>
+      </c>
+      <c r="BI21">
+        <v>3.5</v>
+      </c>
+      <c r="BJ21">
+        <v>15</v>
+      </c>
+      <c r="BK21">
+        <v>2.72</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>3.3</v>
+      </c>
+      <c r="BN21">
+        <v>5.6</v>
+      </c>
+      <c r="BO21">
+        <v>3</v>
+      </c>
+      <c r="BP21">
+        <v>10.5</v>
+      </c>
+      <c r="BQ21">
+        <v>5.1</v>
+      </c>
+      <c r="BR21">
+        <v>26</v>
+      </c>
+      <c r="BS21">
         <v>2.94</v>
       </c>
-      <c r="G21">
-        <v>3.3</v>
-      </c>
-      <c r="H21">
-        <v>2.84</v>
-      </c>
-      <c r="I21">
-        <v>3.25</v>
-      </c>
-      <c r="J21">
-        <v>2.76</v>
-      </c>
-      <c r="K21">
+      <c r="BT21">
+        <v>17.5</v>
+      </c>
+      <c r="BU21">
+        <v>2.78</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>3.2</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
         <v>3.15</v>
       </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.13</v>
-      </c>
-      <c r="N21">
-        <v>2.28</v>
-      </c>
-      <c r="O21">
-        <v>1.66</v>
-      </c>
-      <c r="P21">
-        <v>1.44</v>
-      </c>
-      <c r="Q21">
-        <v>3</v>
-      </c>
-      <c r="R21">
-        <v>1.14</v>
-      </c>
-      <c r="S21">
-        <v>6.4</v>
-      </c>
-      <c r="T21">
-        <v>2.04</v>
-      </c>
-      <c r="U21">
-        <v>1.56</v>
-      </c>
-      <c r="V21">
-        <v>1.44</v>
-      </c>
-      <c r="W21">
-        <v>1.43</v>
-      </c>
-      <c r="X21">
-        <v>8.6</v>
-      </c>
-      <c r="Y21">
-        <v>9.4</v>
-      </c>
-      <c r="Z21">
-        <v>22</v>
-      </c>
-      <c r="AA21">
-        <v>70</v>
-      </c>
-      <c r="AB21">
-        <v>9.6</v>
-      </c>
-      <c r="AC21">
-        <v>8.4</v>
-      </c>
-      <c r="AD21">
-        <v>18</v>
-      </c>
-      <c r="AE21">
-        <v>65</v>
-      </c>
-      <c r="AF21">
-        <v>23</v>
-      </c>
-      <c r="AG21">
-        <v>18.5</v>
-      </c>
-      <c r="AH21">
-        <v>32</v>
-      </c>
-      <c r="AI21">
-        <v>110</v>
-      </c>
-      <c r="AJ21">
-        <v>75</v>
-      </c>
-      <c r="AK21">
-        <v>70</v>
-      </c>
-      <c r="AL21">
-        <v>110</v>
-      </c>
-      <c r="AM21">
-        <v>300</v>
-      </c>
-      <c r="AN21">
-        <v>95</v>
-      </c>
-      <c r="AO21">
-        <v>90</v>
-      </c>
-      <c r="AP21">
-        <v>6.2</v>
-      </c>
-      <c r="AQ21">
-        <v>5.9</v>
-      </c>
-      <c r="AR21">
+      <c r="BZ21">
         <v>13</v>
       </c>
-      <c r="AS21">
-        <v>4.1</v>
-      </c>
-      <c r="AT21">
-        <v>6</v>
-      </c>
-      <c r="AU21">
-        <v>6</v>
-      </c>
-      <c r="AV21">
-        <v>12.5</v>
-      </c>
-      <c r="AW21">
-        <v>4.1</v>
-      </c>
-      <c r="AX21">
-        <v>13.5</v>
-      </c>
-      <c r="AY21">
-        <v>11</v>
-      </c>
-      <c r="AZ21">
-        <v>3.9</v>
-      </c>
-      <c r="BA21">
-        <v>4.2</v>
-      </c>
-      <c r="BB21">
-        <v>4.2</v>
-      </c>
-      <c r="BC21">
-        <v>4.1</v>
-      </c>
-      <c r="BD21">
-        <v>4.2</v>
-      </c>
-      <c r="BE21">
-        <v>4.4</v>
-      </c>
-      <c r="BF21">
-        <v>4.2</v>
-      </c>
-      <c r="BG21">
-        <v>4.2</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.01</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.01</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.01</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.01</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.01</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.01</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.01</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.01</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>1.01</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="CB21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6050,178 +6059,178 @@
         <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
         <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22">
-        <v>1.79</v>
+        <v>2.94</v>
       </c>
       <c r="G22">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="H22">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="I22">
+        <v>3.2</v>
+      </c>
+      <c r="J22">
+        <v>2.76</v>
+      </c>
+      <c r="K22">
+        <v>3.15</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>1.01</v>
+      </c>
+      <c r="O22">
+        <v>1.64</v>
+      </c>
+      <c r="P22">
+        <v>1.42</v>
+      </c>
+      <c r="Q22">
+        <v>2.74</v>
+      </c>
+      <c r="R22">
+        <v>1.12</v>
+      </c>
+      <c r="S22">
+        <v>6.4</v>
+      </c>
+      <c r="T22">
+        <v>2.26</v>
+      </c>
+      <c r="U22">
+        <v>1.67</v>
+      </c>
+      <c r="V22">
+        <v>1.46</v>
+      </c>
+      <c r="W22">
+        <v>1.43</v>
+      </c>
+      <c r="X22">
+        <v>8.4</v>
+      </c>
+      <c r="Y22">
+        <v>9.4</v>
+      </c>
+      <c r="Z22">
+        <v>22</v>
+      </c>
+      <c r="AA22">
+        <v>70</v>
+      </c>
+      <c r="AB22">
+        <v>9.6</v>
+      </c>
+      <c r="AC22">
+        <v>8.4</v>
+      </c>
+      <c r="AD22">
+        <v>18</v>
+      </c>
+      <c r="AE22">
+        <v>65</v>
+      </c>
+      <c r="AF22">
+        <v>23</v>
+      </c>
+      <c r="AG22">
+        <v>18.5</v>
+      </c>
+      <c r="AH22">
+        <v>32</v>
+      </c>
+      <c r="AI22">
+        <v>110</v>
+      </c>
+      <c r="AJ22">
+        <v>75</v>
+      </c>
+      <c r="AK22">
+        <v>70</v>
+      </c>
+      <c r="AL22">
+        <v>110</v>
+      </c>
+      <c r="AM22">
+        <v>300</v>
+      </c>
+      <c r="AN22">
+        <v>95</v>
+      </c>
+      <c r="AO22">
+        <v>90</v>
+      </c>
+      <c r="AP22">
+        <v>6.2</v>
+      </c>
+      <c r="AQ22">
+        <v>6.6</v>
+      </c>
+      <c r="AR22">
+        <v>13</v>
+      </c>
+      <c r="AS22">
         <v>4.2</v>
       </c>
-      <c r="J22">
-        <v>4.6</v>
-      </c>
-      <c r="K22">
-        <v>5.3</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>8</v>
-      </c>
-      <c r="O22">
-        <v>1.1</v>
-      </c>
-      <c r="P22">
-        <v>3.4</v>
-      </c>
-      <c r="Q22">
-        <v>1.32</v>
-      </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22">
-        <v>1.79</v>
-      </c>
-      <c r="T22">
-        <v>1.33</v>
-      </c>
-      <c r="U22">
-        <v>3.05</v>
-      </c>
-      <c r="V22">
-        <v>1.32</v>
-      </c>
-      <c r="W22">
-        <v>2.02</v>
-      </c>
-      <c r="X22">
-        <v>60</v>
-      </c>
-      <c r="Y22">
-        <v>34</v>
-      </c>
-      <c r="Z22">
-        <v>50</v>
-      </c>
-      <c r="AA22">
-        <v>85</v>
-      </c>
-      <c r="AB22">
-        <v>23</v>
-      </c>
-      <c r="AC22">
-        <v>14.5</v>
-      </c>
-      <c r="AD22">
-        <v>19</v>
-      </c>
-      <c r="AE22">
-        <v>36</v>
-      </c>
-      <c r="AF22">
-        <v>21</v>
-      </c>
-      <c r="AG22">
-        <v>13</v>
-      </c>
-      <c r="AH22">
-        <v>15.5</v>
-      </c>
-      <c r="AI22">
-        <v>32</v>
-      </c>
-      <c r="AJ22">
-        <v>26</v>
-      </c>
-      <c r="AK22">
-        <v>17.5</v>
-      </c>
-      <c r="AL22">
-        <v>22</v>
-      </c>
-      <c r="AM22">
-        <v>48</v>
-      </c>
-      <c r="AN22">
-        <v>5.9</v>
-      </c>
-      <c r="AO22">
-        <v>17.5</v>
-      </c>
-      <c r="AP22">
-        <v>32</v>
-      </c>
-      <c r="AQ22">
-        <v>19</v>
-      </c>
-      <c r="AR22">
-        <v>24</v>
-      </c>
-      <c r="AS22">
-        <v>40</v>
-      </c>
       <c r="AT22">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AU22">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AV22">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AX22">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY22">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ22">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA22">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB22">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BC22">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BD22">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE22">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BF22">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BG22">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6284,186 +6293,186 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F23">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="G23">
-        <v>3.85</v>
+        <v>1.98</v>
       </c>
       <c r="H23">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="I23">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="K23">
+        <v>5.3</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>8</v>
+      </c>
+      <c r="O23">
+        <v>1.1</v>
+      </c>
+      <c r="P23">
+        <v>3.4</v>
+      </c>
+      <c r="Q23">
+        <v>1.33</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23">
+        <v>1.79</v>
+      </c>
+      <c r="T23">
+        <v>1.33</v>
+      </c>
+      <c r="U23">
+        <v>3.05</v>
+      </c>
+      <c r="V23">
+        <v>1.32</v>
+      </c>
+      <c r="W23">
+        <v>2.02</v>
+      </c>
+      <c r="X23">
+        <v>60</v>
+      </c>
+      <c r="Y23">
+        <v>34</v>
+      </c>
+      <c r="Z23">
+        <v>50</v>
+      </c>
+      <c r="AA23">
+        <v>85</v>
+      </c>
+      <c r="AB23">
+        <v>23</v>
+      </c>
+      <c r="AC23">
+        <v>14.5</v>
+      </c>
+      <c r="AD23">
+        <v>19</v>
+      </c>
+      <c r="AE23">
+        <v>36</v>
+      </c>
+      <c r="AF23">
+        <v>21</v>
+      </c>
+      <c r="AG23">
+        <v>13</v>
+      </c>
+      <c r="AH23">
+        <v>15.5</v>
+      </c>
+      <c r="AI23">
+        <v>32</v>
+      </c>
+      <c r="AJ23">
+        <v>26</v>
+      </c>
+      <c r="AK23">
+        <v>17.5</v>
+      </c>
+      <c r="AL23">
+        <v>22</v>
+      </c>
+      <c r="AM23">
+        <v>48</v>
+      </c>
+      <c r="AN23">
+        <v>5.9</v>
+      </c>
+      <c r="AO23">
+        <v>17.5</v>
+      </c>
+      <c r="AP23">
+        <v>32</v>
+      </c>
+      <c r="AQ23">
+        <v>19</v>
+      </c>
+      <c r="AR23">
+        <v>24</v>
+      </c>
+      <c r="AS23">
+        <v>40</v>
+      </c>
+      <c r="AT23">
+        <v>18</v>
+      </c>
+      <c r="AU23">
+        <v>11.5</v>
+      </c>
+      <c r="AV23">
+        <v>15.5</v>
+      </c>
+      <c r="AW23">
+        <v>21</v>
+      </c>
+      <c r="AX23">
+        <v>16.5</v>
+      </c>
+      <c r="AY23">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23">
+        <v>12.5</v>
+      </c>
+      <c r="BA23">
+        <v>18.5</v>
+      </c>
+      <c r="BB23">
+        <v>20</v>
+      </c>
+      <c r="BC23">
+        <v>14</v>
+      </c>
+      <c r="BD23">
+        <v>17.5</v>
+      </c>
+      <c r="BE23">
+        <v>23</v>
+      </c>
+      <c r="BF23">
         <v>5</v>
       </c>
-      <c r="L23">
-        <v>1.01</v>
-      </c>
-      <c r="M23">
-        <v>1.01</v>
-      </c>
-      <c r="N23">
-        <v>5.3</v>
-      </c>
-      <c r="O23">
-        <v>1.17</v>
-      </c>
-      <c r="P23">
-        <v>2.48</v>
-      </c>
-      <c r="Q23">
-        <v>1.53</v>
-      </c>
-      <c r="R23">
-        <v>1.57</v>
-      </c>
-      <c r="S23">
-        <v>2.34</v>
-      </c>
-      <c r="T23">
-        <v>1.53</v>
-      </c>
-      <c r="U23">
-        <v>2.5</v>
-      </c>
-      <c r="V23">
-        <v>1.83</v>
-      </c>
-      <c r="W23">
-        <v>1.35</v>
-      </c>
-      <c r="X23">
-        <v>30</v>
-      </c>
-      <c r="Y23">
-        <v>15</v>
-      </c>
-      <c r="Z23">
-        <v>17</v>
-      </c>
-      <c r="AA23">
-        <v>26</v>
-      </c>
-      <c r="AB23">
-        <v>21</v>
-      </c>
-      <c r="AC23">
-        <v>11</v>
-      </c>
-      <c r="AD23">
-        <v>12</v>
-      </c>
-      <c r="AE23">
-        <v>20</v>
-      </c>
-      <c r="AF23">
-        <v>32</v>
-      </c>
-      <c r="AG23">
-        <v>16</v>
-      </c>
-      <c r="AH23">
-        <v>16</v>
-      </c>
-      <c r="AI23">
-        <v>28</v>
-      </c>
-      <c r="AJ23">
-        <v>70</v>
-      </c>
-      <c r="AK23">
-        <v>36</v>
-      </c>
-      <c r="AL23">
-        <v>38</v>
-      </c>
-      <c r="AM23">
-        <v>70</v>
-      </c>
-      <c r="AN23">
-        <v>25</v>
-      </c>
-      <c r="AO23">
-        <v>10.5</v>
-      </c>
-      <c r="AP23">
-        <v>19.5</v>
-      </c>
-      <c r="AQ23">
-        <v>12</v>
-      </c>
-      <c r="AR23">
-        <v>13.5</v>
-      </c>
-      <c r="AS23">
-        <v>21</v>
-      </c>
-      <c r="AT23">
-        <v>16.5</v>
-      </c>
-      <c r="AU23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV23">
-        <v>9.6</v>
-      </c>
-      <c r="AW23">
-        <v>16</v>
-      </c>
-      <c r="AX23">
-        <v>25</v>
-      </c>
-      <c r="AY23">
-        <v>13</v>
-      </c>
-      <c r="AZ23">
-        <v>13</v>
-      </c>
-      <c r="BA23">
-        <v>22</v>
-      </c>
-      <c r="BB23">
-        <v>50</v>
-      </c>
-      <c r="BC23">
-        <v>29</v>
-      </c>
-      <c r="BD23">
-        <v>30</v>
-      </c>
-      <c r="BE23">
-        <v>48</v>
-      </c>
-      <c r="BF23">
-        <v>20</v>
-      </c>
       <c r="BG23">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6526,42 +6535,42 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F24">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="G24">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H24">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="I24">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J24">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="K24">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6570,142 +6579,142 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="O24">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q24">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="S24">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="W24">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6768,7 +6777,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6776,34 +6785,34 @@
         <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F25">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>3.4</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="I25">
-        <v>110</v>
+        <v>2.58</v>
       </c>
       <c r="J25">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="K25">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6812,22 +6821,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O25">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="Q25">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="R25">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="S25">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6836,10 +6845,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7010,42 +7019,42 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F26">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="J26">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="K26">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7054,22 +7063,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
+        <v>1.26</v>
+      </c>
+      <c r="O26">
+        <v>1.07</v>
+      </c>
+      <c r="P26">
+        <v>1.26</v>
+      </c>
+      <c r="Q26">
+        <v>1.07</v>
+      </c>
+      <c r="R26">
         <v>1.25</v>
       </c>
-      <c r="O26">
-        <v>1.09</v>
-      </c>
-      <c r="P26">
-        <v>1.25</v>
-      </c>
-      <c r="Q26">
-        <v>1.09</v>
-      </c>
-      <c r="R26">
-        <v>1.24</v>
-      </c>
       <c r="S26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7078,10 +7087,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7252,42 +7261,42 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F27">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G27">
         <v>1000</v>
       </c>
       <c r="H27">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="K27">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7296,19 +7305,19 @@
         <v>1.01</v>
       </c>
       <c r="N27">
+        <v>1.01</v>
+      </c>
+      <c r="O27">
+        <v>1.09</v>
+      </c>
+      <c r="P27">
+        <v>1.26</v>
+      </c>
+      <c r="Q27">
+        <v>1.09</v>
+      </c>
+      <c r="R27">
         <v>1.25</v>
-      </c>
-      <c r="O27">
-        <v>1.1</v>
-      </c>
-      <c r="P27">
-        <v>1.25</v>
-      </c>
-      <c r="Q27">
-        <v>1.1</v>
-      </c>
-      <c r="R27">
-        <v>1.24</v>
       </c>
       <c r="S27">
         <v>1.1</v>
@@ -7320,7 +7329,7 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W27">
         <v>1.01</v>
@@ -7494,40 +7503,40 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F28">
         <v>1.1</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H28">
+        <v>1.12</v>
+      </c>
+      <c r="I28">
+        <v>140</v>
+      </c>
+      <c r="J28">
         <v>1.1</v>
       </c>
-      <c r="I28">
-        <v>110</v>
-      </c>
-      <c r="J28">
-        <v>1.14</v>
-      </c>
       <c r="K28">
         <v>1000</v>
       </c>
@@ -7538,22 +7547,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
+        <v>1.26</v>
+      </c>
+      <c r="O28">
+        <v>1.09</v>
+      </c>
+      <c r="P28">
+        <v>1.26</v>
+      </c>
+      <c r="Q28">
+        <v>1.09</v>
+      </c>
+      <c r="R28">
         <v>1.25</v>
       </c>
-      <c r="O28">
-        <v>1.1</v>
-      </c>
-      <c r="P28">
-        <v>1.25</v>
-      </c>
-      <c r="Q28">
-        <v>1.1</v>
-      </c>
-      <c r="R28">
-        <v>1.24</v>
-      </c>
       <c r="S28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7562,10 +7571,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7736,7 +7745,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7744,34 +7753,34 @@
         <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7780,34 +7789,34 @@
         <v>1.01</v>
       </c>
       <c r="N29">
+        <v>1.01</v>
+      </c>
+      <c r="O29">
+        <v>1.1</v>
+      </c>
+      <c r="P29">
+        <v>1.26</v>
+      </c>
+      <c r="Q29">
+        <v>1.1</v>
+      </c>
+      <c r="R29">
         <v>1.25</v>
       </c>
-      <c r="O29">
+      <c r="S29">
+        <v>1.11</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
         <v>1.08</v>
       </c>
-      <c r="P29">
-        <v>1.25</v>
-      </c>
-      <c r="Q29">
-        <v>1.08</v>
-      </c>
-      <c r="R29">
-        <v>1.24</v>
-      </c>
-      <c r="S29">
-        <v>1.08</v>
-      </c>
-      <c r="T29">
-        <v>1.01</v>
-      </c>
-      <c r="U29">
-        <v>1.01</v>
-      </c>
-      <c r="V29">
-        <v>1.01</v>
-      </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7978,7 +7987,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7986,34 +7995,34 @@
         <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F30">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8022,142 +8031,142 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="P30">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="Q30">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="R30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="T30">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="W30">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8220,186 +8229,186 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
         <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F31">
-        <v>1.71</v>
+        <v>3.45</v>
       </c>
       <c r="G31">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="H31">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="I31">
-        <v>6.4</v>
+        <v>2.22</v>
       </c>
       <c r="J31">
         <v>3.45</v>
       </c>
       <c r="K31">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P31">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="Q31">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="R31">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S31">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.18</v>
+        <v>1.81</v>
       </c>
       <c r="W31">
-        <v>1.98</v>
+        <v>1.29</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP31">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR31">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT31">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU31">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV31">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW31">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX31">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY31">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ31">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA31">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB31">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC31">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD31">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE31">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8462,66 +8471,66 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
         <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F32">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="G32">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="H32">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="I32">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M32">
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="P32">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="Q32">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="R32">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S32">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8530,118 +8539,118 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W32">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="X32">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8704,186 +8713,186 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F33">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="G33">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="H33">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="I33">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="L33">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N33">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="O33">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P33">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="R33">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S33">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="T33">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W33">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="X33">
+        <v>24</v>
+      </c>
+      <c r="Y33">
+        <v>28</v>
+      </c>
+      <c r="Z33">
+        <v>60</v>
+      </c>
+      <c r="AA33">
+        <v>180</v>
+      </c>
+      <c r="AB33">
+        <v>12</v>
+      </c>
+      <c r="AC33">
+        <v>12</v>
+      </c>
+      <c r="AD33">
+        <v>27</v>
+      </c>
+      <c r="AE33">
+        <v>90</v>
+      </c>
+      <c r="AF33">
         <v>12.5</v>
       </c>
-      <c r="Y33">
-        <v>13</v>
-      </c>
-      <c r="Z33">
-        <v>38</v>
-      </c>
-      <c r="AA33">
-        <v>100</v>
-      </c>
-      <c r="AB33">
-        <v>9.4</v>
-      </c>
-      <c r="AC33">
-        <v>7.6</v>
-      </c>
-      <c r="AD33">
-        <v>15.5</v>
-      </c>
-      <c r="AE33">
-        <v>60</v>
-      </c>
-      <c r="AF33">
-        <v>14.5</v>
-      </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH33">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI33">
         <v>85</v>
       </c>
       <c r="AJ33">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AK33">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AL33">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM33">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN33">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AO33">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AP33">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ33">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AR33">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="AS33">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AT33">
+        <v>7.8</v>
+      </c>
+      <c r="AU33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV33">
+        <v>17.5</v>
+      </c>
+      <c r="AW33">
+        <v>4.8</v>
+      </c>
+      <c r="AX33">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU33">
-        <v>6.6</v>
-      </c>
-      <c r="AV33">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW33">
-        <v>27</v>
-      </c>
-      <c r="AX33">
-        <v>12.5</v>
-      </c>
       <c r="AY33">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ33">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BA33">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BB33">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BC33">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BD33">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BE33">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF33">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG33">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8946,7 +8955,7 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8954,179 +8963,179 @@
         <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
         <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F34">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="G34">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="H34">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="I34">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="J34">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M34">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O34">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P34">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q34">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="R34">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="T34">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="X34">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y34">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z34">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA34">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB34">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AC34">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD34">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE34">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF34">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH34">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AI34">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ34">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AK34">
         <v>27</v>
       </c>
       <c r="AL34">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AM34">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN34">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO34">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AP34">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AQ34">
+        <v>11</v>
+      </c>
+      <c r="AR34">
+        <v>15</v>
+      </c>
+      <c r="AS34">
+        <v>9.4</v>
+      </c>
+      <c r="AT34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU34">
+        <v>6.6</v>
+      </c>
+      <c r="AV34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW34">
+        <v>27</v>
+      </c>
+      <c r="AX34">
         <v>12.5</v>
       </c>
-      <c r="AR34">
-        <v>17.5</v>
-      </c>
-      <c r="AS34">
-        <v>38</v>
-      </c>
-      <c r="AT34">
-        <v>11.5</v>
-      </c>
-      <c r="AU34">
-        <v>7.6</v>
-      </c>
-      <c r="AV34">
-        <v>12</v>
-      </c>
-      <c r="AW34">
-        <v>26</v>
-      </c>
-      <c r="AX34">
-        <v>16</v>
-      </c>
       <c r="AY34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BA34">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BB34">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BC34">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE34">
+        <v>9.6</v>
+      </c>
+      <c r="BF34">
+        <v>13.5</v>
+      </c>
+      <c r="BG34">
         <v>30</v>
       </c>
-      <c r="BE34">
-        <v>32</v>
-      </c>
-      <c r="BF34">
-        <v>15.5</v>
-      </c>
-      <c r="BG34">
-        <v>20</v>
-      </c>
       <c r="BH34">
         <v>1000</v>
       </c>
@@ -9188,7 +9197,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9196,178 +9205,178 @@
         <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F35">
+        <v>2.58</v>
+      </c>
+      <c r="G35">
+        <v>2.62</v>
+      </c>
+      <c r="H35">
+        <v>2.94</v>
+      </c>
+      <c r="I35">
+        <v>2.98</v>
+      </c>
+      <c r="J35">
+        <v>3.6</v>
+      </c>
+      <c r="K35">
+        <v>3.65</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.05</v>
+      </c>
+      <c r="N35">
+        <v>4.4</v>
+      </c>
+      <c r="O35">
+        <v>1.25</v>
+      </c>
+      <c r="P35">
+        <v>2.16</v>
+      </c>
+      <c r="Q35">
+        <v>1.76</v>
+      </c>
+      <c r="R35">
+        <v>1.45</v>
+      </c>
+      <c r="S35">
+        <v>2.94</v>
+      </c>
+      <c r="T35">
+        <v>1.64</v>
+      </c>
+      <c r="U35">
         <v>2.38</v>
       </c>
-      <c r="G35">
-        <v>2.42</v>
-      </c>
-      <c r="H35">
-        <v>3.65</v>
-      </c>
-      <c r="I35">
-        <v>3.75</v>
-      </c>
-      <c r="J35">
-        <v>3.15</v>
-      </c>
-      <c r="K35">
-        <v>3.2</v>
-      </c>
-      <c r="L35">
-        <v>1.01</v>
-      </c>
-      <c r="M35">
-        <v>1.11</v>
-      </c>
-      <c r="N35">
-        <v>3.1</v>
-      </c>
-      <c r="O35">
-        <v>1.45</v>
-      </c>
-      <c r="P35">
-        <v>1.69</v>
-      </c>
-      <c r="Q35">
-        <v>2.36</v>
-      </c>
-      <c r="R35">
-        <v>1.25</v>
-      </c>
-      <c r="S35">
-        <v>4.6</v>
-      </c>
-      <c r="T35">
-        <v>1.98</v>
-      </c>
-      <c r="U35">
-        <v>1.96</v>
-      </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="Y35">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z35">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA35">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AB35">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AC35">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE35">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF35">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AG35">
         <v>12</v>
       </c>
       <c r="AH35">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI35">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AJ35">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK35">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL35">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM35">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AN35">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AO35">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AP35">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AQ35">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR35">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS35">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT35">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU35">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW35">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AX35">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AY35">
         <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA35">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BB35">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC35">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BD35">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BE35">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF35">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BG35">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9430,186 +9439,186 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
         <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F36">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="G36">
-        <v>110</v>
+        <v>2.42</v>
       </c>
       <c r="H36">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="I36">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J36">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K36">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N36">
+        <v>3.1</v>
+      </c>
+      <c r="O36">
+        <v>1.45</v>
+      </c>
+      <c r="P36">
+        <v>1.69</v>
+      </c>
+      <c r="Q36">
+        <v>2.4</v>
+      </c>
+      <c r="R36">
         <v>1.25</v>
       </c>
-      <c r="O36">
-        <v>1.06</v>
-      </c>
-      <c r="P36">
-        <v>1.25</v>
-      </c>
-      <c r="Q36">
-        <v>1.06</v>
-      </c>
-      <c r="R36">
-        <v>1.24</v>
-      </c>
       <c r="S36">
-        <v>1.06</v>
+        <v>4.7</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V36">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW36">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9672,42 +9681,42 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F37">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="G37">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H37">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="I37">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="K37">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9716,22 +9725,22 @@
         <v>1.01</v>
       </c>
       <c r="N37">
+        <v>1.01</v>
+      </c>
+      <c r="O37">
+        <v>1.06</v>
+      </c>
+      <c r="P37">
+        <v>1.26</v>
+      </c>
+      <c r="Q37">
+        <v>1.06</v>
+      </c>
+      <c r="R37">
         <v>1.25</v>
       </c>
-      <c r="O37">
-        <v>1.15</v>
-      </c>
-      <c r="P37">
-        <v>1.25</v>
-      </c>
-      <c r="Q37">
-        <v>1.15</v>
-      </c>
-      <c r="R37">
-        <v>1.24</v>
-      </c>
       <c r="S37">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="T37">
         <v>1.01</v>
@@ -9740,10 +9749,10 @@
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9914,7 +9923,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9922,34 +9931,34 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E38" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9958,22 +9967,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
+        <v>1.26</v>
+      </c>
+      <c r="O38">
+        <v>1.15</v>
+      </c>
+      <c r="P38">
+        <v>1.26</v>
+      </c>
+      <c r="Q38">
+        <v>1.15</v>
+      </c>
+      <c r="R38">
         <v>1.25</v>
       </c>
-      <c r="O38">
-        <v>1.05</v>
-      </c>
-      <c r="P38">
-        <v>1.25</v>
-      </c>
-      <c r="Q38">
-        <v>1.05</v>
-      </c>
-      <c r="R38">
-        <v>1.24</v>
-      </c>
       <c r="S38">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -9982,10 +9991,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W38">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10156,186 +10165,186 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E39" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>1.01</v>
+      </c>
+      <c r="M39">
+        <v>1.01</v>
+      </c>
+      <c r="N39">
+        <v>1.26</v>
+      </c>
+      <c r="O39">
+        <v>1.05</v>
+      </c>
+      <c r="P39">
+        <v>1.26</v>
+      </c>
+      <c r="Q39">
+        <v>1.05</v>
+      </c>
+      <c r="R39">
         <v>1.25</v>
       </c>
-      <c r="J39">
-        <v>6.8</v>
-      </c>
-      <c r="K39">
-        <v>7.4</v>
-      </c>
-      <c r="L39">
-        <v>1.01</v>
-      </c>
-      <c r="M39">
-        <v>1.03</v>
-      </c>
-      <c r="N39">
-        <v>5</v>
-      </c>
-      <c r="O39">
-        <v>1.2</v>
-      </c>
-      <c r="P39">
-        <v>2.4</v>
-      </c>
-      <c r="Q39">
-        <v>1.61</v>
-      </c>
-      <c r="R39">
-        <v>1.56</v>
-      </c>
       <c r="S39">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="T39">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U39">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y39">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD39">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ39">
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AL39">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM39">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AO39">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR39">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AV39">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BA39">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10344,240 +10353,240 @@
         <v>1.01</v>
       </c>
       <c r="BJ39">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN39">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BO39">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP39">
         <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BV39">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX39">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
         <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F40">
-        <v>1.36</v>
+        <v>16.5</v>
       </c>
       <c r="G40">
-        <v>1.38</v>
+        <v>18</v>
       </c>
       <c r="H40">
-        <v>10</v>
+        <v>1.24</v>
       </c>
       <c r="I40">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="J40">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="L40">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N40">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P40">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q40">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="R40">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="S40">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="T40">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U40">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V40">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>3.6</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>25</v>
       </c>
       <c r="Y40">
+        <v>9.4</v>
+      </c>
+      <c r="Z40">
+        <v>7.8</v>
+      </c>
+      <c r="AA40">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AB40">
+        <v>55</v>
+      </c>
+      <c r="AC40">
+        <v>16</v>
+      </c>
+      <c r="AD40">
+        <v>12</v>
+      </c>
+      <c r="AE40">
+        <v>15</v>
+      </c>
+      <c r="AF40">
+        <v>180</v>
+      </c>
+      <c r="AG40">
+        <v>65</v>
+      </c>
+      <c r="AH40">
         <v>40</v>
       </c>
-      <c r="Z40">
-        <v>130</v>
-      </c>
-      <c r="AA40">
-        <v>540</v>
-      </c>
-      <c r="AB40">
-        <v>10.5</v>
-      </c>
-      <c r="AC40">
-        <v>15.5</v>
-      </c>
-      <c r="AD40">
-        <v>48</v>
-      </c>
-      <c r="AE40">
-        <v>230</v>
-      </c>
-      <c r="AF40">
-        <v>8.4</v>
-      </c>
-      <c r="AG40">
+      <c r="AI40">
+        <v>50</v>
+      </c>
+      <c r="AJ40">
+        <v>990</v>
+      </c>
+      <c r="AK40">
+        <v>360</v>
+      </c>
+      <c r="AL40">
+        <v>260</v>
+      </c>
+      <c r="AM40">
+        <v>250</v>
+      </c>
+      <c r="AN40">
+        <v>500</v>
+      </c>
+      <c r="AO40">
+        <v>4.6</v>
+      </c>
+      <c r="AP40">
+        <v>20</v>
+      </c>
+      <c r="AQ40">
+        <v>7.8</v>
+      </c>
+      <c r="AR40">
+        <v>6.8</v>
+      </c>
+      <c r="AS40">
+        <v>8</v>
+      </c>
+      <c r="AT40">
+        <v>40</v>
+      </c>
+      <c r="AU40">
+        <v>13.5</v>
+      </c>
+      <c r="AV40">
+        <v>10</v>
+      </c>
+      <c r="AW40">
         <v>13</v>
       </c>
-      <c r="AH40">
-        <v>38</v>
-      </c>
-      <c r="AI40">
-        <v>180</v>
-      </c>
-      <c r="AJ40">
-        <v>13</v>
-      </c>
-      <c r="AK40">
-        <v>18.5</v>
-      </c>
-      <c r="AL40">
+      <c r="AX40">
+        <v>11</v>
+      </c>
+      <c r="AY40">
         <v>50</v>
       </c>
-      <c r="AM40">
-        <v>220</v>
-      </c>
-      <c r="AN40">
-        <v>5.9</v>
-      </c>
-      <c r="AO40">
-        <v>330</v>
-      </c>
-      <c r="AP40">
-        <v>15</v>
-      </c>
-      <c r="AQ40">
-        <v>4.7</v>
-      </c>
-      <c r="AR40">
-        <v>5.1</v>
-      </c>
-      <c r="AS40">
-        <v>5.3</v>
-      </c>
-      <c r="AT40">
-        <v>6.4</v>
-      </c>
-      <c r="AU40">
-        <v>10.5</v>
-      </c>
-      <c r="AV40">
-        <v>4.8</v>
-      </c>
-      <c r="AW40">
-        <v>5.2</v>
-      </c>
-      <c r="AX40">
-        <v>6</v>
-      </c>
-      <c r="AY40">
-        <v>8</v>
-      </c>
       <c r="AZ40">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BA40">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB40">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BC40">
         <v>11</v>
       </c>
       <c r="BD40">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BE40">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BF40">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG40">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10586,10 +10595,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ40">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BK40">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL40">
         <v>1000</v>
@@ -10598,291 +10607,533 @@
         <v>21</v>
       </c>
       <c r="BN40">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="BO40">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="BP40">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
+        <v>21</v>
+      </c>
+      <c r="BR40">
+        <v>1000</v>
+      </c>
+      <c r="BS40">
+        <v>21</v>
+      </c>
+      <c r="BT40">
         <v>4.9</v>
       </c>
-      <c r="BR40">
+      <c r="BU40">
+        <v>2.54</v>
+      </c>
+      <c r="BV40">
+        <v>9.6</v>
+      </c>
+      <c r="BW40">
+        <v>4.4</v>
+      </c>
+      <c r="BX40">
         <v>36</v>
       </c>
-      <c r="BS40">
+      <c r="BY40">
         <v>14.5</v>
       </c>
-      <c r="BT40">
-        <v>20</v>
-      </c>
-      <c r="BU40">
-        <v>8.4</v>
-      </c>
-      <c r="BV40">
-        <v>1000</v>
-      </c>
-      <c r="BW40">
-        <v>21</v>
-      </c>
-      <c r="BX40">
-        <v>1000</v>
-      </c>
-      <c r="BY40">
-        <v>21</v>
-      </c>
       <c r="BZ40">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="CA40">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="CB40" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
         <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F41">
+        <v>1.36</v>
+      </c>
+      <c r="G41">
+        <v>1.38</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>12.5</v>
+      </c>
+      <c r="J41">
+        <v>5.3</v>
+      </c>
+      <c r="K41">
+        <v>5.9</v>
+      </c>
+      <c r="L41">
+        <v>1.31</v>
+      </c>
+      <c r="M41">
+        <v>1.05</v>
+      </c>
+      <c r="N41">
+        <v>4.5</v>
+      </c>
+      <c r="O41">
+        <v>1.22</v>
+      </c>
+      <c r="P41">
+        <v>2.26</v>
+      </c>
+      <c r="Q41">
+        <v>1.69</v>
+      </c>
+      <c r="R41">
+        <v>1.46</v>
+      </c>
+      <c r="S41">
+        <v>2.74</v>
+      </c>
+      <c r="T41">
+        <v>2.08</v>
+      </c>
+      <c r="U41">
+        <v>1.75</v>
+      </c>
+      <c r="V41">
+        <v>1.1</v>
+      </c>
+      <c r="W41">
+        <v>3.6</v>
+      </c>
+      <c r="X41">
+        <v>25</v>
+      </c>
+      <c r="Y41">
+        <v>40</v>
+      </c>
+      <c r="Z41">
+        <v>130</v>
+      </c>
+      <c r="AA41">
+        <v>540</v>
+      </c>
+      <c r="AB41">
+        <v>10.5</v>
+      </c>
+      <c r="AC41">
+        <v>15.5</v>
+      </c>
+      <c r="AD41">
+        <v>48</v>
+      </c>
+      <c r="AE41">
+        <v>230</v>
+      </c>
+      <c r="AF41">
+        <v>8.4</v>
+      </c>
+      <c r="AG41">
+        <v>13</v>
+      </c>
+      <c r="AH41">
+        <v>38</v>
+      </c>
+      <c r="AI41">
+        <v>180</v>
+      </c>
+      <c r="AJ41">
+        <v>13</v>
+      </c>
+      <c r="AK41">
+        <v>18.5</v>
+      </c>
+      <c r="AL41">
+        <v>50</v>
+      </c>
+      <c r="AM41">
+        <v>220</v>
+      </c>
+      <c r="AN41">
+        <v>5.9</v>
+      </c>
+      <c r="AO41">
+        <v>330</v>
+      </c>
+      <c r="AP41">
+        <v>15</v>
+      </c>
+      <c r="AQ41">
+        <v>4.7</v>
+      </c>
+      <c r="AR41">
+        <v>5.1</v>
+      </c>
+      <c r="AS41">
+        <v>5.3</v>
+      </c>
+      <c r="AT41">
+        <v>6.4</v>
+      </c>
+      <c r="AU41">
+        <v>10.5</v>
+      </c>
+      <c r="AV41">
+        <v>4.8</v>
+      </c>
+      <c r="AW41">
+        <v>5.2</v>
+      </c>
+      <c r="AX41">
+        <v>6</v>
+      </c>
+      <c r="AY41">
+        <v>8</v>
+      </c>
+      <c r="AZ41">
+        <v>4.7</v>
+      </c>
+      <c r="BA41">
+        <v>5.2</v>
+      </c>
+      <c r="BB41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC41">
+        <v>11</v>
+      </c>
+      <c r="BD41">
+        <v>4.8</v>
+      </c>
+      <c r="BE41">
+        <v>5.2</v>
+      </c>
+      <c r="BF41">
+        <v>4.3</v>
+      </c>
+      <c r="BG41">
+        <v>5.3</v>
+      </c>
+      <c r="BH41">
+        <v>1000</v>
+      </c>
+      <c r="BI41">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41">
+        <v>18</v>
+      </c>
+      <c r="BK41">
+        <v>1.01</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>1.01</v>
+      </c>
+      <c r="BN41">
+        <v>5.1</v>
+      </c>
+      <c r="BO41">
+        <v>2.6</v>
+      </c>
+      <c r="BP41">
+        <v>11</v>
+      </c>
+      <c r="BQ41">
+        <v>4.9</v>
+      </c>
+      <c r="BR41">
+        <v>36</v>
+      </c>
+      <c r="BS41">
+        <v>1.01</v>
+      </c>
+      <c r="BT41">
+        <v>20</v>
+      </c>
+      <c r="BU41">
+        <v>1.01</v>
+      </c>
+      <c r="BV41">
+        <v>1000</v>
+      </c>
+      <c r="BW41">
+        <v>1.01</v>
+      </c>
+      <c r="BX41">
+        <v>1000</v>
+      </c>
+      <c r="BY41">
+        <v>1.01</v>
+      </c>
+      <c r="BZ41">
+        <v>18.5</v>
+      </c>
+      <c r="CA41">
+        <v>1.01</v>
+      </c>
+      <c r="CB41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:80">
+      <c r="A42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42">
         <v>2.36</v>
       </c>
-      <c r="G41">
+      <c r="G42">
         <v>2.56</v>
       </c>
-      <c r="H41">
+      <c r="H42">
         <v>3.65</v>
       </c>
-      <c r="I41">
+      <c r="I42">
         <v>4.1</v>
       </c>
-      <c r="J41">
+      <c r="J42">
         <v>2.86</v>
       </c>
-      <c r="K41">
+      <c r="K42">
         <v>3.1</v>
       </c>
-      <c r="L41">
-        <v>1.63</v>
-      </c>
-      <c r="M41">
-        <v>1.01</v>
-      </c>
-      <c r="N41">
+      <c r="L42">
+        <v>1.01</v>
+      </c>
+      <c r="M42">
+        <v>1.01</v>
+      </c>
+      <c r="N42">
         <v>1.45</v>
       </c>
-      <c r="O41">
+      <c r="O42">
         <v>1.59</v>
       </c>
-      <c r="P41">
+      <c r="P42">
         <v>1.45</v>
       </c>
-      <c r="Q41">
+      <c r="Q42">
         <v>2.8</v>
       </c>
-      <c r="R41">
-        <v>1.12</v>
-      </c>
-      <c r="S41">
+      <c r="R42">
+        <v>1.14</v>
+      </c>
+      <c r="S42">
         <v>2.8</v>
       </c>
-      <c r="T41">
-        <v>1.01</v>
-      </c>
-      <c r="U41">
+      <c r="T42">
+        <v>2.18</v>
+      </c>
+      <c r="U42">
         <v>1.65</v>
       </c>
-      <c r="V41">
+      <c r="V42">
         <v>1.32</v>
       </c>
-      <c r="W41">
+      <c r="W42">
         <v>1.64</v>
       </c>
-      <c r="X41">
-        <v>1000</v>
-      </c>
-      <c r="Y41">
-        <v>1000</v>
-      </c>
-      <c r="Z41">
-        <v>1000</v>
-      </c>
-      <c r="AA41">
-        <v>1000</v>
-      </c>
-      <c r="AB41">
-        <v>1000</v>
-      </c>
-      <c r="AC41">
-        <v>1000</v>
-      </c>
-      <c r="AD41">
-        <v>1000</v>
-      </c>
-      <c r="AE41">
-        <v>1000</v>
-      </c>
-      <c r="AF41">
-        <v>1000</v>
-      </c>
-      <c r="AG41">
-        <v>1000</v>
-      </c>
-      <c r="AH41">
-        <v>1000</v>
-      </c>
-      <c r="AI41">
-        <v>1000</v>
-      </c>
-      <c r="AJ41">
-        <v>1000</v>
-      </c>
-      <c r="AK41">
-        <v>1000</v>
-      </c>
-      <c r="AL41">
-        <v>1000</v>
-      </c>
-      <c r="AM41">
-        <v>1000</v>
-      </c>
-      <c r="AN41">
-        <v>1000</v>
-      </c>
-      <c r="AO41">
-        <v>1000</v>
-      </c>
-      <c r="AP41">
+      <c r="X42">
+        <v>1000</v>
+      </c>
+      <c r="Y42">
+        <v>1000</v>
+      </c>
+      <c r="Z42">
+        <v>1000</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
+        <v>1000</v>
+      </c>
+      <c r="AC42">
+        <v>1000</v>
+      </c>
+      <c r="AD42">
+        <v>1000</v>
+      </c>
+      <c r="AE42">
+        <v>1000</v>
+      </c>
+      <c r="AF42">
+        <v>1000</v>
+      </c>
+      <c r="AG42">
+        <v>1000</v>
+      </c>
+      <c r="AH42">
+        <v>1000</v>
+      </c>
+      <c r="AI42">
+        <v>1000</v>
+      </c>
+      <c r="AJ42">
+        <v>1000</v>
+      </c>
+      <c r="AK42">
+        <v>1000</v>
+      </c>
+      <c r="AL42">
+        <v>1000</v>
+      </c>
+      <c r="AM42">
+        <v>1000</v>
+      </c>
+      <c r="AN42">
+        <v>1000</v>
+      </c>
+      <c r="AO42">
+        <v>1000</v>
+      </c>
+      <c r="AP42">
         <v>6.4</v>
       </c>
-      <c r="AQ41">
+      <c r="AQ42">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR41">
+      <c r="AR42">
         <v>17.5</v>
       </c>
-      <c r="AS41">
+      <c r="AS42">
         <v>48</v>
       </c>
-      <c r="AT41">
+      <c r="AT42">
         <v>5.7</v>
       </c>
-      <c r="AU41">
+      <c r="AU42">
         <v>6</v>
       </c>
-      <c r="AV41">
+      <c r="AV42">
         <v>13.5</v>
       </c>
-      <c r="AW41">
+      <c r="AW42">
         <v>42</v>
       </c>
-      <c r="AX41">
+      <c r="AX42">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY41">
+      <c r="AY42">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ41">
+      <c r="AZ42">
         <v>20</v>
       </c>
-      <c r="BA41">
+      <c r="BA42">
         <v>85</v>
       </c>
-      <c r="BB41">
+      <c r="BB42">
         <v>27</v>
       </c>
-      <c r="BC41">
+      <c r="BC42">
         <v>27</v>
       </c>
-      <c r="BD41">
+      <c r="BD42">
         <v>46</v>
       </c>
-      <c r="BE41">
+      <c r="BE42">
         <v>100</v>
       </c>
-      <c r="BF41">
-        <v>1.01</v>
-      </c>
-      <c r="BG41">
-        <v>1.01</v>
-      </c>
-      <c r="BH41">
-        <v>1000</v>
-      </c>
-      <c r="BI41">
-        <v>1.01</v>
-      </c>
-      <c r="BJ41">
-        <v>1000</v>
-      </c>
-      <c r="BK41">
-        <v>1.01</v>
-      </c>
-      <c r="BL41">
-        <v>1000</v>
-      </c>
-      <c r="BM41">
-        <v>1.01</v>
-      </c>
-      <c r="BN41">
-        <v>1000</v>
-      </c>
-      <c r="BO41">
-        <v>1.01</v>
-      </c>
-      <c r="BP41">
-        <v>1000</v>
-      </c>
-      <c r="BQ41">
-        <v>1.01</v>
-      </c>
-      <c r="BR41">
-        <v>1000</v>
-      </c>
-      <c r="BS41">
-        <v>1.01</v>
-      </c>
-      <c r="BT41">
-        <v>1000</v>
-      </c>
-      <c r="BU41">
-        <v>1.01</v>
-      </c>
-      <c r="BV41">
-        <v>1000</v>
-      </c>
-      <c r="BW41">
-        <v>1.01</v>
-      </c>
-      <c r="BX41">
-        <v>1000</v>
-      </c>
-      <c r="BY41">
-        <v>1.01</v>
-      </c>
-      <c r="BZ41">
-        <v>1000</v>
-      </c>
-      <c r="CA41">
-        <v>1.01</v>
-      </c>
-      <c r="CB41" t="s">
-        <v>204</v>
+      <c r="BF42">
+        <v>1.01</v>
+      </c>
+      <c r="BG42">
+        <v>1.01</v>
+      </c>
+      <c r="BH42">
+        <v>1000</v>
+      </c>
+      <c r="BI42">
+        <v>1.01</v>
+      </c>
+      <c r="BJ42">
+        <v>1000</v>
+      </c>
+      <c r="BK42">
+        <v>1.01</v>
+      </c>
+      <c r="BL42">
+        <v>1000</v>
+      </c>
+      <c r="BM42">
+        <v>1.01</v>
+      </c>
+      <c r="BN42">
+        <v>1000</v>
+      </c>
+      <c r="BO42">
+        <v>1.01</v>
+      </c>
+      <c r="BP42">
+        <v>1000</v>
+      </c>
+      <c r="BQ42">
+        <v>1.01</v>
+      </c>
+      <c r="BR42">
+        <v>1000</v>
+      </c>
+      <c r="BS42">
+        <v>1.01</v>
+      </c>
+      <c r="BT42">
+        <v>1000</v>
+      </c>
+      <c r="BU42">
+        <v>1.01</v>
+      </c>
+      <c r="BV42">
+        <v>1000</v>
+      </c>
+      <c r="BW42">
+        <v>1.01</v>
+      </c>
+      <c r="BX42">
+        <v>1000</v>
+      </c>
+      <c r="BY42">
+        <v>1.01</v>
+      </c>
+      <c r="BZ42">
+        <v>1000</v>
+      </c>
+      <c r="CA42">
+        <v>1.01</v>
+      </c>
+      <c r="CB42" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="211">
   <si>
     <t>League</t>
   </si>
@@ -268,12 +268,12 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Slovakian 2 Liga</t>
   </si>
   <si>
-    <t>Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
@@ -289,39 +289,42 @@
     <t>Romanian Liga I</t>
   </si>
   <si>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
-    <t>Czech 2 Liga</t>
-  </si>
-  <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
     <t>Polish I Liga</t>
   </si>
   <si>
-    <t>Swedish Allsvenskan</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
-    <t>Icelandic 1 Deild</t>
-  </si>
-  <si>
-    <t>Icelandic Urvalsdeild</t>
-  </si>
-  <si>
-    <t>Serbian Super League</t>
-  </si>
-  <si>
     <t>Turkish Super League</t>
   </si>
   <si>
@@ -409,12 +412,12 @@
     <t>Tijuana</t>
   </si>
   <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
     <t>Slovan Bratislava II</t>
   </si>
   <si>
-    <t>Polissya Zhytomyr</t>
-  </si>
-  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -433,54 +436,57 @@
     <t>FC Dziugas</t>
   </si>
   <si>
+    <t>Trinec</t>
+  </si>
+  <si>
+    <t>FC Noah</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Trinec</t>
-  </si>
-  <si>
     <t>Sporting Gijon</t>
   </si>
   <si>
+    <t>Hacken</t>
+  </si>
+  <si>
     <t>Brondby</t>
   </si>
   <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Hacken</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
+    <t>Valur</t>
+  </si>
+  <si>
+    <t>IR Reykjavik</t>
+  </si>
+  <si>
+    <t>Volsungur</t>
+  </si>
+  <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
+    <t>FK Novi Pazar</t>
+  </si>
+  <si>
+    <t>Jong Ajax Amsterdam</t>
+  </si>
+  <si>
+    <t>Jong FC Utrecht</t>
+  </si>
+  <si>
     <t>De Graafschap</t>
   </si>
   <si>
-    <t>Jong FC Utrecht</t>
-  </si>
-  <si>
-    <t>Jong Ajax Amsterdam</t>
-  </si>
-  <si>
     <t>Grindavik</t>
   </si>
   <si>
-    <t>Leiknir R</t>
-  </si>
-  <si>
-    <t>Volsungur</t>
-  </si>
-  <si>
-    <t>IR Reykjavik</t>
-  </si>
-  <si>
-    <t>Valur</t>
-  </si>
-  <si>
-    <t>FK Novi Pazar</t>
-  </si>
-  <si>
     <t>Arda</t>
   </si>
   <si>
@@ -532,12 +538,12 @@
     <t>Cruz Azul</t>
   </si>
   <si>
+    <t>Zorya</t>
+  </si>
+  <si>
     <t>FK Humenne</t>
   </si>
   <si>
-    <t>Zorya</t>
-  </si>
-  <si>
     <t>Ilves</t>
   </si>
   <si>
@@ -556,54 +562,57 @@
     <t>FK Suduva</t>
   </si>
   <si>
+    <t>Usti nad Labem</t>
+  </si>
+  <si>
+    <t>Alashkert</t>
+  </si>
+  <si>
     <t>Septemvri</t>
   </si>
   <si>
-    <t>Usti nad Labem</t>
-  </si>
-  <si>
     <t>Sabadell</t>
   </si>
   <si>
+    <t>Halmstads</t>
+  </si>
+  <si>
     <t>SonderjyskE</t>
   </si>
   <si>
     <t>Puszcza Niepolomice</t>
   </si>
   <si>
-    <t>Halmstads</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
+    <t>KA Akureyri</t>
+  </si>
+  <si>
+    <t>Njardvik</t>
+  </si>
+  <si>
+    <t>IF Vestri</t>
+  </si>
+  <si>
+    <t>Aegir</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
     <t>Jong AZ Alkmaar</t>
   </si>
   <si>
-    <t>Vitesse Arnhem</t>
-  </si>
-  <si>
-    <t>Emmen</t>
-  </si>
-  <si>
     <t>Grotta</t>
   </si>
   <si>
-    <t>Aegir</t>
-  </si>
-  <si>
-    <t>IF Vestri</t>
-  </si>
-  <si>
-    <t>Njardvik</t>
-  </si>
-  <si>
-    <t>KA Akureyri</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia</t>
   </si>
   <si>
@@ -637,7 +646,7 @@
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 19:47:42</t>
+    <t>2026-08-15 22:07:52</t>
   </si>
 </sst>
 </file>
@@ -969,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB42"/>
+  <dimension ref="A1:CB43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1219,16 +1228,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F2">
         <v>2.56</v>
@@ -1237,7 +1246,7 @@
         <v>2.94</v>
       </c>
       <c r="H2">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I2">
         <v>2.98</v>
@@ -1246,7 +1255,7 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.29</v>
@@ -1264,16 +1273,16 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
         <v>3.1</v>
       </c>
       <c r="T2">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
         <v>2.24</v>
@@ -1348,7 +1357,7 @@
         <v>14</v>
       </c>
       <c r="AS2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1360,7 +1369,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1372,19 +1381,19 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
         <v>16.5</v>
@@ -1453,7 +1462,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1461,19 +1470,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G3">
         <v>2.62</v>
@@ -1497,13 +1506,13 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
@@ -1515,10 +1524,10 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V3">
         <v>1.39</v>
@@ -1551,7 +1560,7 @@
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG3">
         <v>14.5</v>
@@ -1584,22 +1593,22 @@
         <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
         <v>42</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>5.6</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
         <v>30</v>
@@ -1629,7 +1638,7 @@
         <v>85</v>
       </c>
       <c r="BF3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG3">
         <v>32</v>
@@ -1680,7 +1689,7 @@
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BX3">
         <v>55</v>
@@ -1695,7 +1704,7 @@
         <v>25</v>
       </c>
       <c r="CB3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1703,16 +1712,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1721,13 +1730,13 @@
         <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I4">
         <v>2.44</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -1766,7 +1775,7 @@
         <v>1.69</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1811,7 +1820,7 @@
         <v>34</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1868,7 +1877,7 @@
         <v>22</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1925,7 +1934,7 @@
         <v>12</v>
       </c>
       <c r="BX4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY4">
         <v>19</v>
@@ -1937,7 +1946,7 @@
         <v>14</v>
       </c>
       <c r="CB4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1945,16 +1954,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F5">
         <v>5.9</v>
@@ -1966,7 +1975,7 @@
         <v>1.57</v>
       </c>
       <c r="I5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J5">
         <v>4.6</v>
@@ -1999,13 +2008,13 @@
         <v>2.54</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="W5">
         <v>1.18</v>
@@ -2179,7 +2188,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2187,16 +2196,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F6">
         <v>4.2</v>
@@ -2421,7 +2430,7 @@
         <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2429,16 +2438,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F7">
         <v>3.35</v>
@@ -2453,7 +2462,7 @@
         <v>2.34</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
         <v>3.75</v>
@@ -2474,10 +2483,10 @@
         <v>2.04</v>
       </c>
       <c r="Q7">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
         <v>3.2</v>
@@ -2489,7 +2498,7 @@
         <v>2.26</v>
       </c>
       <c r="V7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W7">
         <v>1.4</v>
@@ -2516,7 +2525,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF7">
         <v>25</v>
@@ -2528,13 +2537,13 @@
         <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
         <v>690</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL7">
         <v>140</v>
@@ -2543,7 +2552,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AO7">
         <v>17</v>
@@ -2564,7 +2573,7 @@
         <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
         <v>10.5</v>
@@ -2663,7 +2672,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2671,184 +2680,184 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F8">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>1.15</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>320</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="Q8">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="R8">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.87</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2905,7 +2914,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2913,184 +2922,184 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F9">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="G9">
+        <v>2.14</v>
+      </c>
+      <c r="H9">
+        <v>3.85</v>
+      </c>
+      <c r="I9">
+        <v>4.9</v>
+      </c>
+      <c r="J9">
+        <v>3.55</v>
+      </c>
+      <c r="K9">
+        <v>4.1</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>3.7</v>
+      </c>
+      <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>1.94</v>
+      </c>
+      <c r="Q9">
+        <v>1.84</v>
+      </c>
+      <c r="R9">
+        <v>1.36</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>1.73</v>
+      </c>
+      <c r="U9">
+        <v>2.08</v>
+      </c>
+      <c r="V9">
+        <v>1.27</v>
+      </c>
+      <c r="W9">
+        <v>1.87</v>
+      </c>
+      <c r="X9">
+        <v>19</v>
+      </c>
+      <c r="Y9">
+        <v>19</v>
+      </c>
+      <c r="Z9">
+        <v>38</v>
+      </c>
+      <c r="AA9">
         <v>110</v>
       </c>
-      <c r="H9">
-        <v>1.15</v>
-      </c>
-      <c r="I9">
-        <v>1000</v>
-      </c>
-      <c r="J9">
-        <v>1.16</v>
-      </c>
-      <c r="K9">
-        <v>320</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>1.2</v>
-      </c>
-      <c r="O9">
-        <v>1.01</v>
-      </c>
-      <c r="P9">
-        <v>1.2</v>
-      </c>
-      <c r="Q9">
-        <v>1.34</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>1.35</v>
-      </c>
-      <c r="T9">
-        <v>1.01</v>
-      </c>
-      <c r="U9">
-        <v>1.01</v>
-      </c>
-      <c r="V9">
-        <v>1.02</v>
-      </c>
-      <c r="W9">
-        <v>1.14</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3147,7 +3156,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3155,16 +3164,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F10">
         <v>2.48</v>
@@ -3182,7 +3191,7 @@
         <v>3.8</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3200,7 +3209,7 @@
         <v>2.42</v>
       </c>
       <c r="Q10">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
         <v>1.54</v>
@@ -3209,7 +3218,7 @@
         <v>2.5</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U10">
         <v>1.01</v>
@@ -3389,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3397,16 +3406,16 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F11">
         <v>2.66</v>
@@ -3631,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3639,34 +3648,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3675,88 +3684,88 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="O12">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="S12">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP12">
         <v>1.01</v>
@@ -3873,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3881,16 +3890,16 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F13">
         <v>5.9</v>
@@ -4115,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4123,19 +4132,19 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G14">
         <v>2.18</v>
@@ -4150,7 +4159,7 @@
         <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
         <v>1.42</v>
@@ -4162,7 +4171,7 @@
         <v>3.3</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P14">
         <v>1.79</v>
@@ -4198,7 +4207,7 @@
         <v>32</v>
       </c>
       <c r="AA14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB14">
         <v>9.199999999999999</v>
@@ -4300,13 +4309,13 @@
         <v>3.35</v>
       </c>
       <c r="BI14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4324,16 +4333,16 @@
         <v>16</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU14">
         <v>5.4</v>
@@ -4342,22 +4351,22 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4365,16 +4374,16 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -4599,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4607,58 +4616,58 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F16">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="H16">
+        <v>1.93</v>
+      </c>
+      <c r="I16">
+        <v>2.24</v>
+      </c>
+      <c r="J16">
         <v>3.85</v>
       </c>
-      <c r="I16">
-        <v>6</v>
-      </c>
-      <c r="J16">
-        <v>1.01</v>
-      </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4667,61 +4676,61 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="W16">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="X16">
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4730,61 +4739,61 @@
         <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
@@ -4835,13 +4844,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4849,34 +4858,34 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F17">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="G17">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="H17">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4885,22 +4894,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>2.48</v>
       </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S17">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4909,10 +4918,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="W17">
-        <v>1.32</v>
+        <v>1.99</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5077,13 +5086,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5091,241 +5100,241 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
         <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F18">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="G18">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="H18">
+        <v>4.3</v>
+      </c>
+      <c r="I18">
         <v>5.1</v>
       </c>
-      <c r="I18">
-        <v>5.9</v>
-      </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K18">
+        <v>3.8</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>1.01</v>
+      </c>
+      <c r="O18">
+        <v>1.37</v>
+      </c>
+      <c r="P18">
+        <v>1.58</v>
+      </c>
+      <c r="Q18">
+        <v>2.12</v>
+      </c>
+      <c r="R18">
+        <v>1.21</v>
+      </c>
+      <c r="S18">
         <v>3.75</v>
       </c>
-      <c r="L18">
-        <v>1.38</v>
-      </c>
-      <c r="M18">
-        <v>1.1</v>
-      </c>
-      <c r="N18">
-        <v>2.92</v>
-      </c>
-      <c r="O18">
-        <v>1.44</v>
-      </c>
-      <c r="P18">
-        <v>1.63</v>
-      </c>
-      <c r="Q18">
-        <v>2.28</v>
-      </c>
-      <c r="R18">
+      <c r="T18">
+        <v>1.9</v>
+      </c>
+      <c r="U18">
+        <v>1.89</v>
+      </c>
+      <c r="V18">
         <v>1.24</v>
       </c>
-      <c r="S18">
-        <v>4.3</v>
-      </c>
-      <c r="T18">
-        <v>2.06</v>
-      </c>
-      <c r="U18">
-        <v>1.78</v>
-      </c>
-      <c r="V18">
-        <v>1.2</v>
-      </c>
       <c r="W18">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>21</v>
+      </c>
+      <c r="Z18">
+        <v>50</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>11</v>
+      </c>
+      <c r="AC18">
+        <v>11.5</v>
+      </c>
+      <c r="AD18">
+        <v>28</v>
+      </c>
+      <c r="AE18">
+        <v>100</v>
+      </c>
+      <c r="AF18">
+        <v>17</v>
+      </c>
+      <c r="AG18">
+        <v>15.5</v>
+      </c>
+      <c r="AH18">
+        <v>30</v>
+      </c>
+      <c r="AI18">
+        <v>100</v>
+      </c>
+      <c r="AJ18">
+        <v>34</v>
+      </c>
+      <c r="AK18">
+        <v>34</v>
+      </c>
+      <c r="AL18">
+        <v>65</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>26</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>5</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>11.5</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>7.2</v>
+      </c>
+      <c r="AY18">
+        <v>6.6</v>
+      </c>
+      <c r="AZ18">
         <v>12.5</v>
       </c>
-      <c r="Y18">
-        <v>17</v>
-      </c>
-      <c r="Z18">
-        <v>48</v>
-      </c>
-      <c r="AA18">
-        <v>180</v>
-      </c>
-      <c r="AB18">
-        <v>7.2</v>
-      </c>
-      <c r="AC18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD18">
-        <v>25</v>
-      </c>
-      <c r="AE18">
-        <v>110</v>
-      </c>
-      <c r="AF18">
-        <v>12</v>
-      </c>
-      <c r="AG18">
-        <v>12</v>
-      </c>
-      <c r="AH18">
-        <v>27</v>
-      </c>
-      <c r="AI18">
-        <v>120</v>
-      </c>
-      <c r="AJ18">
-        <v>25</v>
-      </c>
-      <c r="AK18">
-        <v>27</v>
-      </c>
-      <c r="AL18">
-        <v>60</v>
-      </c>
-      <c r="AM18">
-        <v>200</v>
-      </c>
-      <c r="AN18">
-        <v>21</v>
-      </c>
-      <c r="AO18">
-        <v>160</v>
-      </c>
-      <c r="AP18">
-        <v>9.4</v>
-      </c>
-      <c r="AQ18">
-        <v>12.5</v>
-      </c>
-      <c r="AR18">
-        <v>29</v>
-      </c>
-      <c r="AS18">
-        <v>5.5</v>
-      </c>
-      <c r="AT18">
-        <v>6</v>
-      </c>
-      <c r="AU18">
-        <v>6.8</v>
-      </c>
-      <c r="AV18">
-        <v>18</v>
-      </c>
-      <c r="AW18">
-        <v>5.4</v>
-      </c>
-      <c r="AX18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18">
-        <v>19.5</v>
-      </c>
       <c r="BA18">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BC18">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="BD18">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BG18">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5333,178 +5342,178 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F19">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="G19">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="H19">
+        <v>5.1</v>
+      </c>
+      <c r="I19">
+        <v>5.9</v>
+      </c>
+      <c r="J19">
+        <v>3.4</v>
+      </c>
+      <c r="K19">
+        <v>3.75</v>
+      </c>
+      <c r="L19">
+        <v>1.38</v>
+      </c>
+      <c r="M19">
+        <v>1.1</v>
+      </c>
+      <c r="N19">
+        <v>2.92</v>
+      </c>
+      <c r="O19">
+        <v>1.44</v>
+      </c>
+      <c r="P19">
+        <v>1.63</v>
+      </c>
+      <c r="Q19">
+        <v>2.28</v>
+      </c>
+      <c r="R19">
+        <v>1.24</v>
+      </c>
+      <c r="S19">
+        <v>4.3</v>
+      </c>
+      <c r="T19">
+        <v>2.06</v>
+      </c>
+      <c r="U19">
+        <v>1.78</v>
+      </c>
+      <c r="V19">
+        <v>1.2</v>
+      </c>
+      <c r="W19">
+        <v>2.06</v>
+      </c>
+      <c r="X19">
+        <v>12.5</v>
+      </c>
+      <c r="Y19">
+        <v>17</v>
+      </c>
+      <c r="Z19">
+        <v>48</v>
+      </c>
+      <c r="AA19">
+        <v>180</v>
+      </c>
+      <c r="AB19">
         <v>7.2</v>
       </c>
-      <c r="I19">
-        <v>8.4</v>
-      </c>
-      <c r="J19">
-        <v>4.9</v>
-      </c>
-      <c r="K19">
-        <v>5.1</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>4.8</v>
-      </c>
-      <c r="O19">
-        <v>1.22</v>
-      </c>
-      <c r="P19">
-        <v>2.32</v>
-      </c>
-      <c r="Q19">
-        <v>1.66</v>
-      </c>
-      <c r="R19">
-        <v>1.5</v>
-      </c>
-      <c r="S19">
-        <v>2.68</v>
-      </c>
-      <c r="T19">
-        <v>1.82</v>
-      </c>
-      <c r="U19">
-        <v>2.02</v>
-      </c>
-      <c r="V19">
-        <v>1.14</v>
-      </c>
-      <c r="W19">
-        <v>3</v>
-      </c>
-      <c r="X19">
-        <v>22</v>
-      </c>
-      <c r="Y19">
-        <v>32</v>
-      </c>
-      <c r="Z19">
-        <v>70</v>
-      </c>
-      <c r="AA19">
-        <v>270</v>
-      </c>
-      <c r="AB19">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AC19">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE19">
         <v>110</v>
       </c>
       <c r="AF19">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI19">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AK19">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AL19">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN19">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AO19">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AP19">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AQ19">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AS19">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AW19">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA19">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BC19">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BD19">
-        <v>26</v>
+        <v>5.2</v>
       </c>
       <c r="BE19">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF19">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG19">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5567,7 +5576,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5575,241 +5584,241 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="H20">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="Q20">
+        <v>1.46</v>
+      </c>
+      <c r="R20">
+        <v>1.78</v>
+      </c>
+      <c r="S20">
+        <v>2.16</v>
+      </c>
+      <c r="T20">
         <v>1.79</v>
       </c>
-      <c r="R20">
-        <v>1.34</v>
-      </c>
-      <c r="S20">
-        <v>3</v>
-      </c>
-      <c r="T20">
-        <v>1.76</v>
-      </c>
       <c r="U20">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="X20">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AA20">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC20">
+        <v>17</v>
+      </c>
+      <c r="AD20">
+        <v>40</v>
+      </c>
+      <c r="AE20">
+        <v>130</v>
+      </c>
+      <c r="AF20">
+        <v>12.5</v>
+      </c>
+      <c r="AG20">
         <v>11</v>
       </c>
-      <c r="AD20">
-        <v>24</v>
-      </c>
-      <c r="AE20">
-        <v>80</v>
-      </c>
-      <c r="AF20">
+      <c r="AH20">
+        <v>28</v>
+      </c>
+      <c r="AI20">
+        <v>100</v>
+      </c>
+      <c r="AJ20">
         <v>14</v>
       </c>
-      <c r="AG20">
-        <v>12.5</v>
-      </c>
-      <c r="AH20">
-        <v>23</v>
-      </c>
-      <c r="AI20">
-        <v>80</v>
-      </c>
-      <c r="AJ20">
-        <v>23</v>
-      </c>
       <c r="AK20">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AL20">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM20">
         <v>120</v>
       </c>
       <c r="AN20">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AO20">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AP20">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="AQ20">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR20">
-        <v>29</v>
+        <v>5.5</v>
       </c>
       <c r="AS20">
-        <v>80</v>
+        <v>5.7</v>
       </c>
       <c r="AT20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AV20">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="AW20">
-        <v>46</v>
+        <v>5.5</v>
       </c>
       <c r="AX20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA20">
-        <v>46</v>
+        <v>5.5</v>
       </c>
       <c r="BB20">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC20">
+        <v>12</v>
+      </c>
+      <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
+        <v>5.5</v>
+      </c>
+      <c r="BF20">
+        <v>3.85</v>
+      </c>
+      <c r="BG20">
+        <v>5.5</v>
+      </c>
+      <c r="BH20">
+        <v>6.2</v>
+      </c>
+      <c r="BI20">
+        <v>3.5</v>
+      </c>
+      <c r="BJ20">
+        <v>15</v>
+      </c>
+      <c r="BK20">
+        <v>2.72</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>3.3</v>
+      </c>
+      <c r="BN20">
+        <v>5.6</v>
+      </c>
+      <c r="BO20">
+        <v>3</v>
+      </c>
+      <c r="BP20">
+        <v>10.5</v>
+      </c>
+      <c r="BQ20">
+        <v>5.1</v>
+      </c>
+      <c r="BR20">
+        <v>26</v>
+      </c>
+      <c r="BS20">
+        <v>2.94</v>
+      </c>
+      <c r="BT20">
+        <v>17.5</v>
+      </c>
+      <c r="BU20">
+        <v>2.78</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>3.2</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>3.15</v>
+      </c>
+      <c r="BZ20">
         <v>13</v>
       </c>
-      <c r="BD20">
-        <v>24</v>
-      </c>
-      <c r="BE20">
-        <v>70</v>
-      </c>
-      <c r="BF20">
-        <v>7.8</v>
-      </c>
-      <c r="BG20">
-        <v>48</v>
-      </c>
-      <c r="BH20">
-        <v>4.3</v>
-      </c>
-      <c r="BI20">
-        <v>2.92</v>
-      </c>
-      <c r="BJ20">
-        <v>12</v>
-      </c>
-      <c r="BK20">
-        <v>7.2</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>21</v>
-      </c>
-      <c r="BN20">
-        <v>5.3</v>
-      </c>
-      <c r="BO20">
-        <v>3.45</v>
-      </c>
-      <c r="BP20">
-        <v>14.5</v>
-      </c>
-      <c r="BQ20">
-        <v>8.6</v>
-      </c>
-      <c r="BR20">
-        <v>32</v>
-      </c>
-      <c r="BS20">
-        <v>18</v>
-      </c>
-      <c r="BT20">
-        <v>10.5</v>
-      </c>
-      <c r="BU20">
-        <v>6.2</v>
-      </c>
-      <c r="BV20">
-        <v>50</v>
-      </c>
-      <c r="BW20">
-        <v>29</v>
-      </c>
-      <c r="BX20">
-        <v>60</v>
-      </c>
-      <c r="BY20">
-        <v>32</v>
-      </c>
-      <c r="BZ20">
-        <v>0</v>
-      </c>
       <c r="CA20">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="CB20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5817,241 +5826,241 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F21">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="G21">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="H21">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="K21">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="O21">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="P21">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="Q21">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="S21">
-        <v>2.16</v>
+        <v>2.68</v>
       </c>
       <c r="T21">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U21">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W21">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="X21">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Y21">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AA21">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AB21">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AE21">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF21">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ21">
         <v>14</v>
       </c>
       <c r="AK21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM21">
         <v>120</v>
       </c>
       <c r="AN21">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AO21">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP21">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AQ21">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="AR21">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="AS21">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AT21">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AU21">
+        <v>10</v>
+      </c>
+      <c r="AV21">
+        <v>25</v>
+      </c>
+      <c r="AW21">
+        <v>9.6</v>
+      </c>
+      <c r="AX21">
+        <v>8.6</v>
+      </c>
+      <c r="AY21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>20</v>
+      </c>
+      <c r="BA21">
+        <v>11.5</v>
+      </c>
+      <c r="BB21">
+        <v>12</v>
+      </c>
+      <c r="BC21">
         <v>13</v>
       </c>
-      <c r="AV21">
-        <v>5</v>
-      </c>
-      <c r="AW21">
-        <v>5.5</v>
-      </c>
-      <c r="AX21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21">
-        <v>21</v>
-      </c>
-      <c r="BA21">
-        <v>5.5</v>
-      </c>
-      <c r="BB21">
-        <v>10.5</v>
-      </c>
-      <c r="BC21">
-        <v>12</v>
-      </c>
       <c r="BD21">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BE21">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF21">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="BG21">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH21">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6059,241 +6068,241 @@
         <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
         <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F22">
-        <v>2.94</v>
+        <v>1.72</v>
       </c>
       <c r="G22">
-        <v>3.3</v>
+        <v>1.89</v>
       </c>
       <c r="H22">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="I22">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J22">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="R22">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="S22">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="T22">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="X22">
+        <v>21</v>
+      </c>
+      <c r="Y22">
+        <v>23</v>
+      </c>
+      <c r="Z22">
+        <v>50</v>
+      </c>
+      <c r="AA22">
+        <v>150</v>
+      </c>
+      <c r="AB22">
+        <v>11.5</v>
+      </c>
+      <c r="AC22">
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <v>24</v>
+      </c>
+      <c r="AE22">
+        <v>80</v>
+      </c>
+      <c r="AF22">
+        <v>14</v>
+      </c>
+      <c r="AG22">
+        <v>12.5</v>
+      </c>
+      <c r="AH22">
+        <v>23</v>
+      </c>
+      <c r="AI22">
+        <v>80</v>
+      </c>
+      <c r="AJ22">
+        <v>23</v>
+      </c>
+      <c r="AK22">
+        <v>22</v>
+      </c>
+      <c r="AL22">
+        <v>42</v>
+      </c>
+      <c r="AM22">
+        <v>120</v>
+      </c>
+      <c r="AN22">
+        <v>12.5</v>
+      </c>
+      <c r="AO22">
+        <v>85</v>
+      </c>
+      <c r="AP22">
+        <v>12.5</v>
+      </c>
+      <c r="AQ22">
+        <v>13.5</v>
+      </c>
+      <c r="AR22">
+        <v>29</v>
+      </c>
+      <c r="AS22">
+        <v>80</v>
+      </c>
+      <c r="AT22">
+        <v>7</v>
+      </c>
+      <c r="AU22">
+        <v>6.8</v>
+      </c>
+      <c r="AV22">
+        <v>14.5</v>
+      </c>
+      <c r="AW22">
+        <v>46</v>
+      </c>
+      <c r="AX22">
         <v>8.4</v>
       </c>
-      <c r="Y22">
-        <v>9.4</v>
-      </c>
-      <c r="Z22">
-        <v>22</v>
-      </c>
-      <c r="AA22">
+      <c r="AY22">
+        <v>7.6</v>
+      </c>
+      <c r="AZ22">
+        <v>14</v>
+      </c>
+      <c r="BA22">
+        <v>46</v>
+      </c>
+      <c r="BB22">
+        <v>13.5</v>
+      </c>
+      <c r="BC22">
+        <v>13</v>
+      </c>
+      <c r="BD22">
+        <v>24</v>
+      </c>
+      <c r="BE22">
         <v>70</v>
       </c>
-      <c r="AB22">
-        <v>9.6</v>
-      </c>
-      <c r="AC22">
-        <v>8.4</v>
-      </c>
-      <c r="AD22">
+      <c r="BF22">
+        <v>7.8</v>
+      </c>
+      <c r="BG22">
+        <v>48</v>
+      </c>
+      <c r="BH22">
+        <v>4.3</v>
+      </c>
+      <c r="BI22">
+        <v>2.92</v>
+      </c>
+      <c r="BJ22">
+        <v>12</v>
+      </c>
+      <c r="BK22">
+        <v>7.2</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>21</v>
+      </c>
+      <c r="BN22">
+        <v>5.3</v>
+      </c>
+      <c r="BO22">
+        <v>3.45</v>
+      </c>
+      <c r="BP22">
+        <v>14.5</v>
+      </c>
+      <c r="BQ22">
+        <v>8.6</v>
+      </c>
+      <c r="BR22">
+        <v>32</v>
+      </c>
+      <c r="BS22">
         <v>18</v>
       </c>
-      <c r="AE22">
-        <v>65</v>
-      </c>
-      <c r="AF22">
-        <v>23</v>
-      </c>
-      <c r="AG22">
-        <v>18.5</v>
-      </c>
-      <c r="AH22">
+      <c r="BT22">
+        <v>10.5</v>
+      </c>
+      <c r="BU22">
+        <v>6.2</v>
+      </c>
+      <c r="BV22">
+        <v>50</v>
+      </c>
+      <c r="BW22">
+        <v>29</v>
+      </c>
+      <c r="BX22">
+        <v>60</v>
+      </c>
+      <c r="BY22">
         <v>32</v>
       </c>
-      <c r="AI22">
-        <v>110</v>
-      </c>
-      <c r="AJ22">
-        <v>75</v>
-      </c>
-      <c r="AK22">
-        <v>70</v>
-      </c>
-      <c r="AL22">
-        <v>110</v>
-      </c>
-      <c r="AM22">
-        <v>300</v>
-      </c>
-      <c r="AN22">
-        <v>95</v>
-      </c>
-      <c r="AO22">
-        <v>90</v>
-      </c>
-      <c r="AP22">
-        <v>6.2</v>
-      </c>
-      <c r="AQ22">
-        <v>6.6</v>
-      </c>
-      <c r="AR22">
-        <v>13</v>
-      </c>
-      <c r="AS22">
-        <v>4.2</v>
-      </c>
-      <c r="AT22">
-        <v>6</v>
-      </c>
-      <c r="AU22">
-        <v>6</v>
-      </c>
-      <c r="AV22">
-        <v>12.5</v>
-      </c>
-      <c r="AW22">
-        <v>4.2</v>
-      </c>
-      <c r="AX22">
-        <v>13.5</v>
-      </c>
-      <c r="AY22">
-        <v>12.5</v>
-      </c>
-      <c r="AZ22">
-        <v>3.95</v>
-      </c>
-      <c r="BA22">
-        <v>4.3</v>
-      </c>
-      <c r="BB22">
-        <v>4.2</v>
-      </c>
-      <c r="BC22">
-        <v>4.2</v>
-      </c>
-      <c r="BD22">
-        <v>4.3</v>
-      </c>
-      <c r="BE22">
-        <v>4.4</v>
-      </c>
-      <c r="BF22">
-        <v>4.3</v>
-      </c>
-      <c r="BG22">
-        <v>4.3</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.01</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.01</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.01</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.01</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.01</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
-        <v>1.01</v>
-      </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
-        <v>1.01</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>1.01</v>
-      </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6301,178 +6310,178 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
         <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F23">
-        <v>1.79</v>
+        <v>2.94</v>
       </c>
       <c r="G23">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="H23">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="I23">
+        <v>3.2</v>
+      </c>
+      <c r="J23">
+        <v>2.76</v>
+      </c>
+      <c r="K23">
+        <v>3.15</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.15</v>
+      </c>
+      <c r="N23">
+        <v>2.28</v>
+      </c>
+      <c r="O23">
+        <v>1.66</v>
+      </c>
+      <c r="P23">
+        <v>1.44</v>
+      </c>
+      <c r="Q23">
+        <v>3</v>
+      </c>
+      <c r="R23">
+        <v>1.14</v>
+      </c>
+      <c r="S23">
+        <v>6.6</v>
+      </c>
+      <c r="T23">
+        <v>2.26</v>
+      </c>
+      <c r="U23">
+        <v>1.67</v>
+      </c>
+      <c r="V23">
+        <v>1.46</v>
+      </c>
+      <c r="W23">
+        <v>1.43</v>
+      </c>
+      <c r="X23">
+        <v>8.6</v>
+      </c>
+      <c r="Y23">
+        <v>9.4</v>
+      </c>
+      <c r="Z23">
+        <v>22</v>
+      </c>
+      <c r="AA23">
+        <v>70</v>
+      </c>
+      <c r="AB23">
+        <v>9.6</v>
+      </c>
+      <c r="AC23">
+        <v>8.4</v>
+      </c>
+      <c r="AD23">
+        <v>18</v>
+      </c>
+      <c r="AE23">
+        <v>65</v>
+      </c>
+      <c r="AF23">
+        <v>23</v>
+      </c>
+      <c r="AG23">
+        <v>18.5</v>
+      </c>
+      <c r="AH23">
+        <v>32</v>
+      </c>
+      <c r="AI23">
+        <v>110</v>
+      </c>
+      <c r="AJ23">
+        <v>75</v>
+      </c>
+      <c r="AK23">
+        <v>70</v>
+      </c>
+      <c r="AL23">
+        <v>110</v>
+      </c>
+      <c r="AM23">
+        <v>300</v>
+      </c>
+      <c r="AN23">
+        <v>95</v>
+      </c>
+      <c r="AO23">
+        <v>90</v>
+      </c>
+      <c r="AP23">
+        <v>6.2</v>
+      </c>
+      <c r="AQ23">
+        <v>6.6</v>
+      </c>
+      <c r="AR23">
+        <v>13</v>
+      </c>
+      <c r="AS23">
+        <v>4.1</v>
+      </c>
+      <c r="AT23">
+        <v>6</v>
+      </c>
+      <c r="AU23">
+        <v>6</v>
+      </c>
+      <c r="AV23">
+        <v>12.5</v>
+      </c>
+      <c r="AW23">
+        <v>4.1</v>
+      </c>
+      <c r="AX23">
+        <v>13.5</v>
+      </c>
+      <c r="AY23">
+        <v>12.5</v>
+      </c>
+      <c r="AZ23">
+        <v>3.9</v>
+      </c>
+      <c r="BA23">
         <v>4.2</v>
       </c>
-      <c r="J23">
-        <v>4.6</v>
-      </c>
-      <c r="K23">
-        <v>5.3</v>
-      </c>
-      <c r="L23">
-        <v>1.01</v>
-      </c>
-      <c r="M23">
-        <v>1.01</v>
-      </c>
-      <c r="N23">
-        <v>8</v>
-      </c>
-      <c r="O23">
-        <v>1.1</v>
-      </c>
-      <c r="P23">
-        <v>3.4</v>
-      </c>
-      <c r="Q23">
-        <v>1.33</v>
-      </c>
-      <c r="R23">
-        <v>2</v>
-      </c>
-      <c r="S23">
-        <v>1.79</v>
-      </c>
-      <c r="T23">
-        <v>1.33</v>
-      </c>
-      <c r="U23">
-        <v>3.05</v>
-      </c>
-      <c r="V23">
-        <v>1.32</v>
-      </c>
-      <c r="W23">
-        <v>2.02</v>
-      </c>
-      <c r="X23">
-        <v>60</v>
-      </c>
-      <c r="Y23">
-        <v>34</v>
-      </c>
-      <c r="Z23">
-        <v>50</v>
-      </c>
-      <c r="AA23">
-        <v>85</v>
-      </c>
-      <c r="AB23">
-        <v>23</v>
-      </c>
-      <c r="AC23">
-        <v>14.5</v>
-      </c>
-      <c r="AD23">
-        <v>19</v>
-      </c>
-      <c r="AE23">
-        <v>36</v>
-      </c>
-      <c r="AF23">
-        <v>21</v>
-      </c>
-      <c r="AG23">
-        <v>13</v>
-      </c>
-      <c r="AH23">
-        <v>15.5</v>
-      </c>
-      <c r="AI23">
-        <v>32</v>
-      </c>
-      <c r="AJ23">
-        <v>26</v>
-      </c>
-      <c r="AK23">
-        <v>17.5</v>
-      </c>
-      <c r="AL23">
-        <v>22</v>
-      </c>
-      <c r="AM23">
-        <v>48</v>
-      </c>
-      <c r="AN23">
-        <v>5.9</v>
-      </c>
-      <c r="AO23">
-        <v>17.5</v>
-      </c>
-      <c r="AP23">
-        <v>32</v>
-      </c>
-      <c r="AQ23">
-        <v>19</v>
-      </c>
-      <c r="AR23">
-        <v>24</v>
-      </c>
-      <c r="AS23">
-        <v>40</v>
-      </c>
-      <c r="AT23">
-        <v>18</v>
-      </c>
-      <c r="AU23">
-        <v>11.5</v>
-      </c>
-      <c r="AV23">
-        <v>15.5</v>
-      </c>
-      <c r="AW23">
-        <v>21</v>
-      </c>
-      <c r="AX23">
-        <v>16.5</v>
-      </c>
-      <c r="AY23">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23">
-        <v>12.5</v>
-      </c>
-      <c r="BA23">
-        <v>18.5</v>
-      </c>
       <c r="BB23">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BC23">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BD23">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE23">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BF23">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BG23">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6535,42 +6544,42 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6579,142 +6588,142 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="P24">
-        <v>2.48</v>
+        <v>1.26</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="R24">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
-        <v>2.34</v>
+        <v>1.09</v>
       </c>
       <c r="T24">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6777,42 +6786,42 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F25">
-        <v>2.78</v>
+        <v>1.14</v>
       </c>
       <c r="G25">
-        <v>3.4</v>
+        <v>130</v>
       </c>
       <c r="H25">
-        <v>2.24</v>
+        <v>1.14</v>
       </c>
       <c r="I25">
-        <v>2.58</v>
+        <v>120</v>
       </c>
       <c r="J25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="K25">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6821,22 +6830,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="O25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P25">
-        <v>2.58</v>
+        <v>1.26</v>
       </c>
       <c r="Q25">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="R25">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S25">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6845,10 +6854,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="W25">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7019,36 +7028,36 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F26">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G26">
+        <v>160</v>
+      </c>
+      <c r="H26">
+        <v>1.14</v>
+      </c>
+      <c r="I26">
         <v>110</v>
-      </c>
-      <c r="H26">
-        <v>1.12</v>
-      </c>
-      <c r="I26">
-        <v>120</v>
       </c>
       <c r="J26">
         <v>1.14</v>
@@ -7063,35 +7072,35 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O26">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P26">
         <v>1.26</v>
       </c>
       <c r="Q26">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="R26">
         <v>1.25</v>
       </c>
       <c r="S26">
+        <v>1.11</v>
+      </c>
+      <c r="T26">
+        <v>1.01</v>
+      </c>
+      <c r="U26">
+        <v>1.01</v>
+      </c>
+      <c r="V26">
         <v>1.08</v>
       </c>
-      <c r="T26">
-        <v>1.01</v>
-      </c>
-      <c r="U26">
-        <v>1.01</v>
-      </c>
-      <c r="V26">
+      <c r="W26">
         <v>1.05</v>
       </c>
-      <c r="W26">
-        <v>1.08</v>
-      </c>
       <c r="X26">
         <v>1000</v>
       </c>
@@ -7261,24 +7270,24 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F27">
         <v>1.04</v>
@@ -7293,7 +7302,7 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K27">
         <v>330</v>
@@ -7503,186 +7512,186 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F28">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H28">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="I28">
-        <v>140</v>
+        <v>2.22</v>
       </c>
       <c r="J28">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="O28">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="P28">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q28">
-        <v>1.09</v>
+        <v>1.75</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S28">
-        <v>1.11</v>
+        <v>2.86</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7745,42 +7754,42 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F29">
-        <v>1.12</v>
+        <v>2.78</v>
       </c>
       <c r="G29">
-        <v>140</v>
+        <v>3.4</v>
       </c>
       <c r="H29">
-        <v>1.12</v>
+        <v>2.24</v>
       </c>
       <c r="I29">
-        <v>120</v>
+        <v>2.58</v>
       </c>
       <c r="J29">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="K29">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7789,22 +7798,22 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="O29">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P29">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="R29">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="S29">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="T29">
         <v>1.01</v>
@@ -7813,10 +7822,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7987,42 +7996,42 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8031,142 +8040,142 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="O30">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="P30">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q30">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="R30">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="S30">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8229,187 +8238,187 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F31">
-        <v>3.45</v>
+        <v>1.81</v>
       </c>
       <c r="G31">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="H31">
-        <v>1.92</v>
+        <v>3.5</v>
       </c>
       <c r="I31">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="J31">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="K31">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L31">
         <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="P31">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="R31">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="T31">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="U31">
-        <v>2.14</v>
+        <v>3.05</v>
       </c>
       <c r="V31">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.29</v>
+        <v>2.02</v>
       </c>
       <c r="X31">
+        <v>60</v>
+      </c>
+      <c r="Y31">
+        <v>34</v>
+      </c>
+      <c r="Z31">
+        <v>48</v>
+      </c>
+      <c r="AA31">
+        <v>85</v>
+      </c>
+      <c r="AB31">
+        <v>23</v>
+      </c>
+      <c r="AC31">
+        <v>14.5</v>
+      </c>
+      <c r="AD31">
+        <v>19</v>
+      </c>
+      <c r="AE31">
+        <v>36</v>
+      </c>
+      <c r="AF31">
+        <v>21</v>
+      </c>
+      <c r="AG31">
+        <v>13</v>
+      </c>
+      <c r="AH31">
+        <v>15.5</v>
+      </c>
+      <c r="AI31">
+        <v>32</v>
+      </c>
+      <c r="AJ31">
+        <v>26</v>
+      </c>
+      <c r="AK31">
+        <v>17.5</v>
+      </c>
+      <c r="AL31">
         <v>22</v>
       </c>
-      <c r="Y31">
-        <v>12</v>
-      </c>
-      <c r="Z31">
+      <c r="AM31">
+        <v>48</v>
+      </c>
+      <c r="AN31">
+        <v>5.9</v>
+      </c>
+      <c r="AO31">
+        <v>17</v>
+      </c>
+      <c r="AP31">
+        <v>1.01</v>
+      </c>
+      <c r="AQ31">
+        <v>19</v>
+      </c>
+      <c r="AR31">
+        <v>24</v>
+      </c>
+      <c r="AS31">
+        <v>1.01</v>
+      </c>
+      <c r="AT31">
+        <v>18</v>
+      </c>
+      <c r="AU31">
+        <v>11.5</v>
+      </c>
+      <c r="AV31">
         <v>15.5</v>
       </c>
-      <c r="AA31">
-        <v>27</v>
-      </c>
-      <c r="AB31">
-        <v>18</v>
-      </c>
-      <c r="AC31">
-        <v>9.6</v>
-      </c>
-      <c r="AD31">
-        <v>12</v>
-      </c>
-      <c r="AE31">
+      <c r="AW31">
+        <v>21</v>
+      </c>
+      <c r="AX31">
+        <v>16.5</v>
+      </c>
+      <c r="AY31">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31">
+        <v>12.5</v>
+      </c>
+      <c r="BA31">
+        <v>18.5</v>
+      </c>
+      <c r="BB31">
+        <v>20</v>
+      </c>
+      <c r="BC31">
+        <v>14</v>
+      </c>
+      <c r="BD31">
+        <v>17.5</v>
+      </c>
+      <c r="BE31">
         <v>23</v>
       </c>
-      <c r="AF31">
-        <v>32</v>
-      </c>
-      <c r="AG31">
-        <v>17.5</v>
-      </c>
-      <c r="AH31">
-        <v>18.5</v>
-      </c>
-      <c r="AI31">
-        <v>36</v>
-      </c>
-      <c r="AJ31">
-        <v>80</v>
-      </c>
-      <c r="AK31">
-        <v>50</v>
-      </c>
-      <c r="AL31">
-        <v>60</v>
-      </c>
-      <c r="AM31">
-        <v>90</v>
-      </c>
-      <c r="AN31">
-        <v>44</v>
-      </c>
-      <c r="AO31">
+      <c r="BF31">
+        <v>5</v>
+      </c>
+      <c r="BG31">
         <v>14</v>
       </c>
-      <c r="AP31">
-        <v>12.5</v>
-      </c>
-      <c r="AQ31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR31">
-        <v>11</v>
-      </c>
-      <c r="AS31">
-        <v>20</v>
-      </c>
-      <c r="AT31">
-        <v>11.5</v>
-      </c>
-      <c r="AU31">
-        <v>7.2</v>
-      </c>
-      <c r="AV31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW31">
-        <v>16.5</v>
-      </c>
-      <c r="AX31">
-        <v>23</v>
-      </c>
-      <c r="AY31">
-        <v>11.5</v>
-      </c>
-      <c r="AZ31">
-        <v>12</v>
-      </c>
-      <c r="BA31">
-        <v>23</v>
-      </c>
-      <c r="BB31">
-        <v>50</v>
-      </c>
-      <c r="BC31">
-        <v>30</v>
-      </c>
-      <c r="BD31">
-        <v>34</v>
-      </c>
-      <c r="BE31">
-        <v>55</v>
-      </c>
-      <c r="BF31">
-        <v>30</v>
-      </c>
-      <c r="BG31">
-        <v>10.5</v>
-      </c>
       <c r="BH31">
         <v>1000</v>
       </c>
@@ -8471,66 +8480,66 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
         <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F32">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="G32">
-        <v>2.02</v>
+        <v>110</v>
       </c>
       <c r="H32">
-        <v>3.85</v>
+        <v>1.15</v>
       </c>
       <c r="I32">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>3.45</v>
+        <v>1.14</v>
       </c>
       <c r="K32">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L32">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>1.27</v>
       </c>
       <c r="O32">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="P32">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="Q32">
-        <v>1.86</v>
+        <v>1.07</v>
       </c>
       <c r="R32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S32">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8539,10 +8548,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="W32">
-        <v>1.98</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8713,66 +8722,66 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
         <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F33">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="G33">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="H33">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="K33">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N33">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O33">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="P33">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="Q33">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="R33">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S33">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="T33">
         <v>1.01</v>
@@ -8781,118 +8790,118 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W33">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="X33">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8955,186 +8964,186 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F34">
-        <v>2.24</v>
+        <v>1.58</v>
       </c>
       <c r="G34">
-        <v>2.42</v>
+        <v>1.66</v>
       </c>
       <c r="H34">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="I34">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J34">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="K34">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="L34">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N34">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O34">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="P34">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="Q34">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="R34">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S34">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="T34">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="U34">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
-        <v>1.7</v>
+        <v>2.52</v>
       </c>
       <c r="X34">
+        <v>24</v>
+      </c>
+      <c r="Y34">
+        <v>28</v>
+      </c>
+      <c r="Z34">
+        <v>60</v>
+      </c>
+      <c r="AA34">
+        <v>170</v>
+      </c>
+      <c r="AB34">
+        <v>12</v>
+      </c>
+      <c r="AC34">
+        <v>12</v>
+      </c>
+      <c r="AD34">
+        <v>27</v>
+      </c>
+      <c r="AE34">
+        <v>85</v>
+      </c>
+      <c r="AF34">
         <v>12.5</v>
       </c>
-      <c r="Y34">
-        <v>13</v>
-      </c>
-      <c r="Z34">
-        <v>38</v>
-      </c>
-      <c r="AA34">
-        <v>100</v>
-      </c>
-      <c r="AB34">
-        <v>9.4</v>
-      </c>
-      <c r="AC34">
-        <v>7.6</v>
-      </c>
-      <c r="AD34">
-        <v>15.5</v>
-      </c>
-      <c r="AE34">
-        <v>60</v>
-      </c>
-      <c r="AF34">
-        <v>970</v>
-      </c>
       <c r="AG34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH34">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI34">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ34">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AK34">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AL34">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM34">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN34">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AO34">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AP34">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ34">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AR34">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="AS34">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AT34">
+        <v>8</v>
+      </c>
+      <c r="AU34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV34">
+        <v>17.5</v>
+      </c>
+      <c r="AW34">
+        <v>4.9</v>
+      </c>
+      <c r="AX34">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU34">
-        <v>6.6</v>
-      </c>
-      <c r="AV34">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW34">
-        <v>27</v>
-      </c>
-      <c r="AX34">
-        <v>12.5</v>
-      </c>
       <c r="AY34">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BA34">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="BB34">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BC34">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BD34">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BE34">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF34">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG34">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9197,7 +9206,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9205,179 +9214,179 @@
         <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
         <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F35">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="G35">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="H35">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="I35">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="J35">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K35">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M35">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N35">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O35">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P35">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Q35">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="R35">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S35">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="T35">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="X35">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y35">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z35">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA35">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB35">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AC35">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD35">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE35">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF35">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG35">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH35">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AI35">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ35">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AK35">
         <v>27</v>
       </c>
       <c r="AL35">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AM35">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AN35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO35">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AP35">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AQ35">
+        <v>11</v>
+      </c>
+      <c r="AR35">
+        <v>15</v>
+      </c>
+      <c r="AS35">
+        <v>9.4</v>
+      </c>
+      <c r="AT35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU35">
+        <v>6.6</v>
+      </c>
+      <c r="AV35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW35">
+        <v>27</v>
+      </c>
+      <c r="AX35">
         <v>12.5</v>
       </c>
-      <c r="AR35">
-        <v>17.5</v>
-      </c>
-      <c r="AS35">
-        <v>38</v>
-      </c>
-      <c r="AT35">
-        <v>11.5</v>
-      </c>
-      <c r="AU35">
-        <v>7.6</v>
-      </c>
-      <c r="AV35">
-        <v>12</v>
-      </c>
-      <c r="AW35">
-        <v>26</v>
-      </c>
-      <c r="AX35">
-        <v>16</v>
-      </c>
       <c r="AY35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ35">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BA35">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BB35">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BC35">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE35">
+        <v>9.6</v>
+      </c>
+      <c r="BF35">
+        <v>13.5</v>
+      </c>
+      <c r="BG35">
         <v>30</v>
       </c>
-      <c r="BE35">
-        <v>32</v>
-      </c>
-      <c r="BF35">
-        <v>16</v>
-      </c>
-      <c r="BG35">
-        <v>19.5</v>
-      </c>
       <c r="BH35">
         <v>1000</v>
       </c>
@@ -9439,7 +9448,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9447,178 +9456,178 @@
         <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F36">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="G36">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="H36">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="I36">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="J36">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K36">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="M36">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O36">
+        <v>1.25</v>
+      </c>
+      <c r="P36">
+        <v>2.16</v>
+      </c>
+      <c r="Q36">
+        <v>1.76</v>
+      </c>
+      <c r="R36">
         <v>1.45</v>
       </c>
-      <c r="P36">
-        <v>1.69</v>
-      </c>
-      <c r="Q36">
-        <v>2.4</v>
-      </c>
-      <c r="R36">
-        <v>1.25</v>
-      </c>
       <c r="S36">
-        <v>4.7</v>
+        <v>2.94</v>
       </c>
       <c r="T36">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="U36">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="Y36">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z36">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA36">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AB36">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AC36">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE36">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF36">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AG36">
         <v>12</v>
       </c>
       <c r="AH36">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI36">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AJ36">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK36">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL36">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM36">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AN36">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AO36">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AP36">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AQ36">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR36">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS36">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT36">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU36">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV36">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX36">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AY36">
         <v>10.5</v>
       </c>
       <c r="AZ36">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA36">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BB36">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC36">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BD36">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BE36">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF36">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BG36">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9681,186 +9690,186 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
         <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F37">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="G37">
-        <v>140</v>
+        <v>2.42</v>
       </c>
       <c r="H37">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="I37">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J37">
+        <v>3.15</v>
+      </c>
+      <c r="K37">
+        <v>3.2</v>
+      </c>
+      <c r="L37">
+        <v>1.52</v>
+      </c>
+      <c r="M37">
         <v>1.11</v>
       </c>
-      <c r="K37">
-        <v>1000</v>
-      </c>
-      <c r="L37">
-        <v>1.01</v>
-      </c>
-      <c r="M37">
-        <v>1.01</v>
-      </c>
       <c r="N37">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="P37">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="Q37">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="R37">
         <v>1.25</v>
       </c>
       <c r="S37">
-        <v>1.07</v>
+        <v>4.7</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V37">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z37">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA37">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD37">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH37">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM37">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO37">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9923,42 +9932,42 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F38">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="G38">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H38">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="I38">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J38">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="K38">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -9967,22 +9976,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O38">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="P38">
         <v>1.26</v>
       </c>
       <c r="Q38">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="R38">
         <v>1.25</v>
       </c>
       <c r="S38">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -9991,10 +10000,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10165,7 +10174,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10173,34 +10182,34 @@
         <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10209,34 +10218,34 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O39">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="P39">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q39">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="R39">
         <v>1.25</v>
       </c>
       <c r="S39">
+        <v>1.16</v>
+      </c>
+      <c r="T39">
+        <v>1.01</v>
+      </c>
+      <c r="U39">
+        <v>1.01</v>
+      </c>
+      <c r="V39">
         <v>1.06</v>
       </c>
-      <c r="T39">
-        <v>1.01</v>
-      </c>
-      <c r="U39">
-        <v>1.01</v>
-      </c>
-      <c r="V39">
-        <v>1.01</v>
-      </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10407,186 +10416,186 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F40">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.01</v>
+      </c>
+      <c r="N40">
+        <v>1.26</v>
+      </c>
+      <c r="O40">
+        <v>1.05</v>
+      </c>
+      <c r="P40">
+        <v>1.26</v>
+      </c>
+      <c r="Q40">
+        <v>1.05</v>
+      </c>
+      <c r="R40">
         <v>1.25</v>
       </c>
-      <c r="J40">
-        <v>7</v>
-      </c>
-      <c r="K40">
-        <v>7.4</v>
-      </c>
-      <c r="L40">
-        <v>1.01</v>
-      </c>
-      <c r="M40">
-        <v>1.03</v>
-      </c>
-      <c r="N40">
-        <v>5</v>
-      </c>
-      <c r="O40">
-        <v>1.2</v>
-      </c>
-      <c r="P40">
-        <v>2.4</v>
-      </c>
-      <c r="Q40">
-        <v>1.62</v>
-      </c>
-      <c r="R40">
-        <v>1.56</v>
-      </c>
       <c r="S40">
-        <v>2.54</v>
+        <v>1.06</v>
       </c>
       <c r="T40">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U40">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X40">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y40">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z40">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AA40">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AB40">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC40">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD40">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE40">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF40">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AG40">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AH40">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI40">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ40">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AK40">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AL40">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM40">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN40">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO40">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AP40">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR40">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS40">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT40">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AU40">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV40">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW40">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX40">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY40">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BA40">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB40">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC40">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD40">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE40">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF40">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG40">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10595,240 +10604,240 @@
         <v>1.01</v>
       </c>
       <c r="BJ40">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN40">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU40">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BV40">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW40">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX40">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY40">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA40">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
         <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F41">
-        <v>1.36</v>
+        <v>16.5</v>
       </c>
       <c r="G41">
-        <v>1.38</v>
+        <v>19</v>
       </c>
       <c r="H41">
-        <v>10</v>
+        <v>1.24</v>
       </c>
       <c r="I41">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="J41">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="L41">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N41">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P41">
+        <v>2.36</v>
+      </c>
+      <c r="Q41">
+        <v>1.62</v>
+      </c>
+      <c r="R41">
+        <v>1.56</v>
+      </c>
+      <c r="S41">
+        <v>2.54</v>
+      </c>
+      <c r="T41">
         <v>2.26</v>
       </c>
-      <c r="Q41">
-        <v>1.69</v>
-      </c>
-      <c r="R41">
-        <v>1.46</v>
-      </c>
-      <c r="S41">
-        <v>2.74</v>
-      </c>
-      <c r="T41">
-        <v>2.08</v>
-      </c>
       <c r="U41">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="V41">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>3.6</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>25</v>
       </c>
       <c r="Y41">
+        <v>9.4</v>
+      </c>
+      <c r="Z41">
+        <v>7.8</v>
+      </c>
+      <c r="AA41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AB41">
+        <v>55</v>
+      </c>
+      <c r="AC41">
+        <v>16</v>
+      </c>
+      <c r="AD41">
+        <v>12</v>
+      </c>
+      <c r="AE41">
+        <v>15</v>
+      </c>
+      <c r="AF41">
+        <v>180</v>
+      </c>
+      <c r="AG41">
+        <v>65</v>
+      </c>
+      <c r="AH41">
         <v>40</v>
       </c>
-      <c r="Z41">
-        <v>130</v>
-      </c>
-      <c r="AA41">
-        <v>540</v>
-      </c>
-      <c r="AB41">
-        <v>10.5</v>
-      </c>
-      <c r="AC41">
-        <v>15.5</v>
-      </c>
-      <c r="AD41">
-        <v>48</v>
-      </c>
-      <c r="AE41">
-        <v>230</v>
-      </c>
-      <c r="AF41">
-        <v>8.4</v>
-      </c>
-      <c r="AG41">
+      <c r="AI41">
+        <v>50</v>
+      </c>
+      <c r="AJ41">
+        <v>990</v>
+      </c>
+      <c r="AK41">
+        <v>360</v>
+      </c>
+      <c r="AL41">
+        <v>260</v>
+      </c>
+      <c r="AM41">
+        <v>250</v>
+      </c>
+      <c r="AN41">
+        <v>500</v>
+      </c>
+      <c r="AO41">
+        <v>4.6</v>
+      </c>
+      <c r="AP41">
+        <v>20</v>
+      </c>
+      <c r="AQ41">
+        <v>7.8</v>
+      </c>
+      <c r="AR41">
+        <v>6.8</v>
+      </c>
+      <c r="AS41">
+        <v>8</v>
+      </c>
+      <c r="AT41">
+        <v>40</v>
+      </c>
+      <c r="AU41">
+        <v>13.5</v>
+      </c>
+      <c r="AV41">
+        <v>10</v>
+      </c>
+      <c r="AW41">
         <v>13</v>
       </c>
-      <c r="AH41">
-        <v>38</v>
-      </c>
-      <c r="AI41">
-        <v>180</v>
-      </c>
-      <c r="AJ41">
-        <v>13</v>
-      </c>
-      <c r="AK41">
-        <v>18.5</v>
-      </c>
-      <c r="AL41">
+      <c r="AX41">
+        <v>11</v>
+      </c>
+      <c r="AY41">
         <v>50</v>
       </c>
-      <c r="AM41">
-        <v>220</v>
-      </c>
-      <c r="AN41">
-        <v>5.9</v>
-      </c>
-      <c r="AO41">
-        <v>330</v>
-      </c>
-      <c r="AP41">
-        <v>15</v>
-      </c>
-      <c r="AQ41">
-        <v>4.7</v>
-      </c>
-      <c r="AR41">
-        <v>5.1</v>
-      </c>
-      <c r="AS41">
-        <v>5.3</v>
-      </c>
-      <c r="AT41">
-        <v>6.4</v>
-      </c>
-      <c r="AU41">
-        <v>10.5</v>
-      </c>
-      <c r="AV41">
-        <v>4.8</v>
-      </c>
-      <c r="AW41">
-        <v>5.2</v>
-      </c>
-      <c r="AX41">
-        <v>6</v>
-      </c>
-      <c r="AY41">
-        <v>8</v>
-      </c>
       <c r="AZ41">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BA41">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB41">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BC41">
         <v>11</v>
       </c>
       <c r="BD41">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BE41">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BF41">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG41">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10837,303 +10846,545 @@
         <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN41">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="BO41">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="BP41">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
+        <v>21</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
+        <v>21</v>
+      </c>
+      <c r="BT41">
         <v>4.9</v>
       </c>
-      <c r="BR41">
+      <c r="BU41">
+        <v>2.54</v>
+      </c>
+      <c r="BV41">
+        <v>9.6</v>
+      </c>
+      <c r="BW41">
+        <v>4.4</v>
+      </c>
+      <c r="BX41">
         <v>36</v>
       </c>
-      <c r="BS41">
-        <v>1.01</v>
-      </c>
-      <c r="BT41">
-        <v>20</v>
-      </c>
-      <c r="BU41">
-        <v>1.01</v>
-      </c>
-      <c r="BV41">
-        <v>1000</v>
-      </c>
-      <c r="BW41">
-        <v>1.01</v>
-      </c>
-      <c r="BX41">
-        <v>1000</v>
-      </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BZ41">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB41" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
         <v>124</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F42">
+        <v>1.36</v>
+      </c>
+      <c r="G42">
+        <v>1.38</v>
+      </c>
+      <c r="H42">
+        <v>10</v>
+      </c>
+      <c r="I42">
+        <v>12.5</v>
+      </c>
+      <c r="J42">
+        <v>5.4</v>
+      </c>
+      <c r="K42">
+        <v>5.9</v>
+      </c>
+      <c r="L42">
+        <v>1.31</v>
+      </c>
+      <c r="M42">
+        <v>1.05</v>
+      </c>
+      <c r="N42">
+        <v>4.5</v>
+      </c>
+      <c r="O42">
+        <v>1.22</v>
+      </c>
+      <c r="P42">
+        <v>2.26</v>
+      </c>
+      <c r="Q42">
+        <v>1.69</v>
+      </c>
+      <c r="R42">
+        <v>1.46</v>
+      </c>
+      <c r="S42">
+        <v>2.74</v>
+      </c>
+      <c r="T42">
+        <v>2.08</v>
+      </c>
+      <c r="U42">
+        <v>1.75</v>
+      </c>
+      <c r="V42">
+        <v>1.1</v>
+      </c>
+      <c r="W42">
+        <v>3.6</v>
+      </c>
+      <c r="X42">
+        <v>25</v>
+      </c>
+      <c r="Y42">
+        <v>40</v>
+      </c>
+      <c r="Z42">
+        <v>130</v>
+      </c>
+      <c r="AA42">
+        <v>530</v>
+      </c>
+      <c r="AB42">
+        <v>10.5</v>
+      </c>
+      <c r="AC42">
+        <v>15.5</v>
+      </c>
+      <c r="AD42">
+        <v>48</v>
+      </c>
+      <c r="AE42">
+        <v>230</v>
+      </c>
+      <c r="AF42">
+        <v>8.4</v>
+      </c>
+      <c r="AG42">
+        <v>13</v>
+      </c>
+      <c r="AH42">
+        <v>38</v>
+      </c>
+      <c r="AI42">
+        <v>180</v>
+      </c>
+      <c r="AJ42">
+        <v>13</v>
+      </c>
+      <c r="AK42">
+        <v>18.5</v>
+      </c>
+      <c r="AL42">
+        <v>50</v>
+      </c>
+      <c r="AM42">
+        <v>220</v>
+      </c>
+      <c r="AN42">
+        <v>5.9</v>
+      </c>
+      <c r="AO42">
+        <v>330</v>
+      </c>
+      <c r="AP42">
+        <v>15</v>
+      </c>
+      <c r="AQ42">
+        <v>4.7</v>
+      </c>
+      <c r="AR42">
+        <v>5.2</v>
+      </c>
+      <c r="AS42">
+        <v>5.3</v>
+      </c>
+      <c r="AT42">
+        <v>6.4</v>
+      </c>
+      <c r="AU42">
+        <v>10.5</v>
+      </c>
+      <c r="AV42">
+        <v>4.8</v>
+      </c>
+      <c r="AW42">
+        <v>5.2</v>
+      </c>
+      <c r="AX42">
+        <v>6</v>
+      </c>
+      <c r="AY42">
+        <v>8</v>
+      </c>
+      <c r="AZ42">
+        <v>4.7</v>
+      </c>
+      <c r="BA42">
+        <v>5.2</v>
+      </c>
+      <c r="BB42">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC42">
+        <v>11</v>
+      </c>
+      <c r="BD42">
+        <v>4.8</v>
+      </c>
+      <c r="BE42">
+        <v>5.2</v>
+      </c>
+      <c r="BF42">
+        <v>4.3</v>
+      </c>
+      <c r="BG42">
+        <v>5.3</v>
+      </c>
+      <c r="BH42">
+        <v>1000</v>
+      </c>
+      <c r="BI42">
+        <v>1.91</v>
+      </c>
+      <c r="BJ42">
+        <v>18</v>
+      </c>
+      <c r="BK42">
+        <v>1.73</v>
+      </c>
+      <c r="BL42">
+        <v>1000</v>
+      </c>
+      <c r="BM42">
+        <v>1.91</v>
+      </c>
+      <c r="BN42">
+        <v>5.1</v>
+      </c>
+      <c r="BO42">
+        <v>2.6</v>
+      </c>
+      <c r="BP42">
+        <v>11</v>
+      </c>
+      <c r="BQ42">
+        <v>4.9</v>
+      </c>
+      <c r="BR42">
+        <v>36</v>
+      </c>
+      <c r="BS42">
+        <v>1.82</v>
+      </c>
+      <c r="BT42">
+        <v>20</v>
+      </c>
+      <c r="BU42">
+        <v>1.74</v>
+      </c>
+      <c r="BV42">
+        <v>1000</v>
+      </c>
+      <c r="BW42">
+        <v>1.91</v>
+      </c>
+      <c r="BX42">
+        <v>1000</v>
+      </c>
+      <c r="BY42">
+        <v>1.91</v>
+      </c>
+      <c r="BZ42">
+        <v>18.5</v>
+      </c>
+      <c r="CA42">
+        <v>1.73</v>
+      </c>
+      <c r="CB42" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:80">
+      <c r="A43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43">
         <v>2.36</v>
       </c>
-      <c r="G42">
+      <c r="G43">
         <v>2.56</v>
       </c>
-      <c r="H42">
+      <c r="H43">
         <v>3.65</v>
       </c>
-      <c r="I42">
+      <c r="I43">
         <v>4.1</v>
       </c>
-      <c r="J42">
+      <c r="J43">
         <v>2.86</v>
       </c>
-      <c r="K42">
+      <c r="K43">
         <v>3.1</v>
       </c>
-      <c r="L42">
-        <v>1.01</v>
-      </c>
-      <c r="M42">
-        <v>1.01</v>
-      </c>
-      <c r="N42">
+      <c r="L43">
+        <v>1.01</v>
+      </c>
+      <c r="M43">
+        <v>1.08</v>
+      </c>
+      <c r="N43">
         <v>1.45</v>
       </c>
-      <c r="O42">
-        <v>1.59</v>
-      </c>
-      <c r="P42">
+      <c r="O43">
+        <v>1.63</v>
+      </c>
+      <c r="P43">
         <v>1.45</v>
       </c>
-      <c r="Q42">
-        <v>2.8</v>
-      </c>
-      <c r="R42">
+      <c r="Q43">
+        <v>2.88</v>
+      </c>
+      <c r="R43">
         <v>1.14</v>
       </c>
-      <c r="S42">
-        <v>2.8</v>
-      </c>
-      <c r="T42">
+      <c r="S43">
+        <v>2.88</v>
+      </c>
+      <c r="T43">
         <v>2.18</v>
       </c>
-      <c r="U42">
-        <v>1.65</v>
-      </c>
-      <c r="V42">
+      <c r="U43">
+        <v>1.01</v>
+      </c>
+      <c r="V43">
         <v>1.32</v>
       </c>
-      <c r="W42">
+      <c r="W43">
         <v>1.64</v>
       </c>
-      <c r="X42">
-        <v>1000</v>
-      </c>
-      <c r="Y42">
-        <v>1000</v>
-      </c>
-      <c r="Z42">
-        <v>1000</v>
-      </c>
-      <c r="AA42">
-        <v>1000</v>
-      </c>
-      <c r="AB42">
-        <v>1000</v>
-      </c>
-      <c r="AC42">
-        <v>1000</v>
-      </c>
-      <c r="AD42">
-        <v>1000</v>
-      </c>
-      <c r="AE42">
-        <v>1000</v>
-      </c>
-      <c r="AF42">
-        <v>1000</v>
-      </c>
-      <c r="AG42">
-        <v>1000</v>
-      </c>
-      <c r="AH42">
-        <v>1000</v>
-      </c>
-      <c r="AI42">
-        <v>1000</v>
-      </c>
-      <c r="AJ42">
-        <v>1000</v>
-      </c>
-      <c r="AK42">
-        <v>1000</v>
-      </c>
-      <c r="AL42">
-        <v>1000</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>1000</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
+      <c r="X43">
+        <v>1000</v>
+      </c>
+      <c r="Y43">
+        <v>1000</v>
+      </c>
+      <c r="Z43">
+        <v>1000</v>
+      </c>
+      <c r="AA43">
+        <v>1000</v>
+      </c>
+      <c r="AB43">
+        <v>1000</v>
+      </c>
+      <c r="AC43">
+        <v>1000</v>
+      </c>
+      <c r="AD43">
+        <v>1000</v>
+      </c>
+      <c r="AE43">
+        <v>1000</v>
+      </c>
+      <c r="AF43">
+        <v>1000</v>
+      </c>
+      <c r="AG43">
+        <v>1000</v>
+      </c>
+      <c r="AH43">
+        <v>1000</v>
+      </c>
+      <c r="AI43">
+        <v>1000</v>
+      </c>
+      <c r="AJ43">
+        <v>1000</v>
+      </c>
+      <c r="AK43">
+        <v>1000</v>
+      </c>
+      <c r="AL43">
+        <v>1000</v>
+      </c>
+      <c r="AM43">
+        <v>1000</v>
+      </c>
+      <c r="AN43">
+        <v>1000</v>
+      </c>
+      <c r="AO43">
+        <v>1000</v>
+      </c>
+      <c r="AP43">
         <v>6.4</v>
       </c>
-      <c r="AQ42">
+      <c r="AQ43">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR42">
+      <c r="AR43">
         <v>17.5</v>
       </c>
-      <c r="AS42">
+      <c r="AS43">
         <v>48</v>
       </c>
-      <c r="AT42">
+      <c r="AT43">
         <v>5.7</v>
       </c>
-      <c r="AU42">
+      <c r="AU43">
         <v>6</v>
       </c>
-      <c r="AV42">
+      <c r="AV43">
         <v>13.5</v>
       </c>
-      <c r="AW42">
+      <c r="AW43">
         <v>42</v>
       </c>
-      <c r="AX42">
+      <c r="AX43">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY42">
+      <c r="AY43">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ42">
+      <c r="AZ43">
         <v>20</v>
       </c>
-      <c r="BA42">
+      <c r="BA43">
         <v>85</v>
       </c>
-      <c r="BB42">
+      <c r="BB43">
         <v>27</v>
       </c>
-      <c r="BC42">
+      <c r="BC43">
         <v>27</v>
       </c>
-      <c r="BD42">
+      <c r="BD43">
         <v>46</v>
       </c>
-      <c r="BE42">
+      <c r="BE43">
         <v>100</v>
       </c>
-      <c r="BF42">
-        <v>1.01</v>
-      </c>
-      <c r="BG42">
-        <v>1.01</v>
-      </c>
-      <c r="BH42">
-        <v>1000</v>
-      </c>
-      <c r="BI42">
-        <v>1.01</v>
-      </c>
-      <c r="BJ42">
-        <v>1000</v>
-      </c>
-      <c r="BK42">
-        <v>1.01</v>
-      </c>
-      <c r="BL42">
-        <v>1000</v>
-      </c>
-      <c r="BM42">
-        <v>1.01</v>
-      </c>
-      <c r="BN42">
-        <v>1000</v>
-      </c>
-      <c r="BO42">
-        <v>1.01</v>
-      </c>
-      <c r="BP42">
-        <v>1000</v>
-      </c>
-      <c r="BQ42">
-        <v>1.01</v>
-      </c>
-      <c r="BR42">
-        <v>1000</v>
-      </c>
-      <c r="BS42">
-        <v>1.01</v>
-      </c>
-      <c r="BT42">
-        <v>1000</v>
-      </c>
-      <c r="BU42">
-        <v>1.01</v>
-      </c>
-      <c r="BV42">
-        <v>1000</v>
-      </c>
-      <c r="BW42">
-        <v>1.01</v>
-      </c>
-      <c r="BX42">
-        <v>1000</v>
-      </c>
-      <c r="BY42">
-        <v>1.01</v>
-      </c>
-      <c r="BZ42">
-        <v>1000</v>
-      </c>
-      <c r="CA42">
-        <v>1.01</v>
-      </c>
-      <c r="CB42" t="s">
-        <v>207</v>
+      <c r="BF43">
+        <v>1.01</v>
+      </c>
+      <c r="BG43">
+        <v>1.01</v>
+      </c>
+      <c r="BH43">
+        <v>1000</v>
+      </c>
+      <c r="BI43">
+        <v>1.01</v>
+      </c>
+      <c r="BJ43">
+        <v>1000</v>
+      </c>
+      <c r="BK43">
+        <v>1.01</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>1.01</v>
+      </c>
+      <c r="BN43">
+        <v>1000</v>
+      </c>
+      <c r="BO43">
+        <v>1.01</v>
+      </c>
+      <c r="BP43">
+        <v>1000</v>
+      </c>
+      <c r="BQ43">
+        <v>1.01</v>
+      </c>
+      <c r="BR43">
+        <v>1000</v>
+      </c>
+      <c r="BS43">
+        <v>1.01</v>
+      </c>
+      <c r="BT43">
+        <v>1000</v>
+      </c>
+      <c r="BU43">
+        <v>1.01</v>
+      </c>
+      <c r="BV43">
+        <v>1000</v>
+      </c>
+      <c r="BW43">
+        <v>1.01</v>
+      </c>
+      <c r="BX43">
+        <v>1000</v>
+      </c>
+      <c r="BY43">
+        <v>1.01</v>
+      </c>
+      <c r="BZ43">
+        <v>1000</v>
+      </c>
+      <c r="CA43">
+        <v>1.01</v>
+      </c>
+      <c r="CB43" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="228">
   <si>
     <t>League</t>
   </si>
@@ -268,34 +268,40 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Slovakian 2 Liga</t>
-  </si>
-  <si>
-    <t>Finnish Veikkausliiga</t>
-  </si>
-  <si>
-    <t>Lithuanian A Lyga</t>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
   </si>
   <si>
     <t>Azerbaijan Premier League</t>
   </si>
   <si>
-    <t>Hungarian NB I</t>
-  </si>
-  <si>
-    <t>Romanian Liga I</t>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
   </si>
   <si>
     <t>Czech 2 Liga</t>
   </si>
   <si>
-    <t>Armenian Premier League</t>
-  </si>
-  <si>
-    <t>Bulgarian A League</t>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
   </si>
   <si>
     <t>Spanish Segunda Division</t>
@@ -304,24 +310,18 @@
     <t>Swedish Allsvenskan</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
-    <t>Icelandic 1 Deild</t>
-  </si>
-  <si>
-    <t>Serbian Super League</t>
-  </si>
-  <si>
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
@@ -337,6 +337,12 @@
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
+    <t>Brazilian Serie C</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
     <t>2026-08-17</t>
   </si>
   <si>
@@ -394,6 +400,15 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
@@ -412,37 +427,43 @@
     <t>Tijuana</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava II</t>
+  </si>
+  <si>
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
-    <t>Slovan Bratislava II</t>
-  </si>
-  <si>
-    <t>Gnistan</t>
-  </si>
-  <si>
-    <t>Fk Siauliai</t>
+    <t>Zalaegerszeg</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Qarabag FK</t>
   </si>
   <si>
-    <t>Zalaegerszeg</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
     <t>FC Dziugas</t>
   </si>
   <si>
+    <t>FC Noah</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
     <t>Trinec</t>
   </si>
   <si>
-    <t>FC Noah</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
+    <t>Brondby</t>
+  </si>
+  <si>
+    <t>Arka Gdynia</t>
   </si>
   <si>
     <t>Sporting Gijon</t>
@@ -451,42 +472,36 @@
     <t>Hacken</t>
   </si>
   <si>
-    <t>Brondby</t>
-  </si>
-  <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
+    <t>IR Reykjavik</t>
+  </si>
+  <si>
+    <t>FK Novi Pazar</t>
+  </si>
+  <si>
     <t>Valur</t>
   </si>
   <si>
-    <t>IR Reykjavik</t>
-  </si>
-  <si>
     <t>Volsungur</t>
   </si>
   <si>
+    <t>Jong FC Utrecht</t>
+  </si>
+  <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
+    <t>Jong Ajax Amsterdam</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
     <t>Leiknir R</t>
   </si>
   <si>
-    <t>FK Novi Pazar</t>
-  </si>
-  <si>
-    <t>Jong Ajax Amsterdam</t>
-  </si>
-  <si>
-    <t>Jong FC Utrecht</t>
-  </si>
-  <si>
-    <t>De Graafschap</t>
-  </si>
-  <si>
-    <t>Grindavik</t>
-  </si>
-  <si>
     <t>Arda</t>
   </si>
   <si>
@@ -502,24 +517,42 @@
     <t>Deportivo</t>
   </si>
   <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Throttur</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>Throttur</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
     <t>Almeria</t>
   </si>
   <si>
     <t>Lanus</t>
   </si>
   <si>
+    <t>Deportes Copiapo</t>
+  </si>
+  <si>
+    <t>Club Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Ferroviaria</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Antofagasta</t>
   </si>
   <si>
@@ -538,37 +571,43 @@
     <t>Cruz Azul</t>
   </si>
   <si>
+    <t>Ilves</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>FK Humenne</t>
+  </si>
+  <si>
     <t>Zorya</t>
   </si>
   <si>
-    <t>FK Humenne</t>
-  </si>
-  <si>
-    <t>Ilves</t>
-  </si>
-  <si>
-    <t>Panevezys</t>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>UTA Arad</t>
   </si>
   <si>
     <t>Shamakhi FK</t>
   </si>
   <si>
-    <t>Ferencvaros</t>
-  </si>
-  <si>
-    <t>UTA Arad</t>
-  </si>
-  <si>
     <t>FK Suduva</t>
   </si>
   <si>
+    <t>Alashkert</t>
+  </si>
+  <si>
+    <t>Septemvri</t>
+  </si>
+  <si>
     <t>Usti nad Labem</t>
   </si>
   <si>
-    <t>Alashkert</t>
-  </si>
-  <si>
-    <t>Septemvri</t>
+    <t>SonderjyskE</t>
+  </si>
+  <si>
+    <t>Puszcza Niepolomice</t>
   </si>
   <si>
     <t>Sabadell</t>
@@ -577,42 +616,36 @@
     <t>Halmstads</t>
   </si>
   <si>
-    <t>SonderjyskE</t>
-  </si>
-  <si>
-    <t>Puszcza Niepolomice</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
+    <t>Njardvik</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
-    <t>Njardvik</t>
-  </si>
-  <si>
     <t>IF Vestri</t>
   </si>
   <si>
+    <t>Vitesse Arnhem</t>
+  </si>
+  <si>
+    <t>Grotta</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
+    <t>Jong AZ Alkmaar</t>
+  </si>
+  <si>
     <t>Aegir</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Emmen</t>
-  </si>
-  <si>
-    <t>Vitesse Arnhem</t>
-  </si>
-  <si>
-    <t>Jong AZ Alkmaar</t>
-  </si>
-  <si>
-    <t>Grotta</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia</t>
   </si>
   <si>
@@ -628,25 +661,43 @@
     <t>Elche</t>
   </si>
   <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Stjarnan</t>
+  </si>
+  <si>
+    <t>Fylkir</t>
+  </si>
+  <si>
     <t>HK Kopavogur</t>
   </si>
   <si>
-    <t>Fylkir</t>
-  </si>
-  <si>
-    <t>Stjarnan</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
     <t>Eldense</t>
   </si>
   <si>
     <t>CA Independiente</t>
   </si>
   <si>
-    <t>2026-08-15 22:07:52</t>
+    <t>Curico Unido</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Ypiranga RS</t>
+  </si>
+  <si>
+    <t>2026-08-16 00:24:53</t>
   </si>
 </sst>
 </file>
@@ -978,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB43"/>
+  <dimension ref="A1:CB49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1228,16 +1279,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F2">
         <v>2.56</v>
@@ -1363,7 +1414,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>10.5</v>
@@ -1405,64 +1456,64 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1470,19 +1521,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
         <v>2.62</v>
@@ -1491,7 +1542,7 @@
         <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
         <v>3.1</v>
@@ -1506,31 +1557,31 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
         <v>4</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.62</v>
@@ -1542,10 +1593,10 @@
         <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB3">
         <v>11.5</v>
@@ -1554,10 +1605,10 @@
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>17</v>
@@ -1572,7 +1623,7 @@
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK3">
         <v>34</v>
@@ -1581,25 +1632,25 @@
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3">
         <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS3">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1608,10 +1659,10 @@
         <v>5.6</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
@@ -1623,64 +1674,64 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>21</v>
+      </c>
+      <c r="BG3">
         <v>34</v>
       </c>
-      <c r="BE3">
-        <v>85</v>
-      </c>
-      <c r="BF3">
-        <v>20</v>
-      </c>
-      <c r="BG3">
-        <v>32</v>
-      </c>
       <c r="BH3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
         <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>4.7</v>
@@ -1689,22 +1740,22 @@
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA3">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1712,16 +1763,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1895,13 +1946,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1913,13 +1964,13 @@
         <v>23</v>
       </c>
       <c r="BQ4">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>5.8</v>
@@ -1931,22 +1982,22 @@
         <v>17</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1954,22 +2005,22 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
         <v>1.57</v>
@@ -2032,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="AB5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AC5">
         <v>11.5</v>
@@ -2047,7 +2098,7 @@
         <v>75</v>
       </c>
       <c r="AG5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH5">
         <v>21</v>
@@ -2056,7 +2107,7 @@
         <v>40</v>
       </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK5">
         <v>100</v>
@@ -2086,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="AT5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2098,31 +2149,31 @@
         <v>13</v>
       </c>
       <c r="AX5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5">
         <v>20</v>
       </c>
       <c r="AZ5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA5">
         <v>20</v>
       </c>
       <c r="BB5">
+        <v>9</v>
+      </c>
+      <c r="BC5">
         <v>8.4</v>
       </c>
-      <c r="BC5">
-        <v>8</v>
-      </c>
       <c r="BD5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5">
         <v>5.8</v>
@@ -2131,64 +2182,64 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2196,22 +2247,22 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F6">
         <v>4.2</v>
       </c>
       <c r="G6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H6">
         <v>1.87</v>
@@ -2220,13 +2271,13 @@
         <v>1.89</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -2235,10 +2286,10 @@
         <v>5.4</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q6">
         <v>1.64</v>
@@ -2268,7 +2319,7 @@
         <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>21</v>
@@ -2313,7 +2364,7 @@
         <v>36</v>
       </c>
       <c r="AO6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2370,7 +2421,7 @@
         <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI6">
         <v>3.3</v>
@@ -2424,13 +2475,13 @@
         <v>16</v>
       </c>
       <c r="BZ6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA6">
         <v>11.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2438,16 +2489,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F7">
         <v>3.35</v>
@@ -2456,7 +2507,7 @@
         <v>3.5</v>
       </c>
       <c r="H7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I7">
         <v>2.34</v>
@@ -2480,10 +2531,10 @@
         <v>1.29</v>
       </c>
       <c r="P7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R7">
         <v>1.42</v>
@@ -2495,7 +2546,7 @@
         <v>1.73</v>
       </c>
       <c r="U7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
         <v>1.74</v>
@@ -2537,16 +2588,16 @@
         <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
-        <v>690</v>
+        <v>810</v>
       </c>
       <c r="AK7">
         <v>42</v>
       </c>
       <c r="AL7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2576,7 +2627,7 @@
         <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW7">
         <v>21</v>
@@ -2672,7 +2723,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2680,157 +2731,157 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F8">
-        <v>1.28</v>
+        <v>2.48</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>2.98</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>320</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>1.19</v>
+        <v>2.42</v>
       </c>
       <c r="Q8">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS8">
         <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
         <v>1.01</v>
@@ -2839,19 +2890,19 @@
         <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2860,10 +2911,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2872,49 +2923,49 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2922,184 +2973,184 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F9">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="G9">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3150,13 +3201,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3164,185 +3215,185 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F10">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="G10">
+        <v>2.06</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>4.9</v>
+      </c>
+      <c r="J10">
+        <v>3.6</v>
+      </c>
+      <c r="K10">
+        <v>4.1</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>3.7</v>
+      </c>
+      <c r="O10">
+        <v>1.29</v>
+      </c>
+      <c r="P10">
+        <v>1.96</v>
+      </c>
+      <c r="Q10">
+        <v>1.84</v>
+      </c>
+      <c r="R10">
+        <v>1.37</v>
+      </c>
+      <c r="S10">
+        <v>3.15</v>
+      </c>
+      <c r="T10">
+        <v>1.74</v>
+      </c>
+      <c r="U10">
+        <v>2.08</v>
+      </c>
+      <c r="V10">
+        <v>1.25</v>
+      </c>
+      <c r="W10">
+        <v>1.94</v>
+      </c>
+      <c r="X10">
+        <v>19</v>
+      </c>
+      <c r="Y10">
+        <v>19</v>
+      </c>
+      <c r="Z10">
+        <v>38</v>
+      </c>
+      <c r="AA10">
+        <v>110</v>
+      </c>
+      <c r="AB10">
+        <v>11.5</v>
+      </c>
+      <c r="AC10">
+        <v>10.5</v>
+      </c>
+      <c r="AD10">
+        <v>21</v>
+      </c>
+      <c r="AE10">
+        <v>65</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>22</v>
+      </c>
+      <c r="AI10">
+        <v>70</v>
+      </c>
+      <c r="AJ10">
+        <v>27</v>
+      </c>
+      <c r="AK10">
+        <v>25</v>
+      </c>
+      <c r="AL10">
+        <v>42</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>15.5</v>
+      </c>
+      <c r="AO10">
+        <v>65</v>
+      </c>
+      <c r="AP10">
+        <v>11</v>
+      </c>
+      <c r="AQ10">
+        <v>11.5</v>
+      </c>
+      <c r="AR10">
+        <v>22</v>
+      </c>
+      <c r="AS10">
+        <v>60</v>
+      </c>
+      <c r="AT10">
+        <v>7.2</v>
+      </c>
+      <c r="AU10">
+        <v>6.4</v>
+      </c>
+      <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>36</v>
+      </c>
+      <c r="AX10">
+        <v>9.4</v>
+      </c>
+      <c r="AY10">
+        <v>7.8</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10">
+        <v>40</v>
+      </c>
+      <c r="BB10">
+        <v>17</v>
+      </c>
+      <c r="BC10">
+        <v>15</v>
+      </c>
+      <c r="BD10">
+        <v>25</v>
+      </c>
+      <c r="BE10">
+        <v>65</v>
+      </c>
+      <c r="BF10">
+        <v>10</v>
+      </c>
+      <c r="BG10">
+        <v>36</v>
+      </c>
+      <c r="BH10">
+        <v>4.4</v>
+      </c>
+      <c r="BI10">
         <v>2.68</v>
       </c>
-      <c r="H10">
-        <v>2.7</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>3.8</v>
-      </c>
-      <c r="K10">
-        <v>4.2</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>4.3</v>
-      </c>
-      <c r="O10">
-        <v>1.18</v>
-      </c>
-      <c r="P10">
-        <v>2.42</v>
-      </c>
-      <c r="Q10">
-        <v>1.59</v>
-      </c>
-      <c r="R10">
-        <v>1.54</v>
-      </c>
-      <c r="S10">
-        <v>2.5</v>
-      </c>
-      <c r="T10">
-        <v>1.44</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.5</v>
-      </c>
-      <c r="W10">
-        <v>1.6</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>1.01</v>
-      </c>
-      <c r="AR10">
-        <v>1.01</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>1.01</v>
-      </c>
-      <c r="AU10">
-        <v>1.01</v>
-      </c>
-      <c r="AV10">
-        <v>1.01</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10">
-        <v>1.01</v>
-      </c>
-      <c r="BA10">
-        <v>1.01</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>1.01</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.01</v>
-      </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
@@ -3392,13 +3443,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3406,34 +3457,34 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F11">
-        <v>2.66</v>
+        <v>1.32</v>
       </c>
       <c r="G11">
-        <v>3.6</v>
+        <v>110</v>
       </c>
       <c r="H11">
-        <v>2.16</v>
+        <v>1.15</v>
       </c>
       <c r="I11">
-        <v>2.92</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>320</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3442,22 +3493,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>2.08</v>
+        <v>1.21</v>
       </c>
       <c r="Q11">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="R11">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.28</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3466,10 +3517,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3634,13 +3685,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3648,124 +3699,124 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>6.2</v>
       </c>
       <c r="G12">
-        <v>1.75</v>
+        <v>11.5</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>1.46</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>1.73</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="S12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>2.36</v>
       </c>
       <c r="W12">
-        <v>2.32</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
         <v>1.01</v>
@@ -3882,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3890,241 +3941,241 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F13">
-        <v>5.9</v>
+        <v>2.02</v>
       </c>
       <c r="G13">
+        <v>2.18</v>
+      </c>
+      <c r="H13">
+        <v>3.8</v>
+      </c>
+      <c r="I13">
+        <v>4.5</v>
+      </c>
+      <c r="J13">
+        <v>3.3</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+      <c r="L13">
+        <v>1.42</v>
+      </c>
+      <c r="M13">
+        <v>1.08</v>
+      </c>
+      <c r="N13">
+        <v>3.3</v>
+      </c>
+      <c r="O13">
+        <v>1.35</v>
+      </c>
+      <c r="P13">
+        <v>1.79</v>
+      </c>
+      <c r="Q13">
+        <v>2.02</v>
+      </c>
+      <c r="R13">
+        <v>1.3</v>
+      </c>
+      <c r="S13">
+        <v>3.6</v>
+      </c>
+      <c r="T13">
+        <v>1.82</v>
+      </c>
+      <c r="U13">
+        <v>1.99</v>
+      </c>
+      <c r="V13">
+        <v>1.29</v>
+      </c>
+      <c r="W13">
+        <v>1.84</v>
+      </c>
+      <c r="X13">
+        <v>13.5</v>
+      </c>
+      <c r="Y13">
+        <v>14.5</v>
+      </c>
+      <c r="Z13">
+        <v>32</v>
+      </c>
+      <c r="AA13">
+        <v>100</v>
+      </c>
+      <c r="AB13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13">
+        <v>17.5</v>
+      </c>
+      <c r="AE13">
+        <v>55</v>
+      </c>
+      <c r="AF13">
+        <v>13.5</v>
+      </c>
+      <c r="AG13">
+        <v>11.5</v>
+      </c>
+      <c r="AH13">
+        <v>19.5</v>
+      </c>
+      <c r="AI13">
+        <v>65</v>
+      </c>
+      <c r="AJ13">
+        <v>27</v>
+      </c>
+      <c r="AK13">
+        <v>25</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
+        <v>140</v>
+      </c>
+      <c r="AN13">
+        <v>18.5</v>
+      </c>
+      <c r="AO13">
+        <v>65</v>
+      </c>
+      <c r="AP13">
+        <v>11</v>
+      </c>
+      <c r="AQ13">
+        <v>11.5</v>
+      </c>
+      <c r="AR13">
         <v>7.2</v>
       </c>
-      <c r="H13">
-        <v>1.53</v>
-      </c>
-      <c r="I13">
-        <v>1.67</v>
-      </c>
-      <c r="J13">
-        <v>4.2</v>
-      </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>4.1</v>
-      </c>
-      <c r="O13">
-        <v>1.19</v>
-      </c>
-      <c r="P13">
-        <v>2.1</v>
-      </c>
-      <c r="Q13">
-        <v>1.51</v>
-      </c>
-      <c r="R13">
-        <v>1.46</v>
-      </c>
-      <c r="S13">
-        <v>2.2</v>
-      </c>
-      <c r="T13">
-        <v>1.01</v>
-      </c>
-      <c r="U13">
-        <v>1.01</v>
-      </c>
-      <c r="V13">
-        <v>2.48</v>
-      </c>
-      <c r="W13">
-        <v>1.16</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>1.01</v>
-      </c>
-      <c r="AR13">
-        <v>1.01</v>
-      </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4132,258 +4183,258 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F14">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="G14">
+        <v>1.71</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>7.2</v>
+      </c>
+      <c r="J14">
+        <v>4.1</v>
+      </c>
+      <c r="K14">
+        <v>5.5</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>2.84</v>
+      </c>
+      <c r="O14">
+        <v>1.15</v>
+      </c>
+      <c r="P14">
+        <v>2.36</v>
+      </c>
+      <c r="Q14">
+        <v>1.48</v>
+      </c>
+      <c r="R14">
+        <v>1.56</v>
+      </c>
+      <c r="S14">
         <v>2.18</v>
       </c>
-      <c r="H14">
-        <v>3.8</v>
-      </c>
-      <c r="I14">
-        <v>4.5</v>
-      </c>
-      <c r="J14">
-        <v>3.3</v>
-      </c>
-      <c r="K14">
-        <v>3.8</v>
-      </c>
-      <c r="L14">
-        <v>1.42</v>
-      </c>
-      <c r="M14">
-        <v>1.08</v>
-      </c>
-      <c r="N14">
-        <v>3.3</v>
-      </c>
-      <c r="O14">
-        <v>1.35</v>
-      </c>
-      <c r="P14">
-        <v>1.79</v>
-      </c>
-      <c r="Q14">
-        <v>2.02</v>
-      </c>
-      <c r="R14">
-        <v>1.3</v>
-      </c>
-      <c r="S14">
-        <v>3.6</v>
-      </c>
       <c r="T14">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="U14">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="Y14">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="Z14">
+        <v>60</v>
+      </c>
+      <c r="AA14">
+        <v>160</v>
+      </c>
+      <c r="AB14">
+        <v>14</v>
+      </c>
+      <c r="AC14">
+        <v>13</v>
+      </c>
+      <c r="AD14">
+        <v>27</v>
+      </c>
+      <c r="AE14">
+        <v>80</v>
+      </c>
+      <c r="AF14">
+        <v>14</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>21</v>
+      </c>
+      <c r="AI14">
+        <v>70</v>
+      </c>
+      <c r="AJ14">
+        <v>17.5</v>
+      </c>
+      <c r="AK14">
+        <v>17</v>
+      </c>
+      <c r="AL14">
         <v>32</v>
       </c>
-      <c r="AA14">
-        <v>100</v>
-      </c>
-      <c r="AB14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14">
-        <v>17.5</v>
-      </c>
-      <c r="AE14">
-        <v>55</v>
-      </c>
-      <c r="AF14">
-        <v>13.5</v>
-      </c>
-      <c r="AG14">
-        <v>11.5</v>
-      </c>
-      <c r="AH14">
-        <v>19.5</v>
-      </c>
-      <c r="AI14">
-        <v>65</v>
-      </c>
-      <c r="AJ14">
-        <v>27</v>
-      </c>
-      <c r="AK14">
-        <v>25</v>
-      </c>
-      <c r="AL14">
-        <v>42</v>
-      </c>
       <c r="AM14">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>18.5</v>
+        <v>7.2</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP14">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -4608,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4616,34 +4667,34 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1.54</v>
       </c>
       <c r="G16">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4652,22 +4703,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S16">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4676,10 +4727,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="W16">
-        <v>1.32</v>
+        <v>1.99</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4844,13 +4895,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4858,121 +4909,121 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F17">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="I17">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K17">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q17">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="S17">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V17">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="W17">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="X17">
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA17">
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM17">
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO17">
         <v>1000</v>
@@ -4981,7 +5032,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
         <v>1.01</v>
@@ -4990,34 +5041,34 @@
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD17">
         <v>1.01</v>
@@ -5026,73 +5077,73 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG17">
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB17" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5100,121 +5151,121 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F18">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="H18">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="I18">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P18">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="R18">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S18">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="W18">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="X18">
         <v>1000</v>
       </c>
       <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>20</v>
+      </c>
+      <c r="AA18">
+        <v>36</v>
+      </c>
+      <c r="AB18">
         <v>21</v>
-      </c>
-      <c r="Z18">
-        <v>50</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>11</v>
       </c>
       <c r="AC18">
         <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AG18">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AH18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AJ18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN18">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5226,40 +5277,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT18">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW18">
         <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AY18">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA18">
         <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
         <v>1.01</v>
@@ -5268,73 +5319,73 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH18">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5342,178 +5393,178 @@
         <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F19">
+        <v>1.47</v>
+      </c>
+      <c r="G19">
+        <v>1.49</v>
+      </c>
+      <c r="H19">
+        <v>7.2</v>
+      </c>
+      <c r="I19">
+        <v>8.4</v>
+      </c>
+      <c r="J19">
+        <v>4.9</v>
+      </c>
+      <c r="K19">
+        <v>5.1</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>4.8</v>
+      </c>
+      <c r="O19">
+        <v>1.22</v>
+      </c>
+      <c r="P19">
+        <v>2.32</v>
+      </c>
+      <c r="Q19">
+        <v>1.66</v>
+      </c>
+      <c r="R19">
+        <v>1.5</v>
+      </c>
+      <c r="S19">
+        <v>2.68</v>
+      </c>
+      <c r="T19">
         <v>1.82</v>
       </c>
-      <c r="G19">
-        <v>1.93</v>
-      </c>
-      <c r="H19">
-        <v>5.1</v>
-      </c>
-      <c r="I19">
-        <v>5.9</v>
-      </c>
-      <c r="J19">
-        <v>3.4</v>
-      </c>
-      <c r="K19">
-        <v>3.75</v>
-      </c>
-      <c r="L19">
-        <v>1.38</v>
-      </c>
-      <c r="M19">
-        <v>1.1</v>
-      </c>
-      <c r="N19">
-        <v>2.92</v>
-      </c>
-      <c r="O19">
-        <v>1.44</v>
-      </c>
-      <c r="P19">
-        <v>1.63</v>
-      </c>
-      <c r="Q19">
-        <v>2.28</v>
-      </c>
-      <c r="R19">
-        <v>1.24</v>
-      </c>
-      <c r="S19">
-        <v>4.3</v>
-      </c>
-      <c r="T19">
-        <v>2.06</v>
-      </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W19">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="X19">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Z19">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AA19">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AB19">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD19">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE19">
         <v>110</v>
       </c>
       <c r="AF19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG19">
+        <v>11.5</v>
+      </c>
+      <c r="AH19">
+        <v>23</v>
+      </c>
+      <c r="AI19">
+        <v>95</v>
+      </c>
+      <c r="AJ19">
+        <v>14</v>
+      </c>
+      <c r="AK19">
+        <v>15.5</v>
+      </c>
+      <c r="AL19">
+        <v>32</v>
+      </c>
+      <c r="AM19">
+        <v>120</v>
+      </c>
+      <c r="AN19">
+        <v>6.6</v>
+      </c>
+      <c r="AO19">
+        <v>120</v>
+      </c>
+      <c r="AP19">
+        <v>19</v>
+      </c>
+      <c r="AQ19">
+        <v>25</v>
+      </c>
+      <c r="AR19">
+        <v>55</v>
+      </c>
+      <c r="AS19">
+        <v>10</v>
+      </c>
+      <c r="AT19">
+        <v>8.4</v>
+      </c>
+      <c r="AU19">
+        <v>10</v>
+      </c>
+      <c r="AV19">
+        <v>25</v>
+      </c>
+      <c r="AW19">
+        <v>9.6</v>
+      </c>
+      <c r="AX19">
+        <v>8.6</v>
+      </c>
+      <c r="AY19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ19">
+        <v>20</v>
+      </c>
+      <c r="BA19">
+        <v>11.5</v>
+      </c>
+      <c r="BB19">
         <v>12</v>
       </c>
-      <c r="AG19">
-        <v>12</v>
-      </c>
-      <c r="AH19">
-        <v>27</v>
-      </c>
-      <c r="AI19">
-        <v>120</v>
-      </c>
-      <c r="AJ19">
-        <v>25</v>
-      </c>
-      <c r="AK19">
-        <v>27</v>
-      </c>
-      <c r="AL19">
-        <v>60</v>
-      </c>
-      <c r="AM19">
-        <v>200</v>
-      </c>
-      <c r="AN19">
-        <v>21</v>
-      </c>
-      <c r="AO19">
-        <v>160</v>
-      </c>
-      <c r="AP19">
-        <v>9.4</v>
-      </c>
-      <c r="AQ19">
-        <v>12.5</v>
-      </c>
-      <c r="AR19">
-        <v>29</v>
-      </c>
-      <c r="AS19">
-        <v>5.5</v>
-      </c>
-      <c r="AT19">
-        <v>6</v>
-      </c>
-      <c r="AU19">
-        <v>6.8</v>
-      </c>
-      <c r="AV19">
-        <v>18</v>
-      </c>
-      <c r="AW19">
-        <v>5.4</v>
-      </c>
-      <c r="AX19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19">
-        <v>19.5</v>
-      </c>
-      <c r="BA19">
-        <v>5.4</v>
-      </c>
-      <c r="BB19">
-        <v>18</v>
-      </c>
       <c r="BC19">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BD19">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="BE19">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG19">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5576,7 +5627,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5584,241 +5635,241 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F20">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="G20">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="H20">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J20">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="S20">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
+        <v>1.9</v>
+      </c>
+      <c r="V20">
+        <v>1.19</v>
+      </c>
+      <c r="W20">
         <v>2.12</v>
       </c>
-      <c r="V20">
-        <v>1.11</v>
-      </c>
-      <c r="W20">
-        <v>3.55</v>
-      </c>
       <c r="X20">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Y20">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AA20">
-        <v>310</v>
+        <v>150</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AE20">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AF20">
+        <v>14</v>
+      </c>
+      <c r="AG20">
         <v>12.5</v>
       </c>
-      <c r="AG20">
-        <v>11</v>
-      </c>
       <c r="AH20">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ20">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AK20">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AL20">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM20">
         <v>120</v>
       </c>
       <c r="AN20">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AP20">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="AS20">
-        <v>5.7</v>
+        <v>80</v>
       </c>
       <c r="AT20">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>14.5</v>
+      </c>
+      <c r="AW20">
+        <v>46</v>
+      </c>
+      <c r="AX20">
+        <v>8.4</v>
+      </c>
+      <c r="AY20">
+        <v>7.6</v>
+      </c>
+      <c r="AZ20">
+        <v>14</v>
+      </c>
+      <c r="BA20">
+        <v>46</v>
+      </c>
+      <c r="BB20">
+        <v>13.5</v>
+      </c>
+      <c r="BC20">
         <v>13</v>
       </c>
-      <c r="AV20">
-        <v>5</v>
-      </c>
-      <c r="AW20">
-        <v>5.5</v>
-      </c>
-      <c r="AX20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20">
+      <c r="BD20">
+        <v>24</v>
+      </c>
+      <c r="BE20">
+        <v>70</v>
+      </c>
+      <c r="BF20">
+        <v>7.8</v>
+      </c>
+      <c r="BG20">
+        <v>48</v>
+      </c>
+      <c r="BH20">
+        <v>4.3</v>
+      </c>
+      <c r="BI20">
+        <v>2.92</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>7.2</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
         <v>21</v>
       </c>
-      <c r="BA20">
-        <v>5.5</v>
-      </c>
-      <c r="BB20">
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>3.45</v>
+      </c>
+      <c r="BP20">
+        <v>14.5</v>
+      </c>
+      <c r="BQ20">
+        <v>8.6</v>
+      </c>
+      <c r="BR20">
+        <v>32</v>
+      </c>
+      <c r="BS20">
+        <v>18</v>
+      </c>
+      <c r="BT20">
         <v>10.5</v>
       </c>
-      <c r="BC20">
-        <v>12</v>
-      </c>
-      <c r="BD20">
-        <v>21</v>
-      </c>
-      <c r="BE20">
-        <v>5.5</v>
-      </c>
-      <c r="BF20">
-        <v>3.85</v>
-      </c>
-      <c r="BG20">
-        <v>5.5</v>
-      </c>
-      <c r="BH20">
+      <c r="BU20">
         <v>6.2</v>
       </c>
-      <c r="BI20">
-        <v>3.5</v>
-      </c>
-      <c r="BJ20">
-        <v>15</v>
-      </c>
-      <c r="BK20">
-        <v>2.72</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>3.3</v>
-      </c>
-      <c r="BN20">
-        <v>5.6</v>
-      </c>
-      <c r="BO20">
-        <v>3</v>
-      </c>
-      <c r="BP20">
-        <v>10.5</v>
-      </c>
-      <c r="BQ20">
-        <v>5.1</v>
-      </c>
-      <c r="BR20">
-        <v>26</v>
-      </c>
-      <c r="BS20">
-        <v>2.94</v>
-      </c>
-      <c r="BT20">
-        <v>17.5</v>
-      </c>
-      <c r="BU20">
-        <v>2.78</v>
-      </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW20">
-        <v>3.2</v>
+        <v>29</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY20">
-        <v>3.15</v>
+        <v>32</v>
       </c>
       <c r="BZ20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA20">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5826,178 +5877,178 @@
         <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F21">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="G21">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="H21">
+        <v>5.1</v>
+      </c>
+      <c r="I21">
+        <v>5.9</v>
+      </c>
+      <c r="J21">
+        <v>3.4</v>
+      </c>
+      <c r="K21">
+        <v>3.75</v>
+      </c>
+      <c r="L21">
+        <v>1.38</v>
+      </c>
+      <c r="M21">
+        <v>1.1</v>
+      </c>
+      <c r="N21">
+        <v>2.92</v>
+      </c>
+      <c r="O21">
+        <v>1.44</v>
+      </c>
+      <c r="P21">
+        <v>1.64</v>
+      </c>
+      <c r="Q21">
+        <v>2.28</v>
+      </c>
+      <c r="R21">
+        <v>1.24</v>
+      </c>
+      <c r="S21">
+        <v>4.3</v>
+      </c>
+      <c r="T21">
+        <v>2.06</v>
+      </c>
+      <c r="U21">
+        <v>1.78</v>
+      </c>
+      <c r="V21">
+        <v>1.2</v>
+      </c>
+      <c r="W21">
+        <v>2.06</v>
+      </c>
+      <c r="X21">
+        <v>12.5</v>
+      </c>
+      <c r="Y21">
+        <v>17</v>
+      </c>
+      <c r="Z21">
+        <v>44</v>
+      </c>
+      <c r="AA21">
+        <v>180</v>
+      </c>
+      <c r="AB21">
         <v>7.2</v>
       </c>
-      <c r="I21">
-        <v>8.4</v>
-      </c>
-      <c r="J21">
-        <v>4.9</v>
-      </c>
-      <c r="K21">
-        <v>5.1</v>
-      </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>4.8</v>
-      </c>
-      <c r="O21">
-        <v>1.22</v>
-      </c>
-      <c r="P21">
-        <v>2.32</v>
-      </c>
-      <c r="Q21">
-        <v>1.66</v>
-      </c>
-      <c r="R21">
-        <v>1.5</v>
-      </c>
-      <c r="S21">
-        <v>2.68</v>
-      </c>
-      <c r="T21">
-        <v>1.82</v>
-      </c>
-      <c r="U21">
-        <v>2.02</v>
-      </c>
-      <c r="V21">
-        <v>1.14</v>
-      </c>
-      <c r="W21">
-        <v>3</v>
-      </c>
-      <c r="X21">
-        <v>22</v>
-      </c>
-      <c r="Y21">
-        <v>32</v>
-      </c>
-      <c r="Z21">
-        <v>70</v>
-      </c>
-      <c r="AA21">
-        <v>270</v>
-      </c>
-      <c r="AB21">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AC21">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE21">
         <v>110</v>
       </c>
       <c r="AF21">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI21">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ21">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AK21">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AL21">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM21">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN21">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AO21">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AP21">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AQ21">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AR21">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AT21">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AU21">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AW21">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BB21">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BD21">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="BE21">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF21">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6060,7 +6111,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6068,241 +6119,241 @@
         <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F22">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="G22">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="H22">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="Q22">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="R22">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="S22">
-        <v>2.96</v>
+        <v>2.16</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U22">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V22">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="W22">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="X22">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y22">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Z22">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AA22">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="AB22">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC22">
+        <v>17</v>
+      </c>
+      <c r="AD22">
+        <v>40</v>
+      </c>
+      <c r="AE22">
+        <v>130</v>
+      </c>
+      <c r="AF22">
+        <v>12.5</v>
+      </c>
+      <c r="AG22">
         <v>11</v>
       </c>
-      <c r="AD22">
-        <v>24</v>
-      </c>
-      <c r="AE22">
-        <v>80</v>
-      </c>
-      <c r="AF22">
+      <c r="AH22">
+        <v>28</v>
+      </c>
+      <c r="AI22">
+        <v>100</v>
+      </c>
+      <c r="AJ22">
         <v>14</v>
       </c>
-      <c r="AG22">
-        <v>12.5</v>
-      </c>
-      <c r="AH22">
-        <v>23</v>
-      </c>
-      <c r="AI22">
-        <v>80</v>
-      </c>
-      <c r="AJ22">
-        <v>23</v>
-      </c>
       <c r="AK22">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AL22">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM22">
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AO22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AP22">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="AQ22">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR22">
-        <v>29</v>
+        <v>5.5</v>
       </c>
       <c r="AS22">
-        <v>80</v>
+        <v>5.7</v>
       </c>
       <c r="AT22">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AU22">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AV22">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="AW22">
-        <v>46</v>
+        <v>5.5</v>
       </c>
       <c r="AX22">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY22">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA22">
-        <v>46</v>
+        <v>5.5</v>
       </c>
       <c r="BB22">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC22">
+        <v>12</v>
+      </c>
+      <c r="BD22">
+        <v>21</v>
+      </c>
+      <c r="BE22">
+        <v>5.5</v>
+      </c>
+      <c r="BF22">
+        <v>3.85</v>
+      </c>
+      <c r="BG22">
+        <v>5.5</v>
+      </c>
+      <c r="BH22">
+        <v>6.2</v>
+      </c>
+      <c r="BI22">
+        <v>3.5</v>
+      </c>
+      <c r="BJ22">
+        <v>15</v>
+      </c>
+      <c r="BK22">
+        <v>2.72</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>3.3</v>
+      </c>
+      <c r="BN22">
+        <v>5.6</v>
+      </c>
+      <c r="BO22">
+        <v>3</v>
+      </c>
+      <c r="BP22">
+        <v>10.5</v>
+      </c>
+      <c r="BQ22">
+        <v>5.1</v>
+      </c>
+      <c r="BR22">
+        <v>26</v>
+      </c>
+      <c r="BS22">
+        <v>2.94</v>
+      </c>
+      <c r="BT22">
+        <v>17.5</v>
+      </c>
+      <c r="BU22">
+        <v>2.78</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>3.2</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>3.15</v>
+      </c>
+      <c r="BZ22">
         <v>13</v>
       </c>
-      <c r="BD22">
-        <v>24</v>
-      </c>
-      <c r="BE22">
-        <v>70</v>
-      </c>
-      <c r="BF22">
-        <v>7.8</v>
-      </c>
-      <c r="BG22">
-        <v>48</v>
-      </c>
-      <c r="BH22">
-        <v>4.3</v>
-      </c>
-      <c r="BI22">
-        <v>2.92</v>
-      </c>
-      <c r="BJ22">
-        <v>12</v>
-      </c>
-      <c r="BK22">
-        <v>7.2</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>21</v>
-      </c>
-      <c r="BN22">
-        <v>5.3</v>
-      </c>
-      <c r="BO22">
-        <v>3.45</v>
-      </c>
-      <c r="BP22">
-        <v>14.5</v>
-      </c>
-      <c r="BQ22">
-        <v>8.6</v>
-      </c>
-      <c r="BR22">
-        <v>32</v>
-      </c>
-      <c r="BS22">
-        <v>18</v>
-      </c>
-      <c r="BT22">
-        <v>10.5</v>
-      </c>
-      <c r="BU22">
-        <v>6.2</v>
-      </c>
-      <c r="BV22">
-        <v>50</v>
-      </c>
-      <c r="BW22">
-        <v>29</v>
-      </c>
-      <c r="BX22">
-        <v>60</v>
-      </c>
-      <c r="BY22">
-        <v>32</v>
-      </c>
-      <c r="BZ22">
-        <v>0</v>
-      </c>
       <c r="CA22">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="CB22" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6310,16 +6361,16 @@
         <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E23" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F23">
         <v>2.94</v>
@@ -6334,7 +6385,7 @@
         <v>3.2</v>
       </c>
       <c r="J23">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K23">
         <v>3.15</v>
@@ -6343,25 +6394,25 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="O23">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R23">
         <v>1.14</v>
       </c>
       <c r="S23">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="T23">
         <v>2.26</v>
@@ -6376,7 +6427,7 @@
         <v>1.43</v>
       </c>
       <c r="X23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y23">
         <v>9.4</v>
@@ -6439,7 +6490,7 @@
         <v>13</v>
       </c>
       <c r="AS23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23">
         <v>6</v>
@@ -6451,7 +6502,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX23">
         <v>13.5</v>
@@ -6460,28 +6511,28 @@
         <v>12.5</v>
       </c>
       <c r="AZ23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB23">
         <v>4.2</v>
       </c>
       <c r="BC23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE23">
         <v>4.4</v>
       </c>
       <c r="BF23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6544,7 +6595,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6552,34 +6603,34 @@
         <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6591,19 +6642,19 @@
         <v>1.01</v>
       </c>
       <c r="O24">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P24">
-        <v>1.26</v>
+        <v>2.62</v>
       </c>
       <c r="Q24">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="S24">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6612,10 +6663,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6786,7 +6837,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6794,178 +6845,178 @@
         <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F25">
-        <v>1.14</v>
+        <v>3.45</v>
       </c>
       <c r="G25">
-        <v>130</v>
+        <v>4.4</v>
       </c>
       <c r="H25">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="I25">
-        <v>120</v>
+        <v>2.22</v>
       </c>
       <c r="J25">
-        <v>1.14</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O25">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="P25">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q25">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="R25">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
-        <v>1.11</v>
+        <v>2.86</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V25">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7028,42 +7079,42 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F26">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7072,22 +7123,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P26">
         <v>1.26</v>
       </c>
       <c r="Q26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="R26">
         <v>1.25</v>
       </c>
       <c r="S26">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7096,10 +7147,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7270,42 +7321,42 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F27">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="H27">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I27">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J27">
-        <v>1.06</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
-        <v>330</v>
+        <v>11.5</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7314,22 +7365,22 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="O27">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P27">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q27">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="R27">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="S27">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="T27">
         <v>1.01</v>
@@ -7338,10 +7389,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7512,186 +7563,186 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F28">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="G28">
+        <v>3.8</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>2.26</v>
+      </c>
+      <c r="J28">
+        <v>3.9</v>
+      </c>
+      <c r="K28">
         <v>4.4</v>
       </c>
-      <c r="H28">
-        <v>1.92</v>
-      </c>
-      <c r="I28">
-        <v>2.22</v>
-      </c>
-      <c r="J28">
-        <v>3.45</v>
-      </c>
-      <c r="K28">
-        <v>4.1</v>
-      </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="O28">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="P28">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="Q28">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="R28">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S28">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="T28">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="U28">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W28">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y28">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z28">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AA28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB28">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC28">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD28">
         <v>12</v>
       </c>
       <c r="AE28">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG28">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH28">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI28">
+        <v>28</v>
+      </c>
+      <c r="AJ28">
+        <v>65</v>
+      </c>
+      <c r="AK28">
         <v>36</v>
       </c>
-      <c r="AJ28">
-        <v>80</v>
-      </c>
-      <c r="AK28">
-        <v>50</v>
-      </c>
       <c r="AL28">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM28">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN28">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AO28">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AP28">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AQ28">
+        <v>12</v>
+      </c>
+      <c r="AR28">
+        <v>13.5</v>
+      </c>
+      <c r="AS28">
+        <v>21</v>
+      </c>
+      <c r="AT28">
+        <v>16.5</v>
+      </c>
+      <c r="AU28">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR28">
-        <v>11</v>
-      </c>
-      <c r="AS28">
-        <v>20</v>
-      </c>
-      <c r="AT28">
-        <v>11.5</v>
-      </c>
-      <c r="AU28">
-        <v>7.2</v>
-      </c>
       <c r="AV28">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX28">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY28">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA28">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
+        <v>1.01</v>
+      </c>
+      <c r="BD28">
         <v>30</v>
       </c>
-      <c r="BD28">
-        <v>34</v>
-      </c>
       <c r="BE28">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="BG28">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7754,42 +7805,42 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F29">
-        <v>2.78</v>
+        <v>1.18</v>
       </c>
       <c r="G29">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="H29">
-        <v>2.24</v>
+        <v>1.19</v>
       </c>
       <c r="I29">
-        <v>2.58</v>
+        <v>110</v>
       </c>
       <c r="J29">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K29">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7798,22 +7849,22 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>2.58</v>
+        <v>1.26</v>
       </c>
       <c r="O29">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>1.26</v>
       </c>
       <c r="Q29">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="R29">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="S29">
-        <v>2.12</v>
+        <v>1.09</v>
       </c>
       <c r="T29">
         <v>1.01</v>
@@ -7822,10 +7873,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="W29">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7996,7 +8047,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8004,34 +8055,34 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E30" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F30">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="G30">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="I30">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="J30">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K30">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8040,142 +8091,142 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="O30">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P30">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R30">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="S30">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="T30">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="W30">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="X30">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8238,7 +8289,7 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8246,16 +8297,16 @@
         <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F31">
         <v>1.81</v>
@@ -8267,7 +8318,7 @@
         <v>3.5</v>
       </c>
       <c r="I31">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J31">
         <v>4.6</v>
@@ -8480,66 +8531,66 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E32" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F32">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="G32">
-        <v>110</v>
+        <v>1.73</v>
       </c>
       <c r="H32">
-        <v>1.15</v>
+        <v>3.9</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="K32">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M32">
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O32">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P32">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="R32">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="S32">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8548,10 +8599,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>2.36</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8569,7 +8620,7 @@
         <v>1000</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD32">
         <v>1000</v>
@@ -8578,13 +8629,13 @@
         <v>1000</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG32">
         <v>1000</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI32">
         <v>1000</v>
@@ -8593,16 +8644,16 @@
         <v>1000</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM32">
         <v>1000</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO32">
         <v>1000</v>
@@ -8623,7 +8674,7 @@
         <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV32">
         <v>1.01</v>
@@ -8635,7 +8686,7 @@
         <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ32">
         <v>1.01</v>
@@ -8656,19 +8707,19 @@
         <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG32">
         <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI32">
         <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK32">
         <v>1.01</v>
@@ -8680,25 +8731,25 @@
         <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO32">
         <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ32">
         <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
@@ -8716,33 +8767,33 @@
         <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA32">
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F33">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G33">
         <v>2.02</v>
@@ -8757,7 +8808,7 @@
         <v>3.45</v>
       </c>
       <c r="K33">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8964,66 +9015,66 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E34" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H34">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I34">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K34">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N34">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O34">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P34">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
         <v>1.68</v>
       </c>
       <c r="R34">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="T34">
         <v>1.67</v>
@@ -9032,10 +9083,10 @@
         <v>1.98</v>
       </c>
       <c r="V34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X34">
         <v>24</v>
@@ -9050,10 +9101,10 @@
         <v>170</v>
       </c>
       <c r="AB34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD34">
         <v>27</v>
@@ -9062,10 +9113,10 @@
         <v>85</v>
       </c>
       <c r="AF34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH34">
         <v>23</v>
@@ -9074,58 +9125,58 @@
         <v>80</v>
       </c>
       <c r="AJ34">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK34">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM34">
         <v>110</v>
       </c>
       <c r="AN34">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AO34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP34">
         <v>16</v>
       </c>
       <c r="AQ34">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR34">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS34">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AT34">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU34">
         <v>9.199999999999999</v>
       </c>
       <c r="AV34">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW34">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX34">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY34">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA34">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9134,79 +9185,79 @@
         <v>12</v>
       </c>
       <c r="BD34">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE34">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF34">
         <v>5.9</v>
       </c>
       <c r="BG34">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK34">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB34" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9214,16 +9265,16 @@
         <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F35">
         <v>2.24</v>
@@ -9448,7 +9499,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9456,16 +9507,16 @@
         <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F36">
         <v>2.56</v>
@@ -9690,7 +9741,7 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9698,16 +9749,16 @@
         <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F37">
         <v>2.4</v>
@@ -9872,246 +9923,246 @@
         <v>50</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL37">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO37">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU37">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="CB37" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F38">
-        <v>1.14</v>
+        <v>16.5</v>
       </c>
       <c r="G38">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="H38">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="I38">
-        <v>1000</v>
+        <v>1.25</v>
       </c>
       <c r="J38">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N38">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="O38">
+        <v>1.2</v>
+      </c>
+      <c r="P38">
+        <v>2.36</v>
+      </c>
+      <c r="Q38">
+        <v>1.62</v>
+      </c>
+      <c r="R38">
+        <v>1.53</v>
+      </c>
+      <c r="S38">
+        <v>2.5</v>
+      </c>
+      <c r="T38">
+        <v>2.22</v>
+      </c>
+      <c r="U38">
+        <v>1.65</v>
+      </c>
+      <c r="V38">
+        <v>5</v>
+      </c>
+      <c r="W38">
         <v>1.06</v>
       </c>
-      <c r="P38">
-        <v>1.26</v>
-      </c>
-      <c r="Q38">
-        <v>1.06</v>
-      </c>
-      <c r="R38">
-        <v>1.25</v>
-      </c>
-      <c r="S38">
-        <v>1.07</v>
-      </c>
-      <c r="T38">
-        <v>1.01</v>
-      </c>
-      <c r="U38">
-        <v>1.01</v>
-      </c>
-      <c r="V38">
-        <v>1.02</v>
-      </c>
-      <c r="W38">
-        <v>1.09</v>
-      </c>
       <c r="X38">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC38">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE38">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF38">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AG38">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AP38">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ38">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT38">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AU38">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AV38">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX38">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY38">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AZ38">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BB38">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC38">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD38">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF38">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10153,19 +10204,19 @@
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
@@ -10174,66 +10225,66 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>1.01</v>
+      </c>
+      <c r="M39">
+        <v>1.01</v>
+      </c>
+      <c r="N39">
         <v>1.26</v>
       </c>
-      <c r="G39">
-        <v>110</v>
-      </c>
-      <c r="H39">
+      <c r="O39">
+        <v>1.05</v>
+      </c>
+      <c r="P39">
         <v>1.26</v>
       </c>
-      <c r="I39">
-        <v>110</v>
-      </c>
-      <c r="J39">
-        <v>1.14</v>
-      </c>
-      <c r="K39">
-        <v>520</v>
-      </c>
-      <c r="L39">
-        <v>1.01</v>
-      </c>
-      <c r="M39">
-        <v>1.01</v>
-      </c>
-      <c r="N39">
-        <v>1.3</v>
-      </c>
-      <c r="O39">
-        <v>1.15</v>
-      </c>
-      <c r="P39">
-        <v>1.3</v>
-      </c>
       <c r="Q39">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="R39">
         <v>1.25</v>
       </c>
       <c r="S39">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10242,10 +10293,10 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10416,7 +10467,7 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10424,34 +10475,34 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10460,34 +10511,34 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="O40">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="P40">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q40">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="R40">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="S40">
+        <v>1.92</v>
+      </c>
+      <c r="T40">
+        <v>1.01</v>
+      </c>
+      <c r="U40">
+        <v>1.01</v>
+      </c>
+      <c r="V40">
         <v>1.06</v>
       </c>
-      <c r="T40">
-        <v>1.01</v>
-      </c>
-      <c r="U40">
-        <v>1.01</v>
-      </c>
-      <c r="V40">
-        <v>1.01</v>
-      </c>
       <c r="W40">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10658,186 +10709,186 @@
         <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E41" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F41">
-        <v>16.5</v>
+        <v>1.64</v>
       </c>
       <c r="G41">
-        <v>19</v>
+        <v>1.89</v>
       </c>
       <c r="H41">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="I41">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="J41">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="K41">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N41">
-        <v>5</v>
+        <v>2.86</v>
       </c>
       <c r="O41">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="P41">
-        <v>2.36</v>
+        <v>2.86</v>
       </c>
       <c r="Q41">
+        <v>1.06</v>
+      </c>
+      <c r="R41">
+        <v>2.1</v>
+      </c>
+      <c r="S41">
         <v>1.62</v>
       </c>
-      <c r="R41">
-        <v>1.56</v>
-      </c>
-      <c r="S41">
-        <v>2.54</v>
-      </c>
       <c r="T41">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U41">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V41">
-        <v>5</v>
+        <v>1.17</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>2.12</v>
       </c>
       <c r="X41">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y41">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z41">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AA41">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AB41">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC41">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD41">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE41">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AF41">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AG41">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AH41">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI41">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AK41">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AL41">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM41">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO41">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AP41">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG41">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10846,78 +10897,78 @@
         <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BK41">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BO41">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP41">
         <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU41">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BV41">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW41">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX41">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY41">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA41">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F42">
         <v>1.36</v>
@@ -11082,67 +11133,67 @@
         <v>5.3</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI42">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="BJ42">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BK42">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="BN42">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BO42">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP42">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BQ42">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BR42">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BS42">
-        <v>1.82</v>
+        <v>6.2</v>
       </c>
       <c r="BT42">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BU42">
-        <v>1.74</v>
+        <v>5.2</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW42">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY42">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="BZ42">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA42">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="CB42" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11150,16 +11201,16 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F43">
         <v>2.36</v>
@@ -11183,7 +11234,7 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N43">
         <v>1.45</v>
@@ -11198,16 +11249,16 @@
         <v>2.88</v>
       </c>
       <c r="R43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S43">
-        <v>2.88</v>
+        <v>6.2</v>
       </c>
       <c r="T43">
         <v>2.18</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V43">
         <v>1.32</v>
@@ -11384,7 +11435,1459 @@
         <v>1.01</v>
       </c>
       <c r="CB43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:80">
+      <c r="A44" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44">
+        <v>1.94</v>
+      </c>
+      <c r="G44">
+        <v>2.22</v>
+      </c>
+      <c r="H44">
+        <v>3.65</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>3.25</v>
+      </c>
+      <c r="K44">
+        <v>4.8</v>
+      </c>
+      <c r="L44">
+        <v>1.01</v>
+      </c>
+      <c r="M44">
+        <v>1.01</v>
+      </c>
+      <c r="N44">
+        <v>2.98</v>
+      </c>
+      <c r="O44">
+        <v>1.02</v>
+      </c>
+      <c r="P44">
+        <v>1.77</v>
+      </c>
+      <c r="Q44">
+        <v>2.08</v>
+      </c>
+      <c r="R44">
+        <v>1.23</v>
+      </c>
+      <c r="S44">
+        <v>2.92</v>
+      </c>
+      <c r="T44">
+        <v>1.01</v>
+      </c>
+      <c r="U44">
+        <v>1.01</v>
+      </c>
+      <c r="V44">
+        <v>1.25</v>
+      </c>
+      <c r="W44">
+        <v>1.81</v>
+      </c>
+      <c r="X44">
+        <v>1000</v>
+      </c>
+      <c r="Y44">
+        <v>1000</v>
+      </c>
+      <c r="Z44">
+        <v>1000</v>
+      </c>
+      <c r="AA44">
+        <v>1000</v>
+      </c>
+      <c r="AB44">
+        <v>1000</v>
+      </c>
+      <c r="AC44">
+        <v>1000</v>
+      </c>
+      <c r="AD44">
+        <v>1000</v>
+      </c>
+      <c r="AE44">
+        <v>1000</v>
+      </c>
+      <c r="AF44">
+        <v>1000</v>
+      </c>
+      <c r="AG44">
+        <v>1000</v>
+      </c>
+      <c r="AH44">
+        <v>1000</v>
+      </c>
+      <c r="AI44">
+        <v>1000</v>
+      </c>
+      <c r="AJ44">
+        <v>1000</v>
+      </c>
+      <c r="AK44">
+        <v>1000</v>
+      </c>
+      <c r="AL44">
+        <v>1000</v>
+      </c>
+      <c r="AM44">
+        <v>1000</v>
+      </c>
+      <c r="AN44">
+        <v>1000</v>
+      </c>
+      <c r="AO44">
+        <v>1000</v>
+      </c>
+      <c r="AP44">
+        <v>1.01</v>
+      </c>
+      <c r="AQ44">
+        <v>1.01</v>
+      </c>
+      <c r="AR44">
+        <v>1.01</v>
+      </c>
+      <c r="AS44">
+        <v>1.01</v>
+      </c>
+      <c r="AT44">
+        <v>1.01</v>
+      </c>
+      <c r="AU44">
+        <v>1.01</v>
+      </c>
+      <c r="AV44">
+        <v>1.01</v>
+      </c>
+      <c r="AW44">
+        <v>1.01</v>
+      </c>
+      <c r="AX44">
+        <v>1.01</v>
+      </c>
+      <c r="AY44">
+        <v>1.01</v>
+      </c>
+      <c r="AZ44">
+        <v>1.01</v>
+      </c>
+      <c r="BA44">
+        <v>1.01</v>
+      </c>
+      <c r="BB44">
+        <v>1.01</v>
+      </c>
+      <c r="BC44">
+        <v>1.01</v>
+      </c>
+      <c r="BD44">
+        <v>1.01</v>
+      </c>
+      <c r="BE44">
+        <v>1.01</v>
+      </c>
+      <c r="BF44">
+        <v>1.01</v>
+      </c>
+      <c r="BG44">
+        <v>1.01</v>
+      </c>
+      <c r="BH44">
+        <v>1000</v>
+      </c>
+      <c r="BI44">
+        <v>1.01</v>
+      </c>
+      <c r="BJ44">
+        <v>1000</v>
+      </c>
+      <c r="BK44">
+        <v>1.01</v>
+      </c>
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
+        <v>1.01</v>
+      </c>
+      <c r="BN44">
+        <v>1000</v>
+      </c>
+      <c r="BO44">
+        <v>1.01</v>
+      </c>
+      <c r="BP44">
+        <v>1000</v>
+      </c>
+      <c r="BQ44">
+        <v>1.01</v>
+      </c>
+      <c r="BR44">
+        <v>1000</v>
+      </c>
+      <c r="BS44">
+        <v>1.01</v>
+      </c>
+      <c r="BT44">
+        <v>1000</v>
+      </c>
+      <c r="BU44">
+        <v>1.01</v>
+      </c>
+      <c r="BV44">
+        <v>1000</v>
+      </c>
+      <c r="BW44">
+        <v>1.01</v>
+      </c>
+      <c r="BX44">
+        <v>1000</v>
+      </c>
+      <c r="BY44">
+        <v>1.01</v>
+      </c>
+      <c r="BZ44">
+        <v>1000</v>
+      </c>
+      <c r="CA44">
+        <v>1.01</v>
+      </c>
+      <c r="CB44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:80">
+      <c r="A45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45">
+        <v>1.04</v>
+      </c>
+      <c r="G45">
+        <v>1000</v>
+      </c>
+      <c r="H45">
+        <v>1.04</v>
+      </c>
+      <c r="I45">
+        <v>1000</v>
+      </c>
+      <c r="J45">
+        <v>1.04</v>
+      </c>
+      <c r="K45">
+        <v>470</v>
+      </c>
+      <c r="L45">
+        <v>1.01</v>
+      </c>
+      <c r="M45">
+        <v>1.01</v>
+      </c>
+      <c r="N45">
+        <v>1.01</v>
+      </c>
+      <c r="O45">
+        <v>1.02</v>
+      </c>
+      <c r="P45">
+        <v>1.25</v>
+      </c>
+      <c r="Q45">
+        <v>1.31</v>
+      </c>
+      <c r="R45">
+        <v>1.18</v>
+      </c>
+      <c r="S45">
+        <v>2.06</v>
+      </c>
+      <c r="T45">
+        <v>1.01</v>
+      </c>
+      <c r="U45">
+        <v>1.01</v>
+      </c>
+      <c r="V45">
+        <v>1.02</v>
+      </c>
+      <c r="W45">
+        <v>1.02</v>
+      </c>
+      <c r="X45">
+        <v>1000</v>
+      </c>
+      <c r="Y45">
+        <v>1000</v>
+      </c>
+      <c r="Z45">
+        <v>1000</v>
+      </c>
+      <c r="AA45">
+        <v>1000</v>
+      </c>
+      <c r="AB45">
+        <v>1000</v>
+      </c>
+      <c r="AC45">
+        <v>1000</v>
+      </c>
+      <c r="AD45">
+        <v>1000</v>
+      </c>
+      <c r="AE45">
+        <v>1000</v>
+      </c>
+      <c r="AF45">
+        <v>1000</v>
+      </c>
+      <c r="AG45">
+        <v>1000</v>
+      </c>
+      <c r="AH45">
+        <v>1000</v>
+      </c>
+      <c r="AI45">
+        <v>1000</v>
+      </c>
+      <c r="AJ45">
+        <v>1000</v>
+      </c>
+      <c r="AK45">
+        <v>1000</v>
+      </c>
+      <c r="AL45">
+        <v>1000</v>
+      </c>
+      <c r="AM45">
+        <v>1000</v>
+      </c>
+      <c r="AN45">
+        <v>1000</v>
+      </c>
+      <c r="AO45">
+        <v>1000</v>
+      </c>
+      <c r="AP45">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45">
+        <v>1.01</v>
+      </c>
+      <c r="AR45">
+        <v>1.01</v>
+      </c>
+      <c r="AS45">
+        <v>1.01</v>
+      </c>
+      <c r="AT45">
+        <v>1.01</v>
+      </c>
+      <c r="AU45">
+        <v>1.01</v>
+      </c>
+      <c r="AV45">
+        <v>1.01</v>
+      </c>
+      <c r="AW45">
+        <v>1.01</v>
+      </c>
+      <c r="AX45">
+        <v>1.01</v>
+      </c>
+      <c r="AY45">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45">
+        <v>1.01</v>
+      </c>
+      <c r="BA45">
+        <v>1.01</v>
+      </c>
+      <c r="BB45">
+        <v>1.01</v>
+      </c>
+      <c r="BC45">
+        <v>1.01</v>
+      </c>
+      <c r="BD45">
+        <v>1.01</v>
+      </c>
+      <c r="BE45">
+        <v>1.01</v>
+      </c>
+      <c r="BF45">
+        <v>1.01</v>
+      </c>
+      <c r="BG45">
+        <v>1.01</v>
+      </c>
+      <c r="BH45">
+        <v>1000</v>
+      </c>
+      <c r="BI45">
+        <v>1.01</v>
+      </c>
+      <c r="BJ45">
+        <v>1000</v>
+      </c>
+      <c r="BK45">
+        <v>1.01</v>
+      </c>
+      <c r="BL45">
+        <v>1000</v>
+      </c>
+      <c r="BM45">
+        <v>1.01</v>
+      </c>
+      <c r="BN45">
+        <v>1000</v>
+      </c>
+      <c r="BO45">
+        <v>1.01</v>
+      </c>
+      <c r="BP45">
+        <v>1000</v>
+      </c>
+      <c r="BQ45">
+        <v>1.01</v>
+      </c>
+      <c r="BR45">
+        <v>1000</v>
+      </c>
+      <c r="BS45">
+        <v>1.01</v>
+      </c>
+      <c r="BT45">
+        <v>1000</v>
+      </c>
+      <c r="BU45">
+        <v>1.01</v>
+      </c>
+      <c r="BV45">
+        <v>1000</v>
+      </c>
+      <c r="BW45">
+        <v>1.01</v>
+      </c>
+      <c r="BX45">
+        <v>1000</v>
+      </c>
+      <c r="BY45">
+        <v>1.01</v>
+      </c>
+      <c r="BZ45">
+        <v>1000</v>
+      </c>
+      <c r="CA45">
+        <v>1.01</v>
+      </c>
+      <c r="CB45" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:80">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46">
+        <v>1.68</v>
+      </c>
+      <c r="G46">
+        <v>1.94</v>
+      </c>
+      <c r="H46">
+        <v>4.8</v>
+      </c>
+      <c r="I46">
+        <v>6.4</v>
+      </c>
+      <c r="J46">
+        <v>3.55</v>
+      </c>
+      <c r="K46">
+        <v>4.4</v>
+      </c>
+      <c r="L46">
+        <v>1.01</v>
+      </c>
+      <c r="M46">
+        <v>1.01</v>
+      </c>
+      <c r="N46">
+        <v>2.98</v>
+      </c>
+      <c r="O46">
+        <v>1.37</v>
+      </c>
+      <c r="P46">
+        <v>1.68</v>
+      </c>
+      <c r="Q46">
+        <v>2.16</v>
+      </c>
+      <c r="R46">
+        <v>1.25</v>
+      </c>
+      <c r="S46">
+        <v>4</v>
+      </c>
+      <c r="T46">
+        <v>1.01</v>
+      </c>
+      <c r="U46">
+        <v>1.61</v>
+      </c>
+      <c r="V46">
+        <v>1.22</v>
+      </c>
+      <c r="W46">
+        <v>2.06</v>
+      </c>
+      <c r="X46">
+        <v>1000</v>
+      </c>
+      <c r="Y46">
+        <v>1000</v>
+      </c>
+      <c r="Z46">
+        <v>1000</v>
+      </c>
+      <c r="AA46">
+        <v>1000</v>
+      </c>
+      <c r="AB46">
+        <v>1000</v>
+      </c>
+      <c r="AC46">
+        <v>1000</v>
+      </c>
+      <c r="AD46">
+        <v>1000</v>
+      </c>
+      <c r="AE46">
+        <v>1000</v>
+      </c>
+      <c r="AF46">
+        <v>1000</v>
+      </c>
+      <c r="AG46">
+        <v>1000</v>
+      </c>
+      <c r="AH46">
+        <v>1000</v>
+      </c>
+      <c r="AI46">
+        <v>1000</v>
+      </c>
+      <c r="AJ46">
+        <v>1000</v>
+      </c>
+      <c r="AK46">
+        <v>1000</v>
+      </c>
+      <c r="AL46">
+        <v>1000</v>
+      </c>
+      <c r="AM46">
+        <v>1000</v>
+      </c>
+      <c r="AN46">
+        <v>1000</v>
+      </c>
+      <c r="AO46">
+        <v>1000</v>
+      </c>
+      <c r="AP46">
+        <v>1.01</v>
+      </c>
+      <c r="AQ46">
+        <v>1.01</v>
+      </c>
+      <c r="AR46">
+        <v>1.01</v>
+      </c>
+      <c r="AS46">
+        <v>1.01</v>
+      </c>
+      <c r="AT46">
+        <v>1.01</v>
+      </c>
+      <c r="AU46">
+        <v>6.2</v>
+      </c>
+      <c r="AV46">
+        <v>1.01</v>
+      </c>
+      <c r="AW46">
+        <v>1.01</v>
+      </c>
+      <c r="AX46">
+        <v>1.01</v>
+      </c>
+      <c r="AY46">
+        <v>1.01</v>
+      </c>
+      <c r="AZ46">
+        <v>19</v>
+      </c>
+      <c r="BA46">
+        <v>1.01</v>
+      </c>
+      <c r="BB46">
+        <v>1.01</v>
+      </c>
+      <c r="BC46">
+        <v>1.01</v>
+      </c>
+      <c r="BD46">
+        <v>1.01</v>
+      </c>
+      <c r="BE46">
+        <v>100</v>
+      </c>
+      <c r="BF46">
+        <v>1.01</v>
+      </c>
+      <c r="BG46">
+        <v>1.01</v>
+      </c>
+      <c r="BH46">
+        <v>3.4</v>
+      </c>
+      <c r="BI46">
+        <v>2.34</v>
+      </c>
+      <c r="BJ46">
+        <v>1000</v>
+      </c>
+      <c r="BK46">
+        <v>1.01</v>
+      </c>
+      <c r="BL46">
+        <v>1000</v>
+      </c>
+      <c r="BM46">
+        <v>1.01</v>
+      </c>
+      <c r="BN46">
+        <v>1000</v>
+      </c>
+      <c r="BO46">
+        <v>1.01</v>
+      </c>
+      <c r="BP46">
+        <v>1000</v>
+      </c>
+      <c r="BQ46">
+        <v>1.01</v>
+      </c>
+      <c r="BR46">
+        <v>1000</v>
+      </c>
+      <c r="BS46">
+        <v>1.01</v>
+      </c>
+      <c r="BT46">
+        <v>1000</v>
+      </c>
+      <c r="BU46">
+        <v>1.01</v>
+      </c>
+      <c r="BV46">
+        <v>1000</v>
+      </c>
+      <c r="BW46">
+        <v>1.01</v>
+      </c>
+      <c r="BX46">
+        <v>1000</v>
+      </c>
+      <c r="BY46">
+        <v>1.01</v>
+      </c>
+      <c r="BZ46">
+        <v>1000</v>
+      </c>
+      <c r="CA46">
+        <v>1.01</v>
+      </c>
+      <c r="CB46" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:80">
+      <c r="A47" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+      <c r="F47">
+        <v>2.14</v>
+      </c>
+      <c r="G47">
+        <v>2.44</v>
+      </c>
+      <c r="H47">
+        <v>3.45</v>
+      </c>
+      <c r="I47">
+        <v>4.4</v>
+      </c>
+      <c r="J47">
+        <v>3.1</v>
+      </c>
+      <c r="K47">
+        <v>3.95</v>
+      </c>
+      <c r="L47">
+        <v>1.01</v>
+      </c>
+      <c r="M47">
+        <v>1.01</v>
+      </c>
+      <c r="N47">
+        <v>2.94</v>
+      </c>
+      <c r="O47">
+        <v>1.39</v>
+      </c>
+      <c r="P47">
+        <v>1.68</v>
+      </c>
+      <c r="Q47">
+        <v>2.16</v>
+      </c>
+      <c r="R47">
+        <v>1.2</v>
+      </c>
+      <c r="S47">
+        <v>3.15</v>
+      </c>
+      <c r="T47">
+        <v>1.01</v>
+      </c>
+      <c r="U47">
+        <v>1.01</v>
+      </c>
+      <c r="V47">
+        <v>1.29</v>
+      </c>
+      <c r="W47">
+        <v>1.69</v>
+      </c>
+      <c r="X47">
+        <v>1000</v>
+      </c>
+      <c r="Y47">
+        <v>1000</v>
+      </c>
+      <c r="Z47">
+        <v>1000</v>
+      </c>
+      <c r="AA47">
+        <v>1000</v>
+      </c>
+      <c r="AB47">
+        <v>1000</v>
+      </c>
+      <c r="AC47">
+        <v>1000</v>
+      </c>
+      <c r="AD47">
+        <v>1000</v>
+      </c>
+      <c r="AE47">
+        <v>1000</v>
+      </c>
+      <c r="AF47">
+        <v>1000</v>
+      </c>
+      <c r="AG47">
+        <v>1000</v>
+      </c>
+      <c r="AH47">
+        <v>1000</v>
+      </c>
+      <c r="AI47">
+        <v>1000</v>
+      </c>
+      <c r="AJ47">
+        <v>1000</v>
+      </c>
+      <c r="AK47">
+        <v>1000</v>
+      </c>
+      <c r="AL47">
+        <v>1000</v>
+      </c>
+      <c r="AM47">
+        <v>1000</v>
+      </c>
+      <c r="AN47">
+        <v>1000</v>
+      </c>
+      <c r="AO47">
+        <v>1000</v>
+      </c>
+      <c r="AP47">
+        <v>1.01</v>
+      </c>
+      <c r="AQ47">
+        <v>1.01</v>
+      </c>
+      <c r="AR47">
+        <v>1.01</v>
+      </c>
+      <c r="AS47">
+        <v>1.01</v>
+      </c>
+      <c r="AT47">
+        <v>1.01</v>
+      </c>
+      <c r="AU47">
+        <v>1.01</v>
+      </c>
+      <c r="AV47">
+        <v>1.01</v>
+      </c>
+      <c r="AW47">
+        <v>1.01</v>
+      </c>
+      <c r="AX47">
+        <v>1.01</v>
+      </c>
+      <c r="AY47">
+        <v>1.01</v>
+      </c>
+      <c r="AZ47">
+        <v>1.01</v>
+      </c>
+      <c r="BA47">
+        <v>1.01</v>
+      </c>
+      <c r="BB47">
+        <v>1.01</v>
+      </c>
+      <c r="BC47">
+        <v>1.01</v>
+      </c>
+      <c r="BD47">
+        <v>1.01</v>
+      </c>
+      <c r="BE47">
+        <v>1.01</v>
+      </c>
+      <c r="BF47">
+        <v>1.01</v>
+      </c>
+      <c r="BG47">
+        <v>1.01</v>
+      </c>
+      <c r="BH47">
+        <v>1000</v>
+      </c>
+      <c r="BI47">
+        <v>1.01</v>
+      </c>
+      <c r="BJ47">
+        <v>1000</v>
+      </c>
+      <c r="BK47">
+        <v>1.01</v>
+      </c>
+      <c r="BL47">
+        <v>1000</v>
+      </c>
+      <c r="BM47">
+        <v>1.01</v>
+      </c>
+      <c r="BN47">
+        <v>1000</v>
+      </c>
+      <c r="BO47">
+        <v>1.01</v>
+      </c>
+      <c r="BP47">
+        <v>1000</v>
+      </c>
+      <c r="BQ47">
+        <v>1.01</v>
+      </c>
+      <c r="BR47">
+        <v>1000</v>
+      </c>
+      <c r="BS47">
+        <v>1.01</v>
+      </c>
+      <c r="BT47">
+        <v>1000</v>
+      </c>
+      <c r="BU47">
+        <v>1.01</v>
+      </c>
+      <c r="BV47">
+        <v>1000</v>
+      </c>
+      <c r="BW47">
+        <v>1.01</v>
+      </c>
+      <c r="BX47">
+        <v>1000</v>
+      </c>
+      <c r="BY47">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47">
+        <v>0</v>
+      </c>
+      <c r="CA47">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:80">
+      <c r="A48" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48">
+        <v>1.58</v>
+      </c>
+      <c r="G48">
+        <v>1.66</v>
+      </c>
+      <c r="H48">
+        <v>6.2</v>
+      </c>
+      <c r="I48">
+        <v>7</v>
+      </c>
+      <c r="J48">
+        <v>4.1</v>
+      </c>
+      <c r="K48">
+        <v>4.6</v>
+      </c>
+      <c r="L48">
+        <v>1.3</v>
+      </c>
+      <c r="M48">
+        <v>1.06</v>
+      </c>
+      <c r="N48">
+        <v>4</v>
+      </c>
+      <c r="O48">
+        <v>1.28</v>
+      </c>
+      <c r="P48">
+        <v>2.04</v>
+      </c>
+      <c r="Q48">
+        <v>1.82</v>
+      </c>
+      <c r="R48">
+        <v>1.41</v>
+      </c>
+      <c r="S48">
+        <v>3.1</v>
+      </c>
+      <c r="T48">
+        <v>1.88</v>
+      </c>
+      <c r="U48">
+        <v>1.98</v>
+      </c>
+      <c r="V48">
+        <v>1.17</v>
+      </c>
+      <c r="W48">
+        <v>2.5</v>
+      </c>
+      <c r="X48">
+        <v>19.5</v>
+      </c>
+      <c r="Y48">
+        <v>25</v>
+      </c>
+      <c r="Z48">
+        <v>65</v>
+      </c>
+      <c r="AA48">
         <v>210</v>
+      </c>
+      <c r="AB48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC48">
+        <v>11.5</v>
+      </c>
+      <c r="AD48">
+        <v>28</v>
+      </c>
+      <c r="AE48">
+        <v>110</v>
+      </c>
+      <c r="AF48">
+        <v>11.5</v>
+      </c>
+      <c r="AG48">
+        <v>11.5</v>
+      </c>
+      <c r="AH48">
+        <v>25</v>
+      </c>
+      <c r="AI48">
+        <v>100</v>
+      </c>
+      <c r="AJ48">
+        <v>16</v>
+      </c>
+      <c r="AK48">
+        <v>20</v>
+      </c>
+      <c r="AL48">
+        <v>36</v>
+      </c>
+      <c r="AM48">
+        <v>140</v>
+      </c>
+      <c r="AN48">
+        <v>9</v>
+      </c>
+      <c r="AO48">
+        <v>130</v>
+      </c>
+      <c r="AP48">
+        <v>14.5</v>
+      </c>
+      <c r="AQ48">
+        <v>19</v>
+      </c>
+      <c r="AR48">
+        <v>5.9</v>
+      </c>
+      <c r="AS48">
+        <v>6.4</v>
+      </c>
+      <c r="AT48">
+        <v>7.6</v>
+      </c>
+      <c r="AU48">
+        <v>8.6</v>
+      </c>
+      <c r="AV48">
+        <v>21</v>
+      </c>
+      <c r="AW48">
+        <v>6.2</v>
+      </c>
+      <c r="AX48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ48">
+        <v>18.5</v>
+      </c>
+      <c r="BA48">
+        <v>6.2</v>
+      </c>
+      <c r="BB48">
+        <v>13.5</v>
+      </c>
+      <c r="BC48">
+        <v>15</v>
+      </c>
+      <c r="BD48">
+        <v>5.6</v>
+      </c>
+      <c r="BE48">
+        <v>6.2</v>
+      </c>
+      <c r="BF48">
+        <v>7.8</v>
+      </c>
+      <c r="BG48">
+        <v>6.2</v>
+      </c>
+      <c r="BH48">
+        <v>1000</v>
+      </c>
+      <c r="BI48">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48">
+        <v>1000</v>
+      </c>
+      <c r="BK48">
+        <v>1.01</v>
+      </c>
+      <c r="BL48">
+        <v>1000</v>
+      </c>
+      <c r="BM48">
+        <v>1.01</v>
+      </c>
+      <c r="BN48">
+        <v>1000</v>
+      </c>
+      <c r="BO48">
+        <v>1.01</v>
+      </c>
+      <c r="BP48">
+        <v>1000</v>
+      </c>
+      <c r="BQ48">
+        <v>1.01</v>
+      </c>
+      <c r="BR48">
+        <v>1000</v>
+      </c>
+      <c r="BS48">
+        <v>1.01</v>
+      </c>
+      <c r="BT48">
+        <v>1000</v>
+      </c>
+      <c r="BU48">
+        <v>1.01</v>
+      </c>
+      <c r="BV48">
+        <v>1000</v>
+      </c>
+      <c r="BW48">
+        <v>1.01</v>
+      </c>
+      <c r="BX48">
+        <v>1000</v>
+      </c>
+      <c r="BY48">
+        <v>1.01</v>
+      </c>
+      <c r="BZ48">
+        <v>1000</v>
+      </c>
+      <c r="CA48">
+        <v>1.01</v>
+      </c>
+      <c r="CB48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:80">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" t="s">
+        <v>226</v>
+      </c>
+      <c r="F49">
+        <v>1.74</v>
+      </c>
+      <c r="G49">
+        <v>1.85</v>
+      </c>
+      <c r="H49">
+        <v>4.9</v>
+      </c>
+      <c r="I49">
+        <v>5.8</v>
+      </c>
+      <c r="J49">
+        <v>3.55</v>
+      </c>
+      <c r="K49">
+        <v>4.2</v>
+      </c>
+      <c r="L49">
+        <v>1.01</v>
+      </c>
+      <c r="M49">
+        <v>1.07</v>
+      </c>
+      <c r="N49">
+        <v>3.55</v>
+      </c>
+      <c r="O49">
+        <v>1.33</v>
+      </c>
+      <c r="P49">
+        <v>1.85</v>
+      </c>
+      <c r="Q49">
+        <v>1.98</v>
+      </c>
+      <c r="R49">
+        <v>1.33</v>
+      </c>
+      <c r="S49">
+        <v>3.45</v>
+      </c>
+      <c r="T49">
+        <v>1.87</v>
+      </c>
+      <c r="U49">
+        <v>1.94</v>
+      </c>
+      <c r="V49">
+        <v>1.21</v>
+      </c>
+      <c r="W49">
+        <v>2.16</v>
+      </c>
+      <c r="X49">
+        <v>17.5</v>
+      </c>
+      <c r="Y49">
+        <v>20</v>
+      </c>
+      <c r="Z49">
+        <v>50</v>
+      </c>
+      <c r="AA49">
+        <v>170</v>
+      </c>
+      <c r="AB49">
+        <v>10</v>
+      </c>
+      <c r="AC49">
+        <v>10</v>
+      </c>
+      <c r="AD49">
+        <v>26</v>
+      </c>
+      <c r="AE49">
+        <v>85</v>
+      </c>
+      <c r="AF49">
+        <v>12.5</v>
+      </c>
+      <c r="AG49">
+        <v>12.5</v>
+      </c>
+      <c r="AH49">
+        <v>22</v>
+      </c>
+      <c r="AI49">
+        <v>95</v>
+      </c>
+      <c r="AJ49">
+        <v>24</v>
+      </c>
+      <c r="AK49">
+        <v>24</v>
+      </c>
+      <c r="AL49">
+        <v>46</v>
+      </c>
+      <c r="AM49">
+        <v>150</v>
+      </c>
+      <c r="AN49">
+        <v>15</v>
+      </c>
+      <c r="AO49">
+        <v>110</v>
+      </c>
+      <c r="AP49">
+        <v>10</v>
+      </c>
+      <c r="AQ49">
+        <v>12.5</v>
+      </c>
+      <c r="AR49">
+        <v>1.01</v>
+      </c>
+      <c r="AS49">
+        <v>1.01</v>
+      </c>
+      <c r="AT49">
+        <v>6.2</v>
+      </c>
+      <c r="AU49">
+        <v>6.4</v>
+      </c>
+      <c r="AV49">
+        <v>15</v>
+      </c>
+      <c r="AW49">
+        <v>1.01</v>
+      </c>
+      <c r="AX49">
+        <v>7.8</v>
+      </c>
+      <c r="AY49">
+        <v>7.6</v>
+      </c>
+      <c r="AZ49">
+        <v>15</v>
+      </c>
+      <c r="BA49">
+        <v>1.01</v>
+      </c>
+      <c r="BB49">
+        <v>14.5</v>
+      </c>
+      <c r="BC49">
+        <v>14.5</v>
+      </c>
+      <c r="BD49">
+        <v>1.01</v>
+      </c>
+      <c r="BE49">
+        <v>1.01</v>
+      </c>
+      <c r="BF49">
+        <v>9.4</v>
+      </c>
+      <c r="BG49">
+        <v>1.01</v>
+      </c>
+      <c r="BH49">
+        <v>4.4</v>
+      </c>
+      <c r="BI49">
+        <v>2.58</v>
+      </c>
+      <c r="BJ49">
+        <v>1000</v>
+      </c>
+      <c r="BK49">
+        <v>1.3</v>
+      </c>
+      <c r="BL49">
+        <v>1000</v>
+      </c>
+      <c r="BM49">
+        <v>1.3</v>
+      </c>
+      <c r="BN49">
+        <v>1000</v>
+      </c>
+      <c r="BO49">
+        <v>1.3</v>
+      </c>
+      <c r="BP49">
+        <v>1000</v>
+      </c>
+      <c r="BQ49">
+        <v>1.3</v>
+      </c>
+      <c r="BR49">
+        <v>1000</v>
+      </c>
+      <c r="BS49">
+        <v>1.3</v>
+      </c>
+      <c r="BT49">
+        <v>1000</v>
+      </c>
+      <c r="BU49">
+        <v>1.3</v>
+      </c>
+      <c r="BV49">
+        <v>1000</v>
+      </c>
+      <c r="BW49">
+        <v>1.3</v>
+      </c>
+      <c r="BX49">
+        <v>1000</v>
+      </c>
+      <c r="BY49">
+        <v>1.3</v>
+      </c>
+      <c r="BZ49">
+        <v>0</v>
+      </c>
+      <c r="CA49">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -697,7 +697,7 @@
     <t>Ypiranga RS</t>
   </si>
   <si>
-    <t>2026-08-16 00:24:53</t>
+    <t>2026-08-16 02:41:26</t>
   </si>
 </sst>
 </file>
@@ -1291,31 +1291,31 @@
         <v>179</v>
       </c>
       <c r="F2">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G2">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H2">
         <v>2.62</v>
       </c>
       <c r="I2">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>1.28</v>
@@ -1324,25 +1324,25 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
         <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U2">
         <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W2">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X2">
         <v>19.5</v>
@@ -1369,7 +1369,7 @@
         <v>32</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG2">
         <v>15</v>
@@ -1533,100 +1533,100 @@
         <v>180</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
+        <v>11.5</v>
+      </c>
+      <c r="Z3">
+        <v>18</v>
+      </c>
+      <c r="AA3">
+        <v>46</v>
+      </c>
+      <c r="AB3">
+        <v>11</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>13</v>
+      </c>
+      <c r="AE3">
+        <v>36</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
         <v>13.5</v>
-      </c>
-      <c r="Z3">
-        <v>26</v>
-      </c>
-      <c r="AA3">
-        <v>70</v>
-      </c>
-      <c r="AB3">
-        <v>11.5</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>14.5</v>
-      </c>
-      <c r="AE3">
-        <v>50</v>
-      </c>
-      <c r="AF3">
-        <v>17</v>
-      </c>
-      <c r="AG3">
-        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1635,22 +1635,22 @@
         <v>140</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AP3">
         <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1668,16 +1668,16 @@
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC3">
         <v>1.01</v>
@@ -1692,67 +1692,67 @@
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BW3">
         <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BY3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>227</v>
@@ -1775,22 +1775,22 @@
         <v>181</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.33</v>
@@ -1817,16 +1817,16 @@
         <v>2.78</v>
       </c>
       <c r="T4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1856,7 +1856,7 @@
         <v>24</v>
       </c>
       <c r="AG4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
         <v>16</v>
@@ -1865,13 +1865,13 @@
         <v>34</v>
       </c>
       <c r="AJ4">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AK4">
         <v>34</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1886,22 +1886,22 @@
         <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
         <v>19.5</v>
@@ -1916,19 +1916,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BB4">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BD4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1940,7 +1940,7 @@
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4">
         <v>9.199999999999999</v>
@@ -1967,7 +1967,7 @@
         <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4">
         <v>1.04</v>
@@ -2017,10 +2017,10 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H5">
         <v>1.57</v>
@@ -2029,7 +2029,7 @@
         <v>1.61</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -2038,40 +2038,40 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S5">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>12</v>
@@ -2104,16 +2104,16 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AJ5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK5">
         <v>100</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AM5">
         <v>95</v>
@@ -2122,7 +2122,7 @@
         <v>95</v>
       </c>
       <c r="AO5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -2134,10 +2134,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2149,31 +2149,31 @@
         <v>13</v>
       </c>
       <c r="AX5">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AY5">
         <v>20</v>
       </c>
       <c r="AZ5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA5">
         <v>20</v>
       </c>
       <c r="BB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC5">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BG5">
         <v>5.8</v>
@@ -2271,7 +2271,7 @@
         <v>1.89</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2310,7 +2310,7 @@
         <v>2.12</v>
       </c>
       <c r="W6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X6">
         <v>23</v>
@@ -2337,19 +2337,19 @@
         <v>17.5</v>
       </c>
       <c r="AF6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG6">
         <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
         <v>32</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK6">
         <v>46</v>
@@ -2364,7 +2364,7 @@
         <v>36</v>
       </c>
       <c r="AO6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2430,31 +2430,31 @@
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>100</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>9.4</v>
       </c>
       <c r="BO6">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>36</v>
       </c>
       <c r="BQ6">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>42</v>
       </c>
       <c r="BS6">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>5.8</v>
@@ -2463,22 +2463,22 @@
         <v>3.8</v>
       </c>
       <c r="BV6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>27</v>
       </c>
       <c r="BY6">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>19</v>
       </c>
       <c r="CA6">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>227</v>
@@ -2501,7 +2501,7 @@
         <v>184</v>
       </c>
       <c r="F7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
         <v>3.5</v>
@@ -2519,31 +2519,31 @@
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
         <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U7">
         <v>2.28</v>
@@ -2591,7 +2591,7 @@
         <v>80</v>
       </c>
       <c r="AJ7">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="AK7">
         <v>42</v>
@@ -2603,7 +2603,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO7">
         <v>17</v>
@@ -2654,10 +2654,10 @@
         <v>38</v>
       </c>
       <c r="BE7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG7">
         <v>15</v>
@@ -2666,61 +2666,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>227</v>
@@ -2746,10 +2746,10 @@
         <v>2.48</v>
       </c>
       <c r="G8">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I8">
         <v>2.98</v>
@@ -2758,43 +2758,43 @@
         <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
         <v>2.42</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S8">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="U8">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="V8">
         <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2803,19 +2803,19 @@
         <v>19.5</v>
       </c>
       <c r="Z8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC8">
         <v>11.5</v>
       </c>
       <c r="AD8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE8">
         <v>29</v>
@@ -2854,40 +2854,40 @@
         <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AR8">
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU8">
         <v>8.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2896,64 +2896,64 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK8">
+        <v>6.4</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>6.2</v>
+      </c>
+      <c r="BO8">
+        <v>5</v>
+      </c>
+      <c r="BP8">
+        <v>17.5</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>26</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>6.6</v>
+      </c>
+      <c r="BU8">
         <v>5.4</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO8">
-        <v>3.8</v>
-      </c>
-      <c r="BP8">
-        <v>25</v>
-      </c>
-      <c r="BQ8">
-        <v>1.01</v>
-      </c>
-      <c r="BR8">
-        <v>36</v>
-      </c>
-      <c r="BS8">
-        <v>1.01</v>
-      </c>
-      <c r="BT8">
-        <v>9</v>
-      </c>
-      <c r="BU8">
-        <v>4.1</v>
-      </c>
       <c r="BV8">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
@@ -3015,13 +3015,13 @@
         <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q9">
         <v>1.53</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
         <v>2.28</v>
@@ -3230,10 +3230,10 @@
         <v>1.84</v>
       </c>
       <c r="G10">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
         <v>4.9</v>
@@ -3275,10 +3275,10 @@
         <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W10">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X10">
         <v>19</v>
@@ -3335,46 +3335,46 @@
         <v>65</v>
       </c>
       <c r="AP10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU10">
         <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW10">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10">
         <v>13</v>
       </c>
       <c r="BA10">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BC10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD10">
         <v>25</v>
@@ -3383,10 +3383,10 @@
         <v>65</v>
       </c>
       <c r="BF10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG10">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
@@ -3720,7 +3720,7 @@
         <v>1.46</v>
       </c>
       <c r="I12">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -3759,10 +3759,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3956,10 +3956,10 @@
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I13">
         <v>4.5</v>
@@ -3971,25 +3971,25 @@
         <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M13">
         <v>1.08</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
         <v>1.35</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q13">
         <v>2.02</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13">
         <v>3.6</v>
@@ -4001,10 +4001,10 @@
         <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X13">
         <v>13.5</v>
@@ -4046,7 +4046,7 @@
         <v>27</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13">
         <v>42</v>
@@ -4067,10 +4067,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13">
         <v>7.6</v>
@@ -4082,7 +4082,7 @@
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13">
         <v>11</v>
@@ -4094,7 +4094,7 @@
         <v>16</v>
       </c>
       <c r="BA13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB13">
         <v>7</v>
@@ -4103,34 +4103,34 @@
         <v>20</v>
       </c>
       <c r="BD13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF13">
         <v>13</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13">
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN13">
         <v>4.9</v>
@@ -4142,13 +4142,13 @@
         <v>16</v>
       </c>
       <c r="BQ13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT13">
         <v>7.4</v>
@@ -4160,19 +4160,19 @@
         <v>1000</v>
       </c>
       <c r="BW13">
+        <v>9.4</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>10</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>9.4</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>8.4</v>
       </c>
       <c r="CB13" t="s">
         <v>227</v>
@@ -4198,7 +4198,7 @@
         <v>1.52</v>
       </c>
       <c r="G14">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -4219,22 +4219,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
         <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T14">
         <v>1.58</v>
@@ -4608,49 +4608,49 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>1.8</v>
       </c>
       <c r="G17">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H17">
         <v>3.75</v>
@@ -4963,7 +4963,7 @@
         <v>3.75</v>
       </c>
       <c r="T17">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U17">
         <v>1.89</v>
@@ -4972,7 +4972,7 @@
         <v>1.21</v>
       </c>
       <c r="W17">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5298,13 +5298,13 @@
         <v>18</v>
       </c>
       <c r="AY18">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
         <v>11</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB18">
         <v>1.01</v>
@@ -5411,10 +5411,10 @@
         <v>1.49</v>
       </c>
       <c r="H19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
         <v>4.9</v>
@@ -5453,7 +5453,7 @@
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W19">
         <v>3</v>
@@ -5462,7 +5462,7 @@
         <v>22</v>
       </c>
       <c r="Y19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z19">
         <v>70</v>
@@ -5492,7 +5492,7 @@
         <v>23</v>
       </c>
       <c r="AI19">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ19">
         <v>14</v>
@@ -5522,7 +5522,7 @@
         <v>55</v>
       </c>
       <c r="AS19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT19">
         <v>8.4</v>
@@ -5534,7 +5534,7 @@
         <v>25</v>
       </c>
       <c r="AW19">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX19">
         <v>8.6</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="BA19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB19">
         <v>12</v>
@@ -5558,13 +5558,13 @@
         <v>26</v>
       </c>
       <c r="BE19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF19">
         <v>5.8</v>
       </c>
       <c r="BG19">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5656,16 +5656,16 @@
         <v>4.7</v>
       </c>
       <c r="I20">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J20">
         <v>3.8</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M20">
         <v>1.05</v>
@@ -5677,25 +5677,25 @@
         <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
         <v>3</v>
       </c>
       <c r="T20">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U20">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W20">
         <v>2.12</v>
@@ -5707,7 +5707,7 @@
         <v>23</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA20">
         <v>150</v>
@@ -5740,7 +5740,7 @@
         <v>23</v>
       </c>
       <c r="AK20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL20">
         <v>42</v>
@@ -5749,34 +5749,34 @@
         <v>120</v>
       </c>
       <c r="AN20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO20">
         <v>85</v>
       </c>
       <c r="AP20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
         <v>7</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV20">
         <v>14.5</v>
       </c>
       <c r="AW20">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
         <v>8.4</v>
@@ -5785,82 +5785,82 @@
         <v>7.6</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA20">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
         <v>13.5</v>
       </c>
       <c r="BC20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD20">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>7.8</v>
       </c>
       <c r="BG20">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>4.3</v>
       </c>
       <c r="BI20">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ20">
         <v>12</v>
       </c>
       <c r="BK20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>5.3</v>
       </c>
       <c r="BO20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP20">
         <v>14.5</v>
       </c>
       <c r="BQ20">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>32</v>
       </c>
       <c r="BS20">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>10.5</v>
       </c>
       <c r="BU20">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
         <v>50</v>
       </c>
       <c r="BW20">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>60</v>
       </c>
       <c r="BY20">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5892,13 +5892,13 @@
         <v>1.82</v>
       </c>
       <c r="G21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H21">
         <v>5.1</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J21">
         <v>3.4</v>
@@ -5919,7 +5919,7 @@
         <v>1.44</v>
       </c>
       <c r="P21">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q21">
         <v>2.28</v>
@@ -5931,10 +5931,10 @@
         <v>4.3</v>
       </c>
       <c r="T21">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U21">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V21">
         <v>1.2</v>
@@ -5949,10 +5949,10 @@
         <v>17</v>
       </c>
       <c r="Z21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA21">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB21">
         <v>7.2</v>
@@ -5964,7 +5964,7 @@
         <v>25</v>
       </c>
       <c r="AE21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF21">
         <v>12</v>
@@ -5976,7 +5976,7 @@
         <v>27</v>
       </c>
       <c r="AI21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ21">
         <v>25</v>
@@ -5985,16 +5985,16 @@
         <v>27</v>
       </c>
       <c r="AL21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM21">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN21">
         <v>21</v>
       </c>
       <c r="AO21">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP21">
         <v>9.4</v>
@@ -6006,7 +6006,7 @@
         <v>29</v>
       </c>
       <c r="AS21">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT21">
         <v>6</v>
@@ -6018,7 +6018,7 @@
         <v>18</v>
       </c>
       <c r="AW21">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX21">
         <v>8.800000000000001</v>
@@ -6030,7 +6030,7 @@
         <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB21">
         <v>18</v>
@@ -6039,16 +6039,16 @@
         <v>19.5</v>
       </c>
       <c r="BD21">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE21">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF21">
         <v>13.5</v>
       </c>
       <c r="BG21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6131,7 +6131,7 @@
         <v>199</v>
       </c>
       <c r="F22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G22">
         <v>1.39</v>
@@ -6140,7 +6140,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>5.9</v>
@@ -6158,10 +6158,10 @@
         <v>6.6</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
@@ -6170,13 +6170,13 @@
         <v>1.76</v>
       </c>
       <c r="S22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T22">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
         <v>1.11</v>
@@ -6197,10 +6197,10 @@
         <v>310</v>
       </c>
       <c r="AB22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AD22">
         <v>40</v>
@@ -6209,13 +6209,13 @@
         <v>130</v>
       </c>
       <c r="AF22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG22">
         <v>11</v>
       </c>
       <c r="AH22">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI22">
         <v>100</v>
@@ -6224,7 +6224,7 @@
         <v>14</v>
       </c>
       <c r="AK22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL22">
         <v>34</v>
@@ -6233,22 +6233,22 @@
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO22">
         <v>130</v>
       </c>
       <c r="AP22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS22">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT22">
         <v>11</v>
@@ -6257,10 +6257,10 @@
         <v>13</v>
       </c>
       <c r="AV22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX22">
         <v>9.199999999999999</v>
@@ -6272,7 +6272,7 @@
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB22">
         <v>10.5</v>
@@ -6284,19 +6284,19 @@
         <v>21</v>
       </c>
       <c r="BE22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF22">
         <v>3.85</v>
       </c>
       <c r="BG22">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH22">
         <v>6.2</v>
       </c>
       <c r="BI22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ22">
         <v>15</v>
@@ -6314,7 +6314,7 @@
         <v>5.6</v>
       </c>
       <c r="BO22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP22">
         <v>10.5</v>
@@ -6379,7 +6379,7 @@
         <v>3.3</v>
       </c>
       <c r="H23">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I23">
         <v>3.2</v>
@@ -6388,7 +6388,7 @@
         <v>2.8</v>
       </c>
       <c r="K23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6400,7 +6400,7 @@
         <v>1.01</v>
       </c>
       <c r="O23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P23">
         <v>1.42</v>
@@ -6415,7 +6415,7 @@
         <v>5.7</v>
       </c>
       <c r="T23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U23">
         <v>1.67</v>
@@ -6430,7 +6430,7 @@
         <v>8.4</v>
       </c>
       <c r="Y23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z23">
         <v>22</v>
@@ -6517,7 +6517,7 @@
         <v>4.3</v>
       </c>
       <c r="BB23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC23">
         <v>4.2</v>
@@ -6526,7 +6526,7 @@
         <v>4.3</v>
       </c>
       <c r="BE23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF23">
         <v>4.3</v>
@@ -6615,22 +6615,22 @@
         <v>201</v>
       </c>
       <c r="F24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G24">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H24">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I24">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J24">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6648,13 +6648,13 @@
         <v>2.62</v>
       </c>
       <c r="Q24">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R24">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="S24">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6663,10 +6663,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W24">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6863,10 +6863,10 @@
         <v>4.4</v>
       </c>
       <c r="H25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J25">
         <v>3.45</v>
@@ -6905,7 +6905,7 @@
         <v>2.14</v>
       </c>
       <c r="V25">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W25">
         <v>1.29</v>
@@ -6965,58 +6965,58 @@
         <v>14</v>
       </c>
       <c r="AP25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ25">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS25">
         <v>20</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU25">
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AW25">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX25">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AY25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA25">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BB25">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="BC25">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BD25">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="BE25">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="BF25">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BG25">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7126,7 +7126,7 @@
         <v>1.91</v>
       </c>
       <c r="O26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P26">
         <v>1.26</v>
@@ -7341,112 +7341,112 @@
         <v>204</v>
       </c>
       <c r="F27">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="G27">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="H27">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="I27">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27">
-        <v>2.48</v>
+        <v>6.4</v>
       </c>
       <c r="O27">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P27">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="R27">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="S27">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP27">
         <v>1.01</v>
@@ -7592,7 +7592,7 @@
         <v>2</v>
       </c>
       <c r="I28">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J28">
         <v>3.9</v>
@@ -7622,16 +7622,16 @@
         <v>1.59</v>
       </c>
       <c r="S28">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T28">
         <v>1.53</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W28">
         <v>1.36</v>
@@ -7825,112 +7825,112 @@
         <v>206</v>
       </c>
       <c r="F29">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="G29">
-        <v>110</v>
+        <v>2.98</v>
       </c>
       <c r="H29">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="I29">
-        <v>110</v>
+        <v>2.94</v>
       </c>
       <c r="J29">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K29">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O29">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="P29">
-        <v>1.26</v>
+        <v>2.68</v>
       </c>
       <c r="Q29">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="R29">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="S29">
-        <v>1.09</v>
+        <v>1.93</v>
       </c>
       <c r="T29">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U29">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="V29">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP29">
         <v>1.01</v>
@@ -8070,19 +8070,19 @@
         <v>2.78</v>
       </c>
       <c r="G30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H30">
         <v>2.24</v>
       </c>
       <c r="I30">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="J30">
         <v>3.95</v>
       </c>
       <c r="K30">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8091,10 +8091,10 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P30">
         <v>2.7</v>
@@ -8103,139 +8103,139 @@
         <v>1.5</v>
       </c>
       <c r="R30">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S30">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V30">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W30">
         <v>1.46</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS30">
         <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB30">
         <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE30">
         <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK30">
         <v>1.01</v>
@@ -8247,13 +8247,13 @@
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
@@ -8265,13 +8265,13 @@
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
@@ -8283,7 +8283,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA30">
         <v>1.01</v>
@@ -8309,22 +8309,22 @@
         <v>208</v>
       </c>
       <c r="F31">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G31">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I31">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J31">
         <v>4.6</v>
       </c>
       <c r="K31">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8333,7 +8333,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O31">
         <v>1.1</v>
@@ -8357,10 +8357,10 @@
         <v>3.05</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X31">
         <v>60</v>
@@ -8375,7 +8375,7 @@
         <v>85</v>
       </c>
       <c r="AB31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC31">
         <v>14.5</v>
@@ -8399,7 +8399,7 @@
         <v>32</v>
       </c>
       <c r="AJ31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK31">
         <v>17.5</v>
@@ -8414,7 +8414,7 @@
         <v>5.9</v>
       </c>
       <c r="AO31">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP31">
         <v>1.01</v>
@@ -8551,22 +8551,22 @@
         <v>209</v>
       </c>
       <c r="F32">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G32">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H32">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I32">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L32">
         <v>1.19</v>
@@ -8575,88 +8575,88 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O32">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q32">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="R32">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S32">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W32">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC32">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF32">
         <v>18.5</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH32">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK32">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN32">
         <v>6.2</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP32">
         <v>1.01</v>
@@ -8674,7 +8674,7 @@
         <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
         <v>1.01</v>
@@ -8686,7 +8686,7 @@
         <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
         <v>1.01</v>
@@ -8707,7 +8707,7 @@
         <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
         <v>1.01</v>
@@ -8749,7 +8749,7 @@
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
@@ -8793,13 +8793,13 @@
         <v>210</v>
       </c>
       <c r="F33">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G33">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I33">
         <v>6.4</v>
@@ -8808,7 +8808,7 @@
         <v>3.45</v>
       </c>
       <c r="K33">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8817,7 +8817,7 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
         <v>1.32</v>
@@ -8826,13 +8826,13 @@
         <v>1.68</v>
       </c>
       <c r="Q33">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S33">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T33">
         <v>1.01</v>
@@ -8844,7 +8844,7 @@
         <v>1.18</v>
       </c>
       <c r="W33">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9035,22 +9035,22 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="G34">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="H34">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J34">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K34">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>1.32</v>
@@ -9059,34 +9059,34 @@
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O34">
         <v>1.23</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R34">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S34">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U34">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V34">
         <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="X34">
         <v>24</v>
@@ -9104,31 +9104,31 @@
         <v>11</v>
       </c>
       <c r="AC34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD34">
         <v>27</v>
       </c>
       <c r="AE34">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG34">
         <v>11</v>
       </c>
       <c r="AH34">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI34">
         <v>80</v>
       </c>
       <c r="AJ34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK34">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL34">
         <v>34</v>
@@ -9140,7 +9140,7 @@
         <v>8</v>
       </c>
       <c r="AO34">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP34">
         <v>16</v>
@@ -9176,7 +9176,7 @@
         <v>5.3</v>
       </c>
       <c r="BA34">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9185,10 +9185,10 @@
         <v>12</v>
       </c>
       <c r="BD34">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE34">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF34">
         <v>5.9</v>
@@ -9200,13 +9200,13 @@
         <v>4.1</v>
       </c>
       <c r="BI34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ34">
         <v>10</v>
       </c>
       <c r="BK34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9221,22 +9221,22 @@
         <v>3.85</v>
       </c>
       <c r="BP34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ34">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT34">
         <v>9.800000000000001</v>
       </c>
       <c r="BU34">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV34">
         <v>1000</v>
@@ -9251,10 +9251,10 @@
         <v>36</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA34">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB34" t="s">
         <v>227</v>
@@ -9280,16 +9280,16 @@
         <v>2.24</v>
       </c>
       <c r="G35">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H35">
         <v>3.6</v>
       </c>
       <c r="I35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J35">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K35">
         <v>3.5</v>
@@ -9301,40 +9301,40 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O35">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P35">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q35">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R35">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S35">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="T35">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U35">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
         <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X35">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z35">
         <v>38</v>
@@ -9343,16 +9343,16 @@
         <v>100</v>
       </c>
       <c r="AB35">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC35">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD35">
         <v>15.5</v>
       </c>
       <c r="AE35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF35">
         <v>970</v>
@@ -9361,40 +9361,40 @@
         <v>11.5</v>
       </c>
       <c r="AH35">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AI35">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ35">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AK35">
         <v>27</v>
       </c>
       <c r="AL35">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM35">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN35">
         <v>22</v>
       </c>
       <c r="AO35">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AP35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ35">
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AS35">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT35">
         <v>8.199999999999999</v>
@@ -9415,22 +9415,22 @@
         <v>10</v>
       </c>
       <c r="AZ35">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BA35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB35">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BC35">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BD35">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BE35">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF35">
         <v>13.5</v>
@@ -9597,13 +9597,13 @@
         <v>34</v>
       </c>
       <c r="AF36">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG36">
         <v>12</v>
       </c>
       <c r="AH36">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI36">
         <v>40</v>
@@ -9627,7 +9627,7 @@
         <v>23</v>
       </c>
       <c r="AP36">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ36">
         <v>12.5</v>
@@ -9690,55 +9690,55 @@
         <v>1000</v>
       </c>
       <c r="BK36">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BN36">
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP36">
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB36" t="s">
         <v>227</v>
@@ -9791,10 +9791,10 @@
         <v>1.45</v>
       </c>
       <c r="P37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q37">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R37">
         <v>1.25</v>
@@ -9815,7 +9815,7 @@
         <v>1.7</v>
       </c>
       <c r="X37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>11.5</v>
@@ -9854,7 +9854,7 @@
         <v>34</v>
       </c>
       <c r="AK37">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL37">
         <v>50</v>
@@ -9875,7 +9875,7 @@
         <v>10.5</v>
       </c>
       <c r="AR37">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS37">
         <v>60</v>
@@ -9890,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="AW37">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AX37">
         <v>12.5</v>
@@ -9908,7 +9908,7 @@
         <v>29</v>
       </c>
       <c r="BC37">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BD37">
         <v>46</v>
@@ -9926,7 +9926,7 @@
         <v>2.94</v>
       </c>
       <c r="BI37">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ37">
         <v>10.5</v>
@@ -9935,16 +9935,16 @@
         <v>8</v>
       </c>
       <c r="BL37">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM37">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BN37">
         <v>5.1</v>
       </c>
       <c r="BO37">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP37">
         <v>19.5</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="BZ37">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA37">
         <v>29</v>
@@ -10006,7 +10006,7 @@
         <v>16.5</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H38">
         <v>1.24</v>
@@ -10030,7 +10030,7 @@
         <v>5</v>
       </c>
       <c r="O38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P38">
         <v>2.36</v>
@@ -10042,10 +10042,10 @@
         <v>1.53</v>
       </c>
       <c r="S38">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T38">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U38">
         <v>1.65</v>
@@ -10054,13 +10054,13 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
         <v>25</v>
       </c>
       <c r="Y38">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z38">
         <v>7.8</v>
@@ -10087,7 +10087,7 @@
         <v>65</v>
       </c>
       <c r="AH38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI38">
         <v>50</v>
@@ -10102,10 +10102,10 @@
         <v>260</v>
       </c>
       <c r="AM38">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AN38">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AO38">
         <v>4.6</v>
@@ -10144,13 +10144,13 @@
         <v>34</v>
       </c>
       <c r="BA38">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB38">
         <v>11.5</v>
       </c>
       <c r="BC38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD38">
         <v>11</v>
@@ -10269,13 +10269,13 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O39">
         <v>1.05</v>
       </c>
       <c r="P39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q39">
         <v>1.05</v>
@@ -10284,7 +10284,7 @@
         <v>1.25</v>
       </c>
       <c r="S39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10487,22 +10487,22 @@
         <v>217</v>
       </c>
       <c r="F40">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="G40">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="H40">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="I40">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J40">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10511,22 +10511,22 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P40">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="Q40">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="R40">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="S40">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10535,10 +10535,10 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="W40">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10729,22 +10729,22 @@
         <v>218</v>
       </c>
       <c r="F41">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="G41">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="H41">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="I41">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J41">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K41">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10753,13 +10753,13 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="O41">
         <v>1.06</v>
       </c>
       <c r="P41">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
         <v>1.06</v>
@@ -10768,7 +10768,7 @@
         <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10777,10 +10777,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W41">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10897,7 +10897,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK41">
         <v>1.01</v>
@@ -10909,43 +10909,43 @@
         <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO41">
         <v>1.01</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ41">
         <v>1.01</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS41">
         <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU41">
         <v>1.01</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW41">
         <v>1.01</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY41">
         <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA41">
         <v>1.01</v>
@@ -10974,7 +10974,7 @@
         <v>1.36</v>
       </c>
       <c r="G42">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H42">
         <v>10</v>
@@ -10989,13 +10989,13 @@
         <v>5.9</v>
       </c>
       <c r="L42">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M42">
         <v>1.05</v>
       </c>
       <c r="N42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
         <v>1.22</v>
@@ -11004,10 +11004,10 @@
         <v>2.26</v>
       </c>
       <c r="Q42">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R42">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S42">
         <v>2.74</v>
@@ -11016,13 +11016,13 @@
         <v>2.08</v>
       </c>
       <c r="U42">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V42">
         <v>1.1</v>
       </c>
       <c r="W42">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X42">
         <v>25</v>
@@ -11031,10 +11031,10 @@
         <v>40</v>
       </c>
       <c r="Z42">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA42">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="AB42">
         <v>10.5</v>
@@ -11043,10 +11043,10 @@
         <v>15.5</v>
       </c>
       <c r="AD42">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AE42">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AF42">
         <v>8.4</v>
@@ -11055,10 +11055,10 @@
         <v>13</v>
       </c>
       <c r="AH42">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI42">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ42">
         <v>13</v>
@@ -11067,52 +11067,52 @@
         <v>18.5</v>
       </c>
       <c r="AL42">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM42">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN42">
         <v>5.9</v>
       </c>
       <c r="AO42">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AP42">
         <v>15</v>
       </c>
       <c r="AQ42">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR42">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS42">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU42">
         <v>10.5</v>
       </c>
       <c r="AV42">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW42">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY42">
         <v>8</v>
       </c>
       <c r="AZ42">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA42">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB42">
         <v>9.199999999999999</v>
@@ -11121,19 +11121,19 @@
         <v>11</v>
       </c>
       <c r="BD42">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE42">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF42">
         <v>4.3</v>
       </c>
       <c r="BG42">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH42">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI42">
         <v>3.15</v>
@@ -11142,13 +11142,13 @@
         <v>13</v>
       </c>
       <c r="BK42">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN42">
         <v>3.85</v>
@@ -11160,37 +11160,37 @@
         <v>8</v>
       </c>
       <c r="BQ42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR42">
         <v>26</v>
       </c>
       <c r="BS42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT42">
         <v>14.5</v>
       </c>
       <c r="BU42">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV42">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BW42">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX42">
         <v>110</v>
       </c>
       <c r="BY42">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ42">
         <v>13.5</v>
       </c>
       <c r="CA42">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB42" t="s">
         <v>227</v>
@@ -11213,7 +11213,7 @@
         <v>220</v>
       </c>
       <c r="F43">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G43">
         <v>2.56</v>
@@ -11234,10 +11234,10 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N43">
-        <v>1.45</v>
+        <v>2.36</v>
       </c>
       <c r="O43">
         <v>1.63</v>
@@ -11255,10 +11255,10 @@
         <v>6.2</v>
       </c>
       <c r="T43">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U43">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V43">
         <v>1.32</v>
@@ -11267,112 +11267,112 @@
         <v>1.64</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP43">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ43">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR43">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS43">
-        <v>48</v>
+        <v>4.4</v>
       </c>
       <c r="AT43">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU43">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV43">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW43">
-        <v>42</v>
+        <v>4.4</v>
       </c>
       <c r="AX43">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AY43">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BA43">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="BB43">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="BC43">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="BD43">
-        <v>46</v>
+        <v>4.4</v>
       </c>
       <c r="BE43">
-        <v>100</v>
+        <v>4.5</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11485,16 +11485,16 @@
         <v>1.02</v>
       </c>
       <c r="P44">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q44">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S44">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="T44">
         <v>1.01</v>
@@ -11697,19 +11697,19 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G45">
         <v>1000</v>
       </c>
       <c r="H45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I45">
         <v>1000</v>
       </c>
       <c r="J45">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K45">
         <v>470</v>
@@ -11939,7 +11939,7 @@
         <v>223</v>
       </c>
       <c r="F46">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G46">
         <v>1.94</v>
@@ -12184,16 +12184,16 @@
         <v>2.14</v>
       </c>
       <c r="G47">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H47">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I47">
         <v>4.4</v>
       </c>
       <c r="J47">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K47">
         <v>3.95</v>
@@ -12211,16 +12211,16 @@
         <v>1.39</v>
       </c>
       <c r="P47">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q47">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R47">
         <v>1.2</v>
       </c>
       <c r="S47">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T47">
         <v>1.01</v>
@@ -12232,7 +12232,7 @@
         <v>1.29</v>
       </c>
       <c r="W47">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12456,7 +12456,7 @@
         <v>2.04</v>
       </c>
       <c r="Q48">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R48">
         <v>1.41</v>
@@ -12465,13 +12465,13 @@
         <v>3.1</v>
       </c>
       <c r="T48">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="U48">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W48">
         <v>2.5</v>
@@ -12501,7 +12501,7 @@
         <v>110</v>
       </c>
       <c r="AF48">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG48">
         <v>11.5</v>
@@ -12516,7 +12516,7 @@
         <v>16</v>
       </c>
       <c r="AK48">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL48">
         <v>36</v>
@@ -12537,10 +12537,10 @@
         <v>19</v>
       </c>
       <c r="AR48">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS48">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT48">
         <v>7.6</v>
@@ -12552,7 +12552,7 @@
         <v>21</v>
       </c>
       <c r="AW48">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX48">
         <v>8.800000000000001</v>
@@ -12564,7 +12564,7 @@
         <v>18.5</v>
       </c>
       <c r="BA48">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB48">
         <v>13.5</v>
@@ -12573,16 +12573,16 @@
         <v>15</v>
       </c>
       <c r="BD48">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE48">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF48">
         <v>7.8</v>
       </c>
       <c r="BG48">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12591,7 +12591,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ48">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK48">
         <v>1.01</v>
@@ -12603,25 +12603,25 @@
         <v>1.01</v>
       </c>
       <c r="BN48">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO48">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP48">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ48">
         <v>1.01</v>
       </c>
       <c r="BR48">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS48">
         <v>1.01</v>
       </c>
       <c r="BT48">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU48">
         <v>1.01</v>
@@ -12639,7 +12639,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ48">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA48">
         <v>1.01</v>
@@ -12671,7 +12671,7 @@
         <v>1.85</v>
       </c>
       <c r="H49">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I49">
         <v>5.8</v>
@@ -12692,13 +12692,13 @@
         <v>3.55</v>
       </c>
       <c r="O49">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P49">
         <v>1.85</v>
       </c>
       <c r="Q49">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R49">
         <v>1.33</v>
@@ -12728,7 +12728,7 @@
         <v>50</v>
       </c>
       <c r="AA49">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB49">
         <v>10</v>
@@ -12740,7 +12740,7 @@
         <v>26</v>
       </c>
       <c r="AE49">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF49">
         <v>12.5</v>
@@ -12752,19 +12752,19 @@
         <v>22</v>
       </c>
       <c r="AI49">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ49">
         <v>24</v>
       </c>
       <c r="AK49">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL49">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM49">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN49">
         <v>15</v>
@@ -12773,7 +12773,7 @@
         <v>110</v>
       </c>
       <c r="AP49">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49">
         <v>12.5</v>
@@ -12785,10 +12785,10 @@
         <v>1.01</v>
       </c>
       <c r="AT49">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU49">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV49">
         <v>15</v>
@@ -12797,13 +12797,13 @@
         <v>1.01</v>
       </c>
       <c r="AX49">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY49">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA49">
         <v>1.01</v>
@@ -12812,7 +12812,7 @@
         <v>14.5</v>
       </c>
       <c r="BC49">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD49">
         <v>1.01</v>
@@ -12821,7 +12821,7 @@
         <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG49">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -697,7 +697,7 @@
     <t>Ypiranga RS</t>
   </si>
   <si>
-    <t>2026-08-16 02:41:26</t>
+    <t>2026-08-16 04:57:44</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1300,7 @@
         <v>2.62</v>
       </c>
       <c r="I2">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J2">
         <v>3.4</v>
@@ -1324,7 +1324,7 @@
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R2">
         <v>1.4</v>
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
         <v>2.8</v>
@@ -1611,7 +1611,7 @@
         <v>36</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1775,7 +1775,7 @@
         <v>181</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3.1</v>
@@ -1790,7 +1790,7 @@
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.33</v>
@@ -1805,7 +1805,7 @@
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q4">
         <v>1.71</v>
@@ -1814,19 +1814,19 @@
         <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T4">
         <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
         <v>21</v>
@@ -1847,7 +1847,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE4">
         <v>24</v>
@@ -1877,13 +1877,13 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4">
         <v>15</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ4">
         <v>12</v>
@@ -1937,22 +1937,22 @@
         <v>13</v>
       </c>
       <c r="BH4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI4">
         <v>3.3</v>
       </c>
       <c r="BJ4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1961,40 +1961,40 @@
         <v>5.1</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
         <v>30</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4">
         <v>5.8</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV4">
         <v>17</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX4">
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
         <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
         <v>227</v>
@@ -2017,7 +2017,7 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G5">
         <v>6.2</v>
@@ -2026,13 +2026,13 @@
         <v>1.57</v>
       </c>
       <c r="I5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2050,7 +2050,7 @@
         <v>2.56</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R5">
         <v>1.62</v>
@@ -2065,7 +2065,7 @@
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="W5">
         <v>1.19</v>
@@ -2098,7 +2098,7 @@
         <v>75</v>
       </c>
       <c r="AG5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH5">
         <v>21</v>
@@ -2152,7 +2152,7 @@
         <v>42</v>
       </c>
       <c r="AY5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ5">
         <v>7.2</v>
@@ -2161,19 +2161,19 @@
         <v>20</v>
       </c>
       <c r="BB5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD5">
         <v>44</v>
       </c>
       <c r="BE5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF5">
         <v>9.6</v>
-      </c>
-      <c r="BF5">
-        <v>44</v>
       </c>
       <c r="BG5">
         <v>5.8</v>
@@ -2271,7 +2271,7 @@
         <v>1.89</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -2295,7 +2295,7 @@
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
         <v>2.62</v>
@@ -2304,7 +2304,7 @@
         <v>1.62</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
         <v>2.12</v>
@@ -2430,31 +2430,31 @@
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BL6">
         <v>100</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN6">
         <v>9.4</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
         <v>36</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR6">
         <v>42</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT6">
         <v>5.8</v>
@@ -2466,19 +2466,19 @@
         <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BX6">
         <v>27</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ6">
         <v>19</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="CB6" t="s">
         <v>227</v>
@@ -2501,13 +2501,13 @@
         <v>184</v>
       </c>
       <c r="F7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G7">
         <v>3.5</v>
       </c>
       <c r="H7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I7">
         <v>2.34</v>
@@ -2528,7 +2528,7 @@
         <v>4.2</v>
       </c>
       <c r="O7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P7">
         <v>2.06</v>
@@ -2543,7 +2543,7 @@
         <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
         <v>2.28</v>
@@ -2579,7 +2579,7 @@
         <v>24</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG7">
         <v>14.5</v>
@@ -2660,7 +2660,7 @@
         <v>22</v>
       </c>
       <c r="BG7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2761,7 +2761,7 @@
         <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2785,7 +2785,7 @@
         <v>2.54</v>
       </c>
       <c r="T8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U8">
         <v>2.56</v>
@@ -2860,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2896,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
@@ -2914,13 +2914,13 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN8">
         <v>6.2</v>
@@ -2932,13 +2932,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR8">
         <v>26</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -3009,19 +3009,19 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
         <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
         <v>2.28</v>
@@ -3257,7 +3257,7 @@
         <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
         <v>1.84</v>
@@ -3341,10 +3341,10 @@
         <v>12</v>
       </c>
       <c r="AR10">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
         <v>7</v>
@@ -3377,16 +3377,16 @@
         <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>9.4</v>
       </c>
       <c r="BG10">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
@@ -3398,55 +3398,55 @@
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="CB10" t="s">
         <v>227</v>
@@ -3469,7 +3469,7 @@
         <v>188</v>
       </c>
       <c r="F11">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="G11">
         <v>110</v>
@@ -3968,10 +3968,10 @@
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -4037,7 +4037,7 @@
         <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI13">
         <v>65</v>
@@ -4682,7 +4682,7 @@
         <v>1.54</v>
       </c>
       <c r="G16">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -4730,7 +4730,7 @@
         <v>1.14</v>
       </c>
       <c r="W16">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5420,7 +5420,7 @@
         <v>4.9</v>
       </c>
       <c r="K19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5438,7 +5438,7 @@
         <v>2.32</v>
       </c>
       <c r="Q19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>1.5</v>
@@ -5564,7 +5564,7 @@
         <v>5.8</v>
       </c>
       <c r="BG19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5662,7 +5662,7 @@
         <v>3.8</v>
       </c>
       <c r="K20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L20">
         <v>1.3</v>
@@ -5677,25 +5677,25 @@
         <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S20">
         <v>3</v>
       </c>
       <c r="T20">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="U20">
         <v>2.06</v>
       </c>
       <c r="V20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W20">
         <v>2.12</v>
@@ -5803,7 +5803,7 @@
         <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG20">
         <v>1.01</v>
@@ -5818,13 +5818,13 @@
         <v>12</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BN20">
         <v>5.3</v>
@@ -5836,31 +5836,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BR20">
         <v>32</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT20">
         <v>10.5</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV20">
         <v>50</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX20">
         <v>60</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5892,19 +5892,19 @@
         <v>1.82</v>
       </c>
       <c r="G21">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H21">
         <v>5.1</v>
       </c>
       <c r="I21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J21">
         <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L21">
         <v>1.38</v>
@@ -5919,7 +5919,7 @@
         <v>1.44</v>
       </c>
       <c r="P21">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q21">
         <v>2.28</v>
@@ -5937,10 +5937,10 @@
         <v>1.8</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X21">
         <v>12.5</v>
@@ -6134,19 +6134,19 @@
         <v>1.35</v>
       </c>
       <c r="G22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H22">
         <v>8.800000000000001</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6155,34 +6155,34 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O22">
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
       </c>
       <c r="R22">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T22">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V22">
         <v>1.11</v>
       </c>
       <c r="W22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X22">
         <v>40</v>
@@ -6224,7 +6224,7 @@
         <v>14</v>
       </c>
       <c r="AK22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL22">
         <v>34</v>
@@ -6233,22 +6233,22 @@
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AO22">
         <v>130</v>
       </c>
       <c r="AP22">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AR22">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT22">
         <v>11</v>
@@ -6257,10 +6257,10 @@
         <v>13</v>
       </c>
       <c r="AV22">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AW22">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX22">
         <v>9.199999999999999</v>
@@ -6272,7 +6272,7 @@
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB22">
         <v>10.5</v>
@@ -6284,13 +6284,13 @@
         <v>21</v>
       </c>
       <c r="BE22">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG22">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH22">
         <v>6.2</v>
@@ -6373,22 +6373,22 @@
         <v>200</v>
       </c>
       <c r="F23">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H23">
         <v>2.86</v>
       </c>
       <c r="I23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J23">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K23">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6397,19 +6397,19 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="O23">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q23">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S23">
         <v>5.7</v>
@@ -6418,13 +6418,13 @@
         <v>2.28</v>
       </c>
       <c r="U23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X23">
         <v>8.4</v>
@@ -6493,7 +6493,7 @@
         <v>4.2</v>
       </c>
       <c r="AT23">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU23">
         <v>6</v>
@@ -6615,22 +6615,22 @@
         <v>201</v>
       </c>
       <c r="F24">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G24">
+        <v>4.3</v>
+      </c>
+      <c r="H24">
+        <v>1.92</v>
+      </c>
+      <c r="I24">
+        <v>1.95</v>
+      </c>
+      <c r="J24">
         <v>3.95</v>
       </c>
-      <c r="H24">
-        <v>1.98</v>
-      </c>
-      <c r="I24">
-        <v>2.22</v>
-      </c>
-      <c r="J24">
-        <v>3.85</v>
-      </c>
       <c r="K24">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6639,7 +6639,7 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O24">
         <v>1.12</v>
@@ -6648,25 +6648,25 @@
         <v>2.62</v>
       </c>
       <c r="Q24">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R24">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S24">
+        <v>2</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
         <v>2.04</v>
       </c>
-      <c r="T24">
-        <v>1.01</v>
-      </c>
-      <c r="U24">
-        <v>1.01</v>
-      </c>
-      <c r="V24">
-        <v>1.81</v>
-      </c>
       <c r="W24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6857,7 +6857,7 @@
         <v>202</v>
       </c>
       <c r="F25">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G25">
         <v>4.4</v>
@@ -6869,7 +6869,7 @@
         <v>2.2</v>
       </c>
       <c r="J25">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K25">
         <v>4.1</v>
@@ -6911,7 +6911,7 @@
         <v>1.29</v>
       </c>
       <c r="X25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y25">
         <v>12</v>
@@ -6926,7 +6926,7 @@
         <v>18</v>
       </c>
       <c r="AC25">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD25">
         <v>12</v>
@@ -6956,7 +6956,7 @@
         <v>60</v>
       </c>
       <c r="AM25">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN25">
         <v>44</v>
@@ -6965,7 +6965,7 @@
         <v>14</v>
       </c>
       <c r="AP25">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
         <v>8</v>
@@ -6983,40 +6983,40 @@
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
         <v>14.5</v>
       </c>
       <c r="AX25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
         <v>12</v>
       </c>
       <c r="AZ25">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7123,7 +7123,7 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="O26">
         <v>1.07</v>
@@ -7341,70 +7341,70 @@
         <v>204</v>
       </c>
       <c r="F27">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="G27">
-        <v>2.64</v>
+        <v>15.5</v>
       </c>
       <c r="H27">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="I27">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K27">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
         <v>1.14</v>
       </c>
       <c r="P27">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
         <v>1.42</v>
       </c>
       <c r="R27">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T27">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y27">
         <v>25</v>
       </c>
       <c r="Z27">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA27">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB27">
         <v>24</v>
@@ -7431,7 +7431,7 @@
         <v>34</v>
       </c>
       <c r="AJ27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK27">
         <v>27</v>
@@ -7589,7 +7589,7 @@
         <v>3.8</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I28">
         <v>2.24</v>
@@ -7604,7 +7604,7 @@
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N28">
         <v>5.3</v>
@@ -7825,67 +7825,67 @@
         <v>206</v>
       </c>
       <c r="F29">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="G29">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H29">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I29">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="J29">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K29">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N29">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R29">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="S29">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="T29">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U29">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X29">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA29">
         <v>44</v>
@@ -7894,43 +7894,43 @@
         <v>24</v>
       </c>
       <c r="AC29">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE29">
         <v>27</v>
       </c>
       <c r="AF29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG29">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH29">
         <v>16.5</v>
       </c>
       <c r="AI29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ29">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM29">
         <v>55</v>
       </c>
       <c r="AN29">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO29">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP29">
         <v>1.01</v>
@@ -7969,13 +7969,13 @@
         <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC29">
         <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE29">
         <v>1.01</v>
@@ -8070,25 +8070,25 @@
         <v>2.78</v>
       </c>
       <c r="G30">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H30">
         <v>2.24</v>
       </c>
       <c r="I30">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J30">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
         <v>6</v>
@@ -8106,7 +8106,7 @@
         <v>1.69</v>
       </c>
       <c r="S30">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T30">
         <v>1.4</v>
@@ -8115,10 +8115,10 @@
         <v>2.74</v>
       </c>
       <c r="V30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W30">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X30">
         <v>36</v>
@@ -8190,7 +8190,7 @@
         <v>14.5</v>
       </c>
       <c r="AU30">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV30">
         <v>9</v>
@@ -8229,7 +8229,7 @@
         <v>7.8</v>
       </c>
       <c r="BH30">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI30">
         <v>3.7</v>
@@ -8238,13 +8238,13 @@
         <v>8.6</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN30">
         <v>7</v>
@@ -8256,13 +8256,13 @@
         <v>20</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT30">
         <v>6.2</v>
@@ -8274,19 +8274,19 @@
         <v>16</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ30">
         <v>14</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB30" t="s">
         <v>227</v>
@@ -8330,7 +8330,7 @@
         <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31">
         <v>8.4</v>
@@ -8345,7 +8345,7 @@
         <v>1.33</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
         <v>1.79</v>
@@ -8551,19 +8551,19 @@
         <v>209</v>
       </c>
       <c r="F32">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G32">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
         <v>5.2</v>
@@ -8575,37 +8575,37 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="O32">
         <v>1.13</v>
       </c>
       <c r="P32">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q32">
         <v>1.39</v>
       </c>
       <c r="R32">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S32">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T32">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="U32">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="V32">
         <v>1.25</v>
       </c>
       <c r="W32">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X32">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y32">
         <v>36</v>
@@ -8623,10 +8623,10 @@
         <v>15</v>
       </c>
       <c r="AD32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF32">
         <v>18.5</v>
@@ -8635,7 +8635,7 @@
         <v>13.5</v>
       </c>
       <c r="AH32">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI32">
         <v>46</v>
@@ -8644,7 +8644,7 @@
         <v>23</v>
       </c>
       <c r="AK32">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL32">
         <v>26</v>
@@ -8653,7 +8653,7 @@
         <v>60</v>
       </c>
       <c r="AN32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO32">
         <v>32</v>
@@ -8713,64 +8713,64 @@
         <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BJ32">
         <v>8.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BN32">
         <v>5.2</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP32">
         <v>10.5</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR32">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT32">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ32">
         <v>10.5</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB32" t="s">
         <v>227</v>
@@ -8796,7 +8796,7 @@
         <v>1.78</v>
       </c>
       <c r="G33">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="H33">
         <v>3.85</v>
@@ -8805,7 +8805,7 @@
         <v>6.4</v>
       </c>
       <c r="J33">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K33">
         <v>5.7</v>
@@ -8829,7 +8829,7 @@
         <v>1.81</v>
       </c>
       <c r="R33">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S33">
         <v>3.15</v>
@@ -8844,7 +8844,7 @@
         <v>1.18</v>
       </c>
       <c r="W33">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9035,25 +9035,25 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G34">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I34">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K34">
         <v>5</v>
       </c>
       <c r="L34">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M34">
         <v>1.04</v>
@@ -9068,22 +9068,22 @@
         <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R34">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S34">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T34">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="U34">
         <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
         <v>2.74</v>
@@ -9101,7 +9101,7 @@
         <v>170</v>
       </c>
       <c r="AB34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC34">
         <v>11.5</v>
@@ -9113,7 +9113,7 @@
         <v>90</v>
       </c>
       <c r="AF34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG34">
         <v>11</v>
@@ -9122,7 +9122,7 @@
         <v>21</v>
       </c>
       <c r="AI34">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ34">
         <v>17.5</v>
@@ -9149,10 +9149,10 @@
         <v>20</v>
       </c>
       <c r="AR34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS34">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT34">
         <v>8.800000000000001</v>
@@ -9164,19 +9164,19 @@
         <v>19</v>
       </c>
       <c r="AW34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX34">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY34">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9185,16 +9185,16 @@
         <v>12</v>
       </c>
       <c r="BD34">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF34">
         <v>5.9</v>
       </c>
       <c r="BG34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH34">
         <v>4.1</v>
@@ -9203,25 +9203,25 @@
         <v>3.3</v>
       </c>
       <c r="BJ34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK34">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BN34">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO34">
         <v>3.85</v>
       </c>
       <c r="BP34">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ34">
         <v>7.8</v>
@@ -9230,31 +9230,31 @@
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT34">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU34">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BZ34">
         <v>15.5</v>
       </c>
       <c r="CA34">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB34" t="s">
         <v>227</v>
@@ -9301,28 +9301,28 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R35">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S35">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T35">
         <v>1.79</v>
       </c>
       <c r="U35">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V35">
         <v>1.37</v>
@@ -9331,10 +9331,10 @@
         <v>1.73</v>
       </c>
       <c r="X35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z35">
         <v>38</v>
@@ -9391,10 +9391,10 @@
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS35">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT35">
         <v>8.199999999999999</v>
@@ -9418,19 +9418,19 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BB35">
         <v>19</v>
       </c>
       <c r="BC35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD35">
         <v>26</v>
       </c>
       <c r="BE35">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF35">
         <v>13.5</v>
@@ -9519,10 +9519,10 @@
         <v>213</v>
       </c>
       <c r="F36">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G36">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H36">
         <v>2.94</v>
@@ -9561,16 +9561,16 @@
         <v>2.94</v>
       </c>
       <c r="T36">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U36">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V36">
         <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X36">
         <v>18.5</v>
@@ -9603,7 +9603,7 @@
         <v>12</v>
       </c>
       <c r="AH36">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI36">
         <v>40</v>
@@ -9627,10 +9627,10 @@
         <v>23</v>
       </c>
       <c r="AP36">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR36">
         <v>17.5</v>
@@ -9645,16 +9645,16 @@
         <v>7.6</v>
       </c>
       <c r="AV36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX36">
         <v>16</v>
       </c>
       <c r="AY36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ36">
         <v>14</v>
@@ -9672,7 +9672,7 @@
         <v>30</v>
       </c>
       <c r="BE36">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF36">
         <v>16</v>
@@ -9714,7 +9714,7 @@
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT36">
         <v>1000</v>
@@ -9767,10 +9767,10 @@
         <v>2.42</v>
       </c>
       <c r="H37">
+        <v>3.6</v>
+      </c>
+      <c r="I37">
         <v>3.65</v>
-      </c>
-      <c r="I37">
-        <v>3.75</v>
       </c>
       <c r="J37">
         <v>3.15</v>
@@ -9788,7 +9788,7 @@
         <v>3.1</v>
       </c>
       <c r="O37">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P37">
         <v>1.68</v>
@@ -9806,25 +9806,25 @@
         <v>1.99</v>
       </c>
       <c r="U37">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W37">
         <v>1.7</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y37">
         <v>11.5</v>
       </c>
       <c r="Z37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB37">
         <v>8.4</v>
@@ -9845,7 +9845,7 @@
         <v>11.5</v>
       </c>
       <c r="AH37">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI37">
         <v>70</v>
@@ -9869,7 +9869,7 @@
         <v>60</v>
       </c>
       <c r="AP37">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ37">
         <v>10.5</v>
@@ -9932,7 +9932,7 @@
         <v>10.5</v>
       </c>
       <c r="BK37">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
         <v>160</v>
@@ -9950,37 +9950,37 @@
         <v>19.5</v>
       </c>
       <c r="BQ37">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BR37">
         <v>38</v>
       </c>
       <c r="BS37">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BT37">
         <v>6.6</v>
       </c>
       <c r="BU37">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BV37">
         <v>32</v>
       </c>
       <c r="BW37">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BX37">
         <v>48</v>
       </c>
       <c r="BY37">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37">
         <v>38</v>
       </c>
       <c r="CA37">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="s">
         <v>227</v>
@@ -10006,10 +10006,10 @@
         <v>16.5</v>
       </c>
       <c r="G38">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H38">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I38">
         <v>1.25</v>
@@ -10033,13 +10033,13 @@
         <v>1.21</v>
       </c>
       <c r="P38">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
       </c>
       <c r="R38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S38">
         <v>2.52</v>
@@ -10048,7 +10048,7 @@
         <v>2.28</v>
       </c>
       <c r="U38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -10087,7 +10087,7 @@
         <v>65</v>
       </c>
       <c r="AH38">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI38">
         <v>50</v>
@@ -10099,13 +10099,13 @@
         <v>360</v>
       </c>
       <c r="AL38">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AM38">
         <v>270</v>
       </c>
       <c r="AN38">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AO38">
         <v>4.6</v>
@@ -10135,7 +10135,7 @@
         <v>13</v>
       </c>
       <c r="AX38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY38">
         <v>50</v>
@@ -10144,22 +10144,22 @@
         <v>34</v>
       </c>
       <c r="BA38">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC38">
         <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE38">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF38">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG38">
         <v>4</v>
@@ -10204,19 +10204,19 @@
         <v>1000</v>
       </c>
       <c r="BU38">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
@@ -10735,7 +10735,7 @@
         <v>1.79</v>
       </c>
       <c r="H41">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="I41">
         <v>6.4</v>
@@ -10744,7 +10744,7 @@
         <v>4.5</v>
       </c>
       <c r="K41">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10894,61 +10894,61 @@
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ41">
         <v>11.5</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BN41">
         <v>7.6</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BP41">
         <v>13.5</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BR41">
         <v>21</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT41">
         <v>13</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BV41">
         <v>40</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BX41">
         <v>36</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BZ41">
         <v>11</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="CB41" t="s">
         <v>227</v>
@@ -10971,7 +10971,7 @@
         <v>219</v>
       </c>
       <c r="F42">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G42">
         <v>1.39</v>
@@ -10980,7 +10980,7 @@
         <v>10</v>
       </c>
       <c r="I42">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J42">
         <v>5.4</v>
@@ -11019,7 +11019,7 @@
         <v>1.76</v>
       </c>
       <c r="V42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W42">
         <v>3.55</v>
@@ -11479,16 +11479,16 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O44">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P44">
         <v>1.81</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R44">
         <v>1.26</v>
@@ -11939,7 +11939,7 @@
         <v>223</v>
       </c>
       <c r="F46">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G46">
         <v>1.94</v>
@@ -11987,7 +11987,7 @@
         <v>1.61</v>
       </c>
       <c r="V46">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W46">
         <v>2.06</v>
@@ -12456,7 +12456,7 @@
         <v>2.04</v>
       </c>
       <c r="Q48">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R48">
         <v>1.41</v>
@@ -12465,10 +12465,10 @@
         <v>3.1</v>
       </c>
       <c r="T48">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="U48">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="V48">
         <v>1.16</v>
@@ -12588,19 +12588,19 @@
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BJ48">
         <v>14.5</v>
       </c>
       <c r="BK48">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BN48">
         <v>5.5</v>
@@ -12612,37 +12612,37 @@
         <v>14.5</v>
       </c>
       <c r="BQ48">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BR48">
         <v>34</v>
       </c>
       <c r="BS48">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BT48">
         <v>13.5</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BV48">
         <v>1000</v>
       </c>
       <c r="BW48">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX48">
         <v>1000</v>
       </c>
       <c r="BY48">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BZ48">
         <v>26</v>
       </c>
       <c r="CA48">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB48" t="s">
         <v>227</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -697,7 +697,7 @@
     <t>Ypiranga RS</t>
   </si>
   <si>
-    <t>2026-08-16 04:57:44</t>
+    <t>2026-08-16 07:14:29</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1303,7 @@
         <v>2.92</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
         <v>3.95</v>
@@ -1315,16 +1315,16 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
         <v>1.4</v>
@@ -1378,7 +1378,7 @@
         <v>17</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
         <v>50</v>
@@ -1387,16 +1387,16 @@
         <v>32</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM2">
         <v>95</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1408,7 +1408,7 @@
         <v>14</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1420,7 +1420,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1432,19 +1432,19 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF2">
         <v>16.5</v>
@@ -1533,7 +1533,7 @@
         <v>180</v>
       </c>
       <c r="F3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J3">
         <v>3.25</v>
@@ -1569,7 +1569,7 @@
         <v>2.28</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
         <v>4.3</v>
@@ -1581,7 +1581,7 @@
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.5</v>
@@ -1704,13 +1704,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1719,16 +1719,16 @@
         <v>5.1</v>
       </c>
       <c r="BP3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
         <v>5.8</v>
@@ -1737,13 +1737,13 @@
         <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW3">
         <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY3">
         <v>8.4</v>
@@ -1752,7 +1752,7 @@
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>227</v>
@@ -1778,52 +1778,52 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
         <v>2.46</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T4">
         <v>1.6</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W4">
         <v>1.47</v>
@@ -1868,7 +1868,7 @@
         <v>65</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1883,7 +1883,7 @@
         <v>15</v>
       </c>
       <c r="AP4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>12</v>
@@ -2017,10 +2017,10 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
         <v>1.57</v>
@@ -2032,7 +2032,7 @@
         <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2041,28 +2041,28 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
         <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
         <v>2.72</v>
@@ -2155,7 +2155,7 @@
         <v>18</v>
       </c>
       <c r="AZ5">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BA5">
         <v>20</v>
@@ -2301,7 +2301,7 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U6">
         <v>2.52</v>
@@ -2319,13 +2319,13 @@
         <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA6">
         <v>21</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC6">
         <v>9.6</v>
@@ -2334,10 +2334,10 @@
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG6">
         <v>17.5</v>
@@ -2358,7 +2358,7 @@
         <v>46</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
         <v>36</v>
@@ -2403,7 +2403,7 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BC6">
         <v>38</v>
@@ -2418,13 +2418,13 @@
         <v>30</v>
       </c>
       <c r="BG6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
         <v>4.9</v>
       </c>
       <c r="BI6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2442,13 +2442,13 @@
         <v>9.4</v>
       </c>
       <c r="BO6">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="BP6">
         <v>36</v>
       </c>
       <c r="BQ6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
         <v>42</v>
@@ -2466,10 +2466,10 @@
         <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BX6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY6">
         <v>4.1</v>
@@ -2507,55 +2507,55 @@
         <v>3.5</v>
       </c>
       <c r="H7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J7">
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S7">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
+        <v>1.75</v>
+      </c>
+      <c r="U7">
+        <v>2.24</v>
+      </c>
+      <c r="V7">
         <v>1.73</v>
-      </c>
-      <c r="U7">
-        <v>2.28</v>
-      </c>
-      <c r="V7">
-        <v>1.74</v>
       </c>
       <c r="W7">
         <v>1.4</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
         <v>11</v>
@@ -2564,10 +2564,10 @@
         <v>15.5</v>
       </c>
       <c r="AA7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -2576,7 +2576,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF7">
         <v>24</v>
@@ -2588,7 +2588,7 @@
         <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
         <v>830</v>
@@ -2603,16 +2603,16 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
         <v>13.5</v>
@@ -2621,10 +2621,10 @@
         <v>19</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
         <v>10</v>
@@ -2642,7 +2642,7 @@
         <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB7">
         <v>30</v>
@@ -2660,7 +2660,7 @@
         <v>22</v>
       </c>
       <c r="BG7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2749,7 +2749,7 @@
         <v>2.6</v>
       </c>
       <c r="H8">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I8">
         <v>2.98</v>
@@ -2758,7 +2758,7 @@
         <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>1.29</v>
@@ -2782,13 +2782,13 @@
         <v>1.56</v>
       </c>
       <c r="S8">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T8">
         <v>1.56</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
         <v>1.5</v>
@@ -2860,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2896,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
@@ -3009,19 +3009,19 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
         <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>2.28</v>
@@ -3469,19 +3469,19 @@
         <v>188</v>
       </c>
       <c r="F11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G11">
         <v>110</v>
       </c>
       <c r="H11">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="I11">
         <v>110</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
         <v>320</v>
@@ -3493,13 +3493,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
         <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="Q11">
         <v>1.34</v>
@@ -3517,10 +3517,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3714,7 +3714,7 @@
         <v>6.2</v>
       </c>
       <c r="G12">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="H12">
         <v>1.46</v>
@@ -3732,10 +3732,10 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
         <v>1.19</v>
@@ -3744,7 +3744,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
         <v>1.45</v>
@@ -3753,16 +3753,16 @@
         <v>2.22</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V12">
         <v>2.28</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3956,7 +3956,7 @@
         <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H13">
         <v>3.85</v>
@@ -3971,7 +3971,7 @@
         <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -4001,10 +4001,10 @@
         <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X13">
         <v>13.5</v>
@@ -4207,10 +4207,10 @@
         <v>7.2</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4446,7 +4446,7 @@
         <v>1.96</v>
       </c>
       <c r="I15">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -4461,7 +4461,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="O15">
         <v>1.33</v>
@@ -4485,7 +4485,7 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
         <v>1.27</v>
@@ -4694,7 +4694,7 @@
         <v>3.65</v>
       </c>
       <c r="K16">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4921,22 +4921,22 @@
         <v>194</v>
       </c>
       <c r="F17">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="G17">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J17">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4945,7 +4945,7 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="O17">
         <v>1.37</v>
@@ -4969,10 +4969,10 @@
         <v>1.89</v>
       </c>
       <c r="V17">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5304,7 +5304,7 @@
         <v>11</v>
       </c>
       <c r="BA18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
         <v>1.01</v>
@@ -5408,10 +5408,10 @@
         <v>1.47</v>
       </c>
       <c r="G19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I19">
         <v>8.6</v>
@@ -5420,13 +5420,13 @@
         <v>4.9</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
         <v>4.8</v>
@@ -5456,7 +5456,7 @@
         <v>1.13</v>
       </c>
       <c r="W19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X19">
         <v>22</v>
@@ -5656,85 +5656,85 @@
         <v>4.7</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J20">
+        <v>3.75</v>
+      </c>
+      <c r="K20">
+        <v>4.9</v>
+      </c>
+      <c r="L20">
+        <v>1.31</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
         <v>3.8</v>
-      </c>
-      <c r="K20">
-        <v>4.8</v>
-      </c>
-      <c r="L20">
-        <v>1.3</v>
-      </c>
-      <c r="M20">
-        <v>1.05</v>
-      </c>
-      <c r="N20">
-        <v>4</v>
       </c>
       <c r="O20">
         <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q20">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U20">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W20">
         <v>2.12</v>
       </c>
       <c r="X20">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA20">
         <v>150</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20">
         <v>11</v>
       </c>
       <c r="AD20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE20">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG20">
         <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI20">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ20">
         <v>23</v>
@@ -5746,20 +5746,20 @@
         <v>42</v>
       </c>
       <c r="AM20">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN20">
+        <v>13.5</v>
+      </c>
+      <c r="AO20">
+        <v>95</v>
+      </c>
+      <c r="AP20">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20">
         <v>13</v>
       </c>
-      <c r="AO20">
-        <v>85</v>
-      </c>
-      <c r="AP20">
-        <v>12</v>
-      </c>
-      <c r="AQ20">
-        <v>13.5</v>
-      </c>
       <c r="AR20">
         <v>1.01</v>
       </c>
@@ -5767,10 +5767,10 @@
         <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU20">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
         <v>14.5</v>
@@ -5779,13 +5779,13 @@
         <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
         <v>1.01</v>
@@ -5803,64 +5803,64 @@
         <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG20">
         <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI20">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20">
         <v>12</v>
       </c>
       <c r="BK20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN20">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP20">
         <v>14.5</v>
       </c>
       <c r="BQ20">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BR20">
         <v>32</v>
       </c>
       <c r="BS20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT20">
         <v>10.5</v>
       </c>
       <c r="BU20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX20">
         <v>60</v>
       </c>
       <c r="BY20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>198</v>
       </c>
       <c r="F21">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G21">
         <v>1.92</v>
@@ -5898,7 +5898,7 @@
         <v>5.1</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J21">
         <v>3.4</v>
@@ -6146,16 +6146,16 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O22">
         <v>1.15</v>
@@ -6167,7 +6167,7 @@
         <v>1.46</v>
       </c>
       <c r="R22">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S22">
         <v>2.16</v>
@@ -6176,7 +6176,7 @@
         <v>1.79</v>
       </c>
       <c r="U22">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V22">
         <v>1.11</v>
@@ -6203,13 +6203,13 @@
         <v>15.5</v>
       </c>
       <c r="AD22">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE22">
         <v>130</v>
       </c>
       <c r="AF22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG22">
         <v>11</v>
@@ -6221,34 +6221,34 @@
         <v>100</v>
       </c>
       <c r="AJ22">
+        <v>13</v>
+      </c>
+      <c r="AK22">
         <v>14</v>
       </c>
-      <c r="AK22">
-        <v>16</v>
-      </c>
       <c r="AL22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM22">
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO22">
         <v>130</v>
       </c>
       <c r="AP22">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AQ22">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AR22">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AS22">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="AT22">
         <v>11</v>
@@ -6257,10 +6257,10 @@
         <v>13</v>
       </c>
       <c r="AV22">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AW22">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AX22">
         <v>9.199999999999999</v>
@@ -6269,10 +6269,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA22">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BB22">
         <v>10.5</v>
@@ -6284,31 +6284,31 @@
         <v>21</v>
       </c>
       <c r="BE22">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BF22">
         <v>3.9</v>
       </c>
       <c r="BG22">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BH22">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="BJ22">
         <v>15</v>
       </c>
       <c r="BK22">
-        <v>2.72</v>
+        <v>1.89</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="BN22">
         <v>5.6</v>
@@ -6326,31 +6326,31 @@
         <v>26</v>
       </c>
       <c r="BS22">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="BT22">
         <v>17.5</v>
       </c>
       <c r="BU22">
-        <v>2.78</v>
+        <v>1.93</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="BZ22">
         <v>13</v>
       </c>
       <c r="CA22">
-        <v>2.64</v>
+        <v>1.86</v>
       </c>
       <c r="CB22" t="s">
         <v>227</v>
@@ -6373,112 +6373,112 @@
         <v>200</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G23">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H23">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="I23">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J23">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N23">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="P23">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S23">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="T23">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U23">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X23">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y23">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z23">
+        <v>18.5</v>
+      </c>
+      <c r="AA23">
+        <v>60</v>
+      </c>
+      <c r="AB23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC23">
+        <v>7.4</v>
+      </c>
+      <c r="AD23">
+        <v>17</v>
+      </c>
+      <c r="AE23">
+        <v>160</v>
+      </c>
+      <c r="AF23">
         <v>22</v>
       </c>
-      <c r="AA23">
-        <v>70</v>
-      </c>
-      <c r="AB23">
-        <v>9.6</v>
-      </c>
-      <c r="AC23">
-        <v>8.4</v>
-      </c>
-      <c r="AD23">
+      <c r="AG23">
         <v>18</v>
-      </c>
-      <c r="AE23">
-        <v>65</v>
-      </c>
-      <c r="AF23">
-        <v>23</v>
-      </c>
-      <c r="AG23">
-        <v>18.5</v>
       </c>
       <c r="AH23">
         <v>32</v>
       </c>
       <c r="AI23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>75</v>
+        <v>480</v>
       </c>
       <c r="AK23">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AL23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
         <v>300</v>
       </c>
       <c r="AN23">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AP23">
         <v>6.2</v>
@@ -6490,49 +6490,49 @@
         <v>13</v>
       </c>
       <c r="AS23">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="AT23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW23">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="AX23">
+        <v>17</v>
+      </c>
+      <c r="AY23">
         <v>13.5</v>
       </c>
-      <c r="AY23">
-        <v>12.5</v>
-      </c>
       <c r="AZ23">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="BA23">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="BB23">
-        <v>4.3</v>
+        <v>29</v>
       </c>
       <c r="BC23">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BD23">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="BE23">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="BF23">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BG23">
-        <v>4.3</v>
+        <v>30</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6615,22 +6615,22 @@
         <v>201</v>
       </c>
       <c r="F24">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G24">
+        <v>4.2</v>
+      </c>
+      <c r="H24">
+        <v>1.87</v>
+      </c>
+      <c r="I24">
+        <v>1.88</v>
+      </c>
+      <c r="J24">
         <v>4.3</v>
       </c>
-      <c r="H24">
-        <v>1.92</v>
-      </c>
-      <c r="I24">
-        <v>1.95</v>
-      </c>
-      <c r="J24">
-        <v>3.95</v>
-      </c>
       <c r="K24">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6639,22 +6639,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="O24">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="Q24">
         <v>1.39</v>
       </c>
       <c r="R24">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6663,10 +6663,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="W24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6857,7 +6857,7 @@
         <v>202</v>
       </c>
       <c r="F25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G25">
         <v>4.4</v>
@@ -6881,16 +6881,16 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O25">
         <v>1.25</v>
       </c>
       <c r="P25">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -6908,7 +6908,7 @@
         <v>1.83</v>
       </c>
       <c r="W25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X25">
         <v>21</v>
@@ -6965,7 +6965,7 @@
         <v>14</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ25">
         <v>8</v>
@@ -6983,40 +6983,40 @@
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW25">
         <v>14.5</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY25">
         <v>12</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7123,22 +7123,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O26">
         <v>1.07</v>
       </c>
       <c r="P26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R26">
         <v>1.25</v>
       </c>
       <c r="S26">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7344,10 +7344,10 @@
         <v>2.14</v>
       </c>
       <c r="G27">
-        <v>15.5</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I27">
         <v>2.98</v>
@@ -7356,7 +7356,7 @@
         <v>3.6</v>
       </c>
       <c r="K27">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7589,7 +7589,7 @@
         <v>3.8</v>
       </c>
       <c r="H28">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>2.24</v>
@@ -7828,13 +7828,13 @@
         <v>2.62</v>
       </c>
       <c r="G29">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="H29">
         <v>2.38</v>
       </c>
       <c r="I29">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="J29">
         <v>3.7</v>
@@ -7849,19 +7849,19 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="O29">
         <v>1.15</v>
       </c>
       <c r="P29">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q29">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R29">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="S29">
         <v>2.16</v>
@@ -7873,7 +7873,7 @@
         <v>2.58</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W29">
         <v>1.53</v>
@@ -7894,7 +7894,7 @@
         <v>24</v>
       </c>
       <c r="AC29">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD29">
         <v>15</v>
@@ -7906,7 +7906,7 @@
         <v>29</v>
       </c>
       <c r="AG29">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH29">
         <v>16.5</v>
@@ -7930,7 +7930,7 @@
         <v>15.5</v>
       </c>
       <c r="AO29">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AP29">
         <v>1.01</v>
@@ -7969,13 +7969,13 @@
         <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
         <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
         <v>1.01</v>
@@ -8079,7 +8079,7 @@
         <v>2.5</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K30">
         <v>5.2</v>
@@ -8106,13 +8106,13 @@
         <v>1.69</v>
       </c>
       <c r="S30">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T30">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="U30">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="V30">
         <v>1.66</v>
@@ -8321,7 +8321,7 @@
         <v>4.1</v>
       </c>
       <c r="J31">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K31">
         <v>5.2</v>
@@ -8333,7 +8333,7 @@
         <v>1.02</v>
       </c>
       <c r="N31">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O31">
         <v>1.1</v>
@@ -8411,7 +8411,7 @@
         <v>48</v>
       </c>
       <c r="AN31">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO31">
         <v>17.5</v>
@@ -8551,19 +8551,19 @@
         <v>209</v>
       </c>
       <c r="F32">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G32">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I32">
         <v>4.9</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
         <v>5.2</v>
@@ -8575,7 +8575,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="O32">
         <v>1.13</v>
@@ -8587,7 +8587,7 @@
         <v>1.39</v>
       </c>
       <c r="R32">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S32">
         <v>1.97</v>
@@ -8596,13 +8596,13 @@
         <v>1.49</v>
       </c>
       <c r="U32">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="V32">
         <v>1.25</v>
       </c>
       <c r="W32">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X32">
         <v>44</v>
@@ -8626,13 +8626,13 @@
         <v>23</v>
       </c>
       <c r="AE32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF32">
         <v>18.5</v>
       </c>
       <c r="AG32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH32">
         <v>18.5</v>
@@ -8644,7 +8644,7 @@
         <v>23</v>
       </c>
       <c r="AK32">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL32">
         <v>26</v>
@@ -8728,7 +8728,7 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN32">
         <v>5.2</v>
@@ -8835,7 +8835,7 @@
         <v>3.15</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U33">
         <v>1.01</v>
@@ -9035,13 +9035,13 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G34">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H34">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I34">
         <v>7.2</v>
@@ -9053,7 +9053,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
         <v>1.04</v>
@@ -9077,7 +9077,7 @@
         <v>2.68</v>
       </c>
       <c r="T34">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U34">
         <v>2.08</v>
@@ -9086,7 +9086,7 @@
         <v>1.16</v>
       </c>
       <c r="W34">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="X34">
         <v>24</v>
@@ -9277,13 +9277,13 @@
         <v>212</v>
       </c>
       <c r="F35">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G35">
         <v>2.38</v>
       </c>
       <c r="H35">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I35">
         <v>3.75</v>
@@ -9292,7 +9292,7 @@
         <v>3.35</v>
       </c>
       <c r="K35">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L35">
         <v>1.34</v>
@@ -9355,22 +9355,22 @@
         <v>55</v>
       </c>
       <c r="AF35">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AG35">
         <v>11.5</v>
       </c>
       <c r="AH35">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AI35">
         <v>65</v>
       </c>
       <c r="AJ35">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AK35">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AL35">
         <v>46</v>
@@ -9391,7 +9391,7 @@
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS35">
         <v>8.6</v>
@@ -9519,97 +9519,97 @@
         <v>213</v>
       </c>
       <c r="F36">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G36">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H36">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I36">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J36">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K36">
         <v>3.7</v>
       </c>
       <c r="L36">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O36">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q36">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R36">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S36">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T36">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="U36">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X36">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y36">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z36">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA36">
         <v>50</v>
       </c>
       <c r="AB36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC36">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD36">
         <v>13.5</v>
       </c>
       <c r="AE36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG36">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH36">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AI36">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ36">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK36">
         <v>27</v>
@@ -9618,19 +9618,19 @@
         <v>36</v>
       </c>
       <c r="AM36">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN36">
         <v>21</v>
       </c>
       <c r="AO36">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP36">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR36">
         <v>17.5</v>
@@ -9639,25 +9639,25 @@
         <v>38</v>
       </c>
       <c r="AT36">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU36">
         <v>7.6</v>
       </c>
       <c r="AV36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW36">
         <v>27</v>
       </c>
       <c r="AX36">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY36">
         <v>11</v>
       </c>
       <c r="AZ36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA36">
         <v>32</v>
@@ -9666,16 +9666,16 @@
         <v>32</v>
       </c>
       <c r="BC36">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD36">
         <v>30</v>
       </c>
       <c r="BE36">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG36">
         <v>20</v>
@@ -9702,7 +9702,7 @@
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP36">
         <v>1000</v>
@@ -9770,7 +9770,7 @@
         <v>3.6</v>
       </c>
       <c r="I37">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J37">
         <v>3.15</v>
@@ -9794,7 +9794,7 @@
         <v>1.68</v>
       </c>
       <c r="Q37">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R37">
         <v>1.25</v>
@@ -9803,7 +9803,7 @@
         <v>4.7</v>
       </c>
       <c r="T37">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U37">
         <v>1.95</v>
@@ -9839,10 +9839,10 @@
         <v>55</v>
       </c>
       <c r="AF37">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH37">
         <v>21</v>
@@ -9914,7 +9914,7 @@
         <v>46</v>
       </c>
       <c r="BE37">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="BF37">
         <v>25</v>
@@ -9926,13 +9926,13 @@
         <v>2.94</v>
       </c>
       <c r="BI37">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ37">
         <v>10.5</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL37">
         <v>160</v>
@@ -9950,13 +9950,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR37">
         <v>38</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT37">
         <v>6.6</v>
@@ -9968,19 +9968,19 @@
         <v>32</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX37">
         <v>48</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ37">
         <v>38</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB37" t="s">
         <v>227</v>
@@ -10003,7 +10003,7 @@
         <v>215</v>
       </c>
       <c r="F38">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G38">
         <v>18</v>
@@ -10012,7 +10012,7 @@
         <v>1.23</v>
       </c>
       <c r="I38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J38">
         <v>7</v>
@@ -10030,31 +10030,31 @@
         <v>5</v>
       </c>
       <c r="O38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P38">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q38">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R38">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S38">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T38">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U38">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V38">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>25</v>
@@ -10063,10 +10063,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z38">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB38">
         <v>55</v>
@@ -10087,7 +10087,7 @@
         <v>65</v>
       </c>
       <c r="AH38">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AI38">
         <v>50</v>
@@ -10096,7 +10096,7 @@
         <v>990</v>
       </c>
       <c r="AK38">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AL38">
         <v>270</v>
@@ -10105,16 +10105,16 @@
         <v>270</v>
       </c>
       <c r="AN38">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AO38">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AP38">
         <v>20</v>
       </c>
       <c r="AQ38">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR38">
         <v>6.8</v>
@@ -10126,7 +10126,7 @@
         <v>40</v>
       </c>
       <c r="AU38">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV38">
         <v>10</v>
@@ -10135,7 +10135,7 @@
         <v>13</v>
       </c>
       <c r="AX38">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY38">
         <v>50</v>
@@ -10144,22 +10144,22 @@
         <v>34</v>
       </c>
       <c r="BA38">
+        <v>38</v>
+      </c>
+      <c r="BB38">
+        <v>10</v>
+      </c>
+      <c r="BC38">
         <v>9.800000000000001</v>
       </c>
-      <c r="BB38">
-        <v>12</v>
-      </c>
-      <c r="BC38">
-        <v>11.5</v>
-      </c>
       <c r="BD38">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BE38">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BG38">
         <v>4</v>
@@ -10269,22 +10269,22 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="O39">
         <v>1.05</v>
       </c>
       <c r="P39">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R39">
         <v>1.25</v>
       </c>
       <c r="S39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10735,7 +10735,7 @@
         <v>1.79</v>
       </c>
       <c r="H41">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I41">
         <v>6.4</v>
@@ -10744,10 +10744,10 @@
         <v>4.5</v>
       </c>
       <c r="K41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M41">
         <v>1.01</v>
@@ -10971,7 +10971,7 @@
         <v>219</v>
       </c>
       <c r="F42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G42">
         <v>1.39</v>
@@ -11213,10 +11213,10 @@
         <v>220</v>
       </c>
       <c r="F43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G43">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H43">
         <v>3.65</v>
@@ -11225,7 +11225,7 @@
         <v>4.1</v>
       </c>
       <c r="J43">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K43">
         <v>3.1</v>
@@ -11237,7 +11237,7 @@
         <v>1.15</v>
       </c>
       <c r="N43">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O43">
         <v>1.63</v>
@@ -11261,7 +11261,7 @@
         <v>1.68</v>
       </c>
       <c r="V43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
         <v>1.64</v>
@@ -11464,7 +11464,7 @@
         <v>3.65</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J44">
         <v>3.25</v>
@@ -11473,7 +11473,7 @@
         <v>4.8</v>
       </c>
       <c r="L44">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M44">
         <v>1.01</v>
@@ -11482,13 +11482,13 @@
         <v>3.2</v>
       </c>
       <c r="O44">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="P44">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q44">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="R44">
         <v>1.26</v>
@@ -11697,19 +11697,19 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G45">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H45">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I45">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J45">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K45">
         <v>470</v>
@@ -11721,10 +11721,10 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P45">
         <v>1.25</v>
@@ -11736,7 +11736,7 @@
         <v>1.18</v>
       </c>
       <c r="S45">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
         <v>1.01</v>
@@ -11942,10 +11942,10 @@
         <v>1.73</v>
       </c>
       <c r="G46">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="H46">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I46">
         <v>6.4</v>
@@ -11954,7 +11954,7 @@
         <v>3.55</v>
       </c>
       <c r="K46">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -11963,19 +11963,19 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="O46">
         <v>1.37</v>
       </c>
       <c r="P46">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
         <v>2.16</v>
       </c>
       <c r="R46">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="S46">
         <v>4</v>
@@ -11987,10 +11987,10 @@
         <v>1.61</v>
       </c>
       <c r="V46">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W46">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12005,7 +12005,7 @@
         <v>1000</v>
       </c>
       <c r="AB46">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC46">
         <v>1000</v>
@@ -12020,7 +12020,7 @@
         <v>1000</v>
       </c>
       <c r="AG46">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH46">
         <v>1000</v>
@@ -12047,58 +12047,58 @@
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU46">
-        <v>6.2</v>
+        <v>1.08</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ46">
-        <v>19</v>
+        <v>1.08</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE46">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="BF46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH46">
         <v>3.4</v>
@@ -12199,7 +12199,7 @@
         <v>3.95</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M47">
         <v>1.01</v>
@@ -12208,7 +12208,7 @@
         <v>2.94</v>
       </c>
       <c r="O47">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P47">
         <v>1.71</v>
@@ -12456,7 +12456,7 @@
         <v>2.04</v>
       </c>
       <c r="Q48">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R48">
         <v>1.41</v>
@@ -12465,13 +12465,13 @@
         <v>3.1</v>
       </c>
       <c r="T48">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="U48">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W48">
         <v>2.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -697,7 +697,7 @@
     <t>Ypiranga RS</t>
   </si>
   <si>
-    <t>2026-08-16 07:14:29</t>
+    <t>2026-08-16 09:30:03</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1291,7 @@
         <v>179</v>
       </c>
       <c r="F2">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G2">
         <v>2.88</v>
@@ -1300,7 +1300,7 @@
         <v>2.62</v>
       </c>
       <c r="I2">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J2">
         <v>3.45</v>
@@ -1339,7 +1339,7 @@
         <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W2">
         <v>1.54</v>
@@ -1453,64 +1453,64 @@
         <v>16.5</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB2" t="s">
         <v>227</v>
@@ -1536,7 +1536,7 @@
         <v>2.88</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H3">
         <v>2.72</v>
@@ -1560,7 +1560,7 @@
         <v>3.25</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
         <v>1.74</v>
@@ -1575,7 +1575,7 @@
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
         <v>1.98</v>
@@ -1584,7 +1584,7 @@
         <v>1.55</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
         <v>13.5</v>
@@ -1641,7 +1641,7 @@
         <v>36</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
         <v>8.6</v>
@@ -1656,16 +1656,16 @@
         <v>8</v>
       </c>
       <c r="AU3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY3">
         <v>9.800000000000001</v>
@@ -1674,25 +1674,25 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
         <v>32</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
         <v>3.15</v>
@@ -1787,10 +1787,10 @@
         <v>2.46</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1802,10 +1802,10 @@
         <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
         <v>1.74</v>
@@ -1814,10 +1814,10 @@
         <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -1829,7 +1829,7 @@
         <v>1.47</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4">
         <v>13.5</v>
@@ -1841,7 +1841,7 @@
         <v>34</v>
       </c>
       <c r="AB4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
@@ -1856,10 +1856,10 @@
         <v>24</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
         <v>34</v>
@@ -1874,16 +1874,16 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN4">
         <v>23</v>
       </c>
       <c r="AO4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
         <v>12</v>
@@ -1895,16 +1895,16 @@
         <v>27</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX4">
         <v>19.5</v>
@@ -1916,22 +1916,22 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB4">
         <v>40</v>
       </c>
       <c r="BC4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE4">
         <v>48</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG4">
         <v>13</v>
@@ -2017,7 +2017,7 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G5">
         <v>6.4</v>
@@ -2032,7 +2032,7 @@
         <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2044,13 +2044,13 @@
         <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
         <v>2.54</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
         <v>1.61</v>
@@ -2059,13 +2059,13 @@
         <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
         <v>2.24</v>
       </c>
       <c r="V5">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W5">
         <v>1.19</v>
@@ -2083,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="AB5">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AC5">
         <v>11.5</v>
@@ -2155,7 +2155,7 @@
         <v>18</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
         <v>20</v>
@@ -2164,13 +2164,13 @@
         <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD5">
         <v>44</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>9.6</v>
@@ -2262,19 +2262,19 @@
         <v>4.2</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H6">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I6">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2283,7 +2283,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2295,7 +2295,7 @@
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
         <v>2.62</v>
@@ -2304,13 +2304,13 @@
         <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X6">
         <v>23</v>
@@ -2322,19 +2322,19 @@
         <v>14</v>
       </c>
       <c r="AA6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB6">
         <v>22</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF6">
         <v>36</v>
@@ -2349,16 +2349,16 @@
         <v>32</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL6">
         <v>46</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN6">
         <v>36</v>
@@ -2379,7 +2379,7 @@
         <v>19</v>
       </c>
       <c r="AT6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU6">
         <v>8.800000000000001</v>
@@ -2403,7 +2403,7 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BC6">
         <v>38</v>
@@ -2415,7 +2415,7 @@
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG6">
         <v>8.199999999999999</v>
@@ -2513,7 +2513,7 @@
         <v>2.36</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>3.65</v>
@@ -2525,7 +2525,7 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>1.31</v>
@@ -2534,19 +2534,19 @@
         <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R7">
         <v>1.39</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V7">
         <v>1.73</v>
@@ -2591,7 +2591,7 @@
         <v>38</v>
       </c>
       <c r="AJ7">
-        <v>830</v>
+        <v>960</v>
       </c>
       <c r="AK7">
         <v>42</v>
@@ -2609,16 +2609,16 @@
         <v>18</v>
       </c>
       <c r="AP7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR7">
         <v>13.5</v>
       </c>
       <c r="AS7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT7">
         <v>12</v>
@@ -2627,7 +2627,7 @@
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
         <v>21</v>
@@ -2749,16 +2749,16 @@
         <v>2.6</v>
       </c>
       <c r="H8">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I8">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J8">
         <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.29</v>
@@ -2767,19 +2767,19 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8">
         <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q8">
         <v>1.62</v>
       </c>
       <c r="R8">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S8">
         <v>2.52</v>
@@ -2791,7 +2791,7 @@
         <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
         <v>1.62</v>
@@ -2800,7 +2800,7 @@
         <v>24</v>
       </c>
       <c r="Y8">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
         <v>23</v>
@@ -2812,7 +2812,7 @@
         <v>15.5</v>
       </c>
       <c r="AC8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>13.5</v>
@@ -2827,7 +2827,7 @@
         <v>15</v>
       </c>
       <c r="AH8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
         <v>34</v>
@@ -2842,16 +2842,16 @@
         <v>32</v>
       </c>
       <c r="AM8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ8">
         <v>14</v>
@@ -2860,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2884,10 +2884,10 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB8">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2896,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BF8">
         <v>12.5</v>
@@ -2905,16 +2905,16 @@
         <v>15</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ8">
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2926,7 +2926,7 @@
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
         <v>17.5</v>
@@ -2947,13 +2947,13 @@
         <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY8">
         <v>7.2</v>
@@ -3027,10 +3027,10 @@
         <v>2.28</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.52</v>
@@ -3093,52 +3093,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3233,7 +3233,7 @@
         <v>2.04</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>4.9</v>
@@ -3341,10 +3341,10 @@
         <v>12</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
         <v>7</v>
@@ -3356,7 +3356,7 @@
         <v>13</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX10">
         <v>9.199999999999999</v>
@@ -3368,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10">
         <v>15.5</v>
@@ -3377,16 +3377,16 @@
         <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF10">
         <v>9.4</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
@@ -3469,58 +3469,58 @@
         <v>188</v>
       </c>
       <c r="F11">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="G11">
-        <v>110</v>
+        <v>1.76</v>
       </c>
       <c r="H11">
+        <v>5.7</v>
+      </c>
+      <c r="I11">
+        <v>990</v>
+      </c>
+      <c r="J11">
+        <v>3.45</v>
+      </c>
+      <c r="K11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L11">
+        <v>1.34</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>2.56</v>
+      </c>
+      <c r="O11">
+        <v>1.01</v>
+      </c>
+      <c r="P11">
+        <v>1.67</v>
+      </c>
+      <c r="Q11">
+        <v>1.87</v>
+      </c>
+      <c r="R11">
+        <v>1.23</v>
+      </c>
+      <c r="S11">
+        <v>2.62</v>
+      </c>
+      <c r="T11">
         <v>1.11</v>
       </c>
-      <c r="I11">
-        <v>110</v>
-      </c>
-      <c r="J11">
-        <v>3.2</v>
-      </c>
-      <c r="K11">
-        <v>320</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>2.7</v>
-      </c>
-      <c r="O11">
-        <v>1.01</v>
-      </c>
-      <c r="P11">
-        <v>1.04</v>
-      </c>
-      <c r="Q11">
-        <v>1.34</v>
-      </c>
-      <c r="R11">
-        <v>1.18</v>
-      </c>
-      <c r="S11">
-        <v>1.35</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3577,52 +3577,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3738,7 +3738,7 @@
         <v>2.1</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P12">
         <v>2.1</v>
@@ -3819,52 +3819,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3995,10 +3995,10 @@
         <v>3.6</v>
       </c>
       <c r="T13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V13">
         <v>1.29</v>
@@ -4204,13 +4204,13 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>4.2</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4237,13 +4237,13 @@
         <v>2.2</v>
       </c>
       <c r="T14">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W14">
         <v>2.4</v>
@@ -4303,112 +4303,112 @@
         <v>70</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM14">
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>1.96</v>
       </c>
       <c r="I15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -4479,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
         <v>1.27</v>
@@ -4545,52 +4545,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4679,22 +4679,22 @@
         <v>193</v>
       </c>
       <c r="F16">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="G16">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H16">
         <v>4</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
         <v>3.65</v>
       </c>
       <c r="K16">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4703,16 +4703,16 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="O16">
         <v>1.24</v>
       </c>
       <c r="P16">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R16">
         <v>1.36</v>
@@ -4721,16 +4721,16 @@
         <v>2.46</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4787,52 +4787,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -4921,10 +4921,10 @@
         <v>194</v>
       </c>
       <c r="F17">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H17">
         <v>4.3</v>
@@ -4933,34 +4933,34 @@
         <v>5.2</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="O17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="Q17">
         <v>2.12</v>
       </c>
       <c r="R17">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T17">
         <v>1.92</v>
@@ -4969,178 +4969,178 @@
         <v>1.89</v>
       </c>
       <c r="V17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W17">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z17">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17">
+        <v>8.4</v>
+      </c>
+      <c r="AD17">
+        <v>20</v>
+      </c>
+      <c r="AE17">
+        <v>85</v>
+      </c>
+      <c r="AF17">
+        <v>12</v>
+      </c>
+      <c r="AG17">
         <v>11</v>
       </c>
-      <c r="AC17">
-        <v>11.5</v>
-      </c>
-      <c r="AD17">
-        <v>28</v>
-      </c>
-      <c r="AE17">
-        <v>100</v>
-      </c>
-      <c r="AF17">
-        <v>17</v>
-      </c>
-      <c r="AG17">
-        <v>15.5</v>
-      </c>
       <c r="AH17">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ17">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AK17">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN17">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
+        <v>12</v>
+      </c>
+      <c r="AR17">
+        <v>20</v>
+      </c>
+      <c r="AS17">
+        <v>7.4</v>
+      </c>
+      <c r="AT17">
+        <v>6.6</v>
+      </c>
+      <c r="AU17">
+        <v>6.8</v>
+      </c>
+      <c r="AV17">
+        <v>16</v>
+      </c>
+      <c r="AW17">
+        <v>7</v>
+      </c>
+      <c r="AX17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY17">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
-      <c r="AT17">
-        <v>5</v>
-      </c>
-      <c r="AU17">
-        <v>5</v>
-      </c>
-      <c r="AV17">
-        <v>11.5</v>
-      </c>
-      <c r="AW17">
-        <v>1.01</v>
-      </c>
-      <c r="AX17">
+      <c r="AZ17">
+        <v>17.5</v>
+      </c>
+      <c r="BA17">
         <v>7.2</v>
       </c>
-      <c r="AY17">
-        <v>6.6</v>
-      </c>
-      <c r="AZ17">
-        <v>12.5</v>
-      </c>
-      <c r="BA17">
-        <v>1.01</v>
-      </c>
       <c r="BB17">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BC17">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF17">
+        <v>15</v>
+      </c>
+      <c r="BG17">
+        <v>7.2</v>
+      </c>
+      <c r="BH17">
+        <v>3.2</v>
+      </c>
+      <c r="BI17">
+        <v>2.76</v>
+      </c>
+      <c r="BJ17">
         <v>11</v>
       </c>
-      <c r="BG17">
-        <v>1.01</v>
-      </c>
-      <c r="BH17">
-        <v>3.8</v>
-      </c>
-      <c r="BI17">
-        <v>2.5</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
       <c r="BK17">
-        <v>1.37</v>
+        <v>8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO17">
-        <v>1.37</v>
+        <v>3.95</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ17">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>1.37</v>
+        <v>5.9</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW17">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY17">
-        <v>1.37</v>
+        <v>7.6</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA17">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="CB17" t="s">
         <v>227</v>
@@ -5205,10 +5205,10 @@
         <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
         <v>1.8</v>
@@ -5271,7 +5271,7 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AQ18">
         <v>8.800000000000001</v>
@@ -5283,40 +5283,40 @@
         <v>18.5</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AV18">
         <v>7.8</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AX18">
         <v>18</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AZ18">
         <v>11</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BF18">
         <v>19</v>
@@ -5411,10 +5411,10 @@
         <v>1.48</v>
       </c>
       <c r="H19">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I19">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
         <v>4.9</v>
@@ -5429,22 +5429,22 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P19">
         <v>2.32</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R19">
         <v>1.5</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T19">
         <v>1.82</v>
@@ -5665,7 +5665,7 @@
         <v>4.9</v>
       </c>
       <c r="L20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M20">
         <v>1.06</v>
@@ -5683,19 +5683,19 @@
         <v>1.83</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
         <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V20">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
         <v>2.12</v>
@@ -5761,34 +5761,34 @@
         <v>13</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT20">
         <v>6.8</v>
       </c>
       <c r="AU20">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20">
         <v>14.5</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX20">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ20">
         <v>14</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB20">
         <v>13.5</v>
@@ -5797,16 +5797,16 @@
         <v>13.5</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF20">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH20">
         <v>4.2</v>
@@ -5901,7 +5901,7 @@
         <v>5.7</v>
       </c>
       <c r="J21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21">
         <v>3.7</v>
@@ -6134,7 +6134,7 @@
         <v>1.35</v>
       </c>
       <c r="G22">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H22">
         <v>8.800000000000001</v>
@@ -6146,7 +6146,7 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L22">
         <v>1.19</v>
@@ -6155,19 +6155,19 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O22">
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
       </c>
       <c r="R22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S22">
         <v>2.16</v>
@@ -6182,16 +6182,16 @@
         <v>1.11</v>
       </c>
       <c r="W22">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X22">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y22">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z22">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
         <v>310</v>
@@ -6206,7 +6206,7 @@
         <v>36</v>
       </c>
       <c r="AE22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
         <v>11.5</v>
@@ -6218,10 +6218,10 @@
         <v>25</v>
       </c>
       <c r="AI22">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK22">
         <v>14</v>
@@ -6242,16 +6242,16 @@
         <v>23</v>
       </c>
       <c r="AQ22">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AR22">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS22">
         <v>50</v>
       </c>
       <c r="AT22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU22">
         <v>13</v>
@@ -6260,16 +6260,16 @@
         <v>21</v>
       </c>
       <c r="AW22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX22">
         <v>9.199999999999999</v>
       </c>
       <c r="AY22">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA22">
         <v>44</v>
@@ -6281,13 +6281,13 @@
         <v>12</v>
       </c>
       <c r="BD22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE22">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BF22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG22">
         <v>38</v>
@@ -6379,31 +6379,31 @@
         <v>3.35</v>
       </c>
       <c r="H23">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I23">
+        <v>2.94</v>
+      </c>
+      <c r="J23">
+        <v>2.86</v>
+      </c>
+      <c r="K23">
         <v>2.98</v>
       </c>
-      <c r="J23">
-        <v>2.84</v>
-      </c>
-      <c r="K23">
-        <v>3.05</v>
-      </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N23">
         <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q23">
         <v>3.05</v>
@@ -6412,10 +6412,10 @@
         <v>1.14</v>
       </c>
       <c r="S23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T23">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
         <v>1.67</v>
@@ -6424,7 +6424,7 @@
         <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X23">
         <v>7.2</v>
@@ -6481,10 +6481,10 @@
         <v>980</v>
       </c>
       <c r="AP23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR23">
         <v>13</v>
@@ -6493,7 +6493,7 @@
         <v>26</v>
       </c>
       <c r="AT23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU23">
         <v>6.2</v>
@@ -6508,7 +6508,7 @@
         <v>17</v>
       </c>
       <c r="AY23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ23">
         <v>23</v>
@@ -6520,7 +6520,7 @@
         <v>29</v>
       </c>
       <c r="BC23">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BD23">
         <v>38</v>
@@ -6615,22 +6615,22 @@
         <v>201</v>
       </c>
       <c r="F24">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="G24">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H24">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="I24">
         <v>1.88</v>
       </c>
       <c r="J24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K24">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6639,142 +6639,142 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="R24">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S24">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="V24">
         <v>2.12</v>
       </c>
       <c r="W24">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6902,7 +6902,7 @@
         <v>1.64</v>
       </c>
       <c r="U25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
         <v>1.83</v>
@@ -6977,7 +6977,7 @@
         <v>20</v>
       </c>
       <c r="AT25">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU25">
         <v>7.2</v>
@@ -7141,10 +7141,10 @@
         <v>1.07</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
         <v>1.01</v>
@@ -7341,22 +7341,22 @@
         <v>204</v>
       </c>
       <c r="F27">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="H27">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I27">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="J27">
         <v>3.6</v>
       </c>
       <c r="K27">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7365,31 +7365,31 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="O27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q27">
         <v>1.42</v>
       </c>
       <c r="R27">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="S27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
         <v>1.59</v>
@@ -7828,7 +7828,7 @@
         <v>2.62</v>
       </c>
       <c r="G29">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="H29">
         <v>2.38</v>
@@ -7849,16 +7849,16 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="O29">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P29">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R29">
         <v>1.64</v>
@@ -7876,7 +7876,7 @@
         <v>1.54</v>
       </c>
       <c r="W29">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="X29">
         <v>36</v>
@@ -8079,13 +8079,13 @@
         <v>2.5</v>
       </c>
       <c r="J30">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M30">
         <v>1.02</v>
@@ -8112,7 +8112,7 @@
         <v>1.47</v>
       </c>
       <c r="U30">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="V30">
         <v>1.66</v>
@@ -8124,19 +8124,19 @@
         <v>36</v>
       </c>
       <c r="Y30">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z30">
         <v>25</v>
       </c>
       <c r="AA30">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC30">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD30">
         <v>15</v>
@@ -8163,16 +8163,16 @@
         <v>34</v>
       </c>
       <c r="AL30">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM30">
         <v>60</v>
       </c>
       <c r="AN30">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO30">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP30">
         <v>21</v>
@@ -8181,25 +8181,25 @@
         <v>12.5</v>
       </c>
       <c r="AR30">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS30">
         <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AU30">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV30">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AX30">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY30">
         <v>10</v>
@@ -8208,7 +8208,7 @@
         <v>10.5</v>
       </c>
       <c r="BA30">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
         <v>1.01</v>
@@ -8226,7 +8226,7 @@
         <v>11</v>
       </c>
       <c r="BG30">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH30">
         <v>4.9</v>
@@ -8426,7 +8426,7 @@
         <v>24</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31">
         <v>18</v>
@@ -8563,10 +8563,10 @@
         <v>4.9</v>
       </c>
       <c r="J32">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K32">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L32">
         <v>1.19</v>
@@ -8575,7 +8575,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O32">
         <v>1.13</v>
@@ -8596,7 +8596,7 @@
         <v>1.49</v>
       </c>
       <c r="U32">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V32">
         <v>1.25</v>
@@ -8728,7 +8728,7 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="BN32">
         <v>5.2</v>
@@ -8793,22 +8793,22 @@
         <v>210</v>
       </c>
       <c r="F33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G33">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I33">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J33">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K33">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8817,13 +8817,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>1.32</v>
       </c>
       <c r="P33">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q33">
         <v>1.81</v>
@@ -8835,16 +8835,16 @@
         <v>3.15</v>
       </c>
       <c r="T33">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9053,7 +9053,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M34">
         <v>1.04</v>
@@ -9301,7 +9301,7 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35">
         <v>1.35</v>
@@ -9310,25 +9310,25 @@
         <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R35">
         <v>1.33</v>
       </c>
       <c r="S35">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T35">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U35">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X35">
         <v>16</v>
@@ -9346,7 +9346,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC35">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35">
         <v>15.5</v>
@@ -9367,10 +9367,10 @@
         <v>65</v>
       </c>
       <c r="AJ35">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AK35">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL35">
         <v>46</v>
@@ -9394,7 +9394,7 @@
         <v>10.5</v>
       </c>
       <c r="AS35">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT35">
         <v>8.199999999999999</v>
@@ -9424,13 +9424,13 @@
         <v>19</v>
       </c>
       <c r="BC35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD35">
         <v>26</v>
       </c>
       <c r="BE35">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF35">
         <v>13.5</v>
@@ -9519,10 +9519,10 @@
         <v>213</v>
       </c>
       <c r="F36">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G36">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H36">
         <v>2.92</v>
@@ -9531,7 +9531,7 @@
         <v>2.96</v>
       </c>
       <c r="J36">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K36">
         <v>3.7</v>
@@ -9543,13 +9543,13 @@
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P36">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q36">
         <v>1.89</v>
@@ -9558,7 +9558,7 @@
         <v>1.42</v>
       </c>
       <c r="S36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T36">
         <v>1.71</v>
@@ -9570,7 +9570,7 @@
         <v>1.51</v>
       </c>
       <c r="W36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X36">
         <v>16</v>
@@ -9606,25 +9606,25 @@
         <v>17</v>
       </c>
       <c r="AI36">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ36">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AK36">
         <v>27</v>
       </c>
       <c r="AL36">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM36">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
         <v>21</v>
       </c>
       <c r="AO36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP36">
         <v>14.5</v>
@@ -9633,52 +9633,52 @@
         <v>12</v>
       </c>
       <c r="AR36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT36">
         <v>11</v>
       </c>
       <c r="AU36">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV36">
         <v>12</v>
       </c>
       <c r="AW36">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX36">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY36">
         <v>11</v>
       </c>
       <c r="AZ36">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA36">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC36">
         <v>24</v>
       </c>
       <c r="BD36">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF36">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG36">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9761,16 +9761,16 @@
         <v>214</v>
       </c>
       <c r="F37">
+        <v>2.38</v>
+      </c>
+      <c r="G37">
         <v>2.4</v>
       </c>
-      <c r="G37">
-        <v>2.42</v>
-      </c>
       <c r="H37">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I37">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J37">
         <v>3.15</v>
@@ -9803,16 +9803,16 @@
         <v>4.7</v>
       </c>
       <c r="T37">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U37">
         <v>1.95</v>
       </c>
       <c r="V37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X37">
         <v>9.6</v>
@@ -9821,10 +9821,10 @@
         <v>11.5</v>
       </c>
       <c r="Z37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB37">
         <v>8.4</v>
@@ -9851,7 +9851,7 @@
         <v>70</v>
       </c>
       <c r="AJ37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK37">
         <v>29</v>
@@ -9866,10 +9866,10 @@
         <v>28</v>
       </c>
       <c r="AO37">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP37">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37">
         <v>10.5</v>
@@ -9908,7 +9908,7 @@
         <v>29</v>
       </c>
       <c r="BC37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD37">
         <v>46</v>
@@ -9923,64 +9923,64 @@
         <v>50</v>
       </c>
       <c r="BH37">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI37">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK37">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL37">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM37">
         <v>34</v>
       </c>
       <c r="BN37">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO37">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP37">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR37">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BT37">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU37">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV37">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
         <v>11.5</v>
       </c>
       <c r="BX37">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BZ37">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="CB37" t="s">
         <v>227</v>
@@ -10006,10 +10006,10 @@
         <v>15.5</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H38">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I38">
         <v>1.26</v>
@@ -10024,16 +10024,16 @@
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P38">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q38">
         <v>1.63</v>
@@ -10042,13 +10042,13 @@
         <v>1.56</v>
       </c>
       <c r="S38">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T38">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U38">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V38">
         <v>4.8</v>
@@ -10087,7 +10087,7 @@
         <v>65</v>
       </c>
       <c r="AH38">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI38">
         <v>50</v>
@@ -10099,13 +10099,13 @@
         <v>340</v>
       </c>
       <c r="AL38">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AM38">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN38">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AO38">
         <v>4.5</v>
@@ -10135,7 +10135,7 @@
         <v>13</v>
       </c>
       <c r="AX38">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY38">
         <v>50</v>
@@ -10144,19 +10144,19 @@
         <v>34</v>
       </c>
       <c r="BA38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB38">
         <v>10</v>
       </c>
       <c r="BC38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD38">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE38">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BF38">
         <v>10</v>
@@ -10284,13 +10284,13 @@
         <v>1.25</v>
       </c>
       <c r="S39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V39">
         <v>1.01</v>
@@ -10529,10 +10529,10 @@
         <v>2.12</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
         <v>1.28</v>
@@ -10735,7 +10735,7 @@
         <v>1.79</v>
       </c>
       <c r="H41">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I41">
         <v>6.4</v>
@@ -10744,7 +10744,7 @@
         <v>4.5</v>
       </c>
       <c r="K41">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L41">
         <v>1.13</v>
@@ -10771,10 +10771,10 @@
         <v>1.68</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41">
         <v>1.19</v>
@@ -10974,16 +10974,16 @@
         <v>1.36</v>
       </c>
       <c r="G42">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J42">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K42">
         <v>5.9</v>
@@ -11004,7 +11004,7 @@
         <v>2.26</v>
       </c>
       <c r="Q42">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R42">
         <v>1.48</v>
@@ -11013,28 +11013,28 @@
         <v>2.74</v>
       </c>
       <c r="T42">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U42">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V42">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W42">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X42">
         <v>25</v>
       </c>
       <c r="Y42">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z42">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA42">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="AB42">
         <v>10.5</v>
@@ -11046,10 +11046,10 @@
         <v>42</v>
       </c>
       <c r="AE42">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AF42">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG42">
         <v>13</v>
@@ -11058,7 +11058,7 @@
         <v>36</v>
       </c>
       <c r="AI42">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ42">
         <v>13</v>
@@ -11070,19 +11070,19 @@
         <v>44</v>
       </c>
       <c r="AM42">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN42">
         <v>5.9</v>
       </c>
       <c r="AO42">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AP42">
         <v>15</v>
       </c>
       <c r="AQ42">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR42">
         <v>5.4</v>
@@ -11100,10 +11100,10 @@
         <v>5</v>
       </c>
       <c r="AW42">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY42">
         <v>8</v>
@@ -11121,16 +11121,16 @@
         <v>11</v>
       </c>
       <c r="BD42">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE42">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF42">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG42">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH42">
         <v>4.6</v>
@@ -11142,13 +11142,13 @@
         <v>13</v>
       </c>
       <c r="BK42">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BN42">
         <v>3.85</v>
@@ -11157,7 +11157,7 @@
         <v>3.3</v>
       </c>
       <c r="BP42">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BQ42">
         <v>4.1</v>
@@ -11166,31 +11166,31 @@
         <v>26</v>
       </c>
       <c r="BS42">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BT42">
         <v>14.5</v>
       </c>
       <c r="BU42">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV42">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW42">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX42">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BY42">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BZ42">
         <v>13.5</v>
       </c>
       <c r="CA42">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB42" t="s">
         <v>227</v>
@@ -11225,10 +11225,10 @@
         <v>4.1</v>
       </c>
       <c r="J43">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K43">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11237,7 +11237,7 @@
         <v>1.15</v>
       </c>
       <c r="N43">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
         <v>1.63</v>
@@ -11249,7 +11249,7 @@
         <v>2.88</v>
       </c>
       <c r="R43">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S43">
         <v>6.2</v>
@@ -11288,7 +11288,7 @@
         <v>22</v>
       </c>
       <c r="AE43">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF43">
         <v>16.5</v>
@@ -11354,7 +11354,7 @@
         <v>4</v>
       </c>
       <c r="BA43">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB43">
         <v>4.2</v>
@@ -11369,7 +11369,7 @@
         <v>4.5</v>
       </c>
       <c r="BF43">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG43">
         <v>4.5</v>
@@ -11485,10 +11485,10 @@
         <v>1.02</v>
       </c>
       <c r="P44">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q44">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R44">
         <v>1.26</v>
@@ -11497,10 +11497,10 @@
         <v>3.2</v>
       </c>
       <c r="T44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44">
         <v>1.25</v>
@@ -11620,61 +11620,61 @@
         <v>1000</v>
       </c>
       <c r="BI44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ44">
         <v>1000</v>
       </c>
       <c r="BK44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN44">
         <v>1000</v>
       </c>
       <c r="BO44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP44">
         <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR44">
         <v>1000</v>
       </c>
       <c r="BS44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT44">
         <v>1000</v>
       </c>
       <c r="BU44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV44">
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ44">
         <v>1000</v>
       </c>
       <c r="CA44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB44" t="s">
         <v>227</v>
@@ -11697,22 +11697,22 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G45">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H45">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I45">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J45">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="K45">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11721,28 +11721,28 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P45">
         <v>1.25</v>
       </c>
       <c r="Q45">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R45">
         <v>1.18</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45">
         <v>1.02</v>
@@ -11862,61 +11862,61 @@
         <v>1000</v>
       </c>
       <c r="BI45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ45">
         <v>1000</v>
       </c>
       <c r="BK45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN45">
         <v>1000</v>
       </c>
       <c r="BO45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP45">
         <v>1000</v>
       </c>
       <c r="BQ45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR45">
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT45">
         <v>1000</v>
       </c>
       <c r="BU45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV45">
         <v>1000</v>
       </c>
       <c r="BW45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ45">
         <v>1000</v>
       </c>
       <c r="CA45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB45" t="s">
         <v>227</v>
@@ -11939,22 +11939,22 @@
         <v>223</v>
       </c>
       <c r="F46">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="G46">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I46">
         <v>6.4</v>
       </c>
       <c r="J46">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -11963,10 +11963,10 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="O46">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P46">
         <v>1.67</v>
@@ -11975,22 +11975,22 @@
         <v>2.16</v>
       </c>
       <c r="R46">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S46">
         <v>4</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U46">
         <v>1.61</v>
       </c>
       <c r="V46">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W46">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12223,10 +12223,10 @@
         <v>2.92</v>
       </c>
       <c r="T47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47">
         <v>1.29</v>
@@ -12423,7 +12423,7 @@
         <v>225</v>
       </c>
       <c r="F48">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G48">
         <v>1.66</v>
@@ -12450,31 +12450,31 @@
         <v>4</v>
       </c>
       <c r="O48">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P48">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q48">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R48">
         <v>1.41</v>
       </c>
       <c r="S48">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T48">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U48">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="V48">
         <v>1.17</v>
       </c>
       <c r="W48">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X48">
         <v>19.5</v>
@@ -12665,7 +12665,7 @@
         <v>226</v>
       </c>
       <c r="F49">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G49">
         <v>1.85</v>
@@ -12689,7 +12689,7 @@
         <v>1.07</v>
       </c>
       <c r="N49">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O49">
         <v>1.32</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -754,7 +754,7 @@
     <t>Ypiranga RS</t>
   </si>
   <si>
-    <t>2026-08-16 11:46:01</t>
+    <t>2026-08-16 13:59:19</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
         <v>2.88</v>
       </c>
       <c r="H2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I2">
         <v>2.9</v>
@@ -1363,7 +1363,7 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -1390,7 +1390,7 @@
         <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -1405,25 +1405,25 @@
         <v>20</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
         <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF2">
         <v>23</v>
@@ -1438,22 +1438,22 @@
         <v>46</v>
       </c>
       <c r="AJ2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL2">
         <v>46</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP2">
         <v>14</v>
@@ -1462,13 +1462,13 @@
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>7.2</v>
@@ -1477,7 +1477,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AX2">
         <v>16.5</v>
@@ -1489,25 +1489,25 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BB2">
-        <v>4.6</v>
+        <v>27</v>
       </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>4.6</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BH2">
         <v>4.3</v>
@@ -1516,58 +1516,58 @@
         <v>2.9</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP2">
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV2">
         <v>24</v>
       </c>
       <c r="BW2">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>246</v>
@@ -1590,22 +1590,22 @@
         <v>193</v>
       </c>
       <c r="F3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G3">
         <v>2.98</v>
       </c>
       <c r="H3">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I3">
         <v>2.84</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.48</v>
@@ -1614,7 +1614,7 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
         <v>1.42</v>
@@ -1641,13 +1641,13 @@
         <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
         <v>18</v>
@@ -1689,7 +1689,7 @@
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN3">
         <v>44</v>
@@ -1701,7 +1701,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
         <v>14.5</v>
@@ -1719,10 +1719,10 @@
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1731,28 +1731,28 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BD3">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI3">
         <v>2.46</v>
@@ -1761,13 +1761,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1779,13 +1779,13 @@
         <v>26</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>5.8</v>
@@ -1797,19 +1797,19 @@
         <v>24</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="s">
         <v>246</v>
@@ -1835,22 +1835,22 @@
         <v>3.05</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
         <v>2.44</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.05</v>
@@ -1868,7 +1868,7 @@
         <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
         <v>2.88</v>
@@ -1877,13 +1877,13 @@
         <v>1.62</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V4">
         <v>1.69</v>
       </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X4">
         <v>20</v>
@@ -1892,7 +1892,7 @@
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
         <v>34</v>
@@ -1904,16 +1904,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF4">
         <v>24</v>
       </c>
       <c r="AG4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
         <v>15.5</v>
@@ -1943,7 +1943,7 @@
         <v>17</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
         <v>15.5</v>
@@ -2074,16 +2074,16 @@
         <v>195</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
         <v>1.56</v>
       </c>
       <c r="I5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J5">
         <v>4.9</v>
@@ -2092,16 +2092,16 @@
         <v>5.2</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
         <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
         <v>2.54</v>
@@ -2110,7 +2110,7 @@
         <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
         <v>2.54</v>
@@ -2119,7 +2119,7 @@
         <v>1.76</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
         <v>2.72</v>
@@ -2131,7 +2131,7 @@
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>11.5</v>
@@ -2194,7 +2194,7 @@
         <v>13.5</v>
       </c>
       <c r="AT5">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2215,85 +2215,85 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC5">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BD5">
         <v>44</v>
       </c>
       <c r="BE5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF5">
+        <v>38</v>
+      </c>
+      <c r="BG5">
+        <v>5.7</v>
+      </c>
+      <c r="BH5">
+        <v>4.6</v>
+      </c>
+      <c r="BI5">
+        <v>3.55</v>
+      </c>
+      <c r="BJ5">
         <v>10.5</v>
       </c>
-      <c r="BG5">
+      <c r="BK5">
+        <v>5</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN5">
+        <v>10.5</v>
+      </c>
+      <c r="BO5">
+        <v>5</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>8</v>
+      </c>
+      <c r="BR5">
+        <v>48</v>
+      </c>
+      <c r="BS5">
+        <v>8</v>
+      </c>
+      <c r="BT5">
+        <v>4.6</v>
+      </c>
+      <c r="BU5">
+        <v>3.55</v>
+      </c>
+      <c r="BV5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW5">
+        <v>4.9</v>
+      </c>
+      <c r="BX5">
+        <v>22</v>
+      </c>
+      <c r="BY5">
+        <v>6.8</v>
+      </c>
+      <c r="BZ5">
+        <v>13.5</v>
+      </c>
+      <c r="CA5">
         <v>5.6</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.04</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.04</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.04</v>
-      </c>
-      <c r="BZ5">
-        <v>1000</v>
-      </c>
-      <c r="CA5">
-        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>246</v>
@@ -2316,46 +2316,46 @@
         <v>196</v>
       </c>
       <c r="F6">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="G6">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="I6">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="R6">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="S6">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>1.92</v>
@@ -2364,16 +2364,16 @@
         <v>1.73</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
         <v>1000</v>
@@ -2382,22 +2382,22 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
         <v>1000</v>
       </c>
       <c r="AF6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
         <v>34</v>
@@ -2412,7 +2412,7 @@
         <v>16.5</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM6">
         <v>180</v>
@@ -2472,7 +2472,7 @@
         <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
         <v>1.01</v>
@@ -2558,22 +2558,22 @@
         <v>197</v>
       </c>
       <c r="F7">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="G7">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H7">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.31</v>
@@ -2588,7 +2588,7 @@
         <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q7">
         <v>1.64</v>
@@ -2600,184 +2600,184 @@
         <v>2.62</v>
       </c>
       <c r="T7">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U7">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK7">
+        <v>40</v>
+      </c>
+      <c r="AL7">
         <v>42</v>
       </c>
-      <c r="AL7">
-        <v>44</v>
-      </c>
       <c r="AM7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO7">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AP7">
         <v>20</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA7">
         <v>24</v>
       </c>
       <c r="BB7">
+        <v>60</v>
+      </c>
+      <c r="BC7">
+        <v>34</v>
+      </c>
+      <c r="BD7">
+        <v>36</v>
+      </c>
+      <c r="BE7">
         <v>50</v>
       </c>
-      <c r="BC7">
-        <v>38</v>
-      </c>
-      <c r="BD7">
-        <v>40</v>
-      </c>
-      <c r="BE7">
-        <v>55</v>
-      </c>
       <c r="BF7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7">
         <v>4.9</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7">
         <v>9</v>
       </c>
       <c r="BK7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BM7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN7">
         <v>8</v>
       </c>
       <c r="BO7">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
         <v>30</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR7">
         <v>34</v>
       </c>
       <c r="BS7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT7">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BU7">
         <v>4.4</v>
       </c>
       <c r="BV7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BX7">
         <v>22</v>
       </c>
       <c r="BY7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA7">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="CB7" t="s">
         <v>246</v>
@@ -2848,7 +2848,7 @@
         <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
         <v>1.4</v>
@@ -2890,7 +2890,7 @@
         <v>38</v>
       </c>
       <c r="AJ8">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
         <v>42</v>
@@ -2917,7 +2917,7 @@
         <v>13.5</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT8">
         <v>12</v>
@@ -2926,7 +2926,7 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>21</v>
@@ -2941,7 +2941,7 @@
         <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BB8">
         <v>30</v>
@@ -2962,7 +2962,7 @@
         <v>16</v>
       </c>
       <c r="BH8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI8">
         <v>2.86</v>
@@ -2971,13 +2971,13 @@
         <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
@@ -2989,13 +2989,13 @@
         <v>27</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
@@ -3007,19 +3007,19 @@
         <v>17</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX8">
         <v>30</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
         <v>26</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="s">
         <v>246</v>
@@ -3042,19 +3042,19 @@
         <v>199</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I9">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>4</v>
@@ -3075,7 +3075,7 @@
         <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R9">
         <v>1.58</v>
@@ -3090,10 +3090,10 @@
         <v>2.62</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -3111,7 +3111,7 @@
         <v>15.5</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD9">
         <v>13.5</v>
@@ -3123,7 +3123,7 @@
         <v>21</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>15.5</v>
@@ -3156,10 +3156,10 @@
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS9">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AT9">
         <v>13</v>
@@ -3183,19 +3183,19 @@
         <v>13</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BB9">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BF9">
         <v>12.5</v>
@@ -3213,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="BK9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3252,7 +3252,7 @@
         <v>6.4</v>
       </c>
       <c r="BX9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY9">
         <v>7.2</v>
@@ -3323,13 +3323,13 @@
         <v>1.45</v>
       </c>
       <c r="S10">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T10">
         <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="V10">
         <v>1.52</v>
@@ -3395,49 +3395,49 @@
         <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="BA10">
         <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD10">
         <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3526,16 +3526,16 @@
         <v>201</v>
       </c>
       <c r="F11">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="G11">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="I11">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
         <v>3.65</v>
@@ -3550,34 +3550,34 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P11">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q11">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
         <v>3.05</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="X11">
         <v>19</v>
@@ -3589,7 +3589,7 @@
         <v>38</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
@@ -3598,10 +3598,10 @@
         <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF11">
         <v>15</v>
@@ -3613,7 +3613,7 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
         <v>27</v>
@@ -3622,7 +3622,7 @@
         <v>24</v>
       </c>
       <c r="AL11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -3631,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="AO11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3640,13 +3640,13 @@
         <v>12</v>
       </c>
       <c r="AR11">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3655,19 +3655,19 @@
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11">
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB11">
         <v>15.5</v>
@@ -3676,76 +3676,76 @@
         <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF11">
         <v>9.4</v>
       </c>
       <c r="BG11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
+        <v>3.8</v>
+      </c>
+      <c r="BI11">
+        <v>3.2</v>
+      </c>
+      <c r="BJ11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK11">
+        <v>4.9</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>9</v>
+      </c>
+      <c r="BN11">
+        <v>5.1</v>
+      </c>
+      <c r="BO11">
         <v>3.75</v>
       </c>
-      <c r="BI11">
-        <v>3.15</v>
-      </c>
-      <c r="BJ11">
-        <v>10</v>
-      </c>
-      <c r="BK11">
-        <v>5</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>9.4</v>
-      </c>
-      <c r="BN11">
-        <v>4.9</v>
-      </c>
-      <c r="BO11">
-        <v>3.65</v>
-      </c>
       <c r="BP11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR11">
         <v>28</v>
       </c>
       <c r="BS11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT11">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ11">
         <v>23</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
         <v>246</v>
@@ -3768,58 +3768,58 @@
         <v>202</v>
       </c>
       <c r="F12">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="G12">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I12">
-        <v>870</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O12">
         <v>1.06</v>
       </c>
       <c r="P12">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="T12">
+        <v>1.75</v>
+      </c>
+      <c r="U12">
+        <v>1.58</v>
+      </c>
+      <c r="V12">
         <v>1.11</v>
       </c>
-      <c r="U12">
-        <v>1.11</v>
-      </c>
-      <c r="V12">
-        <v>1.05</v>
-      </c>
       <c r="W12">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="X12">
         <v>17</v>
@@ -3930,13 +3930,13 @@
         <v>160</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
         <v>1.04</v>
@@ -3948,25 +3948,25 @@
         <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS12">
         <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU12">
         <v>1.04</v>
@@ -3984,7 +3984,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA12">
         <v>1.04</v>
@@ -4013,10 +4013,10 @@
         <v>1.54</v>
       </c>
       <c r="G13">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="H13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I13">
         <v>6.6</v>
@@ -4025,10 +4025,10 @@
         <v>4.3</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -4037,31 +4037,31 @@
         <v>5.2</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R13">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S13">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W13">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X13">
         <v>30</v>
@@ -4088,7 +4088,7 @@
         <v>75</v>
       </c>
       <c r="AF13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -4124,22 +4124,22 @@
         <v>20</v>
       </c>
       <c r="AR13">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="AS13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX13">
         <v>9.199999999999999</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB13">
         <v>12</v>
@@ -4163,16 +4163,16 @@
         <v>20</v>
       </c>
       <c r="BE13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF13">
         <v>3.1</v>
       </c>
       <c r="BG13">
+        <v>5.1</v>
+      </c>
+      <c r="BH13">
         <v>5</v>
-      </c>
-      <c r="BH13">
-        <v>5.1</v>
       </c>
       <c r="BI13">
         <v>2.64</v>
@@ -4181,25 +4181,25 @@
         <v>11</v>
       </c>
       <c r="BK13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL13">
         <v>110</v>
       </c>
       <c r="BM13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN13">
         <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BP13">
         <v>11.5</v>
       </c>
       <c r="BQ13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BR13">
         <v>24</v>
@@ -4211,19 +4211,19 @@
         <v>11</v>
       </c>
       <c r="BU13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I14">
         <v>1.64</v>
@@ -4276,142 +4276,142 @@
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>1.2</v>
       </c>
       <c r="P14">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R14">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="T14">
         <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="V14">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AX14">
         <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4506,10 +4506,10 @@
         <v>4.4</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4659,19 +4659,19 @@
         <v>3.3</v>
       </c>
       <c r="BI15">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN15">
         <v>4.9</v>
@@ -4680,16 +4680,16 @@
         <v>3.7</v>
       </c>
       <c r="BP15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT15">
         <v>7.4</v>
@@ -4701,19 +4701,19 @@
         <v>1000</v>
       </c>
       <c r="BW15">
+        <v>10</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>10.5</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
         <v>9.4</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>10</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
-      <c r="CA15">
-        <v>8.800000000000001</v>
       </c>
       <c r="CB15" t="s">
         <v>246</v>
@@ -4736,22 +4736,22 @@
         <v>206</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="G16">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H16">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="I16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4760,16 +4760,16 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O16">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="P16">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q16">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="R16">
         <v>1.18</v>
@@ -4784,10 +4784,10 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4862,13 +4862,13 @@
         <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AW16">
         <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AY16">
         <v>1.03</v>
@@ -4984,7 +4984,7 @@
         <v>1.9</v>
       </c>
       <c r="H17">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I17">
         <v>5.7</v>
@@ -5005,13 +5005,13 @@
         <v>4.1</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P17">
         <v>1.99</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
         <v>1.43</v>
@@ -5020,7 +5020,7 @@
         <v>2.66</v>
       </c>
       <c r="T17">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="U17">
         <v>2.08</v>
@@ -5086,58 +5086,58 @@
         <v>85</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF17">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BH17">
         <v>4.3</v>
@@ -5238,13 +5238,13 @@
         <v>3.8</v>
       </c>
       <c r="L18">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M18">
         <v>1.08</v>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O18">
         <v>1.38</v>
@@ -5253,7 +5253,7 @@
         <v>1.71</v>
       </c>
       <c r="Q18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R18">
         <v>1.27</v>
@@ -5707,7 +5707,7 @@
         <v>1.04</v>
       </c>
       <c r="G20">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H20">
         <v>1.04</v>
@@ -5716,7 +5716,7 @@
         <v>990</v>
       </c>
       <c r="J20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5725,19 +5725,19 @@
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R20">
         <v>1.18</v>
@@ -5752,10 +5752,10 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5830,7 +5830,7 @@
         <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW20">
         <v>1.03</v>
@@ -5845,7 +5845,7 @@
         <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB20">
         <v>1.03</v>
@@ -5946,22 +5946,22 @@
         <v>211</v>
       </c>
       <c r="F21">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G21">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H21">
         <v>7.4</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5979,10 +5979,10 @@
         <v>2.32</v>
       </c>
       <c r="Q21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R21">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21">
         <v>2.64</v>
@@ -6018,10 +6018,10 @@
         <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AE21">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF21">
         <v>9.800000000000001</v>
@@ -6075,7 +6075,7 @@
         <v>25</v>
       </c>
       <c r="AW21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX21">
         <v>8.6</v>
@@ -6087,7 +6087,7 @@
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB21">
         <v>12</v>
@@ -6102,7 +6102,7 @@
         <v>12</v>
       </c>
       <c r="BF21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG21">
         <v>12</v>
@@ -6203,7 +6203,7 @@
         <v>3.75</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>1.37</v>
@@ -6430,28 +6430,28 @@
         <v>213</v>
       </c>
       <c r="F23">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G23">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H23">
         <v>3.15</v>
       </c>
       <c r="I23">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
         <v>3.2</v>
@@ -6478,10 +6478,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6681,7 +6681,7 @@
         <v>5.1</v>
       </c>
       <c r="I24">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J24">
         <v>3.45</v>
@@ -6708,7 +6708,7 @@
         <v>2.28</v>
       </c>
       <c r="R24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
         <v>4.3</v>
@@ -6920,10 +6920,10 @@
         <v>1.37</v>
       </c>
       <c r="H25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I25">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -6935,7 +6935,7 @@
         <v>1.19</v>
       </c>
       <c r="M25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
         <v>6.8</v>
@@ -6947,7 +6947,7 @@
         <v>2.94</v>
       </c>
       <c r="Q25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R25">
         <v>1.79</v>
@@ -6959,7 +6959,7 @@
         <v>1.8</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
         <v>1.11</v>
@@ -6971,13 +6971,13 @@
         <v>36</v>
       </c>
       <c r="Y25">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Z25">
         <v>1000</v>
       </c>
       <c r="AA25">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB25">
         <v>12.5</v>
@@ -6986,7 +6986,7 @@
         <v>15</v>
       </c>
       <c r="AD25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE25">
         <v>1000</v>
@@ -7004,7 +7004,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK25">
         <v>14</v>
@@ -7013,7 +7013,7 @@
         <v>32</v>
       </c>
       <c r="AM25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
         <v>4.3</v>
@@ -7022,13 +7022,13 @@
         <v>130</v>
       </c>
       <c r="AP25">
+        <v>22</v>
+      </c>
+      <c r="AQ25">
         <v>23</v>
       </c>
-      <c r="AQ25">
-        <v>25</v>
-      </c>
       <c r="AR25">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS25">
         <v>50</v>
@@ -7040,7 +7040,7 @@
         <v>13</v>
       </c>
       <c r="AV25">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AW25">
         <v>60</v>
@@ -7055,7 +7055,7 @@
         <v>21</v>
       </c>
       <c r="BA25">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB25">
         <v>10.5</v>
@@ -7156,7 +7156,7 @@
         <v>216</v>
       </c>
       <c r="F26">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G26">
         <v>3.35</v>
@@ -7183,7 +7183,7 @@
         <v>2.28</v>
       </c>
       <c r="O26">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P26">
         <v>1.43</v>
@@ -7225,7 +7225,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD26">
         <v>16</v>
@@ -7249,7 +7249,7 @@
         <v>70</v>
       </c>
       <c r="AK26">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AL26">
         <v>1000</v>
@@ -7261,7 +7261,7 @@
         <v>95</v>
       </c>
       <c r="AO26">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="AP26">
         <v>6.4</v>
@@ -7327,13 +7327,13 @@
         <v>13</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN26">
         <v>6.4</v>
@@ -7345,13 +7345,13 @@
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT26">
         <v>5.8</v>
@@ -7363,19 +7363,19 @@
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB26" t="s">
         <v>246</v>
@@ -7416,7 +7416,7 @@
         <v>4.1</v>
       </c>
       <c r="L27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M27">
         <v>1.05</v>
@@ -7458,7 +7458,7 @@
         <v>12</v>
       </c>
       <c r="Z27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA27">
         <v>27</v>
@@ -7524,22 +7524,22 @@
         <v>7.2</v>
       </c>
       <c r="AV27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW27">
         <v>14.5</v>
       </c>
       <c r="AX27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY27">
         <v>12</v>
       </c>
       <c r="AZ27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA27">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB27">
         <v>6</v>
@@ -7551,22 +7551,22 @@
         <v>5.9</v>
       </c>
       <c r="BE27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF27">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK27">
         <v>1.04</v>
@@ -7578,13 +7578,13 @@
         <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ27">
         <v>1.04</v>
@@ -7596,25 +7596,25 @@
         <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW27">
         <v>1.04</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY27">
         <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA27">
         <v>1.04</v>
@@ -7748,52 +7748,52 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
         <v>1.01</v>
@@ -7888,7 +7888,7 @@
         <v>4.5</v>
       </c>
       <c r="H29">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I29">
         <v>1.87</v>
@@ -7897,13 +7897,13 @@
         <v>4.2</v>
       </c>
       <c r="K29">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>1.24</v>
       </c>
       <c r="M29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29">
         <v>5.8</v>
@@ -7912,7 +7912,7 @@
         <v>1.17</v>
       </c>
       <c r="P29">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="Q29">
         <v>1.52</v>
@@ -7951,7 +7951,7 @@
         <v>25</v>
       </c>
       <c r="AC29">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD29">
         <v>12.5</v>
@@ -7987,7 +7987,7 @@
         <v>32</v>
       </c>
       <c r="AO29">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AP29">
         <v>1.03</v>
@@ -7999,16 +7999,16 @@
         <v>1.03</v>
       </c>
       <c r="AS29">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AT29">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU29">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV29">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW29">
         <v>1.03</v>
@@ -8017,7 +8017,7 @@
         <v>1.03</v>
       </c>
       <c r="AY29">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AZ29">
         <v>1.03</v>
@@ -8053,55 +8053,55 @@
         <v>10</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN29">
         <v>9.199999999999999</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP29">
         <v>34</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR29">
         <v>36</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT29">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BU29">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BV29">
         <v>13.5</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BX29">
         <v>24</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ29">
         <v>16</v>
       </c>
       <c r="CA29">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB29" t="s">
         <v>246</v>
@@ -8154,16 +8154,16 @@
         <v>1.13</v>
       </c>
       <c r="P30">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R30">
         <v>1.79</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T30">
         <v>1.36</v>
@@ -8301,7 +8301,7 @@
         <v>70</v>
       </c>
       <c r="BM30">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BN30">
         <v>7.6</v>
@@ -8313,13 +8313,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ30">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR30">
         <v>26</v>
       </c>
       <c r="BS30">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BT30">
         <v>7.8</v>
@@ -8331,19 +8331,19 @@
         <v>21</v>
       </c>
       <c r="BW30">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BX30">
         <v>26</v>
       </c>
       <c r="BY30">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BZ30">
         <v>15</v>
       </c>
       <c r="CA30">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="CB30" t="s">
         <v>246</v>
@@ -8387,7 +8387,7 @@
         <v>1.19</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31">
         <v>7.4</v>
@@ -8504,7 +8504,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BA31">
         <v>4.6</v>
@@ -8853,13 +8853,13 @@
         <v>2.82</v>
       </c>
       <c r="G33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H33">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I33">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J33">
         <v>3.95</v>
@@ -8880,7 +8880,7 @@
         <v>1.16</v>
       </c>
       <c r="P33">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q33">
         <v>1.5</v>
@@ -8889,19 +8889,19 @@
         <v>1.7</v>
       </c>
       <c r="S33">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T33">
         <v>1.47</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V33">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W33">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X33">
         <v>36</v>
@@ -8961,13 +8961,13 @@
         <v>21</v>
       </c>
       <c r="AQ33">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR33">
         <v>17</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT33">
         <v>17</v>
@@ -8991,10 +8991,10 @@
         <v>10.5</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC33">
         <v>19.5</v>
@@ -9003,7 +9003,7 @@
         <v>21</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF33">
         <v>11</v>
@@ -9027,7 +9027,7 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN33">
         <v>7</v>
@@ -9036,7 +9036,7 @@
         <v>5.1</v>
       </c>
       <c r="BP33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
         <v>7</v>
@@ -9045,7 +9045,7 @@
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT33">
         <v>6.2</v>
@@ -9063,7 +9063,7 @@
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ33">
         <v>14</v>
@@ -9146,7 +9146,7 @@
         <v>1.36</v>
       </c>
       <c r="X34">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y34">
         <v>15</v>
@@ -9233,19 +9233,19 @@
         <v>13</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD34">
         <v>30</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF34">
         <v>17</v>
@@ -9263,13 +9263,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK34">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN34">
         <v>8.199999999999999</v>
@@ -9281,13 +9281,13 @@
         <v>28</v>
       </c>
       <c r="BQ34">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR34">
         <v>34</v>
       </c>
       <c r="BS34">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT34">
         <v>6.2</v>
@@ -9299,19 +9299,19 @@
         <v>16</v>
       </c>
       <c r="BW34">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX34">
         <v>26</v>
       </c>
       <c r="BY34">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ34">
         <v>17.5</v>
       </c>
       <c r="CA34">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB34" t="s">
         <v>246</v>
@@ -9334,22 +9334,22 @@
         <v>225</v>
       </c>
       <c r="F35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G35">
         <v>1000</v>
       </c>
       <c r="H35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I35">
         <v>1000</v>
       </c>
       <c r="J35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K35">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9442,52 +9442,52 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF35">
         <v>1.01</v>
@@ -9585,10 +9585,10 @@
         <v>2.38</v>
       </c>
       <c r="I36">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="J36">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K36">
         <v>4.6</v>
@@ -9624,7 +9624,7 @@
         <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
         <v>1.53</v>
@@ -9642,7 +9642,7 @@
         <v>44</v>
       </c>
       <c r="AB36">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AC36">
         <v>12.5</v>
@@ -9657,7 +9657,7 @@
         <v>29</v>
       </c>
       <c r="AG36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH36">
         <v>16.5</v>
@@ -9684,7 +9684,7 @@
         <v>13.5</v>
       </c>
       <c r="AP36">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ36">
         <v>14</v>
@@ -9693,7 +9693,7 @@
         <v>16.5</v>
       </c>
       <c r="AS36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT36">
         <v>14.5</v>
@@ -9720,7 +9720,7 @@
         <v>20</v>
       </c>
       <c r="BB36">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC36">
         <v>19</v>
@@ -9729,7 +9729,7 @@
         <v>21</v>
       </c>
       <c r="BE36">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF36">
         <v>10</v>
@@ -9747,13 +9747,13 @@
         <v>8.4</v>
       </c>
       <c r="BK36">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN36">
         <v>6.6</v>
@@ -9765,13 +9765,13 @@
         <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR36">
         <v>24</v>
       </c>
       <c r="BS36">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT36">
         <v>6.2</v>
@@ -9783,19 +9783,19 @@
         <v>16.5</v>
       </c>
       <c r="BW36">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ36">
         <v>13.5</v>
       </c>
       <c r="CA36">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB36" t="s">
         <v>246</v>
@@ -9821,19 +9821,19 @@
         <v>1.77</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H37">
         <v>4.2</v>
       </c>
       <c r="I37">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J37">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L37">
         <v>1.33</v>
@@ -9857,7 +9857,7 @@
         <v>1.36</v>
       </c>
       <c r="S37">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T37">
         <v>1.11</v>
@@ -9866,10 +9866,10 @@
         <v>1.11</v>
       </c>
       <c r="V37">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W37">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -10198,7 +10198,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="BA38">
         <v>6.8</v>
@@ -10302,22 +10302,22 @@
         <v>229</v>
       </c>
       <c r="F39">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G39">
         <v>990</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I39">
         <v>990</v>
       </c>
       <c r="J39">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="K39">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10326,13 +10326,13 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O39">
         <v>1.21</v>
       </c>
       <c r="P39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q39">
         <v>1.21</v>
@@ -10341,7 +10341,7 @@
         <v>1.18</v>
       </c>
       <c r="S39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
         <v>1.11</v>
@@ -10353,7 +10353,7 @@
         <v>1.01</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10410,52 +10410,52 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10544,13 +10544,13 @@
         <v>230</v>
       </c>
       <c r="F40">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G40">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H40">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I40">
         <v>3.7</v>
@@ -10568,13 +10568,13 @@
         <v>1.08</v>
       </c>
       <c r="N40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P40">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q40">
         <v>2.06</v>
@@ -10586,43 +10586,43 @@
         <v>3.55</v>
       </c>
       <c r="T40">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U40">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V40">
         <v>1.37</v>
       </c>
       <c r="W40">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X40">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y40">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z40">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AA40">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB40">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC40">
         <v>7.6</v>
       </c>
       <c r="AD40">
+        <v>18</v>
+      </c>
+      <c r="AE40">
+        <v>50</v>
+      </c>
+      <c r="AF40">
         <v>15</v>
-      </c>
-      <c r="AE40">
-        <v>55</v>
-      </c>
-      <c r="AF40">
-        <v>29</v>
       </c>
       <c r="AG40">
         <v>11.5</v>
@@ -10631,43 +10631,43 @@
         <v>17.5</v>
       </c>
       <c r="AI40">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ40">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK40">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AL40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM40">
         <v>110</v>
       </c>
       <c r="AN40">
+        <v>24</v>
+      </c>
+      <c r="AO40">
+        <v>48</v>
+      </c>
+      <c r="AP40">
+        <v>12</v>
+      </c>
+      <c r="AQ40">
+        <v>12</v>
+      </c>
+      <c r="AR40">
         <v>22</v>
       </c>
-      <c r="AO40">
-        <v>50</v>
-      </c>
-      <c r="AP40">
-        <v>10</v>
-      </c>
-      <c r="AQ40">
-        <v>11</v>
-      </c>
-      <c r="AR40">
-        <v>10.5</v>
-      </c>
       <c r="AS40">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AT40">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU40">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV40">
         <v>13</v>
@@ -10676,40 +10676,40 @@
         <v>27</v>
       </c>
       <c r="AX40">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY40">
         <v>10</v>
       </c>
       <c r="AZ40">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA40">
+        <v>46</v>
+      </c>
+      <c r="BB40">
+        <v>27</v>
+      </c>
+      <c r="BC40">
+        <v>22</v>
+      </c>
+      <c r="BD40">
         <v>34</v>
       </c>
-      <c r="BB40">
-        <v>19</v>
-      </c>
-      <c r="BC40">
-        <v>6.8</v>
-      </c>
-      <c r="BD40">
-        <v>26</v>
-      </c>
       <c r="BE40">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BF40">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG40">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH40">
         <v>3.9</v>
       </c>
       <c r="BI40">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ40">
         <v>11</v>
@@ -10721,49 +10721,49 @@
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN40">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BO40">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP40">
         <v>21</v>
       </c>
       <c r="BQ40">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR40">
         <v>38</v>
       </c>
       <c r="BS40">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT40">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BU40">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV40">
         <v>34</v>
       </c>
       <c r="BW40">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX40">
         <v>48</v>
       </c>
       <c r="BY40">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ40">
         <v>34</v>
       </c>
       <c r="CA40">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB40" t="s">
         <v>246</v>
@@ -10789,19 +10789,19 @@
         <v>1.04</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H41">
         <v>1.04</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K41">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10810,28 +10810,28 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="O41">
         <v>1.01</v>
       </c>
       <c r="P41">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R41">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41">
         <v>1.01</v>
@@ -10951,61 +10951,61 @@
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ41">
         <v>1000</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN41">
         <v>1000</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP41">
         <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT41">
         <v>1000</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV41">
         <v>1000</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ41">
         <v>1000</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB41" t="s">
         <v>246</v>
@@ -11031,7 +11031,7 @@
         <v>2.6</v>
       </c>
       <c r="G42">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H42">
         <v>2.92</v>
@@ -11043,16 +11043,16 @@
         <v>3.6</v>
       </c>
       <c r="K42">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L42">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M42">
         <v>1.06</v>
       </c>
       <c r="N42">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O42">
         <v>1.3</v>
@@ -11067,13 +11067,13 @@
         <v>1.42</v>
       </c>
       <c r="S42">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T42">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
         <v>1.51</v>
@@ -11082,10 +11082,10 @@
         <v>1.61</v>
       </c>
       <c r="X42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y42">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z42">
         <v>19.5</v>
@@ -11103,16 +11103,16 @@
         <v>13.5</v>
       </c>
       <c r="AE42">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF42">
         <v>17.5</v>
       </c>
       <c r="AG42">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI42">
         <v>42</v>
@@ -11121,7 +11121,7 @@
         <v>38</v>
       </c>
       <c r="AK42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL42">
         <v>38</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="AP42">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ42">
         <v>12</v>
@@ -11166,7 +11166,7 @@
         <v>11</v>
       </c>
       <c r="AZ42">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA42">
         <v>36</v>
@@ -11178,10 +11178,10 @@
         <v>24</v>
       </c>
       <c r="BD42">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE42">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF42">
         <v>18.5</v>
@@ -11276,10 +11276,10 @@
         <v>2.4</v>
       </c>
       <c r="H43">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I43">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J43">
         <v>3.15</v>
@@ -11288,7 +11288,7 @@
         <v>3.2</v>
       </c>
       <c r="L43">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M43">
         <v>1.11</v>
@@ -11312,13 +11312,13 @@
         <v>4.7</v>
       </c>
       <c r="T43">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U43">
         <v>1.94</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
         <v>1.71</v>
@@ -11330,13 +11330,13 @@
         <v>11.5</v>
       </c>
       <c r="Z43">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA43">
         <v>75</v>
       </c>
       <c r="AB43">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC43">
         <v>6.8</v>
@@ -11423,7 +11423,7 @@
         <v>46</v>
       </c>
       <c r="BE43">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF43">
         <v>25</v>
@@ -11515,19 +11515,19 @@
         <v>16</v>
       </c>
       <c r="G44">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H44">
+        <v>1.23</v>
+      </c>
+      <c r="I44">
         <v>1.24</v>
       </c>
-      <c r="I44">
-        <v>1.26</v>
-      </c>
       <c r="J44">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="K44">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11539,82 +11539,82 @@
         <v>5.2</v>
       </c>
       <c r="O44">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P44">
         <v>2.44</v>
       </c>
       <c r="Q44">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R44">
         <v>1.57</v>
       </c>
       <c r="S44">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T44">
         <v>2.38</v>
       </c>
       <c r="U44">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V44">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="W44">
         <v>1.06</v>
       </c>
       <c r="X44">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Y44">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z44">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA44">
         <v>9.199999999999999</v>
       </c>
       <c r="AB44">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AC44">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD44">
         <v>12</v>
       </c>
       <c r="AE44">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF44">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AG44">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AH44">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI44">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ44">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AK44">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AL44">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AM44">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AN44">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AO44">
         <v>4.5</v>
@@ -11623,16 +11623,16 @@
         <v>20</v>
       </c>
       <c r="AQ44">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR44">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS44">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT44">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AU44">
         <v>14</v>
@@ -11644,31 +11644,31 @@
         <v>13</v>
       </c>
       <c r="AX44">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY44">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AZ44">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BA44">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD44">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE44">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG44">
         <v>4</v>
@@ -11787,7 +11787,7 @@
         <v>4.5</v>
       </c>
       <c r="Q45">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="R45">
         <v>1.25</v>
@@ -11862,52 +11862,52 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF45">
         <v>1.01</v>
@@ -11996,10 +11996,10 @@
         <v>236</v>
       </c>
       <c r="F46">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G46">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H46">
         <v>4.2</v>
@@ -12008,7 +12008,7 @@
         <v>5.5</v>
       </c>
       <c r="J46">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K46">
         <v>6</v>
@@ -12026,13 +12026,13 @@
         <v>1.08</v>
       </c>
       <c r="P46">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R46">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S46">
         <v>1.69</v>
@@ -12047,7 +12047,7 @@
         <v>1.22</v>
       </c>
       <c r="W46">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X46">
         <v>65</v>
@@ -12080,7 +12080,7 @@
         <v>14.5</v>
       </c>
       <c r="AH46">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI46">
         <v>38</v>
@@ -12089,7 +12089,7 @@
         <v>25</v>
       </c>
       <c r="AK46">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL46">
         <v>24</v>
@@ -12104,16 +12104,16 @@
         <v>24</v>
       </c>
       <c r="AP46">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AR46">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AS46">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="AT46">
         <v>19</v>
@@ -12125,7 +12125,7 @@
         <v>16.5</v>
       </c>
       <c r="AW46">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX46">
         <v>14.5</v>
@@ -12137,7 +12137,7 @@
         <v>12</v>
       </c>
       <c r="BA46">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BB46">
         <v>16</v>
@@ -12149,7 +12149,7 @@
         <v>15.5</v>
       </c>
       <c r="BE46">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BF46">
         <v>3.9</v>
@@ -12238,28 +12238,28 @@
         <v>237</v>
       </c>
       <c r="F47">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G47">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="H47">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="I47">
+        <v>4.5</v>
+      </c>
+      <c r="J47">
+        <v>3.7</v>
+      </c>
+      <c r="K47">
         <v>4.6</v>
       </c>
-      <c r="J47">
-        <v>3.3</v>
-      </c>
-      <c r="K47">
-        <v>7</v>
-      </c>
       <c r="L47">
         <v>1.01</v>
       </c>
       <c r="M47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N47">
         <v>2.6</v>
@@ -12268,13 +12268,13 @@
         <v>1.15</v>
       </c>
       <c r="P47">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q47">
         <v>1.46</v>
       </c>
       <c r="R47">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S47">
         <v>2.12</v>
@@ -12289,7 +12289,7 @@
         <v>1.28</v>
       </c>
       <c r="W47">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12492,10 +12492,10 @@
         <v>11</v>
       </c>
       <c r="J48">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K48">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L48">
         <v>1.33</v>
@@ -12504,22 +12504,22 @@
         <v>1.05</v>
       </c>
       <c r="N48">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O48">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P48">
         <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R48">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S48">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T48">
         <v>2.02</v>
@@ -12546,7 +12546,7 @@
         <v>420</v>
       </c>
       <c r="AB48">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC48">
         <v>15.5</v>
@@ -12561,10 +12561,10 @@
         <v>8.6</v>
       </c>
       <c r="AG48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH48">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI48">
         <v>150</v>
@@ -12591,25 +12591,25 @@
         <v>15</v>
       </c>
       <c r="AQ48">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AR48">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS48">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT48">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU48">
         <v>10.5</v>
       </c>
       <c r="AV48">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW48">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX48">
         <v>6.4</v>
@@ -12618,10 +12618,10 @@
         <v>8</v>
       </c>
       <c r="AZ48">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA48">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB48">
         <v>9.199999999999999</v>
@@ -12630,16 +12630,16 @@
         <v>11</v>
       </c>
       <c r="BD48">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE48">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF48">
         <v>4.5</v>
       </c>
       <c r="BG48">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH48">
         <v>4.6</v>
@@ -12663,13 +12663,13 @@
         <v>3.85</v>
       </c>
       <c r="BO48">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP48">
         <v>9.6</v>
       </c>
       <c r="BQ48">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BR48">
         <v>26</v>
@@ -12699,7 +12699,7 @@
         <v>13.5</v>
       </c>
       <c r="CA48">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="CB48" t="s">
         <v>246</v>
@@ -12728,19 +12728,19 @@
         <v>2.54</v>
       </c>
       <c r="H49">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I49">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K49">
         <v>3.05</v>
       </c>
       <c r="L49">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="M49">
         <v>1.15</v>
@@ -12752,7 +12752,7 @@
         <v>1.63</v>
       </c>
       <c r="P49">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q49">
         <v>2.88</v>
@@ -12767,7 +12767,7 @@
         <v>2.24</v>
       </c>
       <c r="U49">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V49">
         <v>1.33</v>
@@ -12893,13 +12893,13 @@
         <v>12.5</v>
       </c>
       <c r="BK49">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN49">
         <v>5.2</v>
@@ -12911,13 +12911,13 @@
         <v>23</v>
       </c>
       <c r="BQ49">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR49">
         <v>55</v>
       </c>
       <c r="BS49">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT49">
         <v>7.2</v>
@@ -12929,19 +12929,19 @@
         <v>42</v>
       </c>
       <c r="BW49">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX49">
         <v>1000</v>
       </c>
       <c r="BY49">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ49">
         <v>1000</v>
       </c>
       <c r="CA49">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB49" t="s">
         <v>246</v>
@@ -12994,136 +12994,136 @@
         <v>1.29</v>
       </c>
       <c r="P50">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R50">
         <v>1.3</v>
       </c>
       <c r="S50">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U50">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V50">
         <v>1.26</v>
       </c>
       <c r="W50">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X50">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y50">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z50">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA50">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB50">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC50">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD50">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE50">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF50">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG50">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH50">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI50">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ50">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK50">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL50">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM50">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN50">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO50">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP50">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ50">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT50">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU50">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV50">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW50">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX50">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY50">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ50">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA50">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB50">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC50">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD50">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE50">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF50">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG50">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13206,22 +13206,22 @@
         <v>241</v>
       </c>
       <c r="F51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G51">
         <v>990</v>
       </c>
       <c r="H51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I51">
         <v>990</v>
       </c>
       <c r="J51">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K51">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13257,7 +13257,7 @@
         <v>1.02</v>
       </c>
       <c r="W51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13451,7 +13451,7 @@
         <v>1.84</v>
       </c>
       <c r="G52">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H52">
         <v>5.2</v>
@@ -13460,7 +13460,7 @@
         <v>5.9</v>
       </c>
       <c r="J52">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K52">
         <v>3.65</v>
@@ -13472,34 +13472,34 @@
         <v>1.1</v>
       </c>
       <c r="N52">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="P52">
         <v>1.67</v>
       </c>
       <c r="Q52">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
+        <v>1.22</v>
+      </c>
+      <c r="S52">
+        <v>4.5</v>
+      </c>
+      <c r="T52">
+        <v>2.12</v>
+      </c>
+      <c r="U52">
+        <v>1.76</v>
+      </c>
+      <c r="V52">
         <v>1.21</v>
       </c>
-      <c r="S52">
-        <v>4</v>
-      </c>
-      <c r="T52">
-        <v>1.11</v>
-      </c>
-      <c r="U52">
-        <v>1.61</v>
-      </c>
-      <c r="V52">
-        <v>1.2</v>
-      </c>
       <c r="W52">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X52">
         <v>12.5</v>
@@ -13514,7 +13514,7 @@
         <v>210</v>
       </c>
       <c r="AB52">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AC52">
         <v>9.800000000000001</v>
@@ -13529,7 +13529,7 @@
         <v>12</v>
       </c>
       <c r="AG52">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AH52">
         <v>30</v>
@@ -13538,7 +13538,7 @@
         <v>140</v>
       </c>
       <c r="AJ52">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK52">
         <v>29</v>
@@ -13562,10 +13562,10 @@
         <v>11</v>
       </c>
       <c r="AR52">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS52">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AT52">
         <v>5.8</v>
@@ -13577,7 +13577,7 @@
         <v>16.5</v>
       </c>
       <c r="AW52">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AX52">
         <v>7.4</v>
@@ -13589,7 +13589,7 @@
         <v>21</v>
       </c>
       <c r="BA52">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="BB52">
         <v>15</v>
@@ -13598,16 +13598,16 @@
         <v>17</v>
       </c>
       <c r="BD52">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE52">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="BF52">
         <v>13</v>
       </c>
       <c r="BG52">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="BH52">
         <v>3.4</v>
@@ -13690,7 +13690,7 @@
         <v>243</v>
       </c>
       <c r="F53">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G53">
         <v>2.46</v>
@@ -13699,13 +13699,13 @@
         <v>3.4</v>
       </c>
       <c r="I53">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J53">
         <v>3.15</v>
       </c>
       <c r="K53">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L53">
         <v>1.45</v>
@@ -13738,7 +13738,7 @@
         <v>1.11</v>
       </c>
       <c r="V53">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W53">
         <v>1.68</v>
@@ -13861,13 +13861,13 @@
         <v>11.5</v>
       </c>
       <c r="BK53">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN53">
         <v>5.6</v>
@@ -13879,13 +13879,13 @@
         <v>21</v>
       </c>
       <c r="BQ53">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR53">
         <v>40</v>
       </c>
       <c r="BS53">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT53">
         <v>7.8</v>
@@ -13897,13 +13897,13 @@
         <v>38</v>
       </c>
       <c r="BW53">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX53">
         <v>55</v>
       </c>
       <c r="BY53">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ53">
         <v>0</v>
@@ -13932,10 +13932,10 @@
         <v>244</v>
       </c>
       <c r="F54">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G54">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H54">
         <v>6.2</v>
@@ -13956,22 +13956,22 @@
         <v>1.06</v>
       </c>
       <c r="N54">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O54">
         <v>1.29</v>
       </c>
       <c r="P54">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q54">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R54">
         <v>1.42</v>
       </c>
       <c r="S54">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T54">
         <v>1.91</v>
@@ -14022,7 +14022,7 @@
         <v>100</v>
       </c>
       <c r="AJ54">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK54">
         <v>19.5</v>
@@ -14049,7 +14049,7 @@
         <v>7</v>
       </c>
       <c r="AS54">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT54">
         <v>7.6</v>
@@ -14061,7 +14061,7 @@
         <v>21</v>
       </c>
       <c r="AW54">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX54">
         <v>8.800000000000001</v>
@@ -14073,7 +14073,7 @@
         <v>18.5</v>
       </c>
       <c r="BA54">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB54">
         <v>13.5</v>
@@ -14085,13 +14085,13 @@
         <v>6.6</v>
       </c>
       <c r="BE54">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF54">
         <v>8</v>
       </c>
       <c r="BG54">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH54">
         <v>3.7</v>
@@ -14198,7 +14198,7 @@
         <v>1.07</v>
       </c>
       <c r="N55">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O55">
         <v>1.32</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -583,15 +583,15 @@
     <t>Velez Sarsfield</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Ferroviaria</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Guarani</t>
-  </si>
-  <si>
     <t>Antofagasta</t>
   </si>
   <si>
@@ -745,16 +745,16 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Ypiranga RS</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Ypiranga RS</t>
-  </si>
-  <si>
-    <t>2026-08-16 13:59:19</t>
+    <t>2026-08-16 16:10:32</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
         <v>2.88</v>
       </c>
       <c r="H2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I2">
         <v>2.9</v>
@@ -1363,7 +1363,7 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -1381,7 +1381,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
         <v>1.41</v>
@@ -1390,7 +1390,7 @@
         <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -1402,7 +1402,7 @@
         <v>1.54</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
         <v>13.5</v>
@@ -1411,7 +1411,7 @@
         <v>21</v>
       </c>
       <c r="AA2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB2">
         <v>13.5</v>
@@ -1420,7 +1420,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE2">
         <v>40</v>
@@ -1429,7 +1429,7 @@
         <v>23</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
         <v>17</v>
@@ -1477,7 +1477,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>16.5</v>
@@ -1489,13 +1489,13 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB2">
         <v>27</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>27</v>
@@ -1504,10 +1504,10 @@
         <v>55</v>
       </c>
       <c r="BF2">
+        <v>16</v>
+      </c>
+      <c r="BG2">
         <v>15.5</v>
-      </c>
-      <c r="BG2">
-        <v>15</v>
       </c>
       <c r="BH2">
         <v>4.3</v>
@@ -1590,19 +1590,19 @@
         <v>193</v>
       </c>
       <c r="F3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
         <v>2.76</v>
       </c>
       <c r="I3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.4</v>
@@ -1623,7 +1623,7 @@
         <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
         <v>1.27</v>
@@ -1632,16 +1632,16 @@
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U3">
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
         <v>11.5</v>
@@ -1689,7 +1689,7 @@
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN3">
         <v>44</v>
@@ -1731,22 +1731,22 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3">
         <v>34</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BD3">
         <v>40</v>
       </c>
       <c r="BE3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BG3">
         <v>24</v>
@@ -1761,7 +1761,7 @@
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1838,16 +1838,16 @@
         <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J4">
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1859,19 +1859,19 @@
         <v>4.9</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
         <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T4">
         <v>1.62</v>
@@ -1880,7 +1880,7 @@
         <v>2.52</v>
       </c>
       <c r="V4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W4">
         <v>1.46</v>
@@ -1904,7 +1904,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE4">
         <v>24</v>
@@ -1913,16 +1913,16 @@
         <v>24</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK4">
         <v>34</v>
@@ -1931,19 +1931,19 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4">
         <v>15.5</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
         <v>15.5</v>
@@ -1952,25 +1952,25 @@
         <v>27</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY4">
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4">
         <v>26</v>
@@ -1982,7 +1982,7 @@
         <v>27</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE4">
         <v>48</v>
@@ -1991,7 +1991,7 @@
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH4">
         <v>4.1</v>
@@ -2003,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -2015,7 +2015,7 @@
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP4">
         <v>22</v>
@@ -2033,7 +2033,7 @@
         <v>5.8</v>
       </c>
       <c r="BU4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>17</v>
@@ -2083,13 +2083,13 @@
         <v>1.56</v>
       </c>
       <c r="I5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J5">
         <v>4.9</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.25</v>
@@ -2101,10 +2101,10 @@
         <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
         <v>1.61</v>
@@ -2116,7 +2116,7 @@
         <v>2.54</v>
       </c>
       <c r="T5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
         <v>2.26</v>
@@ -2125,16 +2125,16 @@
         <v>2.72</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA5">
         <v>15.5</v>
@@ -2143,28 +2143,28 @@
         <v>26</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF5">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AG5">
         <v>23</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ5">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK5">
         <v>100</v>
@@ -2173,13 +2173,13 @@
         <v>70</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5">
         <v>95</v>
       </c>
       <c r="AO5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -2191,10 +2191,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -2203,37 +2203,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AY5">
+        <v>19.5</v>
+      </c>
+      <c r="AZ5">
         <v>18</v>
       </c>
-      <c r="AZ5">
-        <v>18.5</v>
-      </c>
       <c r="BA5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BC5">
         <v>50</v>
       </c>
       <c r="BD5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE5">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF5">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BG5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH5">
         <v>4.6</v>
@@ -2245,7 +2245,7 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2257,7 +2257,7 @@
         <v>10.5</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -2275,13 +2275,13 @@
         <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BV5">
         <v>9.800000000000001</v>
       </c>
       <c r="BW5">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BX5">
         <v>22</v>
@@ -2316,97 +2316,97 @@
         <v>196</v>
       </c>
       <c r="F6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G6">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="H6">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>17.5</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L6">
+        <v>1.23</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>5.7</v>
+      </c>
+      <c r="O6">
+        <v>1.16</v>
+      </c>
+      <c r="P6">
+        <v>2.54</v>
+      </c>
+      <c r="Q6">
+        <v>1.43</v>
+      </c>
+      <c r="R6">
+        <v>1.64</v>
+      </c>
+      <c r="S6">
+        <v>2.08</v>
+      </c>
+      <c r="T6">
+        <v>1.94</v>
+      </c>
+      <c r="U6">
+        <v>1.76</v>
+      </c>
+      <c r="V6">
+        <v>1.06</v>
+      </c>
+      <c r="W6">
+        <v>4.5</v>
+      </c>
+      <c r="X6">
+        <v>36</v>
+      </c>
+      <c r="Y6">
+        <v>60</v>
+      </c>
+      <c r="Z6">
+        <v>160</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>13</v>
+      </c>
+      <c r="AC6">
+        <v>18</v>
+      </c>
+      <c r="AD6">
         <v>950</v>
       </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>4.7</v>
-      </c>
-      <c r="O6">
-        <v>1.14</v>
-      </c>
-      <c r="P6">
-        <v>2.46</v>
-      </c>
-      <c r="Q6">
-        <v>1.15</v>
-      </c>
-      <c r="R6">
-        <v>1.7</v>
-      </c>
-      <c r="S6">
-        <v>1.05</v>
-      </c>
-      <c r="T6">
-        <v>1.92</v>
-      </c>
-      <c r="U6">
-        <v>1.73</v>
-      </c>
-      <c r="V6">
-        <v>1.01</v>
-      </c>
-      <c r="W6">
-        <v>3.9</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF6">
         <v>10</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6">
         <v>34</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK6">
         <v>16.5</v>
@@ -2418,58 +2418,58 @@
         <v>180</v>
       </c>
       <c r="AN6">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2478,64 +2478,64 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="s">
         <v>246</v>
@@ -2558,22 +2558,22 @@
         <v>197</v>
       </c>
       <c r="F7">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H7">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="I7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>1.31</v>
@@ -2582,13 +2582,13 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O7">
         <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
         <v>1.64</v>
@@ -2603,13 +2603,13 @@
         <v>1.59</v>
       </c>
       <c r="U7">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X7">
         <v>22</v>
@@ -2621,7 +2621,7 @@
         <v>15.5</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB7">
         <v>20</v>
@@ -2633,10 +2633,10 @@
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG7">
         <v>15.5</v>
@@ -2651,22 +2651,22 @@
         <v>75</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ7">
         <v>12</v>
@@ -2681,19 +2681,19 @@
         <v>17.5</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX7">
         <v>28</v>
       </c>
       <c r="AY7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ7">
         <v>14</v>
@@ -2714,70 +2714,70 @@
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI7">
         <v>3.85</v>
       </c>
       <c r="BJ7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL7">
         <v>80</v>
       </c>
       <c r="BM7">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN7">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BQ7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT7">
         <v>5.3</v>
       </c>
       <c r="BU7">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW7">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA7">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB7" t="s">
         <v>246</v>
@@ -2800,22 +2800,22 @@
         <v>198</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="I8">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.4</v>
@@ -2824,16 +2824,16 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O8">
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R8">
         <v>1.39</v>
@@ -2845,28 +2845,28 @@
         <v>1.76</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="W8">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
@@ -2875,13 +2875,13 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>16.5</v>
@@ -2890,34 +2890,34 @@
         <v>38</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AO8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP8">
         <v>13</v>
       </c>
       <c r="AQ8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AT8">
         <v>12</v>
@@ -2926,97 +2926,97 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB8">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BC8">
         <v>32</v>
       </c>
       <c r="BD8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BG8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BH8">
         <v>3.45</v>
       </c>
       <c r="BI8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8">
         <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BP8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BW8">
         <v>8.4</v>
       </c>
       <c r="BX8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY8">
         <v>10.5</v>
       </c>
       <c r="BZ8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA8">
         <v>10</v>
@@ -3045,7 +3045,7 @@
         <v>2.46</v>
       </c>
       <c r="G9">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H9">
         <v>2.78</v>
@@ -3054,7 +3054,7 @@
         <v>2.98</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
         <v>4</v>
@@ -3075,7 +3075,7 @@
         <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
         <v>1.58</v>
@@ -3084,7 +3084,7 @@
         <v>2.52</v>
       </c>
       <c r="T9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U9">
         <v>2.62</v>
@@ -3093,7 +3093,7 @@
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -3120,10 +3120,10 @@
         <v>29</v>
       </c>
       <c r="AF9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH9">
         <v>15.5</v>
@@ -3195,13 +3195,13 @@
         <v>22</v>
       </c>
       <c r="BE9">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH9">
         <v>4.5</v>
@@ -3225,7 +3225,7 @@
         <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP9">
         <v>17.5</v>
@@ -3284,22 +3284,22 @@
         <v>200</v>
       </c>
       <c r="F10">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="G10">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H10">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="I10">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3308,121 +3308,121 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O10">
         <v>1.2</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>1.73</v>
       </c>
       <c r="R10">
+        <v>1.53</v>
+      </c>
+      <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
+        <v>1.48</v>
+      </c>
+      <c r="U10">
+        <v>2.46</v>
+      </c>
+      <c r="V10">
+        <v>1.64</v>
+      </c>
+      <c r="W10">
         <v>1.45</v>
       </c>
-      <c r="S10">
-        <v>2.34</v>
-      </c>
-      <c r="T10">
-        <v>1.11</v>
-      </c>
-      <c r="U10">
-        <v>1.47</v>
-      </c>
-      <c r="V10">
-        <v>1.52</v>
-      </c>
-      <c r="W10">
-        <v>1.38</v>
-      </c>
       <c r="X10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>1.06</v>
+        <v>13</v>
       </c>
       <c r="AS10">
         <v>1.26</v>
       </c>
       <c r="AT10">
-        <v>1.06</v>
+        <v>11.5</v>
       </c>
       <c r="AU10">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="AV10">
-        <v>1.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10">
-        <v>1.06</v>
+        <v>16.5</v>
       </c>
       <c r="AX10">
-        <v>1.06</v>
+        <v>16.5</v>
       </c>
       <c r="AY10">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>1.51</v>
+        <v>13</v>
       </c>
       <c r="BA10">
         <v>1.03</v>
@@ -3431,19 +3431,19 @@
         <v>1.22</v>
       </c>
       <c r="BC10">
-        <v>1.06</v>
+        <v>21</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="BE10">
         <v>1.76</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>2.08</v>
       </c>
       <c r="Q11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
         <v>1.44</v>
@@ -3789,31 +3789,31 @@
         <v>1.39</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R12">
         <v>1.33</v>
       </c>
       <c r="S12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T12">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="U12">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V12">
         <v>1.11</v>
@@ -3837,7 +3837,7 @@
         <v>7.8</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>36</v>
@@ -3882,10 +3882,10 @@
         <v>17.5</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
         <v>5.8</v>
@@ -3897,7 +3897,7 @@
         <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
         <v>6.6</v>
@@ -3909,7 +3909,7 @@
         <v>20</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
         <v>10.5</v>
@@ -3918,16 +3918,16 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>3.85</v>
@@ -3939,13 +3939,13 @@
         <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN12">
         <v>4.4</v>
@@ -3963,31 +3963,31 @@
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT12">
         <v>12.5</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB12" t="s">
         <v>246</v>
@@ -4013,46 +4013,46 @@
         <v>1.54</v>
       </c>
       <c r="G13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I13">
         <v>6.6</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
         <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q13">
         <v>1.53</v>
       </c>
       <c r="R13">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U13">
         <v>2.22</v>
@@ -4061,7 +4061,7 @@
         <v>1.18</v>
       </c>
       <c r="W13">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X13">
         <v>30</v>
@@ -4112,13 +4112,13 @@
         <v>90</v>
       </c>
       <c r="AN13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO13">
         <v>65</v>
       </c>
       <c r="AP13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ13">
         <v>20</v>
@@ -4127,19 +4127,19 @@
         <v>38</v>
       </c>
       <c r="AS13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="AU13">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13">
         <v>18.5</v>
       </c>
       <c r="AW13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX13">
         <v>9.199999999999999</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB13">
         <v>12</v>
@@ -4163,19 +4163,19 @@
         <v>20</v>
       </c>
       <c r="BE13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF13">
         <v>3.1</v>
       </c>
       <c r="BG13">
+        <v>5.2</v>
+      </c>
+      <c r="BH13">
         <v>5.1</v>
       </c>
-      <c r="BH13">
-        <v>5</v>
-      </c>
       <c r="BI13">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="BJ13">
         <v>11</v>
@@ -4193,25 +4193,25 @@
         <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BR13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS13">
         <v>4.5</v>
       </c>
       <c r="BT13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV13">
         <v>50</v>
@@ -4255,10 +4255,10 @@
         <v>6.2</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I14">
         <v>1.64</v>
@@ -4267,10 +4267,10 @@
         <v>4.3</v>
       </c>
       <c r="K14">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M14">
         <v>1.03</v>
@@ -4285,19 +4285,19 @@
         <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R14">
         <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
         <v>2.56</v>
@@ -4321,7 +4321,7 @@
         <v>29</v>
       </c>
       <c r="AC14">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4372,7 +4372,7 @@
         <v>11.5</v>
       </c>
       <c r="AT14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU14">
         <v>7.8</v>
@@ -4381,7 +4381,7 @@
         <v>7.4</v>
       </c>
       <c r="AW14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX14">
         <v>1.03</v>
@@ -4390,7 +4390,7 @@
         <v>17.5</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>20</v>
@@ -4414,58 +4414,58 @@
         <v>5.8</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4500,7 +4500,7 @@
         <v>2.14</v>
       </c>
       <c r="H15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I15">
         <v>4.4</v>
@@ -4509,10 +4509,10 @@
         <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M15">
         <v>1.08</v>
@@ -4539,7 +4539,7 @@
         <v>1.83</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V15">
         <v>1.29</v>
@@ -4638,7 +4638,7 @@
         <v>8.4</v>
       </c>
       <c r="BB15">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BC15">
         <v>20</v>
@@ -4659,7 +4659,7 @@
         <v>3.3</v>
       </c>
       <c r="BI15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15">
         <v>10</v>
@@ -4739,7 +4739,7 @@
         <v>3.55</v>
       </c>
       <c r="G16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H16">
         <v>2.14</v>
@@ -4751,13 +4751,13 @@
         <v>3.15</v>
       </c>
       <c r="K16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
         <v>2.96</v>
@@ -4772,184 +4772,184 @@
         <v>2.24</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V16">
         <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
-        <v>1.53</v>
+        <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX16">
         <v>1.1</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH16">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="BI16">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO16">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU16">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW16">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4978,13 +4978,13 @@
         <v>207</v>
       </c>
       <c r="F17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G17">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
         <v>5.7</v>
@@ -4993,7 +4993,7 @@
         <v>3.85</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.33</v>
@@ -5017,7 +5017,7 @@
         <v>1.43</v>
       </c>
       <c r="S17">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
         <v>1.72</v>
@@ -5029,7 +5029,7 @@
         <v>1.21</v>
       </c>
       <c r="W17">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X17">
         <v>22</v>
@@ -5462,13 +5462,13 @@
         <v>209</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G19">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H19">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="I19">
         <v>2.26</v>
@@ -5477,88 +5477,88 @@
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
         <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
         <v>1.67</v>
       </c>
       <c r="R19">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S19">
         <v>2.68</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
         <v>1.79</v>
       </c>
       <c r="W19">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA19">
         <v>36</v>
       </c>
       <c r="AB19">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC19">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF19">
+        <v>28</v>
+      </c>
+      <c r="AG19">
+        <v>15.5</v>
+      </c>
+      <c r="AH19">
+        <v>19.5</v>
+      </c>
+      <c r="AI19">
         <v>34</v>
       </c>
-      <c r="AG19">
-        <v>19</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>40</v>
-      </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM19">
         <v>90</v>
@@ -5567,115 +5567,115 @@
         <v>36</v>
       </c>
       <c r="AO19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP19">
-        <v>1.58</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS19">
         <v>18.5</v>
       </c>
       <c r="AT19">
-        <v>1.47</v>
+        <v>13.5</v>
       </c>
       <c r="AU19">
-        <v>1.39</v>
+        <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW19">
-        <v>1.58</v>
+        <v>15.5</v>
       </c>
       <c r="AX19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY19">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="AZ19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA19">
-        <v>1.52</v>
+        <v>21</v>
       </c>
       <c r="BB19">
-        <v>1.58</v>
+        <v>5.3</v>
       </c>
       <c r="BC19">
-        <v>1.58</v>
+        <v>5.1</v>
       </c>
       <c r="BD19">
-        <v>1.58</v>
+        <v>5.1</v>
       </c>
       <c r="BE19">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="BF19">
         <v>19</v>
       </c>
       <c r="BG19">
+        <v>11</v>
+      </c>
+      <c r="BH19">
+        <v>4.1</v>
+      </c>
+      <c r="BI19">
+        <v>3.15</v>
+      </c>
+      <c r="BJ19">
+        <v>9.4</v>
+      </c>
+      <c r="BK19">
+        <v>4.8</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
         <v>9</v>
       </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.04</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.04</v>
-      </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5704,19 +5704,19 @@
         <v>210</v>
       </c>
       <c r="F20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G20">
         <v>1000</v>
       </c>
       <c r="H20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I20">
         <v>990</v>
       </c>
       <c r="J20">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5743,7 +5743,7 @@
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>2.46</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
         <v>1.11</v>
@@ -5812,52 +5812,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
         <v>1.04</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
         <v>1.04</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5946,25 +5946,25 @@
         <v>211</v>
       </c>
       <c r="F21">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G21">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M21">
         <v>1.04</v>
@@ -5973,7 +5973,7 @@
         <v>4.9</v>
       </c>
       <c r="O21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P21">
         <v>2.32</v>
@@ -5988,7 +5988,7 @@
         <v>2.64</v>
       </c>
       <c r="T21">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U21">
         <v>2.02</v>
@@ -5997,7 +5997,7 @@
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X21">
         <v>22</v>
@@ -6006,10 +6006,10 @@
         <v>30</v>
       </c>
       <c r="Z21">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA21">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AB21">
         <v>9.800000000000001</v>
@@ -6018,10 +6018,10 @@
         <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AE21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF21">
         <v>9.800000000000001</v>
@@ -6030,10 +6030,10 @@
         <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AI21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
         <v>14</v>
@@ -6045,10 +6045,10 @@
         <v>32</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO21">
         <v>120</v>
@@ -6060,7 +6060,7 @@
         <v>25</v>
       </c>
       <c r="AR21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS21">
         <v>10.5</v>
@@ -6075,10 +6075,10 @@
         <v>25</v>
       </c>
       <c r="AW21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
@@ -6087,10 +6087,10 @@
         <v>20</v>
       </c>
       <c r="BA21">
+        <v>12</v>
+      </c>
+      <c r="BB21">
         <v>11.5</v>
-      </c>
-      <c r="BB21">
-        <v>12</v>
       </c>
       <c r="BC21">
         <v>13</v>
@@ -6099,73 +6099,73 @@
         <v>26</v>
       </c>
       <c r="BE21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF21">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB21" t="s">
         <v>246</v>
@@ -6188,7 +6188,7 @@
         <v>212</v>
       </c>
       <c r="F22">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G22">
         <v>1.88</v>
@@ -6197,7 +6197,7 @@
         <v>4.7</v>
       </c>
       <c r="I22">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J22">
         <v>3.75</v>
@@ -6206,19 +6206,19 @@
         <v>4.2</v>
       </c>
       <c r="L22">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M22">
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
         <v>1.28</v>
       </c>
       <c r="P22">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q22">
         <v>1.83</v>
@@ -6230,7 +6230,7 @@
         <v>3.1</v>
       </c>
       <c r="T22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U22">
         <v>2.04</v>
@@ -6433,13 +6433,13 @@
         <v>2.36</v>
       </c>
       <c r="G23">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H23">
         <v>3.15</v>
       </c>
       <c r="I23">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J23">
         <v>3.25</v>
@@ -6451,142 +6451,142 @@
         <v>1.34</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O23">
         <v>1.37</v>
       </c>
       <c r="P23">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q23">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S23">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V23">
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
         <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG23">
         <v>1.01</v>
@@ -6672,19 +6672,19 @@
         <v>214</v>
       </c>
       <c r="F24">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G24">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H24">
         <v>5.1</v>
       </c>
       <c r="I24">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J24">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K24">
         <v>3.7</v>
@@ -6702,7 +6702,7 @@
         <v>1.44</v>
       </c>
       <c r="P24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q24">
         <v>2.28</v>
@@ -6711,7 +6711,7 @@
         <v>1.25</v>
       </c>
       <c r="S24">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T24">
         <v>2.02</v>
@@ -6720,7 +6720,7 @@
         <v>1.8</v>
       </c>
       <c r="V24">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W24">
         <v>2.08</v>
@@ -6914,13 +6914,13 @@
         <v>215</v>
       </c>
       <c r="F25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G25">
         <v>1.37</v>
       </c>
       <c r="H25">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I25">
         <v>9.6</v>
@@ -6932,10 +6932,10 @@
         <v>6.4</v>
       </c>
       <c r="L25">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="M25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
         <v>6.8</v>
@@ -6944,7 +6944,7 @@
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q25">
         <v>1.47</v>
@@ -6980,7 +6980,7 @@
         <v>300</v>
       </c>
       <c r="AB25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC25">
         <v>15</v>
@@ -6992,7 +6992,7 @@
         <v>1000</v>
       </c>
       <c r="AF25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>11</v>
@@ -7007,7 +7007,7 @@
         <v>12</v>
       </c>
       <c r="AK25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL25">
         <v>32</v>
@@ -7019,13 +7019,13 @@
         <v>4.3</v>
       </c>
       <c r="AO25">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP25">
         <v>22</v>
       </c>
       <c r="AQ25">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AR25">
         <v>50</v>
@@ -7043,7 +7043,7 @@
         <v>21</v>
       </c>
       <c r="AW25">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX25">
         <v>9.199999999999999</v>
@@ -7070,70 +7070,70 @@
         <v>60</v>
       </c>
       <c r="BF25">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG25">
         <v>38</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI25">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="BJ25">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK25">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM25">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BN25">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO25">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP25">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BQ25">
         <v>5.1</v>
       </c>
       <c r="BR25">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BS25">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="BT25">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU25">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW25">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY25">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="BZ25">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="CA25">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="CB25" t="s">
         <v>246</v>
@@ -7165,13 +7165,13 @@
         <v>2.78</v>
       </c>
       <c r="I26">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J26">
         <v>2.86</v>
       </c>
       <c r="K26">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L26">
         <v>1.55</v>
@@ -7180,10 +7180,10 @@
         <v>1.16</v>
       </c>
       <c r="N26">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O26">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P26">
         <v>1.43</v>
@@ -7192,19 +7192,19 @@
         <v>3.05</v>
       </c>
       <c r="R26">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S26">
         <v>6.8</v>
       </c>
       <c r="T26">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U26">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W26">
         <v>1.43</v>
@@ -7219,7 +7219,7 @@
         <v>17.5</v>
       </c>
       <c r="AA26">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB26">
         <v>8.800000000000001</v>
@@ -7228,10 +7228,10 @@
         <v>7.4</v>
       </c>
       <c r="AD26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE26">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AF26">
         <v>22</v>
@@ -7249,7 +7249,7 @@
         <v>70</v>
       </c>
       <c r="AK26">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AL26">
         <v>1000</v>
@@ -7261,10 +7261,10 @@
         <v>95</v>
       </c>
       <c r="AO26">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="AP26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26">
         <v>6.8</v>
@@ -7273,7 +7273,7 @@
         <v>14</v>
       </c>
       <c r="AS26">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AT26">
         <v>7.4</v>
@@ -7321,10 +7321,10 @@
         <v>2.54</v>
       </c>
       <c r="BI26">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BJ26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
         <v>6</v>
@@ -7333,7 +7333,7 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN26">
         <v>6.4</v>
@@ -7345,16 +7345,16 @@
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT26">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU26">
         <v>4.2</v>
@@ -7363,19 +7363,19 @@
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB26" t="s">
         <v>246</v>
@@ -7428,7 +7428,7 @@
         <v>1.25</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q27">
         <v>1.74</v>
@@ -7506,13 +7506,13 @@
         <v>14</v>
       </c>
       <c r="AP27">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AQ27">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS27">
         <v>20</v>
@@ -7524,16 +7524,16 @@
         <v>7.2</v>
       </c>
       <c r="AV27">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AW27">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX27">
         <v>5.5</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ27">
         <v>4.9</v>
@@ -7569,13 +7569,13 @@
         <v>10</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BN27">
         <v>7.8</v>
@@ -7587,13 +7587,13 @@
         <v>32</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT27">
         <v>5.3</v>
@@ -7605,19 +7605,19 @@
         <v>15.5</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX27">
         <v>28</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ27">
         <v>23</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB27" t="s">
         <v>246</v>
@@ -7640,22 +7640,22 @@
         <v>218</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7664,22 +7664,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="O28">
         <v>1.07</v>
       </c>
       <c r="P28">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7688,10 +7688,10 @@
         <v>1.11</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7751,55 +7751,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
         <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7888,7 +7888,7 @@
         <v>4.5</v>
       </c>
       <c r="H29">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I29">
         <v>1.87</v>
@@ -7897,10 +7897,10 @@
         <v>4.2</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M29">
         <v>1.02</v>
@@ -7918,10 +7918,10 @@
         <v>1.52</v>
       </c>
       <c r="R29">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S29">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T29">
         <v>1.56</v>
@@ -7990,19 +7990,19 @@
         <v>7.8</v>
       </c>
       <c r="AP29">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ29">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS29">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT29">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AU29">
         <v>9.6</v>
@@ -8011,37 +8011,37 @@
         <v>9.4</v>
       </c>
       <c r="AW29">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX29">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY29">
         <v>15.5</v>
       </c>
       <c r="AZ29">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA29">
         <v>21</v>
       </c>
       <c r="BB29">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC29">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD29">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE29">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF29">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="BG29">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="BH29">
         <v>5.2</v>
@@ -8133,7 +8133,7 @@
         <v>2.5</v>
       </c>
       <c r="I30">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J30">
         <v>3.6</v>
@@ -8142,7 +8142,7 @@
         <v>4.8</v>
       </c>
       <c r="L30">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M30">
         <v>1.02</v>
@@ -8166,13 +8166,13 @@
         <v>2.02</v>
       </c>
       <c r="T30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
         <v>1.59</v>
@@ -8369,7 +8369,7 @@
         <v>1.67</v>
       </c>
       <c r="G31">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H31">
         <v>4.3</v>
@@ -8381,7 +8381,7 @@
         <v>4.6</v>
       </c>
       <c r="K31">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L31">
         <v>1.19</v>
@@ -8417,7 +8417,7 @@
         <v>1.25</v>
       </c>
       <c r="W31">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X31">
         <v>44</v>
@@ -8531,7 +8531,7 @@
         <v>5.4</v>
       </c>
       <c r="BI31">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BJ31">
         <v>8.800000000000001</v>
@@ -8611,7 +8611,7 @@
         <v>1.8</v>
       </c>
       <c r="G32">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H32">
         <v>3.55</v>
@@ -8644,7 +8644,7 @@
         <v>1.33</v>
       </c>
       <c r="R32">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S32">
         <v>1.79</v>
@@ -8716,7 +8716,7 @@
         <v>17.5</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ32">
         <v>19</v>
@@ -8725,7 +8725,7 @@
         <v>24</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32">
         <v>18</v>
@@ -8770,64 +8770,64 @@
         <v>14</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BI32">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM32">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO32">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ32">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS32">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU32">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW32">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY32">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="CB32" t="s">
         <v>246</v>
@@ -8859,7 +8859,7 @@
         <v>2.24</v>
       </c>
       <c r="I33">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J33">
         <v>3.95</v>
@@ -8889,16 +8889,16 @@
         <v>1.7</v>
       </c>
       <c r="S33">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T33">
         <v>1.47</v>
       </c>
       <c r="U33">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V33">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W33">
         <v>1.47</v>
@@ -8907,7 +8907,7 @@
         <v>36</v>
       </c>
       <c r="Y33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z33">
         <v>25</v>
@@ -8919,7 +8919,7 @@
         <v>24</v>
       </c>
       <c r="AC33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD33">
         <v>15</v>
@@ -8955,7 +8955,7 @@
         <v>18.5</v>
       </c>
       <c r="AO33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP33">
         <v>21</v>
@@ -8967,7 +8967,7 @@
         <v>17</v>
       </c>
       <c r="AS33">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT33">
         <v>17</v>
@@ -8991,10 +8991,10 @@
         <v>10.5</v>
       </c>
       <c r="BA33">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB33">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC33">
         <v>19.5</v>
@@ -9003,7 +9003,7 @@
         <v>21</v>
       </c>
       <c r="BE33">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF33">
         <v>11</v>
@@ -9021,13 +9021,13 @@
         <v>8.6</v>
       </c>
       <c r="BK33">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN33">
         <v>7</v>
@@ -9039,16 +9039,16 @@
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU33">
         <v>4.5</v>
@@ -9057,19 +9057,19 @@
         <v>15.5</v>
       </c>
       <c r="BW33">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ33">
         <v>14</v>
       </c>
       <c r="CA33">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB33" t="s">
         <v>246</v>
@@ -9101,7 +9101,7 @@
         <v>2</v>
       </c>
       <c r="I34">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J34">
         <v>3.9</v>
@@ -9122,7 +9122,7 @@
         <v>1.17</v>
       </c>
       <c r="P34">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
         <v>1.58</v>
@@ -9134,13 +9134,13 @@
         <v>2.38</v>
       </c>
       <c r="T34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U34">
         <v>2.52</v>
       </c>
       <c r="V34">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W34">
         <v>1.36</v>
@@ -9263,31 +9263,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN34">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO34">
         <v>5.6</v>
       </c>
       <c r="BP34">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BQ34">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR34">
         <v>34</v>
       </c>
       <c r="BS34">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BT34">
         <v>6.2</v>
@@ -9299,19 +9299,19 @@
         <v>16</v>
       </c>
       <c r="BW34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY34">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ34">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB34" t="s">
         <v>246</v>
@@ -9334,7 +9334,7 @@
         <v>225</v>
       </c>
       <c r="F35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G35">
         <v>1000</v>
@@ -9346,7 +9346,7 @@
         <v>1000</v>
       </c>
       <c r="J35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9382,7 +9382,7 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35">
         <v>1.01</v>
@@ -9591,7 +9591,7 @@
         <v>4</v>
       </c>
       <c r="K36">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L36">
         <v>1.22</v>
@@ -9618,7 +9618,7 @@
         <v>2.18</v>
       </c>
       <c r="T36">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="U36">
         <v>2.8</v>
@@ -9642,7 +9642,7 @@
         <v>44</v>
       </c>
       <c r="AB36">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC36">
         <v>12.5</v>
@@ -9684,7 +9684,7 @@
         <v>13.5</v>
       </c>
       <c r="AP36">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ36">
         <v>14</v>
@@ -9693,7 +9693,7 @@
         <v>16.5</v>
       </c>
       <c r="AS36">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT36">
         <v>14.5</v>
@@ -9720,7 +9720,7 @@
         <v>20</v>
       </c>
       <c r="BB36">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC36">
         <v>19</v>
@@ -9729,7 +9729,7 @@
         <v>21</v>
       </c>
       <c r="BE36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF36">
         <v>10</v>
@@ -9818,40 +9818,40 @@
         <v>227</v>
       </c>
       <c r="F37">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G37">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H37">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I37">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="J37">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K37">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L37">
         <v>1.33</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="Q37">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="R37">
         <v>1.36</v>
@@ -9860,76 +9860,76 @@
         <v>3.5</v>
       </c>
       <c r="T37">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="U37">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V37">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W37">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z37">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA37">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD37">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH37">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM37">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO37">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR37">
         <v>1.01</v>
@@ -9938,34 +9938,34 @@
         <v>1.01</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA37">
         <v>1.01</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD37">
         <v>1.01</v>
@@ -9974,7 +9974,7 @@
         <v>1.01</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG37">
         <v>1.01</v>
@@ -10078,7 +10078,7 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M38">
         <v>1.04</v>
@@ -10111,7 +10111,7 @@
         <v>1.16</v>
       </c>
       <c r="W38">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X38">
         <v>24</v>
@@ -10123,7 +10123,7 @@
         <v>60</v>
       </c>
       <c r="AA38">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
         <v>10.5</v>
@@ -10147,7 +10147,7 @@
         <v>21</v>
       </c>
       <c r="AI38">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ38">
         <v>17.5</v>
@@ -10174,10 +10174,10 @@
         <v>20</v>
       </c>
       <c r="AR38">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AS38">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT38">
         <v>8.800000000000001</v>
@@ -10189,7 +10189,7 @@
         <v>19</v>
       </c>
       <c r="AW38">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX38">
         <v>9</v>
@@ -10201,7 +10201,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB38">
         <v>12</v>
@@ -10210,22 +10210,22 @@
         <v>12</v>
       </c>
       <c r="BD38">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BE38">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF38">
         <v>5.9</v>
       </c>
       <c r="BG38">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH38">
         <v>4.1</v>
       </c>
       <c r="BI38">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ38">
         <v>10.5</v>
@@ -10237,7 +10237,7 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN38">
         <v>4.3</v>
@@ -10255,19 +10255,19 @@
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT38">
         <v>10</v>
       </c>
       <c r="BU38">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX38">
         <v>1000</v>
@@ -10276,7 +10276,7 @@
         <v>11</v>
       </c>
       <c r="BZ38">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA38">
         <v>7.2</v>
@@ -10302,160 +10302,160 @@
         <v>229</v>
       </c>
       <c r="F39">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="G39">
-        <v>990</v>
+        <v>1.72</v>
       </c>
       <c r="H39">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="I39">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="J39">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K39">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>3.7</v>
       </c>
       <c r="O39">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P39">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q39">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="R39">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>2.64</v>
       </c>
       <c r="T39">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V39">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
         <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
         <v>1.01</v>
@@ -10464,58 +10464,58 @@
         <v>1.01</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI39">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK39">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO39">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ39">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS39">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU39">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW39">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY39">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ39">
         <v>0</v>
@@ -10544,22 +10544,22 @@
         <v>230</v>
       </c>
       <c r="F40">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G40">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H40">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I40">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J40">
         <v>3.4</v>
       </c>
       <c r="K40">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L40">
         <v>1.42</v>
@@ -10571,10 +10571,10 @@
         <v>3.7</v>
       </c>
       <c r="O40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P40">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q40">
         <v>2.06</v>
@@ -10583,19 +10583,19 @@
         <v>1.35</v>
       </c>
       <c r="S40">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T40">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U40">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
         <v>1.37</v>
       </c>
       <c r="W40">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X40">
         <v>14.5</v>
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="AC40">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD40">
         <v>18</v>
@@ -10622,7 +10622,7 @@
         <v>50</v>
       </c>
       <c r="AF40">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG40">
         <v>11.5</v>
@@ -10643,7 +10643,7 @@
         <v>44</v>
       </c>
       <c r="AM40">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN40">
         <v>24</v>
@@ -10655,7 +10655,7 @@
         <v>12</v>
       </c>
       <c r="AQ40">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR40">
         <v>22</v>
@@ -10670,7 +10670,7 @@
         <v>6.8</v>
       </c>
       <c r="AV40">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW40">
         <v>27</v>
@@ -10688,7 +10688,7 @@
         <v>46</v>
       </c>
       <c r="BB40">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BC40">
         <v>22</v>
@@ -10697,7 +10697,7 @@
         <v>34</v>
       </c>
       <c r="BE40">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF40">
         <v>17.5</v>
@@ -10709,7 +10709,7 @@
         <v>3.9</v>
       </c>
       <c r="BI40">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ40">
         <v>11</v>
@@ -10721,10 +10721,10 @@
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN40">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO40">
         <v>3.95</v>
@@ -10733,13 +10733,13 @@
         <v>21</v>
       </c>
       <c r="BQ40">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR40">
         <v>38</v>
       </c>
       <c r="BS40">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT40">
         <v>8</v>
@@ -10751,19 +10751,19 @@
         <v>34</v>
       </c>
       <c r="BW40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX40">
         <v>48</v>
       </c>
       <c r="BY40">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ40">
         <v>34</v>
       </c>
       <c r="CA40">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB40" t="s">
         <v>246</v>
@@ -10798,7 +10798,7 @@
         <v>990</v>
       </c>
       <c r="J41">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K41">
         <v>950</v>
@@ -10810,7 +10810,7 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O41">
         <v>1.01</v>
@@ -10819,13 +10819,13 @@
         <v>1.24</v>
       </c>
       <c r="Q41">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="R41">
         <v>1.12</v>
       </c>
       <c r="S41">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="T41">
         <v>1.11</v>
@@ -10834,7 +10834,7 @@
         <v>1.11</v>
       </c>
       <c r="V41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W41">
         <v>1.01</v>
@@ -11034,7 +11034,7 @@
         <v>2.64</v>
       </c>
       <c r="H42">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I42">
         <v>2.96</v>
@@ -11046,7 +11046,7 @@
         <v>3.65</v>
       </c>
       <c r="L42">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M42">
         <v>1.06</v>
@@ -11055,7 +11055,7 @@
         <v>4.2</v>
       </c>
       <c r="O42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P42">
         <v>2.06</v>
@@ -11067,13 +11067,13 @@
         <v>1.42</v>
       </c>
       <c r="S42">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T42">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U42">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
         <v>1.51</v>
@@ -11091,7 +11091,7 @@
         <v>19.5</v>
       </c>
       <c r="AA42">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB42">
         <v>12</v>
@@ -11100,19 +11100,19 @@
         <v>8</v>
       </c>
       <c r="AD42">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE42">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF42">
         <v>17.5</v>
       </c>
       <c r="AG42">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH42">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI42">
         <v>42</v>
@@ -11121,13 +11121,13 @@
         <v>38</v>
       </c>
       <c r="AK42">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL42">
         <v>38</v>
       </c>
       <c r="AM42">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN42">
         <v>21</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="AP42">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ42">
         <v>12</v>
@@ -11145,16 +11145,16 @@
         <v>18</v>
       </c>
       <c r="AS42">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT42">
         <v>11</v>
       </c>
       <c r="AU42">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV42">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW42">
         <v>28</v>
@@ -11181,16 +11181,16 @@
         <v>34</v>
       </c>
       <c r="BE42">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF42">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG42">
         <v>23</v>
       </c>
       <c r="BH42">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BI42">
         <v>2.86</v>
@@ -11199,7 +11199,7 @@
         <v>9.6</v>
       </c>
       <c r="BK42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11217,13 +11217,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ42">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR42">
         <v>32</v>
       </c>
       <c r="BS42">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT42">
         <v>6.4</v>
@@ -11235,19 +11235,19 @@
         <v>23</v>
       </c>
       <c r="BW42">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ42">
         <v>25</v>
       </c>
       <c r="CA42">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB42" t="s">
         <v>246</v>
@@ -11276,10 +11276,10 @@
         <v>2.4</v>
       </c>
       <c r="H43">
+        <v>3.7</v>
+      </c>
+      <c r="I43">
         <v>3.75</v>
-      </c>
-      <c r="I43">
-        <v>3.8</v>
       </c>
       <c r="J43">
         <v>3.15</v>
@@ -11294,7 +11294,7 @@
         <v>1.11</v>
       </c>
       <c r="N43">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O43">
         <v>1.46</v>
@@ -11309,13 +11309,13 @@
         <v>1.25</v>
       </c>
       <c r="S43">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T43">
         <v>2.02</v>
       </c>
       <c r="U43">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V43">
         <v>1.36</v>
@@ -11324,7 +11324,7 @@
         <v>1.71</v>
       </c>
       <c r="X43">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y43">
         <v>11.5</v>
@@ -11351,7 +11351,7 @@
         <v>13.5</v>
       </c>
       <c r="AG43">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH43">
         <v>21</v>
@@ -11363,13 +11363,13 @@
         <v>32</v>
       </c>
       <c r="AK43">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL43">
         <v>55</v>
       </c>
       <c r="AM43">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN43">
         <v>28</v>
@@ -11387,7 +11387,7 @@
         <v>22</v>
       </c>
       <c r="AS43">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT43">
         <v>7.8</v>
@@ -11405,31 +11405,31 @@
         <v>12.5</v>
       </c>
       <c r="AY43">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ43">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA43">
         <v>60</v>
       </c>
       <c r="BB43">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC43">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD43">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE43">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="BF43">
         <v>25</v>
       </c>
       <c r="BG43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH43">
         <v>2.94</v>
@@ -11447,7 +11447,7 @@
         <v>170</v>
       </c>
       <c r="BM43">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BN43">
         <v>5.1</v>
@@ -11512,37 +11512,37 @@
         <v>234</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G44">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H44">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J44">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="K44">
         <v>7.6</v>
       </c>
       <c r="L44">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M44">
         <v>1.04</v>
       </c>
       <c r="N44">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O44">
         <v>1.22</v>
       </c>
       <c r="P44">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q44">
         <v>1.65</v>
@@ -11560,25 +11560,25 @@
         <v>1.67</v>
       </c>
       <c r="V44">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y44">
         <v>9</v>
       </c>
       <c r="Z44">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA44">
         <v>9.199999999999999</v>
       </c>
       <c r="AB44">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AC44">
         <v>16.5</v>
@@ -11587,34 +11587,34 @@
         <v>12</v>
       </c>
       <c r="AE44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF44">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG44">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AH44">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AI44">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AK44">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="AL44">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AM44">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN44">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AO44">
         <v>4.5</v>
@@ -11623,7 +11623,7 @@
         <v>20</v>
       </c>
       <c r="AQ44">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR44">
         <v>6.6</v>
@@ -11632,106 +11632,106 @@
         <v>7.8</v>
       </c>
       <c r="AT44">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AU44">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW44">
         <v>13</v>
       </c>
       <c r="AX44">
+        <v>15.5</v>
+      </c>
+      <c r="AY44">
+        <v>50</v>
+      </c>
+      <c r="AZ44">
+        <v>36</v>
+      </c>
+      <c r="BA44">
+        <v>40</v>
+      </c>
+      <c r="BB44">
+        <v>13</v>
+      </c>
+      <c r="BC44">
+        <v>12.5</v>
+      </c>
+      <c r="BD44">
+        <v>15.5</v>
+      </c>
+      <c r="BE44">
+        <v>14</v>
+      </c>
+      <c r="BF44">
+        <v>12.5</v>
+      </c>
+      <c r="BG44">
+        <v>4.1</v>
+      </c>
+      <c r="BH44">
+        <v>5</v>
+      </c>
+      <c r="BI44">
+        <v>3.3</v>
+      </c>
+      <c r="BJ44">
+        <v>15</v>
+      </c>
+      <c r="BK44">
         <v>10</v>
       </c>
-      <c r="AY44">
-        <v>10</v>
-      </c>
-      <c r="AZ44">
-        <v>9.4</v>
-      </c>
-      <c r="BA44">
-        <v>38</v>
-      </c>
-      <c r="BB44">
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
+        <v>7.2</v>
+      </c>
+      <c r="BN44">
+        <v>21</v>
+      </c>
+      <c r="BO44">
+        <v>5.4</v>
+      </c>
+      <c r="BP44">
+        <v>1000</v>
+      </c>
+      <c r="BQ44">
+        <v>7</v>
+      </c>
+      <c r="BR44">
+        <v>1000</v>
+      </c>
+      <c r="BS44">
+        <v>7</v>
+      </c>
+      <c r="BT44">
+        <v>3.7</v>
+      </c>
+      <c r="BU44">
+        <v>3.15</v>
+      </c>
+      <c r="BV44">
+        <v>7</v>
+      </c>
+      <c r="BW44">
+        <v>5.1</v>
+      </c>
+      <c r="BX44">
+        <v>32</v>
+      </c>
+      <c r="BY44">
+        <v>6</v>
+      </c>
+      <c r="BZ44">
         <v>11</v>
       </c>
-      <c r="BC44">
-        <v>10.5</v>
-      </c>
-      <c r="BD44">
-        <v>10.5</v>
-      </c>
-      <c r="BE44">
-        <v>10.5</v>
-      </c>
-      <c r="BF44">
-        <v>11</v>
-      </c>
-      <c r="BG44">
-        <v>4</v>
-      </c>
-      <c r="BH44">
-        <v>1000</v>
-      </c>
-      <c r="BI44">
-        <v>1.04</v>
-      </c>
-      <c r="BJ44">
-        <v>1000</v>
-      </c>
-      <c r="BK44">
-        <v>1.04</v>
-      </c>
-      <c r="BL44">
-        <v>1000</v>
-      </c>
-      <c r="BM44">
-        <v>1.04</v>
-      </c>
-      <c r="BN44">
-        <v>1000</v>
-      </c>
-      <c r="BO44">
-        <v>1.04</v>
-      </c>
-      <c r="BP44">
-        <v>1000</v>
-      </c>
-      <c r="BQ44">
-        <v>1.04</v>
-      </c>
-      <c r="BR44">
-        <v>1000</v>
-      </c>
-      <c r="BS44">
-        <v>1.04</v>
-      </c>
-      <c r="BT44">
-        <v>1000</v>
-      </c>
-      <c r="BU44">
-        <v>1.04</v>
-      </c>
-      <c r="BV44">
-        <v>1000</v>
-      </c>
-      <c r="BW44">
-        <v>1.04</v>
-      </c>
-      <c r="BX44">
-        <v>1000</v>
-      </c>
-      <c r="BY44">
-        <v>1.04</v>
-      </c>
-      <c r="BZ44">
-        <v>1000</v>
-      </c>
       <c r="CA44">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB44" t="s">
         <v>246</v>
@@ -11862,52 +11862,52 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF45">
         <v>1.01</v>
@@ -11999,7 +11999,7 @@
         <v>1.61</v>
       </c>
       <c r="G46">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H46">
         <v>4.2</v>
@@ -12008,10 +12008,10 @@
         <v>5.5</v>
       </c>
       <c r="J46">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L46">
         <v>1.17</v>
@@ -12023,16 +12023,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O46">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P46">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="Q46">
         <v>1.27</v>
       </c>
       <c r="R46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S46">
         <v>1.69</v>
@@ -12041,10 +12041,10 @@
         <v>1.35</v>
       </c>
       <c r="U46">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="V46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W46">
         <v>2.36</v>
@@ -12056,7 +12056,7 @@
         <v>46</v>
       </c>
       <c r="Z46">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA46">
         <v>110</v>
@@ -12095,7 +12095,7 @@
         <v>24</v>
       </c>
       <c r="AM46">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN46">
         <v>4.7</v>
@@ -12104,16 +12104,16 @@
         <v>24</v>
       </c>
       <c r="AP46">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ46">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR46">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS46">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT46">
         <v>19</v>
@@ -12125,7 +12125,7 @@
         <v>16.5</v>
       </c>
       <c r="AW46">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX46">
         <v>14.5</v>
@@ -12137,7 +12137,7 @@
         <v>12</v>
       </c>
       <c r="BA46">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB46">
         <v>16</v>
@@ -12149,13 +12149,13 @@
         <v>15.5</v>
       </c>
       <c r="BE46">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF46">
         <v>3.9</v>
       </c>
       <c r="BG46">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH46">
         <v>7.2</v>
@@ -12238,175 +12238,175 @@
         <v>237</v>
       </c>
       <c r="F47">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G47">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="H47">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I47">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J47">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K47">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M47">
         <v>1.02</v>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="O47">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P47">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="Q47">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="R47">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S47">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="T47">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U47">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W47">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="X47">
         <v>1000</v>
       </c>
       <c r="Y47">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z47">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA47">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB47">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC47">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD47">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE47">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF47">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG47">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH47">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI47">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ47">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK47">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL47">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM47">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN47">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO47">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS47">
         <v>1.01</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU47">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW47">
         <v>1.01</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA47">
         <v>1.01</v>
       </c>
       <c r="BB47">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE47">
         <v>1.01</v>
       </c>
       <c r="BF47">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG47">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH47">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI47">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ47">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK47">
         <v>1.04</v>
@@ -12418,28 +12418,28 @@
         <v>1.04</v>
       </c>
       <c r="BN47">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO47">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP47">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ47">
         <v>1.04</v>
       </c>
       <c r="BR47">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS47">
         <v>1.04</v>
       </c>
       <c r="BT47">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU47">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV47">
         <v>1000</v>
@@ -12454,7 +12454,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ47">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA47">
         <v>1.04</v>
@@ -12486,16 +12486,16 @@
         <v>1.39</v>
       </c>
       <c r="H48">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I48">
         <v>11</v>
       </c>
       <c r="J48">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K48">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L48">
         <v>1.33</v>
@@ -12507,19 +12507,19 @@
         <v>4.8</v>
       </c>
       <c r="O48">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P48">
         <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R48">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S48">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T48">
         <v>2.02</v>
@@ -12612,7 +12612,7 @@
         <v>5.9</v>
       </c>
       <c r="AX48">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY48">
         <v>8</v>
@@ -12648,16 +12648,16 @@
         <v>3.15</v>
       </c>
       <c r="BJ48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK48">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BN48">
         <v>3.85</v>
@@ -12666,34 +12666,34 @@
         <v>3.35</v>
       </c>
       <c r="BP48">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ48">
         <v>6.6</v>
       </c>
       <c r="BR48">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS48">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT48">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BU48">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV48">
         <v>110</v>
       </c>
       <c r="BW48">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX48">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY48">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BZ48">
         <v>13.5</v>
@@ -12725,7 +12725,7 @@
         <v>2.38</v>
       </c>
       <c r="G49">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H49">
         <v>3.7</v>
@@ -12734,25 +12734,25 @@
         <v>4</v>
       </c>
       <c r="J49">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K49">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L49">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="M49">
         <v>1.15</v>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O49">
         <v>1.63</v>
       </c>
       <c r="P49">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q49">
         <v>2.88</v>
@@ -12764,7 +12764,7 @@
         <v>6.2</v>
       </c>
       <c r="T49">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="U49">
         <v>1.71</v>
@@ -12773,7 +12773,7 @@
         <v>1.33</v>
       </c>
       <c r="W49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X49">
         <v>8.800000000000001</v>
@@ -12785,7 +12785,7 @@
         <v>32</v>
       </c>
       <c r="AA49">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AB49">
         <v>8.199999999999999</v>
@@ -12827,7 +12827,7 @@
         <v>55</v>
       </c>
       <c r="AO49">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP49">
         <v>6.6</v>
@@ -12836,10 +12836,10 @@
         <v>8.4</v>
       </c>
       <c r="AR49">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT49">
         <v>5.9</v>
@@ -12851,7 +12851,7 @@
         <v>15</v>
       </c>
       <c r="AW49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX49">
         <v>11.5</v>
@@ -12860,22 +12860,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ49">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA49">
+        <v>4.6</v>
+      </c>
+      <c r="BB49">
+        <v>4.3</v>
+      </c>
+      <c r="BC49">
+        <v>4.3</v>
+      </c>
+      <c r="BD49">
         <v>4.5</v>
       </c>
-      <c r="BB49">
-        <v>4.2</v>
-      </c>
-      <c r="BC49">
-        <v>4.2</v>
-      </c>
-      <c r="BD49">
-        <v>4.4</v>
-      </c>
       <c r="BE49">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF49">
         <v>4.3</v>
@@ -12964,25 +12964,25 @@
         <v>240</v>
       </c>
       <c r="F50">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G50">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H50">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J50">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K50">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M50">
         <v>1.08</v>
@@ -12991,31 +12991,31 @@
         <v>3.35</v>
       </c>
       <c r="O50">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="P50">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q50">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="R50">
         <v>1.3</v>
       </c>
       <c r="S50">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T50">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U50">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W50">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X50">
         <v>16</v>
@@ -13024,7 +13024,7 @@
         <v>17.5</v>
       </c>
       <c r="Z50">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA50">
         <v>120</v>
@@ -13033,13 +13033,13 @@
         <v>10.5</v>
       </c>
       <c r="AC50">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE50">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF50">
         <v>15</v>
@@ -13054,7 +13054,7 @@
         <v>80</v>
       </c>
       <c r="AJ50">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK50">
         <v>28</v>
@@ -13066,19 +13066,19 @@
         <v>140</v>
       </c>
       <c r="AN50">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO50">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP50">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ50">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR50">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS50">
         <v>4.1</v>
@@ -13096,7 +13096,7 @@
         <v>4</v>
       </c>
       <c r="AX50">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY50">
         <v>7.8</v>
@@ -13108,82 +13108,82 @@
         <v>4</v>
       </c>
       <c r="BB50">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC50">
         <v>16.5</v>
       </c>
       <c r="BD50">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE50">
         <v>4.1</v>
       </c>
       <c r="BF50">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG50">
         <v>4</v>
       </c>
       <c r="BH50">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI50">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ50">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK50">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN50">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO50">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP50">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ50">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR50">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS50">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT50">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU50">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV50">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW50">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX50">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY50">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ50">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA50">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB50" t="s">
         <v>246</v>
@@ -13206,19 +13206,19 @@
         <v>241</v>
       </c>
       <c r="F51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G51">
         <v>990</v>
       </c>
       <c r="H51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I51">
         <v>990</v>
       </c>
       <c r="J51">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K51">
         <v>950</v>
@@ -13230,22 +13230,22 @@
         <v>1.01</v>
       </c>
       <c r="N51">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
         <v>1.02</v>
       </c>
       <c r="P51">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="R51">
         <v>1.18</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="T51">
         <v>1.11</v>
@@ -13257,7 +13257,7 @@
         <v>1.02</v>
       </c>
       <c r="W51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13457,7 +13457,7 @@
         <v>5.2</v>
       </c>
       <c r="I52">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J52">
         <v>3.5</v>
@@ -13466,7 +13466,7 @@
         <v>3.65</v>
       </c>
       <c r="L52">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M52">
         <v>1.1</v>
@@ -13484,7 +13484,7 @@
         <v>2.3</v>
       </c>
       <c r="R52">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S52">
         <v>4.5</v>
@@ -13505,7 +13505,7 @@
         <v>12.5</v>
       </c>
       <c r="Y52">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z52">
         <v>55</v>
@@ -13517,16 +13517,16 @@
         <v>7</v>
       </c>
       <c r="AC52">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD52">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE52">
         <v>130</v>
       </c>
       <c r="AF52">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG52">
         <v>11</v>
@@ -13541,7 +13541,7 @@
         <v>22</v>
       </c>
       <c r="AK52">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL52">
         <v>65</v>
@@ -13550,7 +13550,7 @@
         <v>230</v>
       </c>
       <c r="AN52">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO52">
         <v>200</v>
@@ -13562,10 +13562,10 @@
         <v>11</v>
       </c>
       <c r="AR52">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AS52">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT52">
         <v>5.8</v>
@@ -13574,22 +13574,22 @@
         <v>6.8</v>
       </c>
       <c r="AV52">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW52">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX52">
         <v>7.4</v>
       </c>
       <c r="AY52">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ52">
         <v>21</v>
       </c>
       <c r="BA52">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB52">
         <v>15</v>
@@ -13598,76 +13598,76 @@
         <v>17</v>
       </c>
       <c r="BD52">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE52">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF52">
         <v>13</v>
       </c>
       <c r="BG52">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH52">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI52">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="BJ52">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK52">
-        <v>1.43</v>
+        <v>5.6</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="BN52">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO52">
-        <v>1.43</v>
+        <v>3.3</v>
       </c>
       <c r="BP52">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ52">
-        <v>1.43</v>
+        <v>6</v>
       </c>
       <c r="BR52">
         <v>1000</v>
       </c>
       <c r="BS52">
-        <v>1.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT52">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU52">
-        <v>1.43</v>
+        <v>4.9</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ52">
         <v>1000</v>
       </c>
       <c r="CA52">
-        <v>1.43</v>
+        <v>8</v>
       </c>
       <c r="CB52" t="s">
         <v>246</v>
@@ -13690,220 +13690,220 @@
         <v>243</v>
       </c>
       <c r="F53">
+        <v>1.73</v>
+      </c>
+      <c r="G53">
+        <v>1.85</v>
+      </c>
+      <c r="H53">
+        <v>4.8</v>
+      </c>
+      <c r="I53">
+        <v>5.8</v>
+      </c>
+      <c r="J53">
+        <v>3.55</v>
+      </c>
+      <c r="K53">
+        <v>4.2</v>
+      </c>
+      <c r="L53">
+        <v>1.01</v>
+      </c>
+      <c r="M53">
+        <v>1.07</v>
+      </c>
+      <c r="N53">
+        <v>3.55</v>
+      </c>
+      <c r="O53">
+        <v>1.32</v>
+      </c>
+      <c r="P53">
+        <v>1.85</v>
+      </c>
+      <c r="Q53">
+        <v>1.97</v>
+      </c>
+      <c r="R53">
+        <v>1.33</v>
+      </c>
+      <c r="S53">
+        <v>3.45</v>
+      </c>
+      <c r="T53">
+        <v>1.87</v>
+      </c>
+      <c r="U53">
+        <v>1.94</v>
+      </c>
+      <c r="V53">
+        <v>1.21</v>
+      </c>
+      <c r="W53">
         <v>2.16</v>
       </c>
-      <c r="G53">
-        <v>2.46</v>
-      </c>
-      <c r="H53">
-        <v>3.4</v>
-      </c>
-      <c r="I53">
-        <v>4.1</v>
-      </c>
-      <c r="J53">
-        <v>3.15</v>
-      </c>
-      <c r="K53">
-        <v>3.7</v>
-      </c>
-      <c r="L53">
-        <v>1.45</v>
-      </c>
-      <c r="M53">
-        <v>1.01</v>
-      </c>
-      <c r="N53">
-        <v>2.94</v>
-      </c>
-      <c r="O53">
-        <v>1.02</v>
-      </c>
-      <c r="P53">
-        <v>1.71</v>
-      </c>
-      <c r="Q53">
-        <v>2.12</v>
-      </c>
-      <c r="R53">
-        <v>1.2</v>
-      </c>
-      <c r="S53">
-        <v>2.92</v>
-      </c>
-      <c r="T53">
-        <v>1.11</v>
-      </c>
-      <c r="U53">
-        <v>1.11</v>
-      </c>
-      <c r="V53">
-        <v>1.32</v>
-      </c>
-      <c r="W53">
-        <v>1.68</v>
-      </c>
       <c r="X53">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z53">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA53">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB53">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC53">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF53">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG53">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH53">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI53">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL53">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM53">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP53">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ53">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR53">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS53">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT53">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU53">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV53">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW53">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX53">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY53">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ53">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA53">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB53">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC53">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD53">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE53">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF53">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG53">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH53">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BI53">
         <v>2.58</v>
       </c>
       <c r="BJ53">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK53">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="BN53">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO53">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="BP53">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ53">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="BR53">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS53">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="BT53">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU53">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="BV53">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW53">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="BX53">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY53">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="BZ53">
         <v>0</v>
@@ -13932,10 +13932,10 @@
         <v>244</v>
       </c>
       <c r="F54">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G54">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H54">
         <v>6.2</v>
@@ -13971,10 +13971,10 @@
         <v>1.42</v>
       </c>
       <c r="S54">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T54">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -14034,7 +14034,7 @@
         <v>140</v>
       </c>
       <c r="AN54">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO54">
         <v>130</v>
@@ -14046,16 +14046,16 @@
         <v>19</v>
       </c>
       <c r="AR54">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AS54">
         <v>7.6</v>
       </c>
       <c r="AT54">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU54">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV54">
         <v>21</v>
@@ -14121,7 +14121,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ54">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR54">
         <v>25</v>
@@ -14174,118 +14174,118 @@
         <v>245</v>
       </c>
       <c r="F55">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="G55">
+        <v>2.46</v>
+      </c>
+      <c r="H55">
+        <v>3.4</v>
+      </c>
+      <c r="I55">
+        <v>4.1</v>
+      </c>
+      <c r="J55">
+        <v>3.15</v>
+      </c>
+      <c r="K55">
+        <v>3.7</v>
+      </c>
+      <c r="L55">
+        <v>1.45</v>
+      </c>
+      <c r="M55">
+        <v>1.08</v>
+      </c>
+      <c r="N55">
+        <v>3.05</v>
+      </c>
+      <c r="O55">
+        <v>1.37</v>
+      </c>
+      <c r="P55">
+        <v>1.71</v>
+      </c>
+      <c r="Q55">
+        <v>2.12</v>
+      </c>
+      <c r="R55">
+        <v>1.24</v>
+      </c>
+      <c r="S55">
+        <v>3.65</v>
+      </c>
+      <c r="T55">
         <v>1.84</v>
-      </c>
-      <c r="H55">
-        <v>4.8</v>
-      </c>
-      <c r="I55">
-        <v>5.8</v>
-      </c>
-      <c r="J55">
-        <v>3.55</v>
-      </c>
-      <c r="K55">
-        <v>4.2</v>
-      </c>
-      <c r="L55">
-        <v>1.01</v>
-      </c>
-      <c r="M55">
-        <v>1.07</v>
-      </c>
-      <c r="N55">
-        <v>3.55</v>
-      </c>
-      <c r="O55">
-        <v>1.32</v>
-      </c>
-      <c r="P55">
-        <v>1.85</v>
-      </c>
-      <c r="Q55">
-        <v>1.97</v>
-      </c>
-      <c r="R55">
-        <v>1.33</v>
-      </c>
-      <c r="S55">
-        <v>3.45</v>
-      </c>
-      <c r="T55">
-        <v>1.87</v>
       </c>
       <c r="U55">
         <v>1.94</v>
       </c>
       <c r="V55">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W55">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="X55">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y55">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z55">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA55">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB55">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC55">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD55">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE55">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF55">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG55">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH55">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI55">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ55">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK55">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL55">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM55">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN55">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO55">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP55">
         <v>1.01</v>
       </c>
       <c r="AQ55">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR55">
         <v>1.01</v>
@@ -14300,7 +14300,7 @@
         <v>1.01</v>
       </c>
       <c r="AV55">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW55">
         <v>1.01</v>
@@ -14312,16 +14312,16 @@
         <v>1.01</v>
       </c>
       <c r="AZ55">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA55">
         <v>1.01</v>
       </c>
       <c r="BB55">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC55">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD55">
         <v>1.01</v>
@@ -14330,64 +14330,64 @@
         <v>1.01</v>
       </c>
       <c r="BF55">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG55">
         <v>1.01</v>
       </c>
       <c r="BH55">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI55">
         <v>2.58</v>
       </c>
       <c r="BJ55">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK55">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="BN55">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO55">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="BP55">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ55">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR55">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS55">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT55">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU55">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="BV55">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW55">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX55">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY55">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="BZ55">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-17.xlsx
@@ -376,7 +376,7 @@
     <t>00:00:00</t>
   </si>
   <si>
-    <t>00:30:00</t>
+    <t>00:40:00</t>
   </si>
   <si>
     <t>01:10:00</t>
@@ -385,7 +385,7 @@
     <t>01:30:00</t>
   </si>
   <si>
-    <t>02:30:00</t>
+    <t>02:40:00</t>
   </si>
   <si>
     <t>03:00:00</t>
@@ -787,7 +787,7 @@
     <t>Paysandu</t>
   </si>
   <si>
-    <t>2026-08-16 20:35:58</t>
+    <t>2026-08-16 22:47:13</t>
   </si>
 </sst>
 </file>
@@ -1381,226 +1381,226 @@
         <v>199</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="H2">
+        <v>3.65</v>
+      </c>
+      <c r="I2">
         <v>4</v>
       </c>
-      <c r="I2">
-        <v>4.4</v>
-      </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>1.37</v>
       </c>
       <c r="O2">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="P2">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="Q2">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="T2">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>70</v>
       </c>
       <c r="AN2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AP2">
-        <v>17.5</v>
+        <v>1.05</v>
       </c>
       <c r="AQ2">
-        <v>18</v>
+        <v>1.05</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="AS2">
-        <v>30</v>
+        <v>1.05</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>1.05</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>1.05</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>1.05</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>1.05</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>1.05</v>
       </c>
       <c r="BB2">
-        <v>19</v>
+        <v>1.05</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>1.05</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="BE2">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>8.6</v>
+        <v>1.05</v>
       </c>
       <c r="BG2">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>257</v>
@@ -1623,226 +1623,226 @@
         <v>200</v>
       </c>
       <c r="F3">
-        <v>2.64</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>1.17</v>
       </c>
       <c r="I3">
-        <v>2.9</v>
+        <v>1.19</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>1.15</v>
       </c>
       <c r="Q3">
-        <v>1.86</v>
+        <v>6.8</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
-        <v>3.15</v>
+        <v>40</v>
       </c>
       <c r="T3">
-        <v>1.71</v>
+        <v>4.1</v>
       </c>
       <c r="U3">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>6</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>1.82</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AH3">
-        <v>17</v>
+        <v>340</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>23</v>
+        <v>340</v>
       </c>
       <c r="AP3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>1.78</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AT3">
         <v>11</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
+        <v>16.5</v>
+      </c>
+      <c r="AW3">
+        <v>12</v>
+      </c>
+      <c r="AX3">
         <v>11</v>
       </c>
-      <c r="AW3">
-        <v>24</v>
-      </c>
-      <c r="AX3">
-        <v>16.5</v>
-      </c>
       <c r="AY3">
+        <v>46</v>
+      </c>
+      <c r="AZ3">
         <v>11</v>
       </c>
-      <c r="AZ3">
-        <v>14</v>
-      </c>
       <c r="BA3">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BB3">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BH3">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>257</v>
@@ -1865,226 +1865,226 @@
         <v>201</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>1.29</v>
       </c>
       <c r="I4">
-        <v>3.55</v>
+        <v>1.33</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="O4">
+        <v>3.05</v>
+      </c>
+      <c r="P4">
+        <v>1.04</v>
+      </c>
+      <c r="Q4">
+        <v>20</v>
+      </c>
+      <c r="R4">
+        <v>1.01</v>
+      </c>
+      <c r="S4">
+        <v>110</v>
+      </c>
+      <c r="T4">
+        <v>3.5</v>
+      </c>
+      <c r="U4">
+        <v>1.34</v>
+      </c>
+      <c r="V4">
+        <v>4.2</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
         <v>1.44</v>
       </c>
-      <c r="P4">
-        <v>1.72</v>
-      </c>
-      <c r="Q4">
-        <v>2.32</v>
-      </c>
-      <c r="R4">
-        <v>1.28</v>
-      </c>
-      <c r="S4">
-        <v>4.5</v>
-      </c>
-      <c r="T4">
-        <v>1.93</v>
-      </c>
-      <c r="U4">
-        <v>1.98</v>
-      </c>
-      <c r="V4">
-        <v>1.39</v>
-      </c>
-      <c r="W4">
-        <v>1.67</v>
-      </c>
-      <c r="X4">
+      <c r="Z4">
+        <v>19</v>
+      </c>
+      <c r="AA4">
+        <v>970</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>5.5</v>
+      </c>
+      <c r="AD4">
+        <v>85</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>85</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>1.4</v>
+      </c>
+      <c r="AR4">
         <v>11</v>
       </c>
-      <c r="Y4">
-        <v>10.5</v>
-      </c>
-      <c r="Z4">
-        <v>22</v>
-      </c>
-      <c r="AA4">
-        <v>65</v>
-      </c>
-      <c r="AB4">
-        <v>8.6</v>
-      </c>
-      <c r="AC4">
-        <v>7.2</v>
-      </c>
-      <c r="AD4">
-        <v>15</v>
-      </c>
-      <c r="AE4">
-        <v>46</v>
-      </c>
-      <c r="AF4">
-        <v>15.5</v>
-      </c>
-      <c r="AG4">
+      <c r="AS4">
+        <v>170</v>
+      </c>
+      <c r="AT4">
         <v>11.5</v>
       </c>
-      <c r="AH4">
-        <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>40</v>
-      </c>
-      <c r="AK4">
+      <c r="AU4">
+        <v>5.2</v>
+      </c>
+      <c r="AV4">
+        <v>44</v>
+      </c>
+      <c r="AW4">
+        <v>14</v>
+      </c>
+      <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
+        <v>36</v>
+      </c>
+      <c r="AZ4">
+        <v>14</v>
+      </c>
+      <c r="BA4">
+        <v>11.5</v>
+      </c>
+      <c r="BB4">
+        <v>11.5</v>
+      </c>
+      <c r="BC4">
+        <v>190</v>
+      </c>
+      <c r="BD4">
         <v>32</v>
       </c>
-      <c r="AL4">
-        <v>50</v>
-      </c>
-      <c r="AM4">
-        <v>420</v>
-      </c>
-      <c r="AN4">
-        <v>34</v>
-      </c>
-      <c r="AO4">
-        <v>55</v>
-      </c>
-      <c r="AP4">
-        <v>9.6</v>
-      </c>
-      <c r="AQ4">
-        <v>9.6</v>
-      </c>
-      <c r="AR4">
-        <v>18.5</v>
-      </c>
-      <c r="AS4">
-        <v>42</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>6.8</v>
-      </c>
-      <c r="AV4">
-        <v>13</v>
-      </c>
-      <c r="AW4">
-        <v>38</v>
-      </c>
-      <c r="AX4">
-        <v>13.5</v>
-      </c>
-      <c r="AY4">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4">
-        <v>19</v>
-      </c>
-      <c r="BA4">
-        <v>50</v>
-      </c>
-      <c r="BB4">
-        <v>34</v>
-      </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
-      <c r="BD4">
-        <v>42</v>
-      </c>
       <c r="BE4">
-        <v>100</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>257</v>
@@ -2107,226 +2107,226 @@
         <v>202</v>
       </c>
       <c r="F5">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>1.45</v>
+      </c>
+      <c r="I5">
+        <v>1.46</v>
+      </c>
+      <c r="J5">
+        <v>4.5</v>
+      </c>
+      <c r="K5">
+        <v>4.7</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>5.2</v>
+      </c>
+      <c r="O5">
+        <v>1.23</v>
+      </c>
+      <c r="P5">
+        <v>1.93</v>
+      </c>
+      <c r="Q5">
+        <v>2.04</v>
+      </c>
+      <c r="R5">
+        <v>1.28</v>
+      </c>
+      <c r="S5">
+        <v>4.4</v>
+      </c>
+      <c r="T5">
+        <v>1.77</v>
+      </c>
+      <c r="U5">
+        <v>2.22</v>
+      </c>
+      <c r="V5">
         <v>3.1</v>
       </c>
-      <c r="H5">
-        <v>2.44</v>
-      </c>
-      <c r="I5">
-        <v>2.46</v>
-      </c>
-      <c r="J5">
-        <v>3.7</v>
-      </c>
-      <c r="K5">
-        <v>3.85</v>
-      </c>
-      <c r="L5">
-        <v>1.34</v>
-      </c>
-      <c r="M5">
-        <v>1.05</v>
-      </c>
-      <c r="N5">
-        <v>4.9</v>
-      </c>
-      <c r="O5">
-        <v>1.24</v>
-      </c>
-      <c r="P5">
-        <v>2.32</v>
-      </c>
-      <c r="Q5">
-        <v>1.73</v>
-      </c>
-      <c r="R5">
-        <v>1.51</v>
-      </c>
-      <c r="S5">
-        <v>2.88</v>
-      </c>
-      <c r="T5">
-        <v>1.61</v>
-      </c>
-      <c r="U5">
-        <v>2.54</v>
-      </c>
-      <c r="V5">
-        <v>1.68</v>
-      </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>5.4</v>
+      </c>
+      <c r="Z5">
+        <v>6.2</v>
+      </c>
+      <c r="AA5">
+        <v>15</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>6.6</v>
+      </c>
+      <c r="AD5">
+        <v>7.6</v>
+      </c>
+      <c r="AE5">
+        <v>18.5</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>17.5</v>
+      </c>
+      <c r="AH5">
         <v>19.5</v>
       </c>
-      <c r="Y5">
+      <c r="AI5">
+        <v>50</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>95</v>
+      </c>
+      <c r="AL5">
+        <v>95</v>
+      </c>
+      <c r="AM5">
+        <v>240</v>
+      </c>
+      <c r="AN5">
+        <v>210</v>
+      </c>
+      <c r="AO5">
+        <v>21</v>
+      </c>
+      <c r="AP5">
+        <v>22</v>
+      </c>
+      <c r="AQ5">
+        <v>5.1</v>
+      </c>
+      <c r="AR5">
+        <v>5.9</v>
+      </c>
+      <c r="AS5">
         <v>13.5</v>
       </c>
-      <c r="Z5">
+      <c r="AT5">
+        <v>22</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>7</v>
+      </c>
+      <c r="AW5">
+        <v>16.5</v>
+      </c>
+      <c r="AX5">
+        <v>22</v>
+      </c>
+      <c r="AY5">
+        <v>16</v>
+      </c>
+      <c r="AZ5">
         <v>17.5</v>
       </c>
-      <c r="AA5">
-        <v>34</v>
-      </c>
-      <c r="AB5">
-        <v>15.5</v>
-      </c>
-      <c r="AC5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD5">
-        <v>11.5</v>
-      </c>
-      <c r="AE5">
-        <v>23</v>
-      </c>
-      <c r="AF5">
-        <v>23</v>
-      </c>
-      <c r="AG5">
-        <v>13</v>
-      </c>
-      <c r="AH5">
-        <v>15</v>
-      </c>
-      <c r="AI5">
-        <v>32</v>
-      </c>
-      <c r="AJ5">
-        <v>55</v>
-      </c>
-      <c r="AK5">
-        <v>30</v>
-      </c>
-      <c r="AL5">
-        <v>36</v>
-      </c>
-      <c r="AM5">
+      <c r="BA5">
+        <v>42</v>
+      </c>
+      <c r="BB5">
+        <v>22</v>
+      </c>
+      <c r="BC5">
         <v>65</v>
       </c>
-      <c r="AN5">
-        <v>23</v>
-      </c>
-      <c r="AO5">
-        <v>15.5</v>
-      </c>
-      <c r="AP5">
-        <v>18</v>
-      </c>
-      <c r="AQ5">
-        <v>12.5</v>
-      </c>
-      <c r="AR5">
-        <v>16</v>
-      </c>
-      <c r="AS5">
-        <v>30</v>
-      </c>
-      <c r="AT5">
-        <v>14.5</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>10.5</v>
-      </c>
-      <c r="AW5">
-        <v>21</v>
-      </c>
-      <c r="AX5">
-        <v>21</v>
-      </c>
-      <c r="AY5">
-        <v>12</v>
-      </c>
-      <c r="AZ5">
-        <v>14</v>
-      </c>
-      <c r="BA5">
-        <v>28</v>
-      </c>
-      <c r="BB5">
-        <v>44</v>
-      </c>
-      <c r="BC5">
-        <v>27</v>
-      </c>
       <c r="BD5">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="BF5">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="BG5">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BH5">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>257</v>
@@ -2349,178 +2349,178 @@
         <v>203</v>
       </c>
       <c r="F6">
+        <v>5.7</v>
+      </c>
+      <c r="G6">
         <v>5.8</v>
       </c>
-      <c r="G6">
-        <v>6.2</v>
-      </c>
       <c r="H6">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="I6">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>2.38</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="O6">
+        <v>1.48</v>
+      </c>
+      <c r="P6">
+        <v>1.65</v>
+      </c>
+      <c r="Q6">
+        <v>2.5</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>5.1</v>
+      </c>
+      <c r="T6">
+        <v>2.3</v>
+      </c>
+      <c r="U6">
+        <v>1.67</v>
+      </c>
+      <c r="V6">
+        <v>2.3</v>
+      </c>
+      <c r="W6">
         <v>1.2</v>
       </c>
-      <c r="P6">
-        <v>2.58</v>
-      </c>
-      <c r="Q6">
-        <v>1.61</v>
-      </c>
-      <c r="R6">
-        <v>1.62</v>
-      </c>
-      <c r="S6">
-        <v>2.56</v>
-      </c>
-      <c r="T6">
-        <v>1.72</v>
-      </c>
-      <c r="U6">
-        <v>2.3</v>
-      </c>
-      <c r="V6">
-        <v>2.62</v>
-      </c>
-      <c r="W6">
-        <v>1.19</v>
-      </c>
       <c r="X6">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Y6">
+        <v>6.6</v>
+      </c>
+      <c r="Z6">
+        <v>8.6</v>
+      </c>
+      <c r="AA6">
+        <v>17.5</v>
+      </c>
+      <c r="AB6">
+        <v>14.5</v>
+      </c>
+      <c r="AC6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6">
         <v>11.5</v>
       </c>
-      <c r="Z6">
-        <v>11</v>
-      </c>
-      <c r="AA6">
-        <v>15.5</v>
-      </c>
-      <c r="AB6">
+      <c r="AE6">
+        <v>24</v>
+      </c>
+      <c r="AF6">
+        <v>40</v>
+      </c>
+      <c r="AG6">
+        <v>24</v>
+      </c>
+      <c r="AH6">
         <v>29</v>
       </c>
-      <c r="AC6">
-        <v>11</v>
-      </c>
-      <c r="AD6">
-        <v>10</v>
-      </c>
-      <c r="AE6">
-        <v>15</v>
-      </c>
-      <c r="AF6">
-        <v>55</v>
-      </c>
-      <c r="AG6">
-        <v>22</v>
-      </c>
-      <c r="AH6">
-        <v>20</v>
-      </c>
       <c r="AI6">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
         <v>160</v>
       </c>
       <c r="AK6">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM6">
+        <v>250</v>
+      </c>
+      <c r="AN6">
+        <v>190</v>
+      </c>
+      <c r="AO6">
+        <v>16</v>
+      </c>
+      <c r="AP6">
+        <v>9.6</v>
+      </c>
+      <c r="AQ6">
+        <v>6</v>
+      </c>
+      <c r="AR6">
+        <v>8</v>
+      </c>
+      <c r="AS6">
+        <v>15.5</v>
+      </c>
+      <c r="AT6">
+        <v>13</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>10</v>
+      </c>
+      <c r="AW6">
+        <v>20</v>
+      </c>
+      <c r="AX6">
+        <v>34</v>
+      </c>
+      <c r="AY6">
+        <v>21</v>
+      </c>
+      <c r="AZ6">
+        <v>26</v>
+      </c>
+      <c r="BA6">
+        <v>50</v>
+      </c>
+      <c r="BB6">
+        <v>120</v>
+      </c>
+      <c r="BC6">
         <v>85</v>
       </c>
-      <c r="AN6">
-        <v>65</v>
-      </c>
-      <c r="AO6">
-        <v>6.6</v>
-      </c>
-      <c r="AP6">
+      <c r="BD6">
+        <v>100</v>
+      </c>
+      <c r="BE6">
+        <v>180</v>
+      </c>
+      <c r="BF6">
+        <v>130</v>
+      </c>
+      <c r="BG6">
+        <v>14</v>
+      </c>
+      <c r="BH6">
+        <v>1.75</v>
+      </c>
+      <c r="BI6">
+        <v>1.7</v>
+      </c>
+      <c r="BJ6">
+        <v>32</v>
+      </c>
+      <c r="BK6">
         <v>21</v>
-      </c>
-      <c r="AQ6">
-        <v>10</v>
-      </c>
-      <c r="AR6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS6">
-        <v>14</v>
-      </c>
-      <c r="AT6">
-        <v>24</v>
-      </c>
-      <c r="AU6">
-        <v>10</v>
-      </c>
-      <c r="AV6">
-        <v>9</v>
-      </c>
-      <c r="AW6">
-        <v>13.5</v>
-      </c>
-      <c r="AX6">
-        <v>46</v>
-      </c>
-      <c r="AY6">
-        <v>19.5</v>
-      </c>
-      <c r="AZ6">
-        <v>18</v>
-      </c>
-      <c r="BA6">
-        <v>24</v>
-      </c>
-      <c r="BB6">
-        <v>15</v>
-      </c>
-      <c r="BC6">
-        <v>55</v>
-      </c>
-      <c r="BD6">
-        <v>44</v>
-      </c>
-      <c r="BE6">
-        <v>14</v>
-      </c>
-      <c r="BF6">
-        <v>48</v>
-      </c>
-      <c r="BG6">
-        <v>6.2</v>
-      </c>
-      <c r="BH6">
-        <v>4.3</v>
-      </c>
-      <c r="BI6">
-        <v>3.95</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2529,46 +2529,46 @@
         <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BP6">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="BQ6">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BU6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV6">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BX6">
+        <v>250</v>
+      </c>
+      <c r="BY6">
+        <v>20</v>
+      </c>
+      <c r="BZ6">
+        <v>300</v>
+      </c>
+      <c r="CA6">
         <v>22</v>
-      </c>
-      <c r="BY6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ6">
-        <v>14</v>
-      </c>
-      <c r="CA6">
-        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>257</v>
@@ -2594,223 +2594,223 @@
         <v>1.26</v>
       </c>
       <c r="G7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="K7">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O7">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="P7">
-        <v>2.68</v>
+        <v>5.6</v>
       </c>
       <c r="Q7">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="R7">
-        <v>1.7</v>
+        <v>2.76</v>
       </c>
       <c r="S7">
-        <v>2.22</v>
+        <v>1.53</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="U7">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="X7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>180</v>
       </c>
       <c r="Z7">
-        <v>140</v>
+        <v>820</v>
       </c>
       <c r="AA7">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AC7">
+        <v>990</v>
+      </c>
+      <c r="AD7">
+        <v>990</v>
+      </c>
+      <c r="AE7">
+        <v>400</v>
+      </c>
+      <c r="AF7">
         <v>17</v>
       </c>
-      <c r="AD7">
-        <v>950</v>
-      </c>
-      <c r="AE7">
-        <v>220</v>
-      </c>
-      <c r="AF7">
-        <v>10</v>
-      </c>
       <c r="AG7">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>990</v>
       </c>
       <c r="AI7">
         <v>160</v>
       </c>
       <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>26</v>
+      </c>
+      <c r="AM7">
+        <v>120</v>
+      </c>
+      <c r="AN7">
+        <v>2.74</v>
+      </c>
+      <c r="AO7">
+        <v>150</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>2.98</v>
+      </c>
+      <c r="AR7">
+        <v>7.6</v>
+      </c>
+      <c r="AS7">
+        <v>3</v>
+      </c>
+      <c r="AT7">
+        <v>2.76</v>
+      </c>
+      <c r="AU7">
+        <v>2.74</v>
+      </c>
+      <c r="AV7">
+        <v>2.92</v>
+      </c>
+      <c r="AW7">
+        <v>3</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>2.54</v>
+      </c>
+      <c r="AZ7">
+        <v>2.76</v>
+      </c>
+      <c r="BA7">
+        <v>50</v>
+      </c>
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BC7">
+        <v>3</v>
+      </c>
+      <c r="BD7">
+        <v>2.72</v>
+      </c>
+      <c r="BE7">
+        <v>2.94</v>
+      </c>
+      <c r="BF7">
+        <v>2.16</v>
+      </c>
+      <c r="BG7">
+        <v>2.98</v>
+      </c>
+      <c r="BH7">
+        <v>6.4</v>
+      </c>
+      <c r="BI7">
+        <v>4.7</v>
+      </c>
+      <c r="BJ7">
         <v>11.5</v>
       </c>
-      <c r="AK7">
+      <c r="BK7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL7">
+        <v>960</v>
+      </c>
+      <c r="BM7">
+        <v>6.4</v>
+      </c>
+      <c r="BN7">
+        <v>4.6</v>
+      </c>
+      <c r="BO7">
+        <v>3.8</v>
+      </c>
+      <c r="BP7">
+        <v>8.6</v>
+      </c>
+      <c r="BQ7">
+        <v>6.2</v>
+      </c>
+      <c r="BR7">
+        <v>22</v>
+      </c>
+      <c r="BS7">
         <v>15.5</v>
       </c>
-      <c r="AL7">
-        <v>40</v>
-      </c>
-      <c r="AM7">
-        <v>170</v>
-      </c>
-      <c r="AN7">
-        <v>4.2</v>
-      </c>
-      <c r="AO7">
-        <v>260</v>
-      </c>
-      <c r="AP7">
-        <v>5.7</v>
-      </c>
-      <c r="AQ7">
-        <v>27</v>
-      </c>
-      <c r="AR7">
-        <v>6.4</v>
-      </c>
-      <c r="AS7">
-        <v>6.8</v>
-      </c>
-      <c r="AT7">
-        <v>9.4</v>
-      </c>
-      <c r="AU7">
-        <v>12.5</v>
-      </c>
-      <c r="AV7">
+      <c r="BT7">
+        <v>14</v>
+      </c>
+      <c r="BU7">
+        <v>10</v>
+      </c>
+      <c r="BV7">
+        <v>65</v>
+      </c>
+      <c r="BW7">
         <v>6</v>
       </c>
-      <c r="AW7">
+      <c r="BX7">
+        <v>940</v>
+      </c>
+      <c r="BY7">
+        <v>6</v>
+      </c>
+      <c r="BZ7">
+        <v>7.2</v>
+      </c>
+      <c r="CA7">
         <v>6.6</v>
-      </c>
-      <c r="AX7">
-        <v>7.6</v>
-      </c>
-      <c r="AY7">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7">
-        <v>5.7</v>
-      </c>
-      <c r="BA7">
-        <v>6.6</v>
-      </c>
-      <c r="BB7">
-        <v>8.4</v>
-      </c>
-      <c r="BC7">
-        <v>11</v>
-      </c>
-      <c r="BD7">
-        <v>5.9</v>
-      </c>
-      <c r="BE7">
-        <v>6.6</v>
-      </c>
-      <c r="BF7">
-        <v>3.25</v>
-      </c>
-      <c r="BG7">
-        <v>6.6</v>
-      </c>
-      <c r="BH7">
-        <v>5.2</v>
-      </c>
-      <c r="BI7">
-        <v>3.95</v>
-      </c>
-      <c r="BJ7">
-        <v>13</v>
-      </c>
-      <c r="BK7">
-        <v>4.8</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>7.2</v>
-      </c>
-      <c r="BN7">
-        <v>4.2</v>
-      </c>
-      <c r="BO7">
-        <v>3.2</v>
-      </c>
-      <c r="BP7">
-        <v>7.4</v>
-      </c>
-      <c r="BQ7">
-        <v>5.6</v>
-      </c>
-      <c r="BR7">
-        <v>23</v>
-      </c>
-      <c r="BS7">
-        <v>5.7</v>
-      </c>
-      <c r="BT7">
-        <v>16.5</v>
-      </c>
-      <c r="BU7">
-        <v>5.2</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>7</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>7</v>
-      </c>
-      <c r="BZ7">
-        <v>10.5</v>
-      </c>
-      <c r="CA7">
-        <v>7.2</v>
       </c>
       <c r="CB7" t="s">
         <v>257</v>
@@ -2833,28 +2833,28 @@
         <v>205</v>
       </c>
       <c r="F8">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H8">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.5</v>
@@ -2863,7 +2863,7 @@
         <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
         <v>1.64</v>
@@ -2872,7 +2872,7 @@
         <v>1.59</v>
       </c>
       <c r="S8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
         <v>1.58</v>
@@ -2884,49 +2884,49 @@
         <v>1.98</v>
       </c>
       <c r="W8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
         <v>25</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8">
+        <v>15</v>
+      </c>
+      <c r="AH8">
         <v>15.5</v>
       </c>
-      <c r="AH8">
-        <v>15</v>
-      </c>
       <c r="AI8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL8">
         <v>40</v>
@@ -2938,22 +2938,22 @@
         <v>30</v>
       </c>
       <c r="AO8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU8">
         <v>9</v>
@@ -2962,10 +2962,10 @@
         <v>9.6</v>
       </c>
       <c r="AW8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AY8">
         <v>14</v>
@@ -2977,25 +2977,25 @@
         <v>24</v>
       </c>
       <c r="BB8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BC8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BD8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG8">
         <v>9.199999999999999</v>
       </c>
       <c r="BH8">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
         <v>3.9</v>
@@ -3004,16 +3004,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL8">
         <v>80</v>
       </c>
       <c r="BM8">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BN8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO8">
         <v>6.6</v>
@@ -3022,37 +3022,37 @@
         <v>27</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BT8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW8">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY8">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="s">
         <v>257</v>
@@ -3075,22 +3075,22 @@
         <v>206</v>
       </c>
       <c r="F9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H9">
+        <v>2.32</v>
+      </c>
+      <c r="I9">
         <v>2.38</v>
       </c>
-      <c r="I9">
-        <v>2.42</v>
-      </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
         <v>1.41</v>
@@ -3102,31 +3102,31 @@
         <v>4</v>
       </c>
       <c r="O9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
         <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R9">
         <v>1.39</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
         <v>15</v>
@@ -3144,7 +3144,7 @@
         <v>13.5</v>
       </c>
       <c r="AC9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>11.5</v>
@@ -3165,10 +3165,10 @@
         <v>38</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL9">
         <v>46</v>
@@ -3180,10 +3180,10 @@
         <v>34</v>
       </c>
       <c r="AO9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9">
         <v>10</v>
@@ -3192,13 +3192,13 @@
         <v>14</v>
       </c>
       <c r="AS9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT9">
         <v>12</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV9">
         <v>10</v>
@@ -3213,7 +3213,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
         <v>32</v>
@@ -3225,34 +3225,34 @@
         <v>32</v>
       </c>
       <c r="BD9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH9">
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9">
         <v>9.4</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL9">
         <v>120</v>
       </c>
       <c r="BM9">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="BN9">
         <v>6.4</v>
@@ -3264,37 +3264,37 @@
         <v>25</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR9">
         <v>36</v>
       </c>
       <c r="BS9">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU9">
         <v>4.8</v>
       </c>
       <c r="BV9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BX9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
         <v>26</v>
       </c>
       <c r="CA9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="s">
         <v>257</v>
@@ -3317,7 +3317,7 @@
         <v>207</v>
       </c>
       <c r="F10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
         <v>1.58</v>
@@ -3362,7 +3362,7 @@
         <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V10">
         <v>1.13</v>
@@ -3371,112 +3371,112 @@
         <v>2.7</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
         <v>3.85</v>
@@ -4043,22 +4043,22 @@
         <v>210</v>
       </c>
       <c r="F13">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G13">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H13">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I13">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J13">
         <v>3.85</v>
       </c>
       <c r="K13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.28</v>
@@ -4091,10 +4091,10 @@
         <v>2.64</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X13">
         <v>23</v>
@@ -4112,7 +4112,7 @@
         <v>16.5</v>
       </c>
       <c r="AC13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13">
         <v>13</v>
@@ -4214,7 +4214,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>80</v>
@@ -4288,28 +4288,28 @@
         <v>1.51</v>
       </c>
       <c r="G14">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I14">
         <v>7</v>
       </c>
       <c r="J14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O14">
         <v>1.17</v>
@@ -4318,13 +4318,13 @@
         <v>2.56</v>
       </c>
       <c r="Q14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R14">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T14">
         <v>1.75</v>
@@ -4333,13 +4333,13 @@
         <v>2.22</v>
       </c>
       <c r="V14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
         <v>2.62</v>
       </c>
       <c r="X14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y14">
         <v>32</v>
@@ -4351,7 +4351,7 @@
         <v>160</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC14">
         <v>12.5</v>
@@ -4375,13 +4375,13 @@
         <v>70</v>
       </c>
       <c r="AJ14">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK14">
         <v>17</v>
       </c>
       <c r="AL14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM14">
         <v>90</v>
@@ -4390,7 +4390,7 @@
         <v>6.2</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP14">
         <v>13</v>
@@ -4399,10 +4399,10 @@
         <v>20</v>
       </c>
       <c r="AR14">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS14">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
         <v>9.4</v>
@@ -4414,19 +4414,19 @@
         <v>18.5</v>
       </c>
       <c r="AW14">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX14">
         <v>9.800000000000001</v>
       </c>
       <c r="AY14">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>14</v>
       </c>
       <c r="BA14">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB14">
         <v>12</v>
@@ -4438,19 +4438,19 @@
         <v>20</v>
       </c>
       <c r="BE14">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
         <v>5</v>
       </c>
       <c r="BG14">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI14">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14">
         <v>11</v>
@@ -4459,7 +4459,7 @@
         <v>3.7</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM14">
         <v>5.3</v>
@@ -4468,7 +4468,7 @@
         <v>5.1</v>
       </c>
       <c r="BO14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP14">
         <v>11</v>
@@ -4527,22 +4527,22 @@
         <v>212</v>
       </c>
       <c r="F15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H15">
         <v>1.49</v>
       </c>
       <c r="I15">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J15">
         <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L15">
         <v>1.24</v>
@@ -4569,16 +4569,16 @@
         <v>2.46</v>
       </c>
       <c r="T15">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U15">
         <v>2.14</v>
       </c>
       <c r="V15">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4808,7 +4808,7 @@
         <v>1.32</v>
       </c>
       <c r="S16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T16">
         <v>1.83</v>
@@ -4865,13 +4865,13 @@
         <v>38</v>
       </c>
       <c r="AL16">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AM16">
         <v>580</v>
       </c>
       <c r="AN16">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AO16">
         <v>90</v>
@@ -4880,13 +4880,13 @@
         <v>11</v>
       </c>
       <c r="AQ16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT16">
         <v>7.6</v>
@@ -4898,7 +4898,7 @@
         <v>14</v>
       </c>
       <c r="AW16">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16">
         <v>11</v>
@@ -4910,16 +4910,16 @@
         <v>16</v>
       </c>
       <c r="BA16">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB16">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BE16">
         <v>10.5</v>
@@ -4970,7 +4970,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
@@ -5011,13 +5011,13 @@
         <v>214</v>
       </c>
       <c r="F17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G17">
         <v>4.1</v>
       </c>
       <c r="H17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I17">
         <v>2.36</v>
@@ -5029,7 +5029,7 @@
         <v>3.55</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M17">
         <v>1.1</v>
@@ -5113,10 +5113,10 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO17">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AP17">
         <v>8.199999999999999</v>
@@ -5253,19 +5253,19 @@
         <v>215</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G18">
         <v>990</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I18">
         <v>990</v>
       </c>
       <c r="J18">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5495,67 +5495,67 @@
         <v>216</v>
       </c>
       <c r="F19">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="G19">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="S19">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="T19">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X19">
         <v>950</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA19">
         <v>900</v>
@@ -5564,25 +5564,25 @@
         <v>950</v>
       </c>
       <c r="AC19">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG19">
         <v>950</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ19">
         <v>900</v>
@@ -5606,13 +5606,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ19">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="AR19">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="AS19">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AT19">
         <v>2.5</v>
@@ -5621,40 +5621,40 @@
         <v>4.9</v>
       </c>
       <c r="AV19">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AW19">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AX19">
-        <v>1.34</v>
+        <v>3.65</v>
       </c>
       <c r="AY19">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AZ19">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="BA19">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="BB19">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="BC19">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="BD19">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="BE19">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="BG19">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5740,7 +5740,7 @@
         <v>3.15</v>
       </c>
       <c r="G20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H20">
         <v>2.08</v>
@@ -5782,7 +5782,7 @@
         <v>1.6</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V20">
         <v>1.79</v>
@@ -5803,7 +5803,7 @@
         <v>36</v>
       </c>
       <c r="AB20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC20">
         <v>9.6</v>
@@ -5982,13 +5982,13 @@
         <v>1.69</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J21">
         <v>3.85</v>
@@ -5997,25 +5997,25 @@
         <v>4.4</v>
       </c>
       <c r="L21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M21">
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
         <v>1.25</v>
       </c>
       <c r="P21">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q21">
         <v>1.71</v>
       </c>
       <c r="R21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
         <v>2.8</v>
@@ -6066,7 +6066,7 @@
         <v>19.5</v>
       </c>
       <c r="AI21">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AJ21">
         <v>19.5</v>
@@ -6081,22 +6081,22 @@
         <v>260</v>
       </c>
       <c r="AN21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO21">
         <v>85</v>
       </c>
       <c r="AP21">
+        <v>5.9</v>
+      </c>
+      <c r="AQ21">
         <v>5.8</v>
       </c>
-      <c r="AQ21">
-        <v>5.7</v>
-      </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT21">
         <v>5.8</v>
@@ -6108,7 +6108,7 @@
         <v>9</v>
       </c>
       <c r="AW21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX21">
         <v>5.8</v>
@@ -6117,13 +6117,13 @@
         <v>6.4</v>
       </c>
       <c r="AZ21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC21">
         <v>9</v>
@@ -6132,16 +6132,16 @@
         <v>6.4</v>
       </c>
       <c r="BE21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF21">
         <v>4.4</v>
       </c>
       <c r="BG21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI21">
         <v>2.58</v>
@@ -6150,13 +6150,13 @@
         <v>11</v>
       </c>
       <c r="BK21">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN21">
         <v>4.7</v>
@@ -6168,37 +6168,37 @@
         <v>13</v>
       </c>
       <c r="BQ21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS21">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BT21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU21">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV21">
         <v>46</v>
       </c>
       <c r="BW21">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX21">
         <v>55</v>
       </c>
       <c r="BY21">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BZ21">
         <v>21</v>
       </c>
       <c r="CA21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB21" t="s">
         <v>257</v>
@@ -6221,7 +6221,7 @@
         <v>219</v>
       </c>
       <c r="F22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G22">
         <v>2.06</v>
@@ -6233,7 +6233,7 @@
         <v>5.2</v>
       </c>
       <c r="J22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
         <v>3.65</v>
@@ -6260,10 +6260,10 @@
         <v>1.27</v>
       </c>
       <c r="S22">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T22">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U22">
         <v>1.89</v>
@@ -6332,7 +6332,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR22">
         <v>20</v>
@@ -6463,13 +6463,13 @@
         <v>220</v>
       </c>
       <c r="F23">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G23">
         <v>2.38</v>
       </c>
       <c r="H23">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I23">
         <v>4.2</v>
@@ -6487,13 +6487,13 @@
         <v>1.09</v>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>1.4</v>
       </c>
       <c r="P23">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q23">
         <v>2.16</v>
@@ -6502,7 +6502,7 @@
         <v>1.26</v>
       </c>
       <c r="S23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T23">
         <v>1.89</v>
@@ -6514,7 +6514,7 @@
         <v>1.31</v>
       </c>
       <c r="W23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X23">
         <v>12</v>
@@ -6523,7 +6523,7 @@
         <v>13</v>
       </c>
       <c r="Z23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA23">
         <v>900</v>
@@ -6550,7 +6550,7 @@
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ23">
         <v>32</v>
@@ -6571,16 +6571,16 @@
         <v>140</v>
       </c>
       <c r="AP23">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR23">
         <v>6.6</v>
       </c>
       <c r="AS23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT23">
         <v>4.9</v>
@@ -6589,100 +6589,100 @@
         <v>4.9</v>
       </c>
       <c r="AV23">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX23">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AY23">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
+        <v>7.8</v>
+      </c>
+      <c r="BB23">
+        <v>10.5</v>
+      </c>
+      <c r="BC23">
+        <v>13</v>
+      </c>
+      <c r="BD23">
         <v>7.6</v>
       </c>
-      <c r="BB23">
-        <v>6.6</v>
-      </c>
-      <c r="BC23">
-        <v>6.4</v>
-      </c>
-      <c r="BD23">
-        <v>7.4</v>
-      </c>
       <c r="BE23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BG23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH23">
         <v>3.15</v>
       </c>
       <c r="BI23">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="BJ23">
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BN23">
         <v>5.1</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP23">
         <v>18</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR23">
         <v>36</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BT23">
         <v>7.2</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV23">
         <v>36</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BX23">
         <v>55</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BZ23">
         <v>36</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="CB23" t="s">
         <v>257</v>
@@ -6705,16 +6705,16 @@
         <v>221</v>
       </c>
       <c r="F24">
+        <v>1.43</v>
+      </c>
+      <c r="G24">
         <v>1.44</v>
-      </c>
-      <c r="G24">
-        <v>1.45</v>
       </c>
       <c r="H24">
         <v>8.4</v>
       </c>
       <c r="I24">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>5.3</v>
@@ -6735,7 +6735,7 @@
         <v>1.22</v>
       </c>
       <c r="P24">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q24">
         <v>1.69</v>
@@ -6753,16 +6753,16 @@
         <v>1.96</v>
       </c>
       <c r="V24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X24">
         <v>23</v>
       </c>
       <c r="Y24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z24">
         <v>160</v>
@@ -6774,16 +6774,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD24">
         <v>32</v>
       </c>
       <c r="AE24">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AF24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6792,28 +6792,28 @@
         <v>24</v>
       </c>
       <c r="AI24">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AJ24">
         <v>13</v>
       </c>
       <c r="AK24">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL24">
         <v>32</v>
       </c>
       <c r="AM24">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="AN24">
         <v>6</v>
       </c>
       <c r="AO24">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
         <v>29</v>
@@ -6825,16 +6825,16 @@
         <v>14.5</v>
       </c>
       <c r="AT24">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU24">
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW24">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX24">
         <v>8.199999999999999</v>
@@ -6849,7 +6849,7 @@
         <v>28</v>
       </c>
       <c r="BB24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC24">
         <v>13</v>
@@ -6861,10 +6861,10 @@
         <v>55</v>
       </c>
       <c r="BF24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG24">
-        <v>15.5</v>
+        <v>80</v>
       </c>
       <c r="BH24">
         <v>4.8</v>
@@ -6950,7 +6950,7 @@
         <v>1.76</v>
       </c>
       <c r="G25">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H25">
         <v>4.8</v>
@@ -6989,16 +6989,16 @@
         <v>3.1</v>
       </c>
       <c r="T25">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V25">
         <v>1.22</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X25">
         <v>19.5</v>
@@ -7118,49 +7118,49 @@
         <v>12</v>
       </c>
       <c r="BK25">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BN25">
         <v>5.2</v>
       </c>
       <c r="BO25">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP25">
         <v>14.5</v>
       </c>
       <c r="BQ25">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR25">
         <v>32</v>
       </c>
       <c r="BS25">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT25">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU25">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="BV25">
         <v>55</v>
       </c>
       <c r="BW25">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BX25">
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7207,7 +7207,7 @@
         <v>3.6</v>
       </c>
       <c r="L26">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M26">
         <v>1.08</v>
@@ -7431,7 +7431,7 @@
         <v>224</v>
       </c>
       <c r="F27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G27">
         <v>1.93</v>
@@ -7440,10 +7440,10 @@
         <v>4.8</v>
       </c>
       <c r="I27">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J27">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
         <v>3.65</v>
@@ -7479,7 +7479,7 @@
         <v>1.8</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W27">
         <v>2.06</v>
@@ -7488,7 +7488,7 @@
         <v>12.5</v>
       </c>
       <c r="Y27">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z27">
         <v>40</v>
@@ -7500,7 +7500,7 @@
         <v>7.2</v>
       </c>
       <c r="AC27">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD27">
         <v>24</v>
@@ -7521,7 +7521,7 @@
         <v>240</v>
       </c>
       <c r="AJ27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK27">
         <v>27</v>
@@ -7533,7 +7533,7 @@
         <v>580</v>
       </c>
       <c r="AN27">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO27">
         <v>700</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="AS27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT27">
         <v>6</v>
@@ -7560,7 +7560,7 @@
         <v>18</v>
       </c>
       <c r="AW27">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX27">
         <v>8.800000000000001</v>
@@ -7572,7 +7572,7 @@
         <v>19.5</v>
       </c>
       <c r="BA27">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB27">
         <v>18</v>
@@ -7581,16 +7581,16 @@
         <v>19.5</v>
       </c>
       <c r="BD27">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF27">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7688,19 +7688,19 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L28">
         <v>1.24</v>
       </c>
       <c r="M28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P28">
         <v>3</v>
@@ -7781,10 +7781,10 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ28">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AR28">
         <v>36</v>
@@ -7793,13 +7793,13 @@
         <v>50</v>
       </c>
       <c r="AT28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU28">
         <v>13</v>
       </c>
       <c r="AV28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW28">
         <v>40</v>
@@ -7814,7 +7814,7 @@
         <v>21</v>
       </c>
       <c r="BA28">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BB28">
         <v>10.5</v>
@@ -7826,10 +7826,10 @@
         <v>21</v>
       </c>
       <c r="BE28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF28">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG28">
         <v>40</v>
@@ -7921,28 +7921,28 @@
         <v>3.35</v>
       </c>
       <c r="H29">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I29">
         <v>2.92</v>
       </c>
       <c r="J29">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="K29">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="L29">
         <v>1.55</v>
       </c>
       <c r="M29">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N29">
         <v>2.34</v>
       </c>
       <c r="O29">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P29">
         <v>1.43</v>
@@ -7951,13 +7951,13 @@
         <v>3.15</v>
       </c>
       <c r="R29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U29">
         <v>1.7</v>
@@ -8160,7 +8160,7 @@
         <v>2.36</v>
       </c>
       <c r="G30">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H30">
         <v>2.5</v>
@@ -8172,7 +8172,7 @@
         <v>4</v>
       </c>
       <c r="K30">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L30">
         <v>1.2</v>
@@ -8187,7 +8187,7 @@
         <v>1.14</v>
       </c>
       <c r="P30">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q30">
         <v>1.42</v>
@@ -8199,16 +8199,16 @@
         <v>2.02</v>
       </c>
       <c r="T30">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
         <v>1.53</v>
       </c>
       <c r="W30">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X30">
         <v>42</v>
@@ -8319,10 +8319,10 @@
         <v>10</v>
       </c>
       <c r="BH30">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BI30">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ30">
         <v>9.800000000000001</v>
@@ -8334,7 +8334,7 @@
         <v>70</v>
       </c>
       <c r="BM30">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BN30">
         <v>7.6</v>
@@ -8346,13 +8346,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ30">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BR30">
         <v>26</v>
       </c>
       <c r="BS30">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BT30">
         <v>7.8</v>
@@ -8364,19 +8364,19 @@
         <v>21</v>
       </c>
       <c r="BW30">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BX30">
         <v>27</v>
       </c>
       <c r="BY30">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ30">
         <v>15</v>
       </c>
       <c r="CA30">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="CB30" t="s">
         <v>257</v>
@@ -8402,10 +8402,10 @@
         <v>3.6</v>
       </c>
       <c r="G31">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H31">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I31">
         <v>2.12</v>
@@ -8441,7 +8441,7 @@
         <v>2.88</v>
       </c>
       <c r="T31">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U31">
         <v>2.22</v>
@@ -8450,7 +8450,7 @@
         <v>1.89</v>
       </c>
       <c r="W31">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X31">
         <v>19</v>
@@ -8519,7 +8519,7 @@
         <v>20</v>
       </c>
       <c r="AT31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -8531,25 +8531,25 @@
         <v>16.5</v>
       </c>
       <c r="AX31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY31">
         <v>13.5</v>
       </c>
       <c r="AZ31">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB31">
         <v>6.8</v>
       </c>
       <c r="BC31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE31">
         <v>6.8</v>
@@ -8641,13 +8641,13 @@
         <v>229</v>
       </c>
       <c r="F32">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G32">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H32">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>3.35</v>
@@ -8656,7 +8656,7 @@
         <v>4.4</v>
       </c>
       <c r="K32">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8683,25 +8683,25 @@
         <v>1.79</v>
       </c>
       <c r="T32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X32">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Y32">
         <v>36</v>
       </c>
       <c r="Z32">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AA32">
         <v>65</v>
@@ -8713,7 +8713,7 @@
         <v>14.5</v>
       </c>
       <c r="AD32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE32">
         <v>48</v>
@@ -8725,7 +8725,7 @@
         <v>14</v>
       </c>
       <c r="AH32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI32">
         <v>34</v>
@@ -8749,16 +8749,16 @@
         <v>13</v>
       </c>
       <c r="AP32">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AQ32">
         <v>13</v>
       </c>
       <c r="AR32">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AS32">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AT32">
         <v>19.5</v>
@@ -8794,7 +8794,7 @@
         <v>18</v>
       </c>
       <c r="BE32">
-        <v>27</v>
+        <v>5.9</v>
       </c>
       <c r="BF32">
         <v>6</v>
@@ -8940,10 +8940,10 @@
         <v>32</v>
       </c>
       <c r="Y33">
+        <v>25</v>
+      </c>
+      <c r="Z33">
         <v>15</v>
-      </c>
-      <c r="Z33">
-        <v>16</v>
       </c>
       <c r="AA33">
         <v>25</v>
@@ -8955,7 +8955,7 @@
         <v>11</v>
       </c>
       <c r="AD33">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE33">
         <v>18</v>
@@ -8967,7 +8967,7 @@
         <v>19.5</v>
       </c>
       <c r="AH33">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI33">
         <v>29</v>
@@ -8991,16 +8991,16 @@
         <v>7.8</v>
       </c>
       <c r="AP33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ33">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR33">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS33">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AT33">
         <v>11.5</v>
@@ -9012,37 +9012,37 @@
         <v>8.4</v>
       </c>
       <c r="AW33">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX33">
+        <v>7.4</v>
+      </c>
+      <c r="AY33">
         <v>6.2</v>
       </c>
-      <c r="AY33">
-        <v>5.3</v>
-      </c>
       <c r="AZ33">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BA33">
         <v>19</v>
       </c>
       <c r="BB33">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC33">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD33">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE33">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG33">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH33">
         <v>5.2</v>
@@ -9188,7 +9188,7 @@
         <v>120</v>
       </c>
       <c r="AA34">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB34">
         <v>19.5</v>
@@ -9245,13 +9245,13 @@
         <v>6</v>
       </c>
       <c r="AT34">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU34">
         <v>11</v>
       </c>
       <c r="AV34">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AW34">
         <v>5.8</v>
@@ -9263,19 +9263,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA34">
         <v>5.7</v>
       </c>
       <c r="BB34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC34">
         <v>12</v>
       </c>
       <c r="BD34">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BE34">
         <v>5.8</v>
@@ -9290,13 +9290,13 @@
         <v>5.4</v>
       </c>
       <c r="BI34">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ34">
         <v>8.800000000000001</v>
       </c>
       <c r="BK34">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9326,7 +9326,7 @@
         <v>9</v>
       </c>
       <c r="BU34">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV34">
         <v>1000</v>
@@ -9344,7 +9344,7 @@
         <v>10.5</v>
       </c>
       <c r="CA34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CB34" t="s">
         <v>257</v>
@@ -9370,16 +9370,16 @@
         <v>1.03</v>
       </c>
       <c r="G35">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I35">
         <v>110</v>
       </c>
       <c r="J35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9418,7 +9418,7 @@
         <v>1.02</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9753,7 +9753,7 @@
         <v>13</v>
       </c>
       <c r="BB36">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC36">
         <v>19.5</v>
@@ -9774,7 +9774,7 @@
         <v>4.9</v>
       </c>
       <c r="BI36">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ36">
         <v>8.6</v>
@@ -9851,7 +9851,7 @@
         <v>234</v>
       </c>
       <c r="F37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G37">
         <v>3.75</v>
@@ -9896,7 +9896,7 @@
         <v>1.55</v>
       </c>
       <c r="U37">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V37">
         <v>1.83</v>
@@ -9911,7 +9911,7 @@
         <v>14.5</v>
       </c>
       <c r="Z37">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA37">
         <v>120</v>
@@ -9992,10 +9992,10 @@
         <v>13</v>
       </c>
       <c r="BA37">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BB37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC37">
         <v>16</v>
@@ -10004,13 +10004,13 @@
         <v>30</v>
       </c>
       <c r="BE37">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BF37">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG37">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH37">
         <v>4.7</v>
@@ -10096,10 +10096,10 @@
         <v>1.81</v>
       </c>
       <c r="G38">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H38">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I38">
         <v>4.2</v>
@@ -10108,7 +10108,7 @@
         <v>4.6</v>
       </c>
       <c r="K38">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L38">
         <v>1.16</v>
@@ -10135,7 +10135,7 @@
         <v>1.75</v>
       </c>
       <c r="T38">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U38">
         <v>3.15</v>
@@ -10144,7 +10144,7 @@
         <v>1.32</v>
       </c>
       <c r="W38">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="X38">
         <v>60</v>
@@ -10159,7 +10159,7 @@
         <v>85</v>
       </c>
       <c r="AB38">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC38">
         <v>14.5</v>
@@ -10171,7 +10171,7 @@
         <v>36</v>
       </c>
       <c r="AF38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG38">
         <v>13</v>
@@ -10201,7 +10201,7 @@
         <v>17.5</v>
       </c>
       <c r="AP38">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ38">
         <v>19</v>
@@ -10264,13 +10264,13 @@
         <v>8.4</v>
       </c>
       <c r="BK38">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL38">
         <v>55</v>
       </c>
       <c r="BM38">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN38">
         <v>5.8</v>
@@ -10285,7 +10285,7 @@
         <v>8.6</v>
       </c>
       <c r="BR38">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BS38">
         <v>6.6</v>
@@ -10294,25 +10294,25 @@
         <v>8.6</v>
       </c>
       <c r="BU38">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV38">
         <v>28</v>
       </c>
       <c r="BW38">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX38">
         <v>28</v>
       </c>
       <c r="BY38">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ38">
         <v>9.6</v>
       </c>
       <c r="CA38">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="CB38" t="s">
         <v>257</v>
@@ -10380,7 +10380,7 @@
         <v>1.53</v>
       </c>
       <c r="U39">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V39">
         <v>1.62</v>
@@ -10500,7 +10500,7 @@
         <v>4.9</v>
       </c>
       <c r="BI39">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BJ39">
         <v>8.4</v>
@@ -10589,7 +10589,7 @@
         <v>5.3</v>
       </c>
       <c r="J40">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K40">
         <v>3.95</v>
@@ -10819,7 +10819,7 @@
         <v>238</v>
       </c>
       <c r="F41">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="G41">
         <v>1.57</v>
@@ -10828,7 +10828,7 @@
         <v>6.8</v>
       </c>
       <c r="I41">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J41">
         <v>4.6</v>
@@ -10903,7 +10903,7 @@
         <v>11</v>
       </c>
       <c r="AH41">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI41">
         <v>390</v>
@@ -11061,7 +11061,7 @@
         <v>239</v>
       </c>
       <c r="F42">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G42">
         <v>1.63</v>
@@ -11070,16 +11070,16 @@
         <v>6.2</v>
       </c>
       <c r="I42">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J42">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K42">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L42">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M42">
         <v>1.05</v>
@@ -11094,19 +11094,19 @@
         <v>2.06</v>
       </c>
       <c r="Q42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R42">
         <v>1.42</v>
       </c>
       <c r="S42">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T42">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U42">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V42">
         <v>1.16</v>
@@ -11115,7 +11115,7 @@
         <v>2.58</v>
       </c>
       <c r="X42">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Y42">
         <v>26</v>
@@ -11124,19 +11124,19 @@
         <v>75</v>
       </c>
       <c r="AA42">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AB42">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC42">
         <v>10.5</v>
       </c>
       <c r="AD42">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE42">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF42">
         <v>10.5</v>
@@ -11151,13 +11151,13 @@
         <v>110</v>
       </c>
       <c r="AJ42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK42">
         <v>17</v>
       </c>
       <c r="AL42">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM42">
         <v>580</v>
@@ -11169,67 +11169,67 @@
         <v>140</v>
       </c>
       <c r="AP42">
+        <v>5.8</v>
+      </c>
+      <c r="AQ42">
         <v>6</v>
-      </c>
-      <c r="AQ42">
-        <v>6.6</v>
       </c>
       <c r="AR42">
         <v>19</v>
       </c>
       <c r="AS42">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AT42">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU42">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AV42">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AW42">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX42">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AY42">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AZ42">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA42">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BB42">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC42">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE42">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF42">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG42">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH42">
         <v>4.4</v>
       </c>
       <c r="BI42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ42">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK42">
         <v>3.45</v>
@@ -11238,19 +11238,19 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN42">
         <v>4.8</v>
       </c>
       <c r="BO42">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BP42">
         <v>12</v>
       </c>
       <c r="BQ42">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BR42">
         <v>30</v>
@@ -11268,13 +11268,13 @@
         <v>70</v>
       </c>
       <c r="BW42">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX42">
         <v>75</v>
       </c>
       <c r="BY42">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11306,22 +11306,22 @@
         <v>2.28</v>
       </c>
       <c r="G43">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H43">
         <v>3.65</v>
       </c>
       <c r="I43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J43">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K43">
         <v>3.45</v>
       </c>
       <c r="L43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M43">
         <v>1.08</v>
@@ -11330,31 +11330,31 @@
         <v>3.7</v>
       </c>
       <c r="O43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P43">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q43">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R43">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T43">
         <v>1.79</v>
       </c>
       <c r="U43">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X43">
         <v>16</v>
@@ -11363,19 +11363,19 @@
         <v>13.5</v>
       </c>
       <c r="Z43">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA43">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB43">
         <v>10</v>
       </c>
       <c r="AC43">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD43">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE43">
         <v>50</v>
@@ -11387,10 +11387,10 @@
         <v>11</v>
       </c>
       <c r="AH43">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI43">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ43">
         <v>30</v>
@@ -11402,7 +11402,7 @@
         <v>44</v>
       </c>
       <c r="AM43">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN43">
         <v>24</v>
@@ -11432,7 +11432,7 @@
         <v>13.5</v>
       </c>
       <c r="AW43">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX43">
         <v>13</v>
@@ -11468,7 +11468,7 @@
         <v>3.8</v>
       </c>
       <c r="BI43">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ43">
         <v>11</v>
@@ -11545,19 +11545,19 @@
         <v>241</v>
       </c>
       <c r="F44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G44">
         <v>990</v>
       </c>
       <c r="H44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I44">
         <v>990</v>
       </c>
       <c r="J44">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="K44">
         <v>950</v>
@@ -11787,16 +11787,16 @@
         <v>242</v>
       </c>
       <c r="F45">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G45">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H45">
+        <v>2.84</v>
+      </c>
+      <c r="I45">
         <v>2.88</v>
-      </c>
-      <c r="I45">
-        <v>2.92</v>
       </c>
       <c r="J45">
         <v>3.6</v>
@@ -11805,7 +11805,7 @@
         <v>3.65</v>
       </c>
       <c r="L45">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M45">
         <v>1.06</v>
@@ -11814,7 +11814,7 @@
         <v>4.2</v>
       </c>
       <c r="O45">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P45">
         <v>2.08</v>
@@ -11823,34 +11823,34 @@
         <v>1.88</v>
       </c>
       <c r="R45">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S45">
         <v>3.2</v>
       </c>
       <c r="T45">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U45">
         <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W45">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X45">
         <v>15.5</v>
       </c>
       <c r="Y45">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z45">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA45">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB45">
         <v>12.5</v>
@@ -11862,22 +11862,22 @@
         <v>12.5</v>
       </c>
       <c r="AE45">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF45">
         <v>18</v>
       </c>
       <c r="AG45">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH45">
         <v>15.5</v>
       </c>
       <c r="AI45">
+        <v>40</v>
+      </c>
+      <c r="AJ45">
         <v>42</v>
-      </c>
-      <c r="AJ45">
-        <v>38</v>
       </c>
       <c r="AK45">
         <v>26</v>
@@ -11886,13 +11886,13 @@
         <v>38</v>
       </c>
       <c r="AM45">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN45">
         <v>20</v>
       </c>
       <c r="AO45">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AP45">
         <v>14.5</v>
@@ -11904,7 +11904,7 @@
         <v>18</v>
       </c>
       <c r="AS45">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT45">
         <v>11.5</v>
@@ -11913,10 +11913,10 @@
         <v>7.6</v>
       </c>
       <c r="AV45">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW45">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX45">
         <v>16.5</v>
@@ -11946,25 +11946,25 @@
         <v>19.5</v>
       </c>
       <c r="BG45">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH45">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI45">
         <v>3.25</v>
       </c>
       <c r="BJ45">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK45">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BN45">
         <v>5.8</v>
@@ -11976,13 +11976,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ45">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR45">
         <v>32</v>
       </c>
       <c r="BS45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT45">
         <v>6</v>
@@ -11994,19 +11994,19 @@
         <v>22</v>
       </c>
       <c r="BW45">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ45">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA45">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB45" t="s">
         <v>257</v>
@@ -12029,10 +12029,10 @@
         <v>243</v>
       </c>
       <c r="F46">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G46">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H46">
         <v>3.8</v>
@@ -12047,7 +12047,7 @@
         <v>3.2</v>
       </c>
       <c r="L46">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
         <v>1.11</v>
@@ -12080,7 +12080,7 @@
         <v>1.34</v>
       </c>
       <c r="W46">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X46">
         <v>9.4</v>
@@ -12146,7 +12146,7 @@
         <v>23</v>
       </c>
       <c r="AS46">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT46">
         <v>7.8</v>
@@ -12164,7 +12164,7 @@
         <v>12.5</v>
       </c>
       <c r="AY46">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ46">
         <v>18.5</v>
@@ -12191,7 +12191,7 @@
         <v>55</v>
       </c>
       <c r="BH46">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI46">
         <v>2.72</v>
@@ -12200,13 +12200,13 @@
         <v>10.5</v>
       </c>
       <c r="BK46">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL46">
         <v>170</v>
       </c>
       <c r="BM46">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BN46">
         <v>5</v>
@@ -12218,37 +12218,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ46">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BR46">
         <v>38</v>
       </c>
       <c r="BS46">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT46">
         <v>6.6</v>
       </c>
       <c r="BU46">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV46">
         <v>32</v>
       </c>
       <c r="BW46">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX46">
         <v>50</v>
       </c>
       <c r="BY46">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BZ46">
         <v>38</v>
       </c>
       <c r="CA46">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB46" t="s">
         <v>257</v>
@@ -12274,19 +12274,19 @@
         <v>15.5</v>
       </c>
       <c r="G47">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J47">
+        <v>7</v>
+      </c>
+      <c r="K47">
         <v>7.2</v>
-      </c>
-      <c r="K47">
-        <v>7.4</v>
       </c>
       <c r="L47">
         <v>1.25</v>
@@ -12301,7 +12301,7 @@
         <v>1.22</v>
       </c>
       <c r="P47">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q47">
         <v>1.64</v>
@@ -12310,16 +12310,16 @@
         <v>1.57</v>
       </c>
       <c r="S47">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T47">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U47">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V47">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W47">
         <v>1.06</v>
@@ -12334,16 +12334,16 @@
         <v>7.4</v>
       </c>
       <c r="AA47">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB47">
-        <v>950</v>
+        <v>320</v>
       </c>
       <c r="AC47">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD47">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE47">
         <v>15</v>
@@ -12352,28 +12352,28 @@
         <v>210</v>
       </c>
       <c r="AG47">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AH47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI47">
         <v>50</v>
       </c>
       <c r="AJ47">
-        <v>990</v>
+        <v>960</v>
       </c>
       <c r="AK47">
         <v>330</v>
       </c>
       <c r="AL47">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AM47">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN47">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="AO47">
         <v>4.5</v>
@@ -12403,31 +12403,31 @@
         <v>13</v>
       </c>
       <c r="AX47">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY47">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AZ47">
         <v>36</v>
       </c>
       <c r="BA47">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BB47">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC47">
+        <v>16.5</v>
+      </c>
+      <c r="BD47">
         <v>16</v>
-      </c>
-      <c r="BD47">
-        <v>15.5</v>
       </c>
       <c r="BE47">
         <v>28</v>
       </c>
       <c r="BF47">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG47">
         <v>4.1</v>
@@ -12516,7 +12516,7 @@
         <v>1.93</v>
       </c>
       <c r="G48">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H48">
         <v>3.2</v>
@@ -12564,7 +12564,7 @@
         <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X48">
         <v>170</v>
@@ -12585,7 +12585,7 @@
         <v>17</v>
       </c>
       <c r="AD48">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE48">
         <v>32</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="AJ48">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK48">
         <v>21</v>
@@ -12621,19 +12621,19 @@
         <v>11.5</v>
       </c>
       <c r="AP48">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ48">
+        <v>7</v>
+      </c>
+      <c r="AR48">
+        <v>7.2</v>
+      </c>
+      <c r="AS48">
+        <v>7.6</v>
+      </c>
+      <c r="AT48">
         <v>6.8</v>
-      </c>
-      <c r="AR48">
-        <v>6.8</v>
-      </c>
-      <c r="AS48">
-        <v>7.2</v>
-      </c>
-      <c r="AT48">
-        <v>6.4</v>
       </c>
       <c r="AU48">
         <v>12</v>
@@ -12666,7 +12666,7 @@
         <v>16.5</v>
       </c>
       <c r="BE48">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF48">
         <v>4.6</v>
@@ -12770,7 +12770,7 @@
         <v>5</v>
       </c>
       <c r="K49">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L49">
         <v>1.17</v>
@@ -12794,7 +12794,7 @@
         <v>2.16</v>
       </c>
       <c r="S49">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T49">
         <v>1.39</v>
@@ -13024,13 +13024,13 @@
         <v>5.2</v>
       </c>
       <c r="O50">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P50">
         <v>2.44</v>
       </c>
       <c r="Q50">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R50">
         <v>1.58</v>
@@ -13060,7 +13060,7 @@
         <v>32</v>
       </c>
       <c r="AA50">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AB50">
         <v>14.5</v>
@@ -13072,7 +13072,7 @@
         <v>16</v>
       </c>
       <c r="AE50">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF50">
         <v>16.5</v>
@@ -13108,7 +13108,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ50">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR50">
         <v>14.5</v>
@@ -13120,19 +13120,19 @@
         <v>12</v>
       </c>
       <c r="AU50">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV50">
         <v>12</v>
       </c>
       <c r="AW50">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AX50">
         <v>12</v>
       </c>
       <c r="AY50">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ50">
         <v>11.5</v>
@@ -13150,7 +13150,7 @@
         <v>20</v>
       </c>
       <c r="BE50">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BF50">
         <v>8.4</v>
@@ -13245,7 +13245,7 @@
         <v>1.37</v>
       </c>
       <c r="H51">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I51">
         <v>11</v>
@@ -13269,7 +13269,7 @@
         <v>1.22</v>
       </c>
       <c r="P51">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q51">
         <v>1.67</v>
@@ -13353,10 +13353,10 @@
         <v>16</v>
       </c>
       <c r="AR51">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS51">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT51">
         <v>7.8</v>
@@ -13368,7 +13368,7 @@
         <v>18</v>
       </c>
       <c r="AW51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX51">
         <v>7.4</v>
@@ -13377,10 +13377,10 @@
         <v>9</v>
       </c>
       <c r="AZ51">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB51">
         <v>9.4</v>
@@ -13392,7 +13392,7 @@
         <v>20</v>
       </c>
       <c r="BE51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF51">
         <v>4.9</v>
@@ -13416,7 +13416,7 @@
         <v>1000</v>
       </c>
       <c r="BM51">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN51">
         <v>3.85</v>
@@ -13434,10 +13434,10 @@
         <v>25</v>
       </c>
       <c r="BS51">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT51">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU51">
         <v>5.4</v>
@@ -13446,13 +13446,13 @@
         <v>110</v>
       </c>
       <c r="BW51">
+        <v>8.4</v>
+      </c>
+      <c r="BX51">
+        <v>85</v>
+      </c>
+      <c r="BY51">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BX51">
-        <v>90</v>
-      </c>
-      <c r="BY51">
-        <v>8</v>
       </c>
       <c r="BZ51">
         <v>13.5</v>
@@ -13508,7 +13508,7 @@
         <v>2.44</v>
       </c>
       <c r="O52">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P52">
         <v>1.47</v>
@@ -13559,7 +13559,7 @@
         <v>190</v>
       </c>
       <c r="AF52">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG52">
         <v>13.5</v>
@@ -13598,10 +13598,10 @@
         <v>11.5</v>
       </c>
       <c r="AS52">
+        <v>6.8</v>
+      </c>
+      <c r="AT52">
         <v>6.4</v>
-      </c>
-      <c r="AT52">
-        <v>6</v>
       </c>
       <c r="AU52">
         <v>6.2</v>
@@ -13610,7 +13610,7 @@
         <v>15</v>
       </c>
       <c r="AW52">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX52">
         <v>12</v>
@@ -13622,25 +13622,25 @@
         <v>14.5</v>
       </c>
       <c r="BA52">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB52">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BC52">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BD52">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE52">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF52">
         <v>8</v>
       </c>
       <c r="BG52">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH52">
         <v>2.64</v>
@@ -13723,13 +13723,13 @@
         <v>250</v>
       </c>
       <c r="F53">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G53">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H53">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I53">
         <v>990</v>
@@ -13986,31 +13986,31 @@
         <v>1.36</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N54">
         <v>3.35</v>
       </c>
       <c r="O54">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P54">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q54">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R54">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S54">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T54">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U54">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V54">
         <v>1.26</v>
@@ -14031,7 +14031,7 @@
         <v>120</v>
       </c>
       <c r="AB54">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC54">
         <v>9.800000000000001</v>
@@ -14067,7 +14067,7 @@
         <v>440</v>
       </c>
       <c r="AN54">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO54">
         <v>160</v>
@@ -14079,10 +14079,10 @@
         <v>12</v>
       </c>
       <c r="AR54">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AS54">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT54">
         <v>7.4</v>
@@ -14094,7 +14094,7 @@
         <v>14.5</v>
       </c>
       <c r="AW54">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX54">
         <v>10</v>
@@ -14106,7 +14106,7 @@
         <v>16</v>
       </c>
       <c r="BA54">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB54">
         <v>20</v>
@@ -14115,22 +14115,22 @@
         <v>19</v>
       </c>
       <c r="BD54">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE54">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF54">
         <v>14</v>
       </c>
       <c r="BG54">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BH54">
         <v>3.4</v>
       </c>
       <c r="BI54">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="BJ54">
         <v>10.5</v>
@@ -14225,10 +14225,10 @@
         <v>4.1</v>
       </c>
       <c r="L55">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N55">
         <v>1.64</v>
@@ -14240,28 +14240,28 @@
         <v>1.64</v>
       </c>
       <c r="Q55">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="R55">
         <v>1.18</v>
       </c>
       <c r="S55">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T55">
         <v>1.6</v>
       </c>
       <c r="U55">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.62</v>
       </c>
       <c r="X55">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Y55">
         <v>950</v>
@@ -14318,7 +14318,7 @@
         <v>7</v>
       </c>
       <c r="AQ55">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="AR55">
         <v>2.06</v>
@@ -14327,22 +14327,22 @@
         <v>21</v>
       </c>
       <c r="AT55">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU55">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV55">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW55">
         <v>21</v>
       </c>
       <c r="AX55">
-        <v>7.6</v>
+        <v>1.99</v>
       </c>
       <c r="AY55">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="AZ55">
         <v>2.02</v>
@@ -14351,28 +14351,28 @@
         <v>24</v>
       </c>
       <c r="BB55">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC55">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BD55">
+        <v>20</v>
+      </c>
+      <c r="BE55">
         <v>2.12</v>
-      </c>
-      <c r="BE55">
-        <v>2.5</v>
       </c>
       <c r="BF55">
         <v>4.7</v>
       </c>
       <c r="BG55">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BH55">
         <v>4</v>
       </c>
       <c r="BI55">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="BJ55">
         <v>11.5</v>
@@ -14452,10 +14452,10 @@
         <v>1.84</v>
       </c>
       <c r="G56">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H56">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I56">
         <v>5.7</v>
@@ -14473,19 +14473,19 @@
         <v>1.1</v>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O56">
         <v>1.46</v>
       </c>
       <c r="P56">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q56">
         <v>2.4</v>
       </c>
       <c r="R56">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S56">
         <v>4.7</v>
@@ -14500,16 +14500,16 @@
         <v>1.21</v>
       </c>
       <c r="W56">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X56">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y56">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z56">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA56">
         <v>900</v>
@@ -14518,7 +14518,7 @@
         <v>7</v>
       </c>
       <c r="AC56">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD56">
         <v>24</v>
@@ -14563,10 +14563,10 @@
         <v>11</v>
       </c>
       <c r="AR56">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AS56">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT56">
         <v>5.8</v>
@@ -14578,7 +14578,7 @@
         <v>19.5</v>
       </c>
       <c r="AW56">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX56">
         <v>7.4</v>
@@ -14590,25 +14590,25 @@
         <v>21</v>
       </c>
       <c r="BA56">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB56">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC56">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD56">
         <v>38</v>
       </c>
       <c r="BE56">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF56">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG56">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH56">
         <v>3</v>
@@ -14691,22 +14691,22 @@
         <v>254</v>
       </c>
       <c r="F57">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="G57">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H57">
         <v>5.4</v>
       </c>
       <c r="I57">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J57">
         <v>3.75</v>
       </c>
       <c r="K57">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14715,13 +14715,13 @@
         <v>1.06</v>
       </c>
       <c r="N57">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P57">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q57">
         <v>1.92</v>
@@ -14730,16 +14730,16 @@
         <v>1.35</v>
       </c>
       <c r="S57">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T57">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U57">
         <v>1.94</v>
       </c>
       <c r="V57">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W57">
         <v>2.26</v>
@@ -14796,7 +14796,7 @@
         <v>11.5</v>
       </c>
       <c r="AO57">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP57">
         <v>13</v>
@@ -14820,7 +14820,7 @@
         <v>19.5</v>
       </c>
       <c r="AW57">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX57">
         <v>8.6</v>
@@ -14832,7 +14832,7 @@
         <v>18</v>
       </c>
       <c r="BA57">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB57">
         <v>15</v>
@@ -14844,31 +14844,31 @@
         <v>30</v>
       </c>
       <c r="BE57">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF57">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG57">
         <v>8</v>
       </c>
       <c r="BH57">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI57">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ57">
         <v>11</v>
       </c>
       <c r="BK57">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL57">
         <v>1000</v>
       </c>
       <c r="BM57">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN57">
         <v>4.4</v>
@@ -14880,31 +14880,31 @@
         <v>12</v>
       </c>
       <c r="BQ57">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR57">
         <v>1000</v>
       </c>
       <c r="BS57">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT57">
         <v>9.199999999999999</v>
       </c>
       <c r="BU57">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV57">
         <v>1000</v>
       </c>
       <c r="BW57">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX57">
         <v>1000</v>
       </c>
       <c r="BY57">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ57">
         <v>0</v>
@@ -14933,19 +14933,19 @@
         <v>255</v>
       </c>
       <c r="F58">
+        <v>1.59</v>
+      </c>
+      <c r="G58">
         <v>1.6</v>
       </c>
-      <c r="G58">
-        <v>1.62</v>
-      </c>
       <c r="H58">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I58">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J58">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K58">
         <v>4.4</v>
@@ -14963,28 +14963,28 @@
         <v>1.28</v>
       </c>
       <c r="P58">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q58">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R58">
         <v>1.42</v>
       </c>
       <c r="S58">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T58">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V58">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W58">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X58">
         <v>17</v>
@@ -14993,22 +14993,22 @@
         <v>25</v>
       </c>
       <c r="Z58">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AA58">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB58">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC58">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD58">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE58">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF58">
         <v>9.6</v>
@@ -15017,13 +15017,13 @@
         <v>10</v>
       </c>
       <c r="AH58">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI58">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ58">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK58">
         <v>17.5</v>
@@ -15032,19 +15032,19 @@
         <v>36</v>
       </c>
       <c r="AM58">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN58">
         <v>8.800000000000001</v>
       </c>
       <c r="AO58">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP58">
         <v>15</v>
       </c>
       <c r="AQ58">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR58">
         <v>48</v>
@@ -15053,7 +15053,7 @@
         <v>11.5</v>
       </c>
       <c r="AT58">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU58">
         <v>8.800000000000001</v>
@@ -15062,43 +15062,43 @@
         <v>22</v>
       </c>
       <c r="AW58">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX58">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY58">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ58">
         <v>19</v>
       </c>
       <c r="BA58">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB58">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC58">
         <v>15</v>
       </c>
       <c r="BD58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF58">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG58">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH58">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI58">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ58">
         <v>10.5</v>
@@ -15110,7 +15110,7 @@
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN58">
         <v>4.2</v>
@@ -15122,37 +15122,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ58">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR58">
         <v>25</v>
       </c>
       <c r="BS58">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT58">
         <v>9.800000000000001</v>
       </c>
       <c r="BU58">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV58">
         <v>55</v>
       </c>
       <c r="BW58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX58">
         <v>60</v>
       </c>
       <c r="BY58">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ58">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA58">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB58" t="s">
         <v>257</v>
@@ -15187,7 +15187,7 @@
         <v>4.1</v>
       </c>
       <c r="J59">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K59">
         <v>3.55</v>
@@ -15202,7 +15202,7 @@
         <v>3.05</v>
       </c>
       <c r="O59">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P59">
         <v>1.71</v>
@@ -15211,10 +15211,10 @@
         <v>2.12</v>
       </c>
       <c r="R59">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S59">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="T59">
         <v>1.84</v>
@@ -15229,112 +15229,112 @@
         <v>1.68</v>
       </c>
       <c r="X59">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y59">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z59">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA59">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB59">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC59">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD59">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE59">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF59">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG59">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AH59">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI59">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ59">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK59">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL59">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM59">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN59">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO59">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP59">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="AQ59">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="AR59">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AS59">
         <v>14.5</v>
       </c>
       <c r="AT59">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AU59">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="AV59">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="AW59">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AX59">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY59">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ59">
-        <v>1.04</v>
+        <v>16</v>
       </c>
       <c r="BA59">
         <v>14.5</v>
       </c>
       <c r="BB59">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BC59">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BD59">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BE59">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BF59">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="BG59">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BH59">
         <v>3.45</v>
